--- a/data/validation/discipline_verification_sample.xlsx
+++ b/data/validation/discipline_verification_sample.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coding" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fields" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Confidence" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,9 +499,21 @@
           <t>The post COVID-19 challenge is to build-back-better. Yellow Sub Hydro will instigate a step-change in the way the global mining industry manages our most precious of finite resources - water. United Nations research suggests more than half of the global population will be exposed to severe water scarcity within the next four decades as a result of both climate change and growing demand. We all have a stake in ensuring water is used ethically, responsibly and sustainably. One of the most water-intensive industries is the metals and mining sector, where no water literally means no business. Mine operators rely on 'water-balance' models to underpin many of their strategic decisions and risk management. These are mathematical representations of the way the water cycles from precipitation through the ground before ultimately leaving the local system via an outflowing river. The current state-of-the-art water-balance modelling typically takes a team of highly specialised hydrogeologists 1-3 years and up to a million dollars for a single mine site (there are tens of thousands of mine sites globally). Our idea is to use digital and machine learning technology, together with proprietary algorithms to reduce the modelling output into near real time, whilst losing none of the accuracy. Yellow Sub Hydro aims to help mining companies meet their environmental and social obligations (and their licence to operate) at the same time as saving them time and money. The innovation we are delivering will promote circular economy by providing a new landscape for other advances in efficiency and impact reduction from mining operations. For us, driving a sustainability agenda and making an impact socially and environmentally as well as economically has huge appeal, and we envisage this manifesting through driving a step-change in water resource management across a globally important industry.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Core work is ML/digital modelling product for mine water balance; hydrology application (Env Sci) considered</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,9 +541,21 @@
           <t>Single-use plastic (SUP) packaging is now firmly on the public agenda. Whilst the government and industry have started to look for solutions, most innovation to date has focused on creating alternatives to SUP packaging, such as bio plastics or paper, or improving collection and recycling systems, because this allowed 'business as usual' to continue. Whilst these are valuable improvements, we believe the focus should be at the top of the waste hierarchy - i.e. the reduction and reuse of packaging - which would represent a true shift from a linear to a circular economy solution for plastic packaging. With over 13 years of experience in zero-waste retail, and actively promoting reuse across the sector, Unpackaged proposes to work with a consortium of experts and industry partners to explore the feasibility of reusable packaging in the supply chain. We will leverage existing logistics infrastructure to move bulk products in a 100% circular system in order to service bulk dispensers in-store. We believe that innovation in this area is necessary to enable retailers to implement and scale bulk (zero packaging) solutions for their customers. We aim to prove that it is possible to get rid of SUP packaging within the supply chain with a reusable alternative that is financially, operationally and environmentally viable. The results of this research will lead to live in-store trials with our partners as we test and build our solution.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Supply-chain/retail feasibility for reusable packaging; effort is logistics/operations, not packaging technology</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,9 +583,21 @@
           <t>This project will allow Steamology to demonstrate zero emission off grid power and storage at the micro grid scale in Kenya with our partners Strathmore University, specialists in Renewable Energy (RE) research and training. Steamology is an innovative technology development company with an extreme engineering pedigree and a land speed record breaking heritage. Steamology is developing a zero-emission energy generation and storage system designed to be used with RE generation such as PV solar, geothermal or wind turbine. Our W2W (Water to Water) system contains a compact energy dense steam generator. Steam is generated using energy stored as compressed hydrogen and oxygen gas in tanks. High pressure superheated steam is used to drive a turbine to do useful work generating electricity. RE is used to power electrolysis to generate and compress hydrogen and oxygen gas into storage tanks. Traditional battery solutions for off grid energy storage use a wide range of often toxic or scarce chemistries such as Lithium, Cadmium, Lead, Antimony. These batteries have limited charging cycles (typically 500- 2,000) and do not have recycling plans in place for end of life. The W2W system has: - Zero emission - No CO2, NOX, SOX, or particulates - High power and torque - 10kW to 1MW range, scalable and modular units - Low noise and thermal signature - Quiet vibration free operation, low temperature signature - Operating temperature agnostic - Functional in a wide range of environments - Low maintenance - Few moving parts made of standard engineering materials - Without loss of performance over charging cycles -- Long life and service interval - Without toxic or scarce materials -- No Pb, Sb, Cd, Li or other rare earth elements It is widely accepted that global energy is required to meet net zero emissions by 2050. Steamology have a product to meet this challenge and realise the market opportunity. RE is plentiful but intermittent, 10,000 times more solar energy strikes the earth ev</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Zero-emission generation and storage system; energy is the object of the research</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -589,9 +625,21 @@
           <t>As part of the biggest infrastructure project in the UK (High Speed 2), enormous quantities of material are being excavated due to tunnelling and other operations, approximately 5,000,000 m3, its majority London Clay. Transportation of the excavated clay for off-site disposal leads to significant carbon dioxide emissions and costs. Current practice for repurposing of the excavated material is regarded as "low value" since it is normally sent to landfill. An innovative approach for high value repurposing of the excavated clay has been developed, where the excavated London Clay is treated and repurposed in concrete. A method has been established to process and calcine the spoil to use them in specific concrete mixes as a Portland cement replacement. Since Portland cement is the primary contributor of CO2 emissions in concrete, the proposed method offers major improvements in terms of reducing the carbon footprint of the significant concrete volumes that are going to be cast as part of High Speed 2 works and beyond. For context, Portland cement in project specific concretes can be replaced with up to 70% calcined London Clay while maintaining the onerous requirements for 120-years service life which results in major savings in concrete embodied carbon and promotes high value waste utilisation. Construction logistics, particularly for projects in dense, urban environments such as London, are complex to execute, challenging to budget and programme, and impact the environment and local surroundings. It is estimated that this pioneering approach reduces the carbon footprint for the concrete and associated disposal operations by up to 70%, revolutionizing the way excavated clay materials can be repurposed towards sustainable infrastructure development with maximised circularity. Additionally, this technology can be transferred to other major infrastructure projects or mining operations across the UK and beyond where clayed spoils are generated, with immense potential to red</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High-value repurposing of excavation waste; engineering in character but object is waste/resource recovery</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,9 +667,21 @@
           <t>The project aims to develop advanced metrics that can be used to develop and test control algorithms for real-time monitoring of anaerobic digestion (an initial step for artificial intelligence control of biorefinery). Anaerobic digestion (AD) is a nature inspired technology converting organic waste to biogas and nutrition rich digestate. The implementation of AD can lead to generation of renewable energy and circular economy solutions to organic waste. However, uptake of industrial-scale AD in the developing world, and high standards of process control have been limited by monitoring equipment and the limited local research work done on locally available feedstock. For the same reason, existing AD plants offer no rapid or detailed diagnosis of the biochemical balance of digesters, such as stress, build-up of inhibitors, scope for feedstock to be fed or reduced etc. As a result, most AD plants are not optimally operated, are oversized, and still run blind regarding the onset of inhibition or toxicity. No real-time metrics have been developed for use by industry to proactively optimise performance through new feedstock, nutrient supplementation, changes in organic loading rate, or temperature. This project, supported by Anaero Technology, aims to develop advanced metrics that can be used to develop and test control algorithms for real-time monitoring (an initial step for artificial intelligence control of biorefinery), and to acquire or develop dedicated Nano sensors for industrial control probes. The research will involve a range of methods including statistically-robust experimental work, analytical chemistry protocols, and big data analytical methods etc. The student will be required to work closely with Anaero Technology, have access to their state of art facilities and spend a minimum of three months in Anaero Technology based in Cambridge.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monitoring/control of anaerobic digestion, i.e. bioprocess control; sensors and algorithms serve the digester</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -649,9 +709,21 @@
           <t>The introduction of digital technologies in the fourth industrial revolution is rapidly transforming supply chains (Ridgway, Clegg, &amp; Williams, 2013). The early adoption of digitalisation in the supply chain is already resulting in a disruptive change in many industries. Companies are realising the importance of digital technologies early adoption to stay competitive and prosper (Srai, et al., 2017). Most research on this topic has been focusing on novel technologies rather than what the technologies can offer. Recent issues with supply chains stressed the need for them to be more visible, transparent, responsive, dynamic. Digital transformation technologies can provide greater flexibility through digital platforms, greater transparency through controlled towers, be able to better meet variable supply and demand than traditional supply chains, and the potential for developing a circular economy. As these seem to be structural changes, the use of configuration as a lens to explore the adoption of digital technologies becomes an interesting and exciting area to pursue. The research question to be covered are: 1. How can supply network reconfiguration through digital technologies enhance organisational performance and resilience? 2. How can digital supply chain technologies and a systems approach be used to develop a circular economy?</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Supply chain management research; organisational performance and resilience</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,9 +751,21 @@
           <t>The Circular Books Project will create a circular economy and more sustainable method of manufacturing for the UK publishing sector by exploring innovative materials and methods of book production for children's books that will extend book life, enable them to be re-manufactured at end-of-use and reduce the volume of books reaching landfill. It will also lower the high carbon footprint of the children's books industry -- printing in the UK instead of relying on overseas imports. Focusing on remanufacturing waste high-density polythene plastic (from sources such as carrier bags and milk bottles) into a pliable, printable and robust 'paper', we plan to create a series of colourful and engaging books for babies and toddlers. The Project helps achieve UK publishing goals of ending air freight, halving its carbon footprint by 2030 and being carbon neutral by 2050\.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Remanufacturing waste HDPE into printable 'paper' and book production methods; materials processing/manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -709,9 +793,21 @@
           <t>Challenge: Nylon-6,6 is produced by the esterification of adipic acid (ADP) and hexamethylenediamine (HMDA) monomers via energy intensive industrial processes (consuming between 80-60 MJ per tonne Nylon-6,6 manufactured). Annual global Nylon-6,6 manufacturing releases ~12 million tonne CO2 and ~2 million tonnes of nitrous oxide (NOx). 75% of the world's ADP is used for Nylon-6,6\. ADP manufacturing is itself highly problematic: ~1% of global NOx emissions and 0.2% of CO2 emissions are caused by ADP production. The benzene feedstock is a non-renewable petroleum compound and volatile carcinogen. Spent metal catalysts create toxic waste streams. The high temperatures and pressure required for ADP manufacture consume 100-120 GJ energy per tonne of ADP manufactured. Nylon-6,6 can be recycled mechanically, but the recycled material can contain impurities and is not as a strong as virgin Nylon-6,6 polymer. Chemical recycling of Nylon-6,6 can generate a higher quality of remanufactured product. However, the chemical recycling methods available are more complex and more expensive than mechanical recycling. Moreover, chemical recycling of Nylon-6,6 requires harmful and toxic chemical adjuvants. There is an unmet need for improved Nylon-6,6 recycling methods, reducing demand for virgin Nylon-6,6 and reducing demand for ADP and HMDA monomers. Innovation: Epoch Biodesign (formerly Mellizyme Biotechnology) recently purified a nylon hydrolase codenamed 'DAM-2'. Laboratory work-to-date shows DAM-2 can catalyse the depolymerization of Nylon-6,6 at room temperature and atmospheric pressure -- representing significant innovation in the processes currently available for Nylon-6,6 recycling. Project focus: Epoch will use proprietary synthetic biology tools and approaches to improve the activity of DAM-2\. They will also generate protocols for extruding new Nylon-6,6 filament from the degradation products of the DAM-2 mediated depolymerisation reaction. By completing this work Epoch will</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Enzyme engineering via synthetic biology (molecular scale); Chem Eng (biocatalysis) considered. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -739,9 +835,21 @@
           <t>What if you can power your workplace with renewable energy alone? Achieve up to 90% fuel efficiency compared with 35-45% of a typical power plant? Cost 30-50% less per kWhr than grid prices? Heating for building that is nearly free all year round? Have a system that is scalable and customisable to the type and size of space to maximize efficiency and cost? ALP Technologies Ltd is developing a fully automated, small-scale, combined heat and power (CHP) biomass gasification power plant for a renewable energy generating system that will have minimal moving parts and will provide heating and power at low cost. Our innovative and greatly simplified design will be at least half the production cost than currently offered small scale CHP systems, will be easy to maintain, reliable, fully automated and operate from local fuel sources. It will be ideally suited to the CHP requirements of dwellings, small to medium sized offices and retail spaces. It therefore has the potential to be a world leading, near-zero carbon CHP technology that will utilise local circular economy principles for almost any communities on earth.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Funded work is a market research feasibility study; the CHP technology is the subject, not the work</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -769,9 +877,21 @@
           <t>This project is associated with the EPSRC LightForm programme grant ( led by the University of Manchester, in collaboration with Cambridge University and Imperial College. The overall goals of LightForm are to develop the enabling science to embed materials engineering into manufacturing practice, driving improved performance and sustainability in applications of Al, Mg and Ti alloys. This DTP-funded project is in collaboration with Norsk Hydro (Norway and UK), who are providing a CASE top-up. As the Al industry strives for an increasingly circular economy, there is an urgent need to address the implications of impurity build-up on the formability, microstructure and final properties of wrought alloys. The objectives of this project are: (a) targetted experimental and modelling work on the sensitivity of key process steps to specific impurities, e.g. extrudability, sheet formability and age hardening of 6000 series alloys containing increased levels of Mn; (b) exploration of the potential for "alloy compensation", i.e. further alloying additions that counteract the detrimental effects of higher impurity levels in wrought Al alloys.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Impurity effects on microstructure/formability/properties of Al alloys; material behaviour focus. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,9 +919,21 @@
           <t>An innovative technology for materials of the future. The aim of the project is to increase the longevity of clothing and increase remanufacturing services through sustainable transformative innovation.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Abstract too thin/generic (two sentences); could be materials technology or clothing remanufacturing service</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,9 +961,21 @@
           <t>‘The Many Lives of Cardboard’ will establish a new multi-disciplinary network to investigate a versatile material that is essential to contemporary culture, yet often overlooked. Cardboard is a ubiquitous symptom of everyday consumption and the global movement of stuff under late capitalism. As packaging, it is transient and disposable; yet it is also economically valuable, dubbed ‘beige gold’ after pandemic-related shortages. Cardboard takes humans from cradle to grave: since 2017 a government-sponsored cardboard ‘baby box’ has been offered to every newborn in Scotland, providing a safe place to sleep, while there is a growing market for cardboard coffins. It is promoted as a ‘sustainable’ alternative to plastics, yet the environmental impacts of its production and recycling are considerable. It holds conflicting cultural meanings, from temporariness and permanence, to preservation and decay. The varied life cycles of cardboard signal wider issues of contemporary environmental culture, politics and practice. This project is a scoping exercise to identify areas for future arts, humanities and GLAM research, collaboration and network development. It will create a network for exploratory research, linking three institutions from London to Orkney (The National Archives (TNA); University of Edinburgh (UoE); University of Highlands &amp; Islands (UH&amp;I)). This new collaboration will unite histories of cardboard documented in the records of the state at TNA with people, collections, and institutions in Scotland, a key site in the history of paper and cardboard production in the British Isles. Exploring the local lives of this global material within the UK, this cross-border project extends recent trends in environmental humanities, especially sustainability and circular economies, waste and discard studies, and histories of resource extraction, to develop an exemplar of collaborative experimental research practice. Co-led by three ECRs with complementary expertise in histories</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Off-list field: Arts and Humanities (environmental humanities/heritage network on cardboard, AHRC)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -859,9 +1003,21 @@
           <t>As the second largest market for EVs in Europe and with the sale of new petrol and diesel cars banned from 2030, the UK is at the forefront of the transition to an electrified transport sector. However, with growing demand for the critical raw materials required for the production of EV batteries and concerns over global supply chains, an industrial scale battery recycling industry is urgently needed to help secure a stable and sustainable domestic supply of these materials. The UK is dependent on the global market for these raw materials, which presents a number of challenges. International supply chains are complex and vulnerable to disruption from geopolitical events, while environ­mental, social, and governance (ESG) factors are also becoming a growing concern for the EV industry. With this challenge comes an opportunity -- to build a sustainable and stable supply chain by developing a circular economy for critical battery minerals here in the UK. Altilium Metals is the only company in the UK recovering critical minerals from end-of-life EV battery waste. These valuable materials are recovered in a quality and format that can be directly reused in battery manufacturing in the most environmentally friendly and cost-effective way. Unlike existing pyrometallurgical processes, it can recover the lithium and manganese. Altilium's first UK plant is expected to be operational in Teesside by 2026, with the capacity to process 50,000 tonnes per annum (tpa) of lithium-ion battery black mass, equivalent to approximately 150,000 EVs per year or 10 GWh/annum. This strategic waste will be processed to make 30,000 tpa cathode active metals (CAM) to be recovered and supplied back into a UK EV automotive supply chain. This feasibility study will see the company partner with Lunaz, the UK's fastest growing vehicle electrification and upcycling business, to develop an innovative and sustainable solution for the transportation and discharging of end-of-life EV batteries, prior to r</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>EoL EV battery transport/discharge feeding recycling chain; object is the resource recovery system</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -889,9 +1045,21 @@
           <t>Fossil-derived liquid fuels have dominated the aviation and motor transport industry due to their high energy density and ease of manipulation. However, ever-growing concerns over CO2 emissions and improving battery technology are leading to rapid changes in energy sources for motor transportation. Consequently, the UK government, like many others, has announced a ban on the sale of new petrol and diesel cars from 2035. Unfortunately, batteries cannot be deployed for commercial aviation due to the low power to weight density of current battery technology. Developing carbon neutral aviation fuel through CO2 hydrogenation, where H2 is derived from water electrolysis, is a priority for the aviation industry and UKRI ( Recent reports show that intimate combinations of zeolite catalysts with zinc-based hydrogenation catalysts produces a multifunctional material that can hydrogenate CO2 to liquid range fuels (e.g. Nat. Commun., 2017, 8, 15174; ACS Cent. Sci., 2020, 6, 1657). Early work has shown that macroscopic control of the catalyst composite can tune the product range to different fuel types (gasoline vs jet fuel). However, much less is known about how the speciation and microscopic intimacy of the catalyst components affects product selectivity. Using our knowledge and control of zinc speciation in modified zeolites (Sustainable Energy Fuels, 2021, 5, 2136 and ChemPhysChem, 2020, 21, 673) we will develop structure-function activity relationships that will enable rational catalyst design to target sustainable jet fuel. The multifunctional catalysts will be made solely from earth abundant, non-toxic elements (Al, Si, Zn, Fe, Cu) and enable a circular aviation fuel economy.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Catalyst speciation and structure-function for CO2-to-jet-fuel; mechanism/characterisation, not process scale-up</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -919,9 +1087,21 @@
           <t>Most polymer films used in food packaging are multilayer laminates of very different polymers or metal films, due to the wide range of properties which need to be satisfied and balanced. Unfortunately, such mixed materials are extremely difficult or impossible to recycle, reducing the overall sustainability of polymer packaging. In addition, the polymers are mostly made from non-renewable sources and are non-degradable. Approaches to these challenges include: (a) producing laminates that can be separated for recycling by "debonding on demand" with an external chemical or physical trigger, allowing the material layers to be separated; (b) producing films and laminates from renewable sources which can be degraded at end-of-life. Such innovations will be key for decreasing polymer waste and enabling recycling and the circular economy for plastics. However, characterization of multilayer polymer films, and other polymer films which have through-thickness variation in chemistry (e.g. resulting from degradation or small molecule uptake) is challenging. This main objective of this project is to develop a new analysis capability - infrared spectroscopic ellipsometry (IRSE) - for the in-situ analysis of multilayer polymer laminates and polymer films with through-thickness variation in chemistry. This optical technique is fast, non-destructive and can be used with measurement cells for heating, solvent or vapour exposure, allowing dynamic processes such as curing, drying, swelling, degradation and delamination to be observed in-situ. Commercial IRSE systems are not widely available and the technique has been rarely applied to polymer challenges. We will use the new IRSE capability within the Henry Royce Institute Sustainable Materials Innovation Hub at Manchester to develop this key enabling technology for polymer innovation. The student will measure model multilayer polymer samples (including real polymer packaging samples and in-house fabricated films) by IRSE and develop t</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>IRSE characterisation of multilayer polymer films; material behaviour. Chemistry (chemical measurement) considered. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -949,9 +1129,21 @@
           <t>This project aims to support sheep farmers in Mid and North Wales by enhancing soil fertility and crop yields using biochar, a sustainable soil amendment produced from local agricultural and forestry residues. As the cost of traditional fertilisers rises and climate change impacts farming, this innovative approach offers a practical solution to improve grass and root crop production, essential for feeding sheep flocks throughout the year. We will conduct field trials on a one-hectare farmland site in Denbighshire, using biochar produced locally from sawmill offcuts. The trials will compare different application methods of biochar, including its combination with organic materials like sheep manure and goose dung homemade fertiliser. Our goal is to determine the most effective practices for incorporating biochar into the soil to boost crop growth while reducing the reliance on synthetic fertilisers. The project will increase the capacity of a local biochar production facility by adding a third kiln and improving drying processes. This will enable the production of up to 300kg of biochar per day, meeting the needs of the trials and supporting future agricultural applications. The biochar production process is sustainable and verified by ISO 14064-3, ensuring its environmental integrity. By demonstrating the benefits of biochar through scientifically rigorous trials, we aim to provide sheep farmers with a viable, cost-effective alternative to traditional fertilisers. This project has the potential to revolutionise agricultural practices in the region, promoting a circular economy that utilizes local waste materials and enhances soil health. Our findings will be shared widely to benefit the broader farming community, ensuring that the knowledge gained contributes to sustainable agriculture across Wales. Additionally, this project will help mitigate the environmental impact of agricultural practices by reducing greenhouse gas emissions associated with synthetic fertiliser</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Agricultural and Biological Sciences</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Biochar field trials for soil fertility and crop yields on farmland</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -979,9 +1171,21 @@
           <t>Hydrogen is considered one of the most promising substitutes for fossil fuels, being a source of green energy that could potentially lead to decarbonization. Its combustion only delivers water and heat energy as reaction products, making it a pollution free alternative. Dark fermentation (DF) is a biological hydrogen production method in which under anaerobic conditions and absence of light, microorganisms break down complex organic matter into simpler compounds producing biohydrogen and volatile fatty acids (VFAs). Given the high cost of using pure carbohydrates as a substrate on a commercial scale, there has been a lot of interest in biohydrogen production using renewable and less expensive feedstocks. Over 220 billion tonnes of agricultural waste are generated yearly, making it an accessible renewable resource to use as feedstock for dark fermentation. Therefore, using agricultural waste for biohydrogen production is a circular economy approach in which organic waste is treated to produce renewable energy, making the dark fermentation of these substrates both environmentally and economically compelling. Theoretically, a maximum of 12 mol of H2 can be obtained from the complete oxidation of one mole of glucose. However, only 4 mol of H2 can be obtained per mole of glucose through dark fermentation, with acetate and CO2 as the other fermentation end products, and this yield is obtained when the particle pressure of H2 is kept adequately low. Theoretically, during the acidogenesis for fermentative hydrogen generation, one-third of carbon from glucose is broken down into hydrogen (H2) and carbon dioxide (CO2), while the remaining two-thirds remain soluble as VFAs in the and less than 20% of the chemical oxygen demand (COD) is removed. Nowadays, the yield of biohydrogen production by dark fermentation is between 1.2 and 2.3 mol H2/mol hexose, which is only 30-50% of the maximum theoretical production of 4 mol H2/mol glucose. The low yield of H2 by biohydrogen producti</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Cell/strain engineering for biohydrogen; molecular-cellular scale; Chem Eng bioprocessing considered. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1009,9 +1213,21 @@
           <t>TOPUP TRUCK presents an innovative solution to combat single-use plastic waste and promote a circular economy. Our mobile refill service operates from electric vehicles, strategically positioned in various neighborhoods, offering convenient access to sustainably sourced products. By encouraging refill shopping and reducing reliance on plastic packaging, TOPUP TRUCK aims to revolutionise traditional retail practices and strive towards net zero. As we near the completion of the Sustainable Street Plan Project (SSPP), supported by Innovate UK, we are excited to introduce TOPUP TRUCK version 2.0\. Building on insights gained from extensive research and development, we have enhanced our service range, vehicle design, website functionality, and overall user experience. Now, we seek pre-commercialisation support to further refine and test our innovative concept in the market, focusing on key areas such as: 1. Marketing Strategy Development: Our marketing approach emphasises the "place" element, strategically positioning our trucks in high-footfall locations to maximise consumer engagement. Through a data-driven marketing plan, we aim to attract and retain customers cost-effectively to support our longterm growth while leveraging insights from previous interventions 2. Scheduling Optimisation: Streamlining our scheduling process is essential for scaling TOPUP TRUCK efficiently. By collaborating with local councils and aggregating customer interest, we aim to automate scheduling decisions, ensuring optimal trading locations and maximising uptake 3. Stakeholder Engagement: Establishing strong relationships with local authorities and community organizations is crucial for securing favourable trading locations and regulatory support. By addressing these challenges and opportunities, we aim to position TOPUP TRUCK for nationwide scalability and long-term success. Our project falls under the umbrella of marketing plan development, with a focus on validated market research and cus</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Marketing strategy, scheduling optimisation, stakeholder engagement for refill retail service</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1039,9 +1255,21 @@
           <t>The London Borough of Newham (LBN) is working in partnership with Tipping Point East (TPE) -- led by founding experts Material Cultures, Yes Make and RESOLVE Collective -- to pilot a new model for circular construction and demonstrate how reclaimed and bio-based materials can be used at scale in the built environment sector. The outcome will be the UK's first Circular Economy Construction Hub: a space that captures and reuses materials, proves operational systems at scale, engages businesses and the community, and provides market-tested pathways for councils and developers to follow. By doing so, it reduces emissions and waste from the construction while creating local green jobs and upskilling opportunities for local residents. Our project focuses on transforming a disused site in Silvertown into a Circular Economy Construction Hub built entirely from reclaimed and low-carbon materials. This retrofit is a live test case for how councils, contractors, and communities can adopt more resource-efficient approaches to our built environment industry. The project has three key pillars. First, reclaiming a disused site and delivering an industrial retrofit using 100% circular and bio-based materials: Newham has identified the lack of local storage and processing space as a critical barrier to reuse of construction materials. This project directly addresses that gap by transforming a disused site into an operational logistics hub through the retrofit of a decommissioned building using 100% reclaimed and bio-based materials, unlocking critical physical infrastructure while providing a live test case for material reuse. Second, Circular Economy Construction Hub with operations testing at scale and market activation: the project includes setting up an operational logistics hub for material reuse, enabling flows from demolition contractors, developers, and reuse platforms to be captured and redeployed at scale. We will develop and test physical and logistical infrastructure tha</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Construction materials reuse hub; object is a reuse/recycling system, methods built-environment in character</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1069,9 +1297,21 @@
           <t>We are the only design studio to offer high quality luxury products from alpaca fibre sourced in Europe where we can control the entire supply chain from farm to fashion. Our project will address both cycles in the circular economy, the technical cycle and the biological cycle. The introduction of digital passports will provide a system of certification for all products focusing on animal welfare ethical sourcing and environmentally friendly process for the garments created Our USP \Utilization of a renewable raw material which is wasted and has not reached its potential in Europe \Controlling the production and processing of the raw material to ensure that there are no artificial polymers or hazardous substances introduced at any stage of the cycle in the conversion to product \Working with nature and within the natural environment to produce our products which will be totally compostable \Controlling our supply chain so we can ensure that from the outset products are designed and manufactured so that materials used can continuously cycle through the system maintaining the highest value at all times \Making to remake reusing with innovative designs \Offering repair and recycling of our products</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Circular supply chain control and product certification for a fashion firm</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1099,9 +1339,21 @@
           <t>Our vision is to transform the one of the most environmentally-damaging resources used in society, vehicle tyres, into a circular economy by reusing materials that currently cause air and ocean pollution, which have a detrimental impact on human health. In this project, The Tyre Collective will complete development of three critical components of their novel tyre rubber capture device: the cleaning mechanism, storage tank and power configuration. The Tyre Collective will also work with Atlantis Carbon Black, experts in tyre pyrolysis and Europe's leading manufacturer for turning micronized rubber powder into regranulated rubber for tyre treading. We will work together to understand the scalability, manufacturability and commercialisation for reuse of our high grade and uncontaminated powderized tyre rubber. This project completes the lifecycle: capturing tyre rubber particulate matter at tyre source, conducting materials characterisation, matching the material quality to appropriate reuse market and building scalable and route-to-market at speed. Tyres shed half-a-million tonnes of carcinogenic, toxic carbon dust every year. Accelerating the shift to low carbon transport will increase carbon emissions from tyres as a direct consequence. EVs and ULEVs are heavier and have higher torque, causing their tyres to wear down 30% faster.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Capturing tyre-wear particulate (air/ocean pollution) and enabling rubber reuse; pollution capture + resource recovery convention outweighs the device-engineering aspect</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1129,9 +1381,21 @@
           <t xml:space="preserve">Bell &amp; Loxton Innovations is a highly innovative, circular-economy spin-out from a working farm in South Devon. Our consortium has recognised an opportunity to produce high-value biorenewable (HVB) materials from abundant agricultural and food-processing co-streams. Many co-streams such as oilseed presscake created during oil extraction and spent brewing yeast and grain are high in protein and are routinely discarded or used downstream in low-economic value applications. Proteins from different natural sources have unique compositions of amino acids both in prevalence and in terms of their sequence. Consequently, proteolysis of these biorenewable proteins will create unique distributions of smaller peptides that differ in size, amino acid compositions and sequence. This diversity enables different high-value market sectors to be catered for such as nutrition, personal care and pharmaceuticals as different peptides have different biological properties. Historically, bespoke peptides have been chemically synthesised at high cost from chemical/fossil fuel feedstocks. Identifying unique high-value biorenewable proteins and then producing tailored peptides and blends (hydrolysates) will enable a circular economy approach to supplying multiple industry sectors with a consequent benefit to the environment. Our consortium brings together the necessary parts for developing a successful and scalable 'green' chemicals business: Bell &amp; Loxton Innovations with its strong farming, food and agricultural production experience, The Biorenewables Development Centre (BDC) with its in-depth knowledge of waste and co-stream valorisation techniques, and Thomas Swan &amp; Co Ltd as an established chemicals manufacturing business to enable scale-up production coupled with a mission to move to 100% biorenewable feedstocks. Continuing this project from a successful valorisation feasibility study conducted with the BDC, we will work with our route to market manufacturing partner, Thomas Swan, to </t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Valorising agri/food protein co-streams into peptides via proteolysis, with scale-up; bioprocessing. Chemistry considered</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1159,9 +1423,21 @@
           <t>"The move to a circular economy is vital for the development of industry and the protection of the environment. One material constantly in the spotlight is plastics. Plastic is a highly engineered, indispensable material used over a wide range of applications. One of the strengths of thermoplastics is the potential ability to recycle the same material many times and make use of it in a circular economy. However, there is still a significant volume of plastic that is not recycled currently, and is destined for landfill or incineration. This material is the residual Mixed Engineering Plastics (MEP), which contains a wide range of less-common polymer types and importantly a significant proportion of legacy additives which are a concern when recycling the material. Within the ReCLAIM project, Axion Recycling, Trojan Services, Crompton Mouldings, and University of Birmingham will address these problems by: developing new processes for greater recovery of polymer fractions from MEP; creating chemical and physical methods for making BFRs biologically unavailable in the recycled polymers and verifying their efficacy; and proving that the polymer is suitable for real end markets. The results from ReCLAIM will boost competitiveness of the partner organisations by adding to their product lines, increasing revenue, and reducing operating costs. The benefits to the UK will be increased economic activity, new jobs, a reduction in waste incinerated or sent to landfill, and significant CO2 savings."</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Recovery/recycling of polymer fractions from mixed engineering plastic waste; object is recycling/resource recovery though methods are chem/physical</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1189,9 +1465,21 @@
           <t>Non-viral, plasmid DNA (pDNA) is the focus of great interest as therapeutic as well as a starting material for gene and cell therapies. The quality and quantity of the pDNA recovered from industrial processes is however affected by context-related impact of the plasmid, the presence of cryptic sequences, multimerisation leading to instability and non-optimal coiling. In this project we will work with AstraZeneca to consider how therapeutic plasmid sequences impact on the host cell and use engineering design rules to minimise such interactions while maximising plasmid replication stability and quality. The constructs of interest are already in use at AstraZeneca (AZ) and we will use transcriptomic analysis and engineering control rules to re-design them in order to achieve improved quantity and quality of the pDNA while minimising impact on the host. Lab work will entail state-of-the-art molecular cloning, transcriptomic analysis and design of CRISPR-based and RNA-based feedback controllers.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Re-designing plasmid DNA via molecular cloning, transcriptomics, CRISPR/RNA controllers; molecular/genetic work. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1219,9 +1507,21 @@
           <t>Our aim in this project is to engineer arbitrary analogue computation into bacterial biofilms. To explore this, we will implement a type of artificial neural network (ANN) using engineered bacterial populations arranged spatially and linked by intercellular signals. Previous work on computation in biological systems has mostly tried to emulate the digital logic capabilities of electronic circuits. This is a potentially limiting constraint on the naturally analogue processes that occur in biological systems. In comparison, ANNs are not constrained by these limitations, meaning they could be a useful framework for building artificial biological computers. We will engineer E. coli strains with intercellular signalling (quorum sensing) systems, where spatial separation of communicating colonies form a neural network structure. There are three objectives: 1. Develop an in silico design process for computational biofilms 2. Create engineered bacterial neurons 3. Demonstrate computational capabilities of spatial biofilms Our approach will open up new ways to perform biological computation, with applications in synthetic biology, bioengineering and biosensing. Ultimately, these neural-network-inspired bacterial communities will help us explore information processing in natural biological systems.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Synthetic-biology cell engineering (E. coli, quorum sensing) is the bulk of effort, but 'analogue computing/ANN' framing gives Computer Science a near-equal claim; bioengineering also possible. Field not in dropdown</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1249,9 +1549,21 @@
           <t>Since the industrial revolution, society and industry has been adopting a linear approach to business and production i.e. 'Take, make, dispose'. With the world's population expecting to increase to 9 billion, the world's economy will quadruple creating a greater demand for energy and natural resources. If new concepts and business models are not conceived and implemented, there could be considerable environmental implications. By exploring the principles of emotional durable design, the circular economy and service innovation we cold find new ways to create value for industry, delight the consumer and fulfill their needs while reducing the strain that modern day consumption has put on the environment. But most importantly do good design; create better, smarter products and services that will bring about a more sustainable future. Since the industrial revolution, society and industry has been adopting a linear approach to business and production i.e. 'Take, make, dispose'. With the world's population expecting to increase to 9 billion, the world's economy will quadruple creating a greater demand for energy and natural resources. If new concepts and business models are not conceived and implemented, there could be considerable environmental implications. By exploring the principles of emotional durable design, the circular economy and service innovation we cold find new ways to create value for industry, delight the consumer and fulfill their needs while reducing the strain that modern day consumption has put on the environment. But most importantly do good design; create better, smarter products and services that will bring about a more sustainable future.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Product-as-a-service ('light as a service') business models and service innovation; design framing is method. Engineering(design) considered</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1279,9 +1591,21 @@
           <t>The fashion and textile industries are significant contributors to pollution, resource depletion, and climate change. To steer human activity back within the limits of the earth's carrying capacity, the way we produce, use, and dispose of textiles needs to undergo radical transformation. This work is embedded in principles of sustainability such as reducing negative social and environmental impacts at each stage of a product or material's lifecycle, alongside circularity as a leading approach to sustainability, which endeavours to circulate resources without waste. The New Composites project aims to increase the diversity of resources used in textile design as a contribution to sustainability targets while embedding recyclability in textile design. The industry currently relies in overwhelming majority on two types of fibres, cotton and polyester, which together account for 76% of all global textile production (Textile Exchange, 2021). While improvements can be made in these fibre categories by using organic or recycled input, it is imperative that a wider variety of fibres should complement their use. The current focus on such a narrow range of resources leads to a lack of resilience in the sector as current price spikes or major disruptions caused by conflict or other obstructions of trade routes have shown. The project tackles the environmental and social impacts linked to the reduced biodiversity which comes from a focus on conventional fibres. Exciting and diverse innovation is currently taking place in the sector of alternative materials, for example materials made from pre- and post-consumer recycled fibres, bio-polyesters from corn, or regenerated cellulose from agricultural waste. However, these innovations are often not fully transparent in their composition and are difficult to access at scale. Moreover, as current guidelines for circular design focus on the fibres with the highest market share, little is known about how these new fibres are best employed</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Textile/material design for circularity (diversifying fibres, embedding recyclability); design maps to Engineering, but AHRC practice-led design could be Arts and Humanities. Near coin-flip</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1309,9 +1633,21 @@
           <t>Safe-and green-by-design are pre-market design approaches whereby the objectives of minimizing the use of hazardous chemicals, reducing greenhouse gas emissions, and fostering the reuse and recycling of materials in a circular economy are built into product design. SUSPHARMA fits the European need for sustainable development in modern industry and will develop during the action greener routes to prepare molecules, such as therapeutics and diagnostics. The breakthrough innovation will involve: - use of renewable (bio-based) carbon for the building block of scaffolds and motifs for drug synthesis; - cleaner synthetic methodologies for C-X bond formation (that is, C-H functionalization to obtain C-C, C-F, and C-I bond formation); - development of new benchtop continuous purification methods, to remove impurity and recycle synthetic solvents; - integration of digitalization methods. - LCA and TEA assessment for sensibly reducing the impact of pharmaceutical production. The project will thus benefit from an interdisciplinary domain, involving: - recent advances in biomass conversion for drug synthesis; - new developments in heterogeneous catalysis; - cutting-edge flow chemistry technologies (including synthesis and purification); - automation and machine learning. To address the challenge of green and digital transition and proper supply of health technologies and products, SUSPHARMA will focus on research and innovation activities that aim at integrating five breakthrough concepts: CAT-to-PHARMA, WASTE-to-PHARMA, FLOW-to-PHARMA, PUR-to-PHARMA, and DIGITAL to PHARMA. This will deliver results that are directed to pharmaceutical industries, researchers, and innovators, prompting them to develop and produce greener pharmaceuticals that are either greener by design, intrinsically less harmful for the environment, or use greener and economically more sustainable manufacturing processes and technologies.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Greener synthetic methodology (C-H/C-X bond formation, bio-based building blocks) is the scientific core; heavy flow-chemistry/continuous-purification/catalysis content gives Chemical Engineering a near-equal claim</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1339,9 +1675,21 @@
           <t>WarnerPatch is a medical device for non-invasive remote monitoring (virtual ward). It measures tissue health to predict disease worsening using a specifically designed sensing method and developed AI-algorithm. While being used at the hospital or at home, early degrading symptoms are identified so clinicians can give preventive care to improve patient outcomes and reduce care costs. We are focusing on diabetes and vascular diseases (i.e. peripheral vascular disease (PVD)), which can be the result of, or cause, heart attack, stroke, general infection, ulceration or gangrene, potentially leading to amputation and death. Worldwide, 200M people are at risk of developing this condition accounting for 13M in EU27, slightly more in the USA and 5M in the UK. Amputation is performed on 600K patients a year, with 50% death rate within two years after amputation and 30% of unnecessary amputation due to late recognition of disease-worsening. During the pandemic and with the long COVID-19 syndrome, the number of patients requiring emergency hospital care has increased by 60%, significantly stretching the current remaining resources. The minimum viable product development was finalised with its AI-algorithm and tested/validated in a simulated environment. The goal of this project is to finalise the R&amp;D of the physical product under regulatory requirement while improving the product manufacturability including recycling/refurbishment processes of non-critical parts. At the end of the project, we will be able to start the certification processes for commercial activities. We will continue working with the Leeds-Teaching-Hospital-NHS-Trust (LTHT) and NHS-Arden-and-Greater-East-Midlands-Commissioning-Support-Unit (AGEM) for a more detailed data-pack development with health-economics (budget-impact and cost-effectiveness). Using our device will improve patient outcomes while reducing care costs by: 1. Quickly identifying patients at risk of developing life threatening conditions, to t</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Developing a physical medical sensing device (instrumentation/sensors) and its manufacturability; embedded AI algorithm is a component. Computer Science considered</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1369,9 +1717,21 @@
           <t>Development of Knowledge base systems for optimisation and automation of electrical car engine within the manufacturing sector towards achieving the Net Zero targets in the manufacturing sector. This project aims to develop a a proof of concept Knowledge Based systems as an application, with generative and intuitive capabilities to optimise and automate electrical car engine design processes and principles enabling fast tracking of the UK manufacturing sector towards achieving UK Net Zero targets. The project will address the environmentally focused manufacturing design, for the delivery of supply chains and circular economy challenge as part of this call, with the focus on Manufacturing design for Net Zero using knowledge base engineering, Artificial intelligence (AI) , symbolic languages and advanced computing.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Building knowledge-based/AI systems (symbolic languages, generative, advanced computing) for manufacturing design; work is the software/AI. Engineering(manufacturing) considered</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1399,9 +1759,21 @@
           <t>The global impact of laundry detergent production on energy consumption and environmental conservation underscores the need for innovative solutions, particularly in the development of organic and eco-friendly laundry care products1. While surfactants remain integral to laundry formulations, the current detergents have evolved to also include polymers, builders, bleaching agents, enzymes, and chelating agents, playing a crucial role in controlling cleaning performance2. Despite the several benefits of polymers and how they improved today's quality of life, the fossil nature of over 98% of current polymers and their disposal via incineration contribute significantly to CO2 emissions3. Addressing this challenge requires the utilization of polymers designed for complete biodegradation or degradation into environmentally benign products, given the limited biodegradability of many currently employed polymers4. Biological polymers, such as chitosan, cellulose, and starch, provide a promising foundation for the development of biodegradable polymers due to their non-toxic nature and natural metabolization. However, native biological polymers often lack the desired performance for specific applications, necessitating chemical modification. Hybrid polymers, combining biological and synthetic components, represent an approach to leverage the best properties of both polymer classes3. Chitosan oligosaccharide (COS), derived from chitosan, exhibits excellent water solubility and low viscosity, even under strong alkaline conditions5. The presence of reactive amino and hydroxyl groups in chitosan's macromolecular structure allows for various modifications, such as alkylation, acylation, and Schiff base formation, tailoring its properties for diverse applications. However, chemical modifications can compromise the biodegradability of chitosan, since molecular weight, macromolecular architecture and the end groups of the polymer can affect this property4. Hydrophobic modifications ha</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Chemical modification (alkylation/acylation/Schiff base) and evaluation of polysaccharide polymers for detergents; synthetic polymer chemistry. Materials Science considered</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1429,9 +1801,21 @@
           <t>Covid-19 has impacted many sectors; one such sector is the waste management and recycling industry. The sector is facing many challenges; increasing levels of waste generated by households during the pandemic and disruption to waste and recycling collection services, against a background of stagnant recycling rates, increased public and regulatory pressures and a collapse of global recycling markets. A solution is needed which responds to these challenges and supports the UK's green recovery, by developing sustainable and circular economy. The FARRM (Fiberight Advanced Recovery and Recycling of Materials) project is a feasibility study of Fiberight's circular economy technology which creates value-added products from residual waste. In Phase 1 of the project the opportunity for an innovative advanced recovery and recycling solution for the UK's municipal solid waste stream will be evaluated.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Feasibility of advanced recovery/recycling of municipal solid waste into value-added products; object is waste recovery. Business(feasibility) considered</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1459,9 +1843,21 @@
           <t>Automotive safety is one of the most crucial factors in vehicle development and future vehicles need novel, lightweight structures that are safer and sustainable throughout their life-cycle. Hence, the long-term aim for SALIENT is to make our roads safer and reduce serious injuries and fatalities. To reach this ambition, SALIENT will present novel structural and vehicle concepts that are safer, lighter, circular, and smarter, which can be adapted to accommodate different crash scenarios. SALIENT will focus on innovating new technologies and will develop, demonstrate, and validate the effectiveness of light front-end structure (FES), considering eco-design and circular economy principles, to enhance vehicle safety. SALIENT will adapt advanced light materials, improved manufacturing and joining techniques, innovative circular design, and emerging active safety technologies to develop a smart FES with high energy absorption capability and to be adapted (prior crash events) with future mixed traffic scenarios to meet or exceed future vehicle demands in terms of safety, structural integrity, crashworthiness, and compatibility. SALIENT will build a pathway for the newly accumulated strategic knowledge to impact EU industries and society. Its ambition is to create global impacts and to play a key role to support EU strategic needs, and economic and societal challenges. The consortium consists of twelve partners from seven countries, representing the full automotive value chain, with leading European car manufacturer working alongside world-class research and education organisations, plus innovative SMEs. The project has been engineered to ensure maximum impact for the automotive industry in particular and society as a whole, significantly contributing to the evolving field of automotive safety.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Lightweight vehicle front-end structural design for crashworthiness, manufacturing/joining; mechanical/structural engineering</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1489,9 +1885,21 @@
           <t xml:space="preserve">SARS-2-Covid is not an airborne virus, but it has been proven that during aerosol generating procedures, such as intubation and extubation, the virus becomes airborne. Healthcare staff performing these procedures are at high risk of contracting the virus. Even with adequate PPE, the viral load transmitted to the face, neck and trunk of healthcare staff makes the process of 'doffing' (safely removing PPE) extremely dangerous. An aerosol shield box: significantly reduces the amount of viral load transmitted to staff significantly reduces settling time to the environment improves staff safety has positive psychological effects on healthcare staff who, by protocol, have to consider all patients positive to COVID19 if not previously tested allows operating theatres to be cleaned and turned round more quickly, without compromising safety Existing aerosol shield boxes that are currently available have a number of ldesign imitations that restrict their use across the healthcare sector. Through a collaboration between renowned medical specialists and high tech innovators, the Oxford Box aerosol shield has been designed to overcome the identified limitations by: 1\. allowing more access for staff to manoeuvre their arms and equipment within the box 2\. accommodating larger patients 3\. being able to be used on a variety of bed and trolley widths 4\. being lighter 5\. being suitable for thorough cleaning and re-use 6\. being compact, foldable and easy to store 7\. being affordable As a result of its innovative design the Oxford Box will be a safe, cost effective shield that will continue to be used as a means of barrier protection long after the pandemic has subsided, as the aerosol infection risk will always be present during intubation and extubation. A proof of concept prototype of the Oxford Box has already been built and tested, and medical approval has been recently granted by Oxford University Hospitals NHS Trust. A proof of concept prototype of a paediatric Oxford Box </t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Design of a physical aerosol-shield device (product/mechanical design) for clinical use; instrumentation/product engineering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1519,9 +1927,21 @@
           <t>The ResiCharge project will extend an existing planned field trial of ELEVEN's innovative home battery by 60 units to include 30 second life EV battery modules sourced from vehicles in the UK to be installed alongside 30 new modules for comparison. The use of second life EV modules in ELEVEN's all-in-one home battery helps to build a circular economy for EV batteries and extends time before modules are recycled allowing industry to improve processes. At the time of writing it is common for used batteries to be either sold on the grey market, stockpiled or incinerated due to the cost and immaturity of recycling processes. The project will provide an impact validation report to cover reduction in whole life carbon impact (manufacture of battery, use in EV, use in static storage, disposal/recycling) to include offset / payback in second life, energy system efficiencies, cost and end of life disposal.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Field trial of home battery energy storage using second-life EV modules; energy storage/system is the object. Environmental Science (reuse) considered</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1549,9 +1969,21 @@
           <t>This research project explores the mechanical and chemical recycling of waste plastics and textiles to both understand and optimise value in these materials to promote circularity. This involves both the separation of materials, the chemical depolymerisation of products and the mechanical processing and extrusion of commercially relevant plastics and textiles. The challenge is to understand how processing conditions can be optimised to create more consistent value in the recyclate quality in concert with improved sorting methods. The project has a strong sustainability and circular economy focus as well as targets on future manufacturing.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Mechanical/chemical recycling of waste plastics and textiles, optimising recyclate quality; object is recycling/resource recovery. Chem Eng (processing) considered</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1579,9 +2011,21 @@
           <t>Aim: To use the latest 3D manufacturing technology to create aesthetic, functional and sustainable woven materials for the 21st century. Objectives: 1. To identify the historical developments of the weaving loom and understand those aspects of standardisation that contribute to the 2D nature of weave. 2. To evaluate methods of integrating traditional weaving with 3D technology. To combine craft with digital to provide new visual, tactile and structural properties. 3. To identify characteristics required of new materials that may benefit from the integration of 2D technology with the latest 3D technology. 4. To develop new techniques for the manufacture of new smart materials with the circular economy in mind. Background: There is currently an absence of 3D printing technology in weave design. We have seen a move towards the 3D printing of textiles, but this focuses on the development of knitted structures and less on woven ones (CITA's Hybrid Tower). A weave structure is an interlacing of yarns that cross one another at right angles. As a weaver, I understand the potential weave structures have to influence the nature of fabrics. Lack of consideration of the circular economy in textile design is apparent. There are many projects that focus on the re-use and recycling of textiles, but few that are considering the future of textiles with a cyclical life cycle. Research Methodology: Year 1 Literature reviews, start of practice-led action research, first hand interviews with design studios/ makers/ other research institutions. Research visits to museums, textile mills. Life Cycle Assessment training course. Testing of equipment such as digital jacquard loom, 3D printing facilities. Continue in the collaborative partnership with Sosanya, formed during Sophie's time at the RCA, to develop a hybrid 3D printing/weaving machine in collaboration with the Centre for Fine Print Research at UWE Bristol. Year 2 Continuation of practice led action research. Sophie will develop tec</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Developing 3D-weaving manufacturing techniques and a hybrid 3D-printing/weaving machine; design/manufacturing maps to Engineering, but AHRC practice-led craft could be Arts and Humanities. Near coin-flip</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1609,9 +2053,21 @@
           <t>Development of a shredder to assist with the processing of problematic global waste streams to aid the circular economy towards achieving Net Zero by 2050\.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Developing a shredder (a machine/product) for waste processing; object is a machine per boundary rule. Thin abstract; Environmental Science (recycling) considered</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1639,9 +2095,21 @@
           <t>UK-based SME, Aspcold, aims to develop a pioneering alum-sludge treatment solution that offers an energy-efficient, alternative End-of-Waste option for alum-sludge and a circular economy avenue as an additive to high-performance building adhesives. Alum-sludge is a waste by-product generated by water-treatment and is traditionally disposed of in landfills. No viable treatment options currently exist for alum-sludge. In the UK, ~500,000 tonnes of alum-sludge is landfilled annually costing ~£53m. Worldwide the production of alum-sludge is ~10m tonnes each year. The rate of this production is expected to increase with water demand (~20-30% by 2050). With landfill space in the UK expected to run out in 20 years and alum-sludge documented to leach harmful levels of aluminium into the ground. UKWIR has objectives to achieve zero waste by 2050, and the Environment Agency sets out to enforce reuse of sludge where possible, highlighting the demand for alternative/circular treatment options for untreatable waste like alum-sludge. Aspcold has created a demonstrable prototype that uses a low-energy process to convert water-bound alum-sludge into a dried product that can be used as a low-carbon additive to high-performance building adhesive. The process relies on readily accessible materials, allowing rapid manufacturability and scalability. Aspcold anticipates the serviceable available market (Water-and-Waste-Water-Treatment) of ASP is £4bn. In this 21-month project, Aspcold will optimise its unique alum-sludge water separation and drying process to identify the most efficient combination for use by water-treatment facilities. Industrial testing and research of the dried solid as an additive to building adhesives will inform on the best circular use cases. ASP addresses the global need for a cost-effective and sustainable alum-sludge End-of-Waste solution.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Treating alum-sludge waste (End-of-Waste) into a reusable powder additive; object is waste treatment/resource recovery. Chem Eng (dewatering/separation) considered</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1669,9 +2137,21 @@
           <t>10000 wind turbine blades (WTBs) were installed in Europe in 2019, and the largest are &gt;100 m long. Yet the manufacturing methods have not changed significantly since the 1970s, with little or no NDT or in-line control, leading to high defect, repair and scrap rates. TURB0 will reduce defects and improve repair strategies in WTB composites and coatings. -Improved composite production processes: By using the latest simulation techniques to avoid defect formation and understand how defects affect structural integrity. -In-line NDT: Combining three cutting-edge NDT technologies (dielectric, wireless, sensor-less) for the first large scale in-line in situ composite production monitoring. -Sub-surface WTB coating inspection: Currently coatings only undergo visual surface inspection or destructive testing. TURB0 will combine ultrasound and mid-IR OCT for the most detailed coating assessment ever performed. -Digital twin and data warehouse: Production equipment, monitoring and in-line NDT data will be combined to establish a digital twin for real-time analysis of production. This has never been attempted for a large-scale composite part. It will populate a data warehouse accessible from multiple production sites. -In-line system control: Using the digital twin, a ML-based algorithm will provide closed-loop process control to minimise defect formation and waste and optimise process efficiency. -Automated repair strategy: The digital twin enables a ML analysis of defect severity in composites, with automated strategies to reduce repairs by 90 % and increase recycling of off-cuts. -Full-scale demo: A demo on a full size &gt;80 m WTB section will be performed at the SGRE factory in Aalborg. -Quantified sustainability improvements: including life cycle analysis (LCA), social LCA and circular economy assessments to quantify environmental and socioeconomic benefits. -Dissemination and exploitation activity: includes a powerful Advisory Board, training, standards and business plan.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Composite manufacturing process for wind-turbine blades (defect reduction, in-line NDT, process control, digital twin); work is manufacturing/materials processing, energy is the sector. Energy considered</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1699,9 +2179,21 @@
           <t>The Fast-Moving Consumer Goods (FMCGs) sector aspires to transition to a Circular Economy (CE) but there is a lack of knowledge and support methods. This research has investigated how material resources flow in FMCG systems and developed new design support for the sector. Initially, we focused on the moment when resources become obsolete which can disrupt flows. Consumers were found to have critical roles to ensure resource revalorisation and the findings of this study can inform the design of future revalorisation services. We then looked at Product-Service Systems (PSSs) and studied the elements that could help overcome obsolescence and enable closed loops resource flows. A framework presents these elements, mapped against requirements for PSSs that close loops. Subsequently, we investigated the resource flow-system, which encompasses all the elements in place to produce a resource flow. A new modelling method is proposed that describes the movements and transformations of resources, and helps configure FMCG sector-specific system elements. The model can be used to explain how FMCG systems work. Finally a tool is presented, which embeds the modelling method as well as the process to apply it and analyse the model. The tool enables industrial users to develop a holistic view and an in-depth understanding of the resource flow-system informing the development of future systems solutions. Journal papers featuring work presented in this thesis Zeeuw van der Laan, A. and Aurisicchio, M. (2020), "A framework to use product-service systems as plans to produce closed-loop resource flows", Journal of Cleaner Production, Vol. 252, p. 119733. Zeeuw van der Laan, A. and Aurisicchio, M. (2019), "Archetypical consumer roles in closing the loops of resource flows for Fast-Moving Consumer Goods", Journal of Cleaner Production, Vol. 236,. Conference papers featuring work presented in this thesis Zeeuw van der Laan, A. and Aurisicchio, M. (2021), "The Flow Mapper : A Tool to Model S</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Product-service systems, consumer roles and resource-flow modelling/design support for the FMCG sector; management-of-resource-flows problem. Engineering(design) considered</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1729,9 +2221,21 @@
           <t>In the UK 51% of food is wasted before it gets to the consumer during agricultural post-harvest distribution or processing. Globally, over one third of all food produced across the food chain is wasted. A significant proportion of food loss relates to the inherent physiology of the crops, poor control of post-harvest biology and the efficacy and appropriateness of the control systems applied. To generate economic value from waste, the valorisation of agri-food by-products (AFBPs) and mapping of supply chains to manage agricultural waste systems is crucial. There is a lack of consolidated knowledge of existing agricultural waste, its categorisation and potential uses, including how agri-food by-products (AFBPs) can become a valuable feedstock resource for other applications and products. Currently huge portions of agricultural waste are undervalued and underutilised. This project encompasses the development of a proof-of-concept digital platform for trading in AFBPs, setting the scene from a move away from a waste model to a resource that has economic value. We are aiming to use a Human Centered Design model for the creation of a digital marketplace, by interviewing representatives from the value-chain, we will gain information for the design of the platform that will be of use for both food producers, processors and those looking to purchase feedstock. The Human Centered Design (HCD) approach, combined with performance testing of the digital platform, will ensure that future developments in the digital platform meet the requirements of prospective end-users, increasing their acceptability, uptake and use. Our business plan is based on a subscription model for those looking to buy or sell feedstock. The platform will be free to researchers in the public sector based on anonymised data sets that could be used for development of public policy. Sustainability is crucial and set to remain firmly at the centre of future international agricultural policy given the continue</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Building a digital marketplace/platform (HCD, performance testing) for trading agri-food by-products; work is the platform. Business(marketplace/model) considered</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1759,9 +2263,21 @@
           <t>Batch.works is using 3D-printers to create new methods for prototyping and sustainable product design utilising continuous production methods. This reduces speed from design-to-manufacture and enables use of higher quantities of recycled materials. Our vision is to disrupt traditional manufacturing, creating a circular network of distributed 3D-printing sites around the world. Decentralisation enables designers/retailers/manufacturers to rapidly produce products on-site and in time will enable closed-loop manufacturing. We want to see products remanufactured at the end-of-life. This project is a global collaboration feasibility study exploring the opportunities in a booming 3D-printing market in Germany. We will establish a new global collaboration with Caribou3d, a high-performance 3D-printing business in Germany to explore the technical possibilities of using their machinery under a new collaboration. This collaboration will also enable us access to the European single market through the existing value chains Caribou3d has established.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Distributed 3D-printing/additive-manufacturing network feasibility; domain is manufacturing, but heavy market-entry/business-collaboration framing gives Business a claim</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1789,9 +2305,21 @@
           <t>New lightweight High-Performance Composite (HPC) materials and efficient sustainable processing technologies will have an enormous environmental and performance benefit in all sectors of application. However, current sustainable HPC application is limited to large sectors due to their limitations in terms of long processing times, high prices and low recyclability. To overcome these limitations, rLightBioCom propose a paradigm shift in the way HPC are manufactured and recycled, unlocking sustainable-by-design production of lightweight HPC. Therefore, the project will enable new circular value chains towards r-LightBioCom results, contributing to environmental-related EU goals and reducing the HPC waste generation and the use of non-sustainable fossil resources. To this end, a sustainable catalogue of new advanced biobased and recycled HPC materials will be initially developed with inherent recyclability properties (at least 3 new types of bio-resins, 4 new biomass-derived nanofillers and additives, and 3 families of sustainable fibre-based textile products). To reduce current associated manufacturing costs and high energy consumptions and emissions, efficient processing techniques will be developed (2 new fast curing techniques) combined with recycling technologies for the new catalogue of materials to reduce waste generation and induce circularity. A new open method and related tools (Coupled Ecological Optimisation framework) will promote and standardise holistic sustainable HPC design, modelling and systematic optimisation, leading to continuous sustainable catalogue growth and inclusion of new families of biobased, recyclable lightweight HPC at competitive cost. All results will be validated in 3 use cases at automotive, infrastructure and aeronautic industries with specific business cases, contributing to establishing new resilient, sustainable and innovative value chains in the EU HPC industry, promoting a change of paradigm from linear to circular ones.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Developing new bio-based recyclable composite materials (bio-resins, nanofillers, fibres) plus processing; materials development leads, but processing(Engineering) and Chemistry are close. Field not in dropdown</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1819,9 +2347,21 @@
           <t>Plastics have helped to build the modern world, and the current era has been dubbed “The Plastic Age” due to the ubiquity and influence of these materials. Yet plastics are both a friend and foe to the environment. While plastic pollution poses a very real environmental danger, plastics are also powering the green revolution as key components of wind turbine blades, batteries, and lightweight electric vehicles. Plastics have reduced CO2 emissions across Europe by a factor of 5-9, and address the global challenge of food security by reducing food waste by 20%. However, current production methods are unsustainable. Over 99% of plastics are currently produced from crude oil, and by 2050, annual plastic production is predicted to use 20% of global oil reserves and generate twice as much CO2 as the aviation industry. Approximately 60% of the 8300 Mt of plastic produced globally by 2015 has been discarded. Plastic waste is thus an attractive alternative feedstock to help conserve oil stocks and avoid energy intensive cracking processes. Transitioning from a linear plastic production model to a circular economy is of urgent importance, yet this requires innovative scientific technologies. Only 10% of plastics are currently recycled. This is partly because "recycled" materials are generally downcycled, with a reduction in material properties such as strength and flexibility leading to progressively lower value applications until recycling is no longer cost effective. This process is further complicated because plastic products often contain multiple types of plastic, such as polyethylene (PE) milk cartons which have lids and labels made from polypropylene (PP). Recycling feedstocks thus often contain a mixture of different plastics that require intensive separation processes and subsequent recycling as individual components. Creative scientific solutions are crucial to address these problems in order to upcycle plastic waste into useful value-added products. The creation of</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Catalysis + copolymer/compatibilizer chemistry to upcycle plastic waste; bench chemistry method development. Chem Eng(catalysis) and Env Sci(plastic waste) are strong alternatives</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1849,9 +2389,21 @@
           <t>Buildings and infrastructure are responsible for over 30% of the UK's carbon emissions, produce over 60% of the UK's waste, and consume approximately 50% of all extracted materials globally. Radical change is urgently required to achieve a sustainable construction sector. The circular economy (CE) is a well-recognised opportunity to turn waste into resources while reducing carbon emissions. CE aims to keep materials at the highest value possible, via a hierarchy of strategies, e.g. first prioritising extending the lifetime of buildings, then reusing building elements directly in-situ or on another site, then remanufacturing elements, and finally recycling material to conserve resources and avoid disposal. However, CE is still far from typical construction practice. Action to date has largely focused on one-off case studies of individual buildings, or recycling targets leading to wasteful downcycling, and lacks the national-scale, systems-level impact that is so desperately needed. BuildZero's vision is one of a building stock that delivers the UK's space requirements but no longer relies on extraction of new resources, by leveraging the CE to meet materials needs, and eliminating both waste and carbon emissions from material extraction and production. Using this highly ambitious end goal as a springboard, we will explore CE solutions across multiple scales, identified, co-created and co-delivered with our highly engaged industrial consortium, assess the extent to which this vision is achievable nationally, regionally and in relation to individual buildings, and determine the conditions in which the BuildZero vision leads to favourable social, environmental, and economic outcomes. This new knowledge base will provide a platform to enable these solutions to be translated into practice at scale, catalysing regional and national policy to stimulate real change. To achieve this, we will develop an interdisciplinary, multi-scale systems model of buildings and resources fl</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Circular economy for the building stock: waste-to-resource, material reuse, systems model at national/policy scale; object is materials/waste/resources. Engineering(built environment) and Social(policy) considered</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1879,9 +2431,21 @@
           <t>SageTech Medical have developed a highly innovative technology that captures, recovers, and recycles anaesthetic gases that are used in healthcare facilities around the world. We have developed this technology because anaesthetic gases, when released to the atmosphere after use, contribute significantly to global warming because of their high carbon footprints. Globally, anaesthetic gases contribute approximately the same carbon footprint as 5000 flights between London and New York. There is no need to dispose of used gases and manufacture brand new anaesthetics - that process itself produces high levels of carbon dioxide equivalents needlessly - the gases are minimally metabolised in the body, they are robust chemicals, and relatively easy to handle and process. These factors make them ideal targets for capturing and reusing. As this technology is adopted by healthcare facilities around the world, the scale of the technological and operational systems must evolve to maintain optimal levels of sustainability. If successful, this grant will enable SageTech to work with industry experts to bring transformational developments to the core innovative technology that SageTech has built. This will make it possible for SageTech to build a truly ground-breaking business with global reach, here in the UK. SageTech have enquiries from healthcare markets around the world and we are highly motivated to take the business to the next level.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Capturing, recovering and recycling anaesthetic gases to cut emissions; emissions reduction + resource recovery. Chem Eng(gas separation) considered</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1909,9 +2473,21 @@
           <t>A New, clean, low-carbon technology to reclaim valuable nylon textile materials from swimwear and womens tights, and create a circular economy business model to close the loop on pre and post consumer waste.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Technology to reclaim nylon from swimwear/tights textile waste; textile recycling/resource recovery. Thin; business-model element noted</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1939,9 +2515,21 @@
           <t>The project aims to establish and clarify the benefits and added value of more aligned and harmonised regulations and standards for prioritised topics related to decommissioning and initial phases of radioactive waste handling, including shared processing facilities between Member States (MS). The project has a two-phase approach: first engaging with Stakeholders to assess needs and pros/cons for harmonisation and identify priority areas for deeper analysis (WP2). The second phase will pursue deeper engagement with Stakeholders to further assess the highest ranked priority areas in Work Packages (WP) focusing on (i) cross border services and cooperation (WP3), (ii) circular economy (WP4), and (iii) advanced technologies (WP5). These WPs will review (inter)national practices, capture lessons learned, and assess opportunities. WP6 on Regulatory Framework will identify regulatory differences between MS and evaluate strengths, weaknesses, opportunities, and threats associated with harmonisation, while quantifying the benefits of aligned regulations and proposing harmonisation methodologies. The project will: - support coordination between Stakeholders - enhance existing commitments to facilitate sharing and exchange of knowledge and experience - develop strategies for shared treatment and storage facilities, cross border services and cooperation, and explore additional mechanisms to build capacity in MS - assess and clarify the benefits and any disadvantages of harmonisation, - deliver S&amp;T-based solutions and share best practices by engaging and supporting coordination between different actors through the TSOs and regulators - define conditions and opportunities of a high safety circular economy. The action will reinforce the activities of the EURAD, PREDIS, and SHARE projects, while encompassing activities within MS national programmes and the wider European Community, including e.g. ERDO, ENSREG, WENRA, IAEA, OECD NEA, IGDTP, SNETP, and DigiDecom.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Social Sciences</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Harmonising regulations/standards and stakeholder coordination for radioactive-waste decommissioning; law/regulation/institutions. Env Sci(radioactive waste) considered</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1969,9 +2557,21 @@
           <t>Digital research infrastructure (DRI) is revolutionising environmental science, enabling a new data-driven approach for monitoring and modelling that enhances scientific collaboration and decision making. At the same time, these infrastructures are made up of digital technologies that emit carbon across every phase of their lifecycle (i.e., manufacture, use, disposal), causing significant waste and social risks (e.g., harms to international communities from waste exports). A careful balancing act, therefore, lies ahead: the environmental gains achieved through DRI-enabled science must be levelled against its social and environmental costs. How can the crucial scientific progress required to support people and the planet be ensured, whilst also remaining within planetary boundaries? How can DRI systems be designed to achieve this future balance? This project seeks to address these questions, creating a bold initiative that reimagines DRI futures with environmental scientists to increase sustainability across its lifecycle by emphasising sustainable design, reuse, and waste reduction (i.e., circularity). Focusing on land use as a case study to contextualise our research, we will work with stakeholders in the scientific community to build an in depth understanding of the DRI landscape and its complexities; from this, we will add to current systems with new digital tools, data science techniques and innovation processes that maximise the benefits of DRI use in environmental science whilst minimising its detriments. Recognising the need for a cultural shift within the scientific community for these futures to be realised, we have embedded a range of impact and engagement activities to work with, and extend, our powerful network of stakeholder experts and partners, and support the wider DRI and digital technology communities in achieving a more circular and sustainable future. This project offers a crucial first step that is essential in mitigating digital technology's po</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Reimagining digital research infrastructure and building digital tools/data-science for its sustainability; object is the digital infrastructure. Env Sci(e-waste/circularity) and Social(STS/culture) near-equal</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1999,9 +2599,21 @@
           <t>This feasibility study will enable peat-free production of mushrooms and leafy salads by recycling plant-based substrates from other sectors (including anaerobic digestion, soft fruit and mushrooms). The main technical challenges in recycling peat-free organic materials for these specialist sectors are quality, consistency, crop timing and nutrient balance. This project will help to meet the DEFRA target of phasing out peat from UK horticulture. Currently exemptions are proposed for mushroom growing and salad propagation where no peat-free substrates exist on the market. By delivering a circular economy solution we will also contribute to achieving net zero emissions. The project team conducting the work includes leading growers, scientists and substrate processing experts.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Agricultural and Biological Sciences</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Peat-free horticultural production of mushrooms/salads via recycled substrates; crop production/horticulture (timing, nutrient balance). Env Sci(substrate recycling) considered</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2029,9 +2641,21 @@
           <t>To establish an holistic test development environment enabling design engineers to create and end users to execute test procedures on leading-edge automotive powertrain management systems for remanufacture.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Test-development environment and test procedures for automotive powertrain management systems for remanufacture; systems/automotive engineering. Thin; CS(test software) considered</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2059,9 +2683,21 @@
           <t>This project will take recent advances in protein evolution methods to develop entirely novel DNA binding domains as a basis for new synthetic transcription factors in genetic regulation. The development of new-to-nature protein functionality remains a significant challenge even given recent computational advances in protein structure determination. To address this we will take an experimental approach that combines CIS peptide display for the in vitro expression and selection of massive libraries (Patel et al. Protein Engineering, Design &amp; Selection 26, 307-315, 2013), with phage-based in vivo selection (Brodel et al. Nature Communications 7, 13858, 2016), which gives exponential amplification of genetically selectable traits. At 66 amino acids, lambda cro is perhaps the smallest known transcription factor that functions in E. coli, and it can be converted into an activator (Brodel et al. Science Advances 6: eaba2728, 2020). Therefore, providing an unstructured gene sequence coding for 70 - 100 aa, could in principle provide a reasonable starting point for de novo evolution of a transcription factor. The ~1091 - 10130 amino acid combinations seem daunting, but that is also why it is a fascinating question to ask whether the compounding advantages of evolution, which we will employ, will lead to an exponential selection trajectory. The project will take a staged approached to ensure viable progression and development of the techniques during the project. Initially, we will screen large libraries of structured but non-DNA binding sequences based on familiar DNA regulatory elements (e.g. helix-turn-helix), using in vitro CIS display. Subsequently, this will be expanded to create massive libraries of unstructured proteins to screen for novel DNA binding scaffolds. DNA binding domains from these studies will then be developed as transcription factors using further protein engineering and in vivo accelerated evolution using a phage-based microbial gene drive as well as a</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Protein evolution/engineering of de novo DNA-binding domains and synthetic transcription factors; molecular biology/genetics. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2089,9 +2725,21 @@
           <t>To meet the UK Governments commitment to net zero we must move away from using gas and oil to heat homes and commercial space. Our new products can make an important contribution to solving this problem. We are developing a novel sustainable heating product incorporating recycled materials. This project will develop new processes to increase these recycled materials to high percentages without adversely affecting the product's performance. The project will enable the development of a truly circular business model for manufacturing and recycling of this novel product The next stage of development for us, is to increase our recycled materials used in our products from 40% to potentially 95%. This will make our products more appealing to environmentally conscious clients as it adds to their eco life cycle, circular economy product.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Developing a heating product (radiator) and processes to raise recycled-material content; product development/materials processing. Energy(heating application) and recycled-content considered</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2119,9 +2767,21 @@
           <t>The ReMake Glasgow Extension project builds on the success of the original ReMake Glasgow initiative, which established a world-class Remake Hub in the Glasgow City Region. This project will expand and scale the impact of circular manufacturing by engaging with businesses across multiple sectors to drive sustainable production, economic growth, and environmental benefits. Circular manufacturing is key to achieving net-zero goals, reducing waste, and retaining value in high-integrity sectors such as aerospace, energy, and construction. The ReMake Glasgow Extension will deliver five key work packages: 1. Circular Manufacturing -- Repair, Remanufacture, Recycle Engage businesses to implement circular economy principles. Develop new remanufacturing processes to address industrial challenges. Facilitate co-investment in sustainable technology adoption. 1. Digital Product Passport (DPP) -- Compliance and Implementation Deploy functional and scalable DPP systems with companies. Extend DPP adoption to sectors such as construction and textiles. 1. Skills -- CPD, Culture, and Workforce Reskilling Deliver CPD training for businesses to adopt circular manufacturing practices. Develop new in-person training courses to support industry transformation. 1. Design for Circularity Support companies in implementing Design for ReX (remanufacture, repair, reuse) principles. Contribute to Glasgow's Circular Economy Route Map by embedding sustainable design practices. 1. Exploitation, Commercialisation, and Investment Support commercialisation opportunities for circular economy solutions. Engage in Glasgow's investment ecosystem to enable long-term sustainability of circular initiatives. The expected impact of the project includes: Engaging businesses in circular economy adoption. Directly supporting companies in transitioning to circular manufacturing. Delivering CPD training to companies, equipping the workforce with essential skills. Reducing emissions, contributing to Glasgow's net-ze</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Business engagement, adoption, DPP, commercialisation and skills to scale circular manufacturing; largely business/economic development + skills. Social(skills) and Engineering(remanufacturing) considered</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2149,9 +2809,21 @@
           <t>Sustainable Sailing is a marine industry R&amp;D company, with a track record of innovation to address the grand challenges of the industry. In this project the challenge of recycling carbon fibre composites is targeted, specifically sails. Modern carbon sails are built from high technology carbon fibre composites, however like most composites, recycling and reuse of these sails once they have reached the end of their useful life are not currently available for sailors across the UK. With over 1.5 million yachts and 1 million dinghies globally, this source of waste is one which is both growing and is not being addressed within the industry. Working with B&amp;M Longworth, the Advanced Materials Research Centre, Farapack polymers and Precision Yachting, Sustainable Sailing is building upon existing collaboration to scale-up their recycling process. They will do this by going from 0.5kg of sails recycled to 50kg in the next 6 months. Along the way, this collaboration will understand the effects of their recycling process upon the different components of the sails. This will include analysis of the fibres to maximise their useability for future projects, including development of technologies to improve Sustainable Sailing's existing Chlorofoils product line. Furthermore, their existing work suggests that some other components of the recycled sail can also be reused, so this project will be using advances in industrial and green chemistry the return these components back other products. This project aims to "close the loop" of high-performance carbon fibre composites, by returning all the components that make up these sails into other products. This will help the UK and the marine industry realise the "circular economy" in which all waste products can be reused and returned into circulation. By focusing upon sails this project will demonstrate that it is possible to recycle other carbon fibre composites, reducing the environmental impact of carbon fibre production and eliminati</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scaling a recycling process for end-of-life carbon-fibre composite sails to recover/reuse components; recycling/resource recovery. Chem Eng/Materials(fibre analysis) considered</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2179,9 +2851,21 @@
           <t>Polymeric nanofiltration membranes are used for organics removal from raw water during drinking water production. A highly selective separation is fostered by accommodating a strict pore size which can also improve continuity in downstream asset operation (e.g. disinfection), therefore enhancing resilience of drinking water supply. However, current polymeric membranes exhibit several challenges. Ceramic nanofiltration (C-NF) is an emerging technology that introduces a thin separation layer to foster selectivity without significant loss to permeability. Several advantages are proposed. While these unique properties can foster a radical shift in the economics, operability and resilience of nanofiltration, C-NF has yet to be developed explicitly for drinking water treatment, where these separation attributes must be challenged to evidence their translatability to this industrial context. This project therefore seeks to evaluate C-NF as a next generation technology for the production of drinking water from organic rich raw waters.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ceramic nanofiltration membrane separation for drinking-water production (selectivity/permeability); separation process. Env Sci(water treatment) and Materials(ceramic membrane) near-equal</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2209,9 +2893,21 @@
           <t>In 2019, the global textile market reached 111 million tons (mt), with less than 1% coming from textile-to-textile recycling (Exchange, 2020). Synthetic fibres and polymer blends are often used, with 63% of the current market being comprised of petroleum-based virgin fibres (Borneman, 2015). Recycling of these polymer blends and petroleum-based fibres is difficult, and lack of component recovery means a large number of these materials end up in landfills or incinerators. Reaching a circular textile economy by recovering individual components of these non-renewable polymer blends, with emphasis on achieving the same properties (e.g., thermal and tensile strength) as the respective starting materials, is imperative for sustainability and reduction of environmental impact (Jönsson et al., 2021). Elastane, a poly(urethane-urea) copolymer, is often used in textile blends to increase elasticity and tensile strength (with e.g., denim, cotton, or polyamide) (AK and Bansal, 2018; Dhouib, 2006). Approximately 20% of recyclable textile waste contains elastane (Jönsson et al., 2021). Current separation methods fail to fully separate elastane for reprocessing. For example, melt filtration and melt spinning are not sufficient to separate elastane from polyamide (PA), as the elastane degrades and passes through filters. Also, mechanical separation results in elastane disappearing from the tearing machine in PA fabric with high elastane content (~22%), and fails to fully separate PA fabric with low elastane content (~5%). Therefore, reprocessing cannot continue as elastane acts as a contaminant (Jönsson et al., 2021). A method for separating elastane and achieving the same properties as the virgin fibre does not currently exist. The aim of this research is to develop a method to enzymatically degrade elastane for the de-polymerisation of textiles, whilst investigating chemical/thermal pre-treatment, and optimising biotransformation conditions affecting conversion yields - for futur</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Developing/optimising an enzymatic biotransformation to depolymerise elastane for textile recycling; bioprocessing. Env Sci(textile recycling) and BGMB(enzymatic) are strong alternatives</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2239,9 +2935,21 @@
           <t>RePolyWise: Revolutionizing Waste Recycling RePolyWise is on a mission to revolutionize waste recycling by introducing an innovative method for atomic recycling. Founded by two leading researchers from the Chemistry Department at the University of Oxford, RePolyWise is dedicated to addressing the challenges of plastic waste recycling in the UK, leveraging their extensive expertise in chemical processing. At the core of RePolyWise's pioneering work is a groundbreaking process that enables the recycling of polyolefin plastics atomically back to their monomers. This breakthrough offers a transformative solution, paving the way for a fully circular plastics economy. RePolyWise's vision for recycling is set to redefine the future of plastic waste management, promoting sustainability, and ushering in a circular economy for plastics not only in the UK but on a global scale. With their unwavering commitment to innovation and sustainability, RePolyWise is poised to make a profound impact in the field of waste recycling.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Chemical/atomic recycling of polyolefins back to monomers (C3), by chemists; molecular-level conversion. Thin/promotional; Chem Eng(process) and Env Sci(plastic waste) alternatives</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2269,9 +2977,21 @@
           <t>Due to the growing demand in Energy Storage Systems (ESS) in Europe, Chimera Energy's aim through this feasibility study to is to learn and establish a route to market that will have a considerable impact to the circular economy. Besides the UK, Germany and Italy have a considerable market share within this sector, so understanding the market policies and needs in these territories would be advantageous in delivering a crucial solution without delay. Time is of the essence. Chimera Energy proposes packs constructed with proprietary weld-free technology designed for re-manufacture and second-life potential ensuring unrivalled: Scalability (flexibility) Performance Safety Longevity (endurance) Cost effective solution Currently working on projects addressing the ATV, Forklift and Marine markets, Chimera Energy's focus is to provide a unique and innovative solution for the Energy Storage sector and more importantly, work towards a net-zero future globally.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Feasibility study to establish route-to-market and assess market policies for second-life battery energy storage; market/business focus. Energy/Engineering(battery packs) considered</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2299,9 +3019,21 @@
           <t>This project (LINK) will develop a digital system to connect end-user buyers directly to salvage material owners (usually construction/renovation/demolition/deconstruction sites). This will minimize logistics costs and thereby reduce price and increase usage. LINK will include Machine learning-enabled Rapid listing mobile app (Rambo): Extender: digital extension that allows SC2M connect their customer bases directly to salvage construction material owners (SCMOs) Connector: Online commercial platform that connects buyers directly SCMOs Material reuse data to support green credentials(G-cert)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Building a digital system/marketplace (ML listing app, online commercial platform) to connect salvage-material owners and buyers; work is the platform. Business(marketplace) considered</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2329,9 +3061,21 @@
           <t>UK-RELOAD, is an initiative by Talga Anode UK Ltd, aiming to establish an innovative lithium ion battery anode manufacturing plant in the UK. Graphite, an active anode material, is the single most abundant material in lithium ion batteries. It is currently almost exclusively imported to the UK from Asia, predominantly China. Graphite is recognised as both a critical as well as a strategic raw material. This project focuses on repurposing recycled graphite from used batteries and battery production scrap back into battery use. The project builds on the company's knowledge of manufacturing pristine, natural graphite anode material as well as on a previous successful technical feasibility study for the repurposing of recycled graphite. The project is focused on establishing the commercial viability of the product manufacturing in the UK. The project deliverables include process engineering design, process scaleup trials for customer validation, financial model, comprehensive project risk analysis and an execution plan. This innovative project supports circular economy by reusing a valuable critical raw material, graphite, sourced from UK's battery recycling businesses and marketed into UK's battery manufacturing. It also enhances the sustainability of battery manufacturing through low carbon footprint manufacturing processes and by minimizing waste in battery production. Additionally it provides a crucial solution towards achieving regulatory recycled content targets for the electric vehicle value chain in Europe.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Economic/commercial feasibility of a recycled-graphite anode plant (financial model, risk, execution plan); firm-level viability. Chem Eng(process design/scale-up) and Env Sci(graphite recycling) considered</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2359,9 +3103,21 @@
           <t>The internet's energy and carbon footprints are estimated to exceed those of air travel with around 1.7 billion tonnes of greenhouse gas emissions per year produced in the manufacture and running of digital technologies (climatecare.org and BBC 2020). Computers and network hardware such as data centres must be powered and cooled drawing electricity from non-renewable fuel sources. During the height of COVID19 lockdown, UK's internet usage surges to record levels. Time spent online due to working from home is up by 67% compared with pre-lockdown usage (Opinium April 2020 survey). Remote online work has significantly increased the energy and associated carbon footprint that power the internet and the equipment that support it such as the data centres and server networks at companies and offices that enable remote working. A promising solution to address this problem is to transform an idle backup energy storage device into an asset with an investment return and carbon savings potential. UPS - Uninterruptible Power Supply - systems are commonly used in commercial buildings and industries to protect hardware such as computers, data centers, telecommunication equipment or other electrical equipment in case there are any unexpected power disruptions that could cause injuries, fatalities, serious business disruption or data loss. UPS can be used as energy storage systems additionally to their primary use in order to generate additional benefits to their users. Alp has developed a utility scale smart battery system called BRIC which reduces total system cost by over 30% by using smarter electronics and AI. With environmental sustainability and circular economy principles in mind, BRIC is designed and tested to utilize new or second-life cells and substantially increase useful life. Our game changing innovations accomplish this by an electronic design, AI and software that proactively monitor and manage the battery at the individual cell level to anticipate issues before the</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Smart battery-management system (electronics + AI, cell-level monitoring) for UPS/energy storage; electrical/electronic advance, energy is the setting. Energy(storage) and CS(AI) considered</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2389,9 +3145,21 @@
           <t>Welsh Wool into Premium Feed Ingredients The Challenge Welsh farmers often pay more for shearing than they receive for shorn wool, a significant business problem. Current wool processing wastes valuable lanolin as expensive sludge, costing the industry £19.2 million annually (Standard Wool, 2025). Meanwhile, the UK imports £90 million worth of soy and palm oil for livestock feed annually, driving deforestation and creating supply chain vulnerability that threatens food security (DEFRA 2022). Our Innovation LanoTech has developed breakthrough extraction methods that recover significantly more grease from wool than the industry standard---a 4x productivity improvement. This project refines this into feed-grade lanolin with higher energy density than soy, creating three commercial products from one waste stream: feed-grade lanolin, cholesterol for aquaculture, and cleaned wool. Our business model ensures the value of this innovation is returned to farmers within Mid and North Wales. Impact for Mid and North Wales Economic Regeneration: Our sourcing model targets often unsold wool and improves rural cash flow. This creates immediate economic benefit for upland farmers who rely more heavily on sheep income than lowland counterparts. Strategic Job Creation: Wool processing will create 50+ positions across engineering, chemisty and operations. These facilities target rural Mid and North Wales areas, breathing new economic life into communities. Environmental Leadership: Each tonne of Welsh lanolin that replaces imported soy oil, may reduce carbon emissions by up to 3-4 tonnes CO2e and supports Wales' Net Zero commitments. Our innovation creates a circular agricultural economy; farmers supply wool and eventually purchase the lanolin-based feed, eliminating waste while strengthening local supply chains. Proven R&amp;D Journey This project builds on validated progression through three consecutive R&amp;D phases. Innovate UK New Innovators established lanolin feed feasibility, SBRI We</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Extraction/refining process to recover lanolin from wool into feed-grade products; separation/processing is the core innovation. Agricultural(animal feed) and Business(model) considered</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2419,9 +3187,21 @@
           <t>The UK construction sector is one of the largest contributors to carbon emissions and waste. Local planning authorities (LPAs) play a crucial role in reducing these impacts, as planning decisions determine what is built, how, and with what materials. However, despite ambitious policies such as the London Plan's Whole Life Carbon Assessments (WLCAs) and Circular Economy Statements, Scotland's NPF4, and emerging retrofit-first requirements, many LPAs lack the digital infrastructure and expertise needed to enforce compliance. The CLEAR project (Carbon Lifecycle Evaluation for Authority Reviews) will demonstrate how PACER --- the UK's first digital WLCA review platform --- can provide LPAs with the tools and evidence required to enforce carbon and resource efficiency policies. CLEAR emphasises clarity and transparency in WLCA compliance, enabling officers to move from manual, fragmented processes (such as Excel spreadsheets and static PDFs) to an automated, consistent, and transparent digital review process. Running from November 2025 to March 2026, the project will be delivered by Preoptima Ltd, a UK climate-tech company founded on over 25 years of academic research into whole life carbon. The project will be carried out in partnership with Tower Hamlets and the City of London, who will provide real planning cases for testing. To guarantee sufficient case data, the project will also draw on publicly available Greater London Authority (GLA) referable schemes. During the project, PACER will be used to process planning applications twice --- once at baseline and once for comparative review --- to demonstrate measurable improvements and enforcement outcomes. Key features to be tested include: WLCA review and compliance checking against local and national policy. Retrofit vs. new-build comparison tools to evidence retrofit-first decisions. Local benchmarking engine to create datasets specific to boroughs and typologies. Officer guidance and applicant--officer portal to impr</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Demonstrating a digital whole-life-carbon review platform (automated compliance checking, benchmarking) for planning authorities; work is the platform. Env Sci(environmental planning/carbon) and Social(planning policy) near-equal</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2449,9 +3229,21 @@
           <t>Introduction 'Enabling the Brewing Industry's Circular Economy' is a bold project to transform the brewing industry. This proposal has been submitted by the founders of Draught Drop -- a young, ambitious company. We bring local draught beer to your door in reusable glass growlers and are known as the milkman for beer! We began Draught Drop to help the UK's vibrant brewing industry and offer customers high quality draught beer in the comfort of their home, in a way that is kind to the planet. - Project opportunity COVID-19 has had a particularly detrimental impact on the brewing industry which we will detail throughout this proposal. However, it has also provided the opportunity to bounce back greener and accelerate the transition to a circular economy. The global brewing market is worth $592bn with growth and long-term trends meaning Draught Drop and the UK industry are well placed to capitalise. As the sole operators in this market we have identified the technological and commercial constraints to be overcome and are proposing this six-month project, costing c.£100,000 to focus on two categories of innovation: Technical R&amp;D is needed to design and test core technologies required for a wider roll-out of the Draught Drop business model Business model innovation to help scale the Draught Drop business and accelerate the positive environmental impact for the beer industry - Execution plan and team We have a detailed plan of how we would conduct this project, the resources required and the deliverables we will produce, namely: 1. A detailed design for the ecosystem and the technical requirements of the industry 2. Functioning prototypes of the unsolved technical challenges 3. The IP protection and potential patents to exploit this work Our team have successful careers in beer, e-commerce and innovation and have significant experience in managing innovative projects and programmes, recruiting talent and working with multiple organisations to achieve outcomes. We have als</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Reusable-growler beer-delivery circular business; business-model innovation with supporting technical R&amp;D. Engineering(prototypes/technical R&amp;D) considered</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2479,9 +3271,21 @@
           <t>In STREAMS, a comprehensive portfolio of at least 12 scalable and flexible technologies and pilot scale solutions for the sustainable production of battery-grade precursors and their respective anode and cathode active materials will be developed, evaluated and successfully demonstrated. These technological processes will be applied to materials from primary and secondary sources including recycled battery mass and photovoltaic waste. This will strengthen Europe’s domestic battery materials supply chain and reduce Europe’s dependency on imported critical and strategic raw materials supplies. The production technologies will also increase Europe’s resilience, competitiveness and strategic autonomy in the global battery manufacturing industry. STREAMS’ technological solutions will meet EU requirements for environmentally responsible design, and scale up, and anticipate regulatory compliance by conducting techno-economic, environmental, social impact and integrated risks assessments combined with life cycle sustainability and circularity assessments. The cathode and anode active materials synthesized in STREAMS will be used to manufacture 10 Ah battery cells at pilot scale using sustainable electrode processing. Prototype cells will be tested according to established standards and subjected to advanced post-mortem characterization. STREAM will also identify optimal conditions for future exploitation of the project results.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Developing scalable production/pilot processes for battery-grade precursors and anode/cathode materials from primary and recycled sources; process/scale-up. Materials Science, Energy, Env Sci considered</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2509,9 +3313,21 @@
           <t>This work aims to evaluate and utilise agricultural co-products, byproducts and green waste streams that are currently not properly accounted for and create new and innovative approaches for resource recovery and sustainable energy generation using anaerobic digestion. Anaerobic digestion of agricultural residues could not only help to produce biomethane but could be tailored to produce and recover high value chemicals for various industrial applications. The integration of anaerobic digestion of agricultural residues with the biorefinery concept will not only advance the field but also open up different avenues for underutilised residues which in turn help in creating a sustainable and circular economy in the agricultural and green energy sector.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Anaerobic digestion/biorefinery of agricultural residues for biomethane and high-value chemicals; bioprocessing. Energy(bioenergy), Env Sci(resource recovery), Agricultural considered</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2539,9 +3355,21 @@
           <t>Currently, economies worldwide are pursuing mostly a linear model of production which leads to massive material losses, dependency on geopolitically instable states and volatile markets for primary resources. A circular economy, on the contrary, seeks to counter this approach to preserve the value of utilized resources and materials as long as possible, to use them as frequently as possible, and to produce as little waste as possible. European industry needs solutions to mitigate the barriers for industrial data reusability and facilitate the unlocking of value from data. Joint Industrial Data Exchange Platform is a place where industrial data is fused for interconnecting seemingly different sectors into the collaboration pipeline. It builds upon the principles of Industry 4.0, by adopting a coherent approach for the semantic communication between diverse actors aimed towards direct or indirect contribution to the EU’ s climate neutrality goals of 2050. JIDEP is a landing place to any organization which has any kind of data obstacle to be addressed, on its paths towards delivering more sustainable material, product, service, or solution. Within JIDEP, built-in tools are made available for unlocking the value of the data, which can lead to the development of more sustainable solutions, technologies, and materials. JIDEP is also an optimizing continuum, covering the entire product lifecycle and steering it towards circular standards implementation at technological and regulatory levels. Finally, JIDEP is a tool equipped with resilience frameworks for growing organizational and industrial capacities to withstand supply chain disruptions in short-, medium- and long-term clauses. As such, JIDEP ingests industrial data and produces sustainability, resilience, and circularity artifacts for its participants.</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Industrial data-exchange platform (data fusion, semantic interoperability, analytics tools) for circular value chains; data infrastructure. Business(supply-chain collaboration) considered</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2569,9 +3397,21 @@
           <t>Research aim The main aims of this project are: to understand the role of waste1 (Thompson 1979) in a community affected by the economic crisis ("age of austerity", Streeck and Schafer 2013); to study a community organization in a context of transformation promoted by a process of re-thinking of waste as community resources. My research is an ethnographic engagement related to the concepts of "sustainable development", "circular economy" and "waste studies" (O'Brien 2008). Since 2012, the EU commission has proposed several legislative amendments about resources and waste management (Gregson et.al.2015), introducing the idea of "circular economy" (European Commission 2014). This idea 1 I will take into consideration mostly households waste with exception for pulper waste from paper mills' residuals. refers to an economy premised on keeping resources in circulation for as long as possible and so aims to eradicate waste. This "long term solution" is defined as "sustainable" development (Miller 2012). In this context, wastes are considered useful materials in order to partially reduce the European demand for natural resources. To consider wastes as resources is important to think those as materials (e.g.paper). These materials have monetary value if categorized and sold separately.</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Social Sciences</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ethnographic case study of a community re-thinking waste as resource; sociology/anthropology, waste studies, sustainable development (ESRC)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2599,9 +3439,21 @@
           <t>The Sustainable Home Survey Company (“SHS”) works with community partners, refurbishment providers and homeowners to identify and catalyse domestic energy efficiency improvements. SHS was the first CIC to be certified as a Green Deal Assessor Organisation. As an adjunct to the core business of providing regulated energy surveys, in mid-2012 SHS identified a need for an innovative assessment system that enables the cost effective screening of households prior to a full Green Deal Assessment (“GDA”). The proposition was successfully market tested as part of a TSB “Proof of Market” study. The introduction of the Green Deal in 2013 marked the start of “the biggest home improvement programme since the Second World War”. However, the mass consumer market remains reluctant to pay upfront for assessments. Green Deal Providers profitability will be materially impacted by absorbing “at-risk” costs of ~£125-150 per GDA at anticipated 25-33% conversion rates. The basic SHS screening system uses key information on the property to estimate the set of measures that can be economically implemented combined with householder behavioural survey results to evaluate their propensity to implement the measures. This enables scarce surveying resources to be directed to the highest potential households, boosting conversion rates to reduce net costs per implemented Green Deal package by at least £150. This project will allow SHS to develop a cost-effective area based household engagement system. SHS proposes to repurpose political engagement systems, integrate existing GIS stock data and household survey data. By tracking actual implementation by household, the system will develop intelligent, self-learning lead-scoring algorithms. The successful launch of the SHS screening service is estimated to directly create up to 40 new jobs and help accelerate the uptake of the Green Deal which is estimated will deliver carbon savings of 1.8MtCO2 MtCO2 p.a. by 2020, with an NPV of £8.3billion.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Self-learning lead-scoring algorithms plus GIS/behavioural data to target homes for energy-efficiency uptake; algorithmic screening system. Business(marketing) and Energy(efficiency) considered</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2629,9 +3481,21 @@
           <t>GoodMine is an early stage growth business that has developed a waste prevention platform that collates open source data and creates networks to connect the dots between consumers and the circular ecosystem. The platform includes a data analytics dashboard for local authorities to observe local waste prevention activities and behaviours as they work towards net zero goals. This project relates to a demonstrator trial of GoodMine's technology within the London Borough of Islington in collaboration with Islington Council.</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Waste-prevention platform collating open data with an analytics dashboard for local authorities; digital platform/analytics. Env Sci(waste prevention) considered</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2659,9 +3523,21 @@
           <t xml:space="preserve">This project is focused on developing a methodology to improve iron catalysed alkyl-alkyl Kumada cross couplings. This type of reaction is a promising sustainable alternative to traditionally palladium catalysed reactions, but improving the efficiency, selectivity, and catalyst turnover is important to make the reaction more sustainable and viable for industry. This will be done by developing and using flow apparatus to explore kinetics and reaction pathway. This type of reaction has been previously reported in the literature using Fe(II) acetate, and a xantphos or N-heterocyclic carbene (NHC) ligand; these reactions have achieved yields up to 64% for the xantphos system after 15 mins, and 67% after a total of 27 hours for the NHC reaction. Whilst these yields are promising further optimisation of the catalyst and reaction conditions would make the reaction a cheap, sustainable, and viable option for large-scale chemical production; in particular for the pharmaceutical, agrochemical, and fine chemicals industries , where more expensive and environmentally costly palladium catalysts are commonly relied upon. We plan to exploit the fact that reactions carried out in continuous flow reactors can be probed at steady state to better insight into the reaction and aid the optimisation process. It is anticipated that the additional control over the reaction that can be achieved using flow equipment will also aid in this process. Additionally, this project will focus on expanding the substrate scope to enable the synthesis of beta-functionalised amines, such as functionalised piperadines, azetidines, and man-made amino acids. These are valuable building blocks e.g. for fragment based drug discovery and the synthesis of active pharmaceutical intermediates (APIs). The project will focus on developing a model reaction and general method that can used and applied by other research groups and industry. Finally, throughout this project we will investigate designing a flow reactor </t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Developing iron-catalysed Kumada cross-coupling methodology (kinetics, reaction pathway, substrate scope, synthesis of amines); synthetic chemistry/mechanism. Chem Eng(flow/catalysis) considered</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2689,9 +3565,21 @@
           <t>The reality of climate change is something that governments across the world are having to come to terms with. It is imperative that greenhouse gas emissions are both reduced and offset to prevent global warming, with the aim of limiting temperature increases to a maximum of 1.5 degrees by the end of the century. In order to limit this global temperature rise, many countries have committed to achieving net zero emissions by 2050, which is to say that man-made greenhouse gas emissions are cut as close to zero as possible, while remaining emissions are removed naturally (such as by forests or oceans). There are many different pathways needed to achieve this such as wind, solar, and carbon capture &amp; storage (CCS), to name a few. The focus of this project is to look at the waste streams generated from subsurface green energy projects such as CCS, hydrogen storage, and geothermal. These projects generate large volumes of waste brines that need to be treated and disposed of. Due to the geochemical environment that these brines are formed in, they may contain technologically critical elements (TCEs) in solution such as lithium, cobalt, or rare earth metals, that are valuable in other green technologies such as batteries and solar cells. They may also contain high concentrations of toxic elements such as cadmium which require a higher degree of treatment to dispose of. This project aims to address three different areas regarding subsurface green energy projects in the UK. The first is to analyse groundwater data currently available in the UK to understand where the geochemical conditions are best for the formation of TCE rich brines. Statistical analyses and geographic information systems (GIS) will be used to visualise the groundwater data that has been compiled. Secondly, it is important to understand the chemical composition of the brines that are already being produced by CCS clusters in the UK, and this will be done by analysing samples from four of the UK's CCS cluste</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Treating waste brines from CCS/geothermal/H2 storage and recovering critical elements; resource recovery + pollution treatment. Earth Sciences(geochemistry/groundwater, off-list) and Energy considered</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2719,9 +3607,21 @@
           <t>By combining design with ground-breaking material research, The Home of Sustainable Things is pioneering "ReCinder Ceramics". A project aiming to convert challenging industrial waste into a primary material and high-quality goods for the market. ReCinder Ceramics however, is not solely about the creation of sustainable products. It is about fostering collaboration, reducing environmental impact and promoting the transition towards a circular economy with focus on developing a locally produced sustainable homeware. The material source consists of discarded, broken and defective fired ceramics, primarily a by-product from the ceramic producers. Annually, the UK generates over 32 million tonnes of fired scrap. Using waste as raw material will decrease the amount of waste sent to landfills, minimise material loss and reduce dependency on natural materials, while concurrently offering sustainable alternatives to everyday products traditionally manufactured in environmentally unfriendly ways. Waste materials will be sourced from a network of ceramic producers, capitalising on established relationships and scaling the supplier base as production grows. The Home of Sustainable Things will introduce a range of tableware and tiles, followed by raw materials, including ceramic glazes. The range is intended to meet the needs of domestic, commercial and educational sectors.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Converting industrial ceramic waste ('fired scrap') into a primary material and homeware; waste valorisation/resource recovery. Materials Science and Engineering/design(product) considered</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2749,9 +3649,21 @@
           <t>This project aims to evaluate the feasibility of establishing local manufacturing capabilities for perovskite solar cells (PSCs) by investigating supply chains, indigenous materials, and sustainable development pathways. In addition to exploring locally sourced, sustainable materials for PSC production, the research will quantify waste generation and assess the potential for using secondary materials within the manufacturing process. This dual focus on waste reduction and material reuse seeks to address environmental impacts associated with PSC production, reduce reliance on imported, high-impact materials, and strengthen regional supply chains. By examining the availability, compatibility, and performance of alternative, locally derived materials, this work aligns with goals for a sustainable energy transition and energy access in developing regions, advancing scalable manufacturing solutions that support economic resilience, lower production costs, and promote environmentally responsible technology deployment</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Feasibility of local perovskite-solar-cell manufacturing (supply chains, sustainable materials, waste); manufacturing/supply-chain focus. Energy(PV), Business(feasibility), Materials, Env Sci all in play</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2779,9 +3691,21 @@
           <t>This project, a collaboration between Generation Phoenix and De Montfort University, aims to transform post-consumer fashion leather waste into high-quality materials through advanced fibre characterisation and processing techniques. By recycling post-consumer leather, the initiative reduces landfill impact, promotes fashion circularity, and meets market demand for sustainable circular fashion materials.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Recycling post-consumer leather waste into materials via fibre characterisation and processing; recycling/resource recovery. Thin; Materials Science(characterisation) and Engineering(processing) considered</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2809,9 +3733,21 @@
           <t>We seek support for the development of an in-depth market analysis and a robust market strategy for the exploitation of highly versatile, portable equipment for machining, grinding and lapping of gas safety valves to facilitate a total in situ refurbishment solution. We have 30 years experience and a proven track record in the service and repair of gas safety valves in the UK, Europe and Asia. Through our in-house research and development have identified a gap in the market for in-situ repairs which can significantly reduce operational down time in large scale industrial facilities. We are seeking support to investigate a route to development for an prototype machine that has already been proven on a bespoke basis with a selection of our industrial clients. We would like to offer the market a generic tool that can allow in-situ repairs across a range of safety critical infrastructure platforms in the oil, gas and power industries. To achieve this we need to increase the visibility of our company and expand our client base through a programme of targeted visits and attendance at key trade shows, thus we can develop a deeper understanding of the market and the requirements of our primary clients and develop our working prototypes to meet industrial need. The development of a generic repair tool is a challenging idea for our company and would be a step change for our current business, however our strong international profile means we are expertly placed to exploit the current gap in the market.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Business, Management and Accounting</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Market analysis and commercialisation strategy for portable in-situ valve-repair equipment; this phase is market/exploitation. Engineering(tool/prototype) considered</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2839,9 +3775,21 @@
           <t>In England alone, 3.2 million households are located in areas at risk of surface water flooding, with annual damages exceeding £300 million. It is projected that this cost of associated damage could increase by 40% by the 2050s. Green infrastructure (GI) can provide a means of reducing the amount of water entering drainage systems via infiltration, interception, transpiration and providing both temporary and more longer-term storage. Evidence is needed to understand how, where and when GI aids flood risk mitigation over time and space. This project will consider the following research questions: How can we better represent the structure and function of green infrastructure in our flood risk impact models? How can we design green infrastructure into the existing urban fabric to maximise benefits and reduce costs? How effective will green infrastructure be as a flood mitigation measure under future climate? This project will conduct a number of controlled experiments at the National Green Infrastructure Facility and at locations of different GI types across the city. Observations will then be used to inform a reliable and robust physically-based infiltration component in CityCAT, a hydrodynamic model capable of simulating flood risk, and the role of GI in mitigating that risk at high resolutions over large spatial domains. Outcomes from this project will include improved understanding of GI performance; assess long-term performance and costs of GI, including management and maintenance; and aid design of future GI strategies to mitigate climate-induced flood risk in urban areas.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Green infrastructure for urban flood-risk mitigation (infiltration/storage, hydrodynamic flood modelling, climate); freshwater/climate/environmental planning. Engineering(civil/hydraulic modelling) considered</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2869,9 +3817,21 @@
           <t>The use of novel feed materials to increase sustainable protein production whilst improving the health and survival of piglets post-weaning will be addressed. Poor growth rates and high disease incidence are associated with the early post-weaning period due to factors such as oxidative stress that causes gut damage. Sustainable alternatives to zinc oxide, added to feed as an anti-microbial and growth promoter, are required to reduce morbidity and mortality and improve subsequent growth and productivity. Improved pig nutrition across the lifespan will also improve meat quality, reducing import dependence. The project will build on prior feasibility studies where supplementation of pig feed with polyphenols provided protective effects, improving piglet gut health and survival, as well as meat quality and shelf life. Polyphenols are anti-microbial, anti-inflammatory, anti-oxidant compounds present in plant materials. Agri-food by-products (AFBPs) generated by agriculture and food processing activities are readily available for processing to provide a sustainable source of polyphenol-rich feed supplements. Conventional methods (e.g., drying and milling) will be used to process AFBPs for inclusion in pig feed. Polyphenol extraction using previously developed sustainable methods will enable separation of polyphenols from plant fibre. These polyphenol rich extracts can then be standardised for use as supplements. Separation from fibre is important when feeding the young pig as high dietary fibre around weaning reduces nutrient utilisation and thus feed effciency. The benefits of polyphenol supplementation will be examined across the pig lifespan through controlled feeding trials at the University of Leeds National Pig Centre and commercial farms at Cranswick facilities. The economic and sustainability benefits of these innovative approaches will be compared to existing practices. Successful AFBP exploitation will generate additional revenue streams for farmers, divert wast</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Agricultural and Biological Sciences</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pig nutrition/animal science: novel feed supplements (polyphenols) for piglet health, growth and meat quality via feeding trials. Chem Eng(extraction of supplements) considered</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2899,9 +3859,21 @@
           <t>To transfer and embed Circular Economy knowledge and related innovation.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Abstract too thin to judge: single sentence ("transfer and embed Circular Economy knowledge and related innovation"), no field content. Looks like a KTP; field indeterminable</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2929,9 +3901,21 @@
           <t>Covid-19 has impacted many sectors; one such sector is the waste management and recycling industry. The amount of waste generated by households in the 'first wave' of the pandemic has increased significantly, whilst the collection of recyclables has been suspended by many local authorities. The current waste management and recycling sector struggles to efficiently cope with changes in waste volumes and composition. In parallel there are calls for a 'green recovery' for the UK, with waste management, recycling and renewable energy at the forefront of the much-needed transformation. The ReSuB (Renewable &amp; Sustainable Biomass) project responds to both these challenges. The project will demonstrate and develop new value chains and markets for recycled paper, simultaneously supporting the UK's growing renewable energy industry. Fiberight has developed an innovative circular economy solution to create value-added products from residual waste, which is typically landfilled or incinerated. The ReSuB project will demonstrate the recovery of pulp from residual waste and the manufacture of products for the biomass fuels market. This market is actively searching for alternative products to current wood-based materials due to shortage of supply and therefore increasing costs. The project will carry out market testing with a biomass plant producing electricity. The ReSuB project will generate significant positive environmental impacts by diverting recyclable waste from landfill, by recovering valuable materials to be used again, by displacing virgin materials and helping to combat climate change. There will also be wider advantages of developing UK industry, with associated job creation and wider socio-economic benefits.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Recovering pulp/materials from residual waste and diverting from landfill (Fiberight, as V032); recycling/resource recovery. Energy(biomass fuel) considered</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2959,9 +3943,21 @@
           <t>Rare earth magnets, based upon neodymium iron boron (NdFeB), are a key component / material in direct drive wind turbines, where they are used in the generator. However these materials are top of the risk register on the UK's critical minerals list. The UK has vast wind resources and as such the government has invested heavily, in particular, in offshore wind turbines where direct drive turbines play a key role. As these turbines reach end of life it will present a significant opportunity as a secondary source for recycling or re-use. The aim of the Re-REwind project is to develop a circular economy for rare earth magnets from end-of-life wind turbines. This additional volume will be critical for not only the UK, but also the global decarbonisation agenda, with this being 'additional' material which can help avoid the upcoming global supply shortfall which is predicted. This project will look to build the basis for a new complete circular supply chain for these magnets, a completely new industry and sector which the UK currently does not have. To do this, it will tackle several key challenges; firstly how to dismantle the turbines, secondly to develop techniques to safely demagnetise and separate the rare earth magnets from the generators and then how to purify and to recycle the extracted materials back into new NdFeB magnets with properties which can be used in another generator. The Offshore Renewable Energy Catapult (OREC) will undertake a life cycle, and techno economic assessment, looking at the opportunity for recycled magnets, and critically their CO2 footprint, relative to virgin supply. This will allow the UK to fully understand the additional material which can be supplied, and the competitive advantage these will bring. All partners are also heavily involved in improving and disseminating industry best practise with regards to the safe handling of magnets. This will look at demagnetisation options, in addition to handling of full assemblies, magnet stack</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Circular economy/recycling of rare-earth magnets from end-of-life wind turbines (dismantle, demagnetise, purify, recover); resource recovery of critical materials. Materials(magnets) and Engineering(separation) considered</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2989,9 +3985,21 @@
           <t>The fundamental goal of this collaborative research project is the development of synthetic methodologies that will allow for the efficient construction of medicinally relevant compounds from simple, readily available starting materials. In this context, the project involves the design and synthesis of novel photocatalysts that can be exploited in synthetic organic reactions. Harnessing light to promote reactivity can be viewed as a more sustainable and economic energy source when compared to conventional methods such as heat and can be used to overcome significant reaction barriers. The most used catalysts in organic photoredox chemistry involve transition-metal complexes comprised of iridium, rhodium, or ruthenium. However, these platinum-group metals are rare, expensive, and usually require pre-functionalised starting materials for the reactions to proceed. In recent years, the development of catalysts that avoid these metals have shown promise in this field. However, these catalysts have limitations including low selectivity and the requirement of high energy UV-light. Furthermore, the reactions developed using these catalysts can be low yielding, be limited in scope and display competitive product decomposition. Crucial to progressing in this area is the development of novel visible light responsive photocatalysts that can be modified to (i) enhance the catalytic efficiency, (ii) exhibit additional functionality - that can be used to facilitate catalyst isolation and/or recycling, and (iii) increase the reaction rates and yield. This has sparked the drive towards more sustainable, tuneable, and selective visible-light active photocatalysts that can be used in synthetic organic reactions. In terms of organic reaction types, particular attention will be focused on photocatalytic C-H functionalisation for this project. Couplings through C-H bond functionalisation involves the use of simple substrates that are directly converted into more complex molecules, without</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Designing/synthesising novel photocatalysts and synthetic methodology (photoredox C-H functionalisation) to make compounds; bench synthetic chemistry</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3019,9 +4027,21 @@
           <t>Solid catalysts are employed in more than 85% of industrial reactions, whose economic impact is estimated to 30-40% of global GDP. Heterogeneous catalysts also play a central role in the production of high-value chemical compounds, such as fuels and additives, pharmaceuticals, and polymers (plastics). Recently, these materials have attracted significant interest in the context of sustainability, CO2 utilisation, and green-chemistry, as they can facilitate transformations such as CO2 or biomass to useful chemicals at high efficiencies. Thus, motivated, the project will develop advanced computational methodologies and an integrated kinetic Monte Carlo (KMC) framework for the simulation of complex reaction kinetics on solid surfaces, focusing in particular on photo(electro)catalysts which may undergo structural changes as the reaction progresses. In this D.Phil. project, these methods will be extended aiming at (i) improving the robustness of the approximate acceleration algorithms by introducing mathematically rigorous ways to calculate error norms and improved strategies to down-scale kinetic constants, (ii) tackling the simulation of dynamic lattices, to take into account catalytic surface reconstruction explicitly in the modelling, (iii) introducing photo(electro)chemical events in the KMC framework making it possible to model chemistries relevant to sustainability, such as solar-powered CO2 conversion to valuable products. The project includes mainly mathematical computational method development activities, and will deliver a general-purpose framework for the accurate simulation of photo(electro)chemical processes. The host lab has previously developed computationally efficient approaches, algorithms and code, based on the KMC method, enabling the high-fidelity modelling of catalytic reactions in which several parallel and competing reaction pathways exist, and the participating surface species may exhibit alternative binding configurations and may be subject to l</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Computational kinetic-Monte-Carlo method development for reaction kinetics/mechanisms on catalytic surfaces; reaction dynamics/mechanisms. Chem Eng(catalysis and surfaces) is a strong alternative</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3049,9 +4069,21 @@
           <t>Photonics is set to become the UKs third most productive manufacturing sector by 2035 with many innovations enabled by photonic integrated circuits (PICs). The development of PICs, whilst necessary, requires many energy intensive cycles which negatively affect the environment. These development cycles are needed because once fabricated the layout of the device cannot be improved without additional fabrication. At Light Trace Photonics, we are developing the next generation of optics components that go beyond the limited scope of current fibre-based componentry and which enable reconfigurability without additional fabrication. Our component modules provide high-performance, tunable, optics componentry that can be used to cut the number of energy intensive development cycles required to bring photonic products to market. Crucially, our core technology is long lasting and therefore can be leased to multiple users over its lifetime, helping to contribute to the circular economy. Our innovation, if brought to market, will help reduce the footprint of photonics innovation - crucial for helping the UK tackle many of its other key strategic challenges such as the ageing society and future mobility.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Developing reconfigurable/tunable photonic (optics) components and integrated circuits as products; applied photonics/electronic engineering. Physics(photonics, off-list) considered</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3079,9 +4111,21 @@
           <t>Research aim: To investigate digital solutions to promote a circular use of traditional/collaborative industrial robots (IR) in manufacturing lines by extending the useful life as well as enabling their end-of-life (EoL) remanufacturing and recycling of embedded critical raw materials (CRM). Context: The UK, being the eight largest manufacturing economy, is increasing its reliance on industrial robots (IR) within its manufacturing sector. According to BEIS's research, the country's industrial robots market is projected to grow at over 40% annually from 2020-2030. However, this rapid integration brings concerns with regards to environmental sustainability, given that decommissioned robots and related equipment often contain large amount of CRM. Challenge: The primary challenge is managing the environmental impacts of the widespread use of IR in various sectors like automotive, aeronautical, and healthcare. Current maintenance practices in the UK often rely on manual checks and standard procedures, leading to over-maintenance, high costs, and missed faults. (lack of trusted monitoring data) during use stage, the EoL management involves costly refurbishment to enable a secondary use cycle (often by a different end-user) and/or downcycling of CRM due to adoption of inappropriate material recycling processes. Objectives: Enable real-time access to authentic performance and service history data of IRs recorded within a digital passport, using advances in AI and blockchain. Prolong the operational life of IRs, thereby reducing the need for repairs or replacements. Facilitate remanufacturing and circular use of CRM. Develop a digitally-enabled EoL management system for IRs. This system aims to predict future IR failure scenarios, promote industry-wide collaboration, and enhance operational efficiency and resilience. Implement a proactive, data-driven lifecycle maintenance approach that is cost-efficient, optimizes equipment performance, and ensures environmental sustainabil</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Digital solutions (AI, blockchain digital passport, predictive analytics) for circular use/EoL management of industrial robots; the research is the digital/data system. Engineering(robots/remanufacturing) is a strong alternative</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3109,9 +4153,21 @@
           <t>The main objective of this project is to computationally design sustainable organic coated steel (OCS) products with tailored functional properties that meet operational performance while addressing environmental and social concerns. Global challenges associated with resource scarcity, climate change, overpopulation and overconsumption have resulted in recent global and regional initiatives such as the United Nation's 2030 Agenda with the sustainable development goals (SDG) and the European Green Deal. Such initiatives, in parallel with social concerns, have highlighted the importance of driving sustainability across most of the sectors of our society. Aligning with these ambitions of achieving climate neutrality by 2050, implementing circular economy principles, reducing waste, and increasing materials efficiency and resiliency, the steel industry must make pioneering changes towards new product and process developments for all its upstream and downstream value chain operations. This project will provide a computational design framework to assist the development of sustainable OCS materials, with a focus on molecular reactivity, electronic and mechanical properties, in connection to materials' flexibility, corrosion, and stability under UV light.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Computationally designing organic-coated-steel materials and their properties (corrosion, mechanical, stability); material behaviour. Chemistry(computational/molecular reactivity) strong alternative. Field not in dropdown</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3139,9 +4195,21 @@
           <t>To revolutionise fashion content creation by using Haiper's AI model to transform single photographs into diverse digital content, reducing the need for multiple shoots. This innovation can facilitate sustainable choices such as minimising travel, reducing resources, and enhancing demand planning, driving the fashion industry towards a more circular economy.</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Applying a generative AI model to turn single photos into varied fashion content; AI/ML is the innovation. Thin; Arts(fashion) considered</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3169,9 +4237,21 @@
           <t>Using a deliberative approach, ECOSENS will analyse citizens’ views and risk perceptions, benefits and potentials of current and new nuclear technologiesin the context of majorsocietal challenges(climate crisis,sustainable energy policies, energy security). It will review through a socio-ethical lens the uptake of recommendations on stakeholder engagement and transdisciplinarity (notably integration of social sciences and humanities) in nuclear research and decision making, developing recommendations to overcome challenges. Societal stakeholders (authorities, industry, academia and civil society) are engaged to explore and co-construct possible energy futures and the role of nuclear energy therein. Sustainability assessment of current nuclear energy technologies will take into account the entire life of the nuclear investment including the nuclear fuel cycle. Integration of new technologies (Gen III+, IV, SMR) is then explored in the context of the future energy market and societal developments to identify the possible roles of nuclear energy in the climate neutral economy targeted for 2050. Multiple perspectives (nuclear experts, social scientist, stakeholder, society) are integrated and methodological recommendations for sustainability assessment are agreed. To address the weaknesses of existing economic models, ECOSENS develops a novel model based on the system of provision approach in order to create and calculate indicators relevant for a plethora of stakeholders (consumers, governments, suppliers). The model will include the “social discount rate” and considers the limits of our planet, as reflected in the “circular economy” system. A series of national case studies evaluates the model and provides relevant recommendations to stakeholders. ECOSENS activities and results will be largely communicated and disseminated through the network of stakeholders established to support innovative involvement, as well as through Open Access facilities</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Social Sciences</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Deliberative analysis of citizens' views/risk perceptions and socio-ethical/stakeholder study of nuclear energy's societal role; sociology/STS/policy. Economics(the economic model) considered</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3199,9 +4279,21 @@
           <t>The Circular Economy requirements and sustainability goals have been set out by the UK government and the United Nations to address the climate crisis and maintain our standard of living. The environmental impact from the global consumption of engineering materials is expected to double in the next forty years (OECD: Global Material Recourses to 2060, 2018), while annual waste generation is projected to increase by 70% by 2050 (World Bank What a Waste 2.0 report, 2018). A radical departure from traditional forward manufacturing is needed that no longer exclusively focuses on the original manufacturing process and the end of life dispose of manufactured products, parts, and materials. Processes are needed that will significantly prolong the useful life of engineering and especially critical materials (minerals with high economic vulnerability and high global supply risk e.g. rare earth elements for batteries, magnets and medical devices) by increasing the effectiveness of reuse, repurpose, repair, remanufacture, and recycle (Re-X) manufacturing processes. These Re-X processes are currently 3-6 times more labour intensive than traditional manufacturing processes. They are often not economic resulting in many engineering materials being disposed on landfill sites, degraded, or incinerated. UK businesses could benefit by up to £23 billion per year through low cost or no cost improvements in the efficient use of resources. The vision of this hub is to pursue an integrated, holistic approach toward creating a new manufacturing ecosystem for circular resource use of high value products through advances in AI and intelligent automation, empowering the UK to be a world leader in circular manufacturing. To deliver this ambition the hub will focused on two grand challenges: GC1: Radically transform the sustainable use of critical materials. (Goal: &gt;75% Critical components reuse; &gt;20% critical material use decrease; &gt;50% component reclaim increase). GC2: Radically improve the p</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Re-X (reuse/repair/remanufacture/recycle) circular-manufacturing processes with robotics/AI automation for critical materials; manufacturing. Env Sci(circular resource use) considered</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3229,9 +4321,21 @@
           <t>Single atom catalysis (SAC) is an exciting, growing field of research which has attracted considerable attention over the last decade. While the field is in its relative infancy, single atom catalysts have been observed to hold a plethora of advantageous characteristics. Aside from an inherent decrease in degree of saturation which can result in higher activity, moving towards smaller catalyst systems results in a shift from the continuous energy bands present in bulk metals, to discrete energy levels in single atoms or small clusters. This change facilitates a range of unique electronic and geometric structures which possess distinct, size-dependent properties relative to the bulk material which have the potential to be exploited for applications such as catalysis, if the relationship between cluster-size and activity can be understood and controlled. In fact, a number of studies have reported distinct catalytic pathways observed for SACs in comparison to their nanoparticle counterparts, with some displaying enhanced activities and selectivities. This enhancement has been attributed to factors including a higher degree of unsaturation, quantum size effects, significant support-metal interactions and access to different quantum states and configurations. With each of these aspects imparting the possibility of tuneability, SACs provide an opportunity to revisit the optimisation of reactions from a completely new perspective and toolkit. The Haber-Bosch Process (HBP) is arguably the most famous catalytic reaction, which is estimated to account for 1% of the world's energy usage, because of the harsh operating conditions required. Despite 100 years having passed since the invention of the HBP and substantial research efforts, the ammonia synthesis industry remains dominated by the historic iron catalyst with operating conditions mirroring those described in Haber's Nobel lecture in 1920. This presents the perfect opportunity to revisit ammonia synthesis from a new lens</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Fundamental single-atom catalysis: electronic/geometric structure, catalytic pathways, activity/selectivity for ammonia synthesis; catalyst science/mechanisms. Chem Eng(catalysis and surfaces) strong alternative</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3259,9 +4363,21 @@
           <t>A key challenge in engineering biological systems is the development of re-usable, precise and tunable gene expression control elements. Currently, developing these systems requires expensive and time-consuming experiments based on trial-and-error. This is particularly problematic for applications requiring complex systems with multiple co-regulated components or systems that use components obtained from non-model microorganisms. This project will develop tools to systematically characterise transcriptional control elements, uncovering their design rules to enable re-use of these control elements in alternative hosts and genetic contexts. Transcriptional regulation in prokaryotes is achieved primarily through the binding of transcription factors (TFs) to a promoter. Each TF has a specific binding preference, which determines its function (activator or repressor) and the location of its binding site(s) within a promoter. Knowing the biophysical binding preferences of TFs, hence, enables computational prediction of the regulatory logic and the transcriptional activity of any given promoter1,2. Currently, however, the biophysical binding preferences are known for only a handful of TFs, meaning that we cannot easily exploit heterologous TFs in bioengineering. In this interdisciplinary project, the student will utilize a range of molecular/synthetic biology, microbiology, and biophysical approaches to: (i) develop an experimental and data analysis pipeline that can determine the binding preferences of any given TF; (ii) unravel design rules of activators; (iii) use the pipeline to study the evolutionary rules governing how TFs adapt to heterologous hosts. As such the student will acquire skills that are highly relevant for future careers in the molecular biology and microbiology, biotechnology, biopharmaceutical, industrial biotechnology and related industries. Achieving these objectives will enable researchers to rapidly characterize the function (i.e. binding preferenc</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Characterising transcription factors/promoters and design rules for gene-expression control via molecular/synthetic biology; molecular genetics. Field not in workbook dropdown; coded per protocol's twelve</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3289,9 +4405,21 @@
           <t>Hubs for Circularity (H4C) are to be the European lighthouses of resource efficiency: through implementing best practice in industrial and urban symbiosis (I-US), the H4C are intended to achieve a step change in circular utilisation of resources and GHG emission reductions within given geographic areas. The European Community of Practice (ECoP) builds on and brings together ongoing work and expertise on H4C and I-US, initially supporting the H4C demonstrations funded under Horizon Europe. This project will develop both the ECoP network of stakeholders (commencing with funded H4C demo projects) together with an information and knowledge platform to enable stakeholders to take action. By creating awareness and fostering knowledge sharing between regions/cities and their industries, the H4C Platform will provide the tools and the evidence base for the approach to be adopted widely across Europe. A sustainable business model for deployment of the toolkit and services developed under the project will ensure the H4C ECoP is maintained well into the future. This consortium led by ISQ not only includes world leaders in the field (experienced in delivery, training, stakeholder engagement, models and methodologies) but also has the specific committed support and participation of many of the European bodies (those representing regions, cities, industry, educational institutions etc) that are needed to both disseminate the project outcomes and initiate implementation. Working closely with its sister consortium H4C-Europe, the H4C ECoP consortium is confident of delivering an ECoP and H4C platform that will achieve the target of greater circularity and carbon neutrality through profitable actions that also benefit communities/civil society.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Social Sciences</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Building a community-of-practice stakeholder network and knowledge platform for industrial/urban symbiosis; knowledge exchange/coordination. Business(model) and Env Sci(industrial symbiosis) considered</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3319,9 +4447,21 @@
           <t>The disposal of waste tyres is a significant environmental issue particularly as their disposal in landfill was banned in 2003 in the UK and Europe. Most tyres are "mechanically" recovered i.e. they're shredded, and the recovered rubber shreds and crumbs used in road and other rubberised surfaces and the recovered steel and textile reinforcements either re-melted or valorised, respectively. In the UK about a quarter of the 550,000 tonnes of arising waste tyres are exported as shreds -- much of it ending up in India, where they batch pyrolyse the shreds to produce tyre recovered oil, a heavily polluting sulphur containing fuel. In 2019, the Indian authorities began restricting tyre waste imports to the extent that this permanent change is expected by UK's Tyre Recovery Association, Environment Agency and Defra to place significant strain on UK recycler's ability to meet demand for recycling services. The UK desperately needs new capacity (in the form of pyrolysis operations and other technology) to avert heightening levels of fly tipping and make this waste stream more sustainable. BIG ATOM has developed the concept of a novel pyrolysis reactor with improved temperature control with the vision of a circular economy for waste tyres. We now propose to construct, test, and prove the concept of a quarter-scale reactor that is big enough to demonstrate the issues associated with scale-up. If the project is successful it will form the basis of a full-scale reactor for the commercial production of recovered Carbon Black (rCB) and Tyre Recovered Oil (TRO) of an improved quality that can be used as part of the circular economy to create new truly recycled materials.</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Waste-tyre pyrolysis to recover carbon black and oil (circular economy for waste tyres); recycling/resource recovery per the scheme's convention. The pyrolysis reactor + scale-up give Chem Eng a strong claim</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3349,9 +4489,21 @@
           <t>The Solar Battery Hub Phase 2 project is an ambitious project taking a holistic approach to addressing Nigeria's significant energy access challenges by replacing diesel generators with scalable, renewable energy systems tailored to underserved communities. With over 85 million Nigerians lacking access to energy, and 34 million SMEs reliant on costly diesel generators, this project delivers innovative clean energy solutions to bridge this gap. The Solar Battery Hub is a central energy distribution that will sit at the heart of communities, offering solar-powered battery swapping services for households, businesses, schools, and healthcare facilities. The holistic approach now also incorporates Moonlight Energy's e-mobility system that enhances renewable energy adoption through swappable battery technology for electric scooters and motorcycles, reducing reliance on diesel for transportation. Tree Associates' AirBattery introduces a novel compressed air energy storage system, delivering reliable baseload power for energy-intensive applications such as rice milling, healthcare, and irrigation. The project will be demonstrated in Tudun Wada, a rural community in Kano State with a population of over 228,000, where only 8 hours of electricity from the grid is available daily. The region heavily relies on diesel and petrol generators to support its vibrant agricultural economy, including 400 rice millers and over 3,470 SMEs. This demonstration will showcase how integrated clean energy solutions can transform productivity and resilience in regions facing severe energy access challenges. Key use cases include productive applications like agriculture, where 45% of farmers face post-harvest losses due to unreliable energy, and education, where 65% of schools lack electricity, hindering access to technology-based learning. By ensuring reliable electricity, the project directly addresses these critical sectors. The project creates economic resilience by creating local employment</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Renewable energy systems for energy access (solar generation, battery swapping, compressed-air storage) replacing diesel; energy is the object. Social(development/access) considered</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3379,9 +4531,21 @@
           <t>The overall objective of CIRCUIT is to develop a holistic approach supported by digital solutions and guidelines to foster the introduction of innovative engineering practices in the whole construction supply/value chain to foster The overall objective of CIRCUIT is to develop a holistic approach supported by digital solutions and guidelines to foster the introduction of innovative engineering practices in the whole construction supply/value chain enabling circular, sustainable resilient and smart transport infrastructure and a wider deployment of Green Public and Innovation Procurement. This will be achieved by: i. developing and deploying an innovative open-source digital platform (with advanced Circularity analytics and Supply/value chain matchmaking tools) interoperable with traditional engineering/ design (BIM, Digital Twinm LCC, LCA) and traffic simulation tools; ii. introducing modular solutions, ecodesign and reusing concepts as alternative to traditional designs; iii. maximizing the use of biobased, Secondary Raw Materials (SRM) and Secondary Construction Elements (SCE) as alternative to traditional ones; iv. including in the decision making process of transport infrastructures design and route planning, information from updated traffic simulation tools to reduce incidents, accidents, congestion and future scenarios with autonomous vehicles). New elements and technologies for Circular, Smart, Resilient and Sustainable transport will be included in the design process to facilitate infrastructures upgrading and a quick adaptation to smart mobility and operations. CIRCUIT will also provide knowledge and technicalsolutions by exploiting the potential of fourstrategic pillars: Digitalisation, Recycle, Reuse and Energy. Different technologies will be validated in each of the pillars to deliver a holistic approach suitable for different transport modes, the urban and interurban environment, and the different stages of the life cycle of infrastructures.</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>guess</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Circular, sustainable construction of transport infrastructure via engineering practices, modular/ecodesign, secondary materials; civil/built-environment. CS(digital platform/BIM) and Env Sci(circularity) considered</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3409,9 +4573,21 @@
           <t>The purpose of this research project is to evaluate the future of islands and the potential of transforming them in sustainable energy resource hubs by taking into account of circular economy principles. The proposed Phd topic takes an interdisciplinary approach to analyse trade-offs associated with energy and resource use, by analysing consumption patterns and supply chains. Various environmental and economic factors will be considered to enable better management of energy resources in a circular economy. It will first start with a clustering analysis to identify patterns that might be relevant to several of them. Will then continue to gather data for energy and other resources for Scottish Islands and study the impact of various energy supply sources (e.g renewable energy, waste to energy, hydrogen) on energy demand-supply balance and potential for storage and interconnections under different climate scenarios. This will be achieved through scenarios analysis considering detailed modelling of energy demand (buildings, transport, service sectors), by determining the optimal combination of energy solutions for Scottish islands as a case study. The project is highly interdisciplinary one requiring an understanding of data processing, different modelling techniques, value stream mapping.</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Energy-systems analysis for islands: demand/supply modelling, supply sources, storage, scenarios; energy systems as a whole. Env Sci(resource use) and Engineering(systems) considered</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3439,9 +4615,21 @@
           <t>Concrete, the most used material in the world after water, is responsible for 8% of global CO2 emissions. Most of such emissions come from the cement needed to give concrete its strength. At the same time, the UK's concrete industry extracts 180Mt/year of natural aggregates (sand/gravel) from our quarries and riverbeds, with huge negative environmental impact. The UK also produces 45Mt/year of 'waste' concrete from old, demolished buildings. Concrete absorbs CO2 through a chemical process called 'carbonation', which increases its strength. Concrete carbonation rarely happens naturally as it needs specific temperature, relative humidity, and can take 100+ years to occur. End-of-life concrete has huge potential to absorb significant amounts of CO2 and to be replace natural aggregates to produce new concretes. However, end-of-life concrete from demolition is very porous, and thus the strength of the new concrete is always below standards. Therefore the UK's concrete/construction industry downcycles end-of-life concrete in backfill/drainage applications. This project aims to develop new CO2-absorbing aggregates made of crushed upcycled end-of-life concrete from demolished buildings. We have an innovative technology that sequesters CO2 into end-of-life concrete (30% btw) and reduces carbonation time to around 100 hours, instead of years. By speeding up carbonation, we can a) reduce the porosity of end-of-life concrete from demolition, b) increase the strength and durability of new concrete, and c) replace natural aggregates with crushed end-of-life concrete in the production of new concrete for structural applications. Valorising the properties of end-of-life concrete and sequestering CO2 into it allows our technology to be economically viable at large scale. Our approach recycles end-of-life concrete and injects CO2 into it, making concrete a very low-emission material. The UK is committed to large infrastructure projects (HS2, Sizewell C, thus huge demand for concrete)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Upcycling demolished-concrete waste into CO2-absorbing aggregates (accelerated carbonation) to replace natural aggregates; waste valorisation + CO2 sequestration (as V004). Engineering/Materials(concrete) and Chem Eng(carbonation) considered</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3469,9 +4657,21 @@
           <t>England faces serious risks of water shortages, especially in the drier south and east. Climate change, an increasing population and the need to protect the environment bring further challenges to an already strained system. The National Infrastructure Commission is calling for £21 billion of investment over the next 30 years to avoid £40 billion in emergency response costs. As part of the new National Framework for Water Resources, this project will look at the best options for meeting this challenge within the Water Resources West region by optimal use of water abstractions, storage and transfers. The project requires engagement potentially across diverse topics such as climate change, aquatic ecology, fluvial geomorphology, surface and groundwater hydrology, water infrastructure engineering and economics. It will also require the application of new multi-scale optimisation methods to water resources planning and an evaluation of such an approach in a real-world application. The task is challenging as the Water Resources West region crosses a national border (with Wales) as well as catchment boundaries. New multi-criteria decision-making methods are therefore sought to satisfy the requirements at scales from individual catchments through water resource zones to multi-national, and across a wide range of sectors. There are currently no established industry methods for this in the UK. Part of this project will be to work alongside Water Resources West and its members to evaluate the approach used. It will also involve a review of the literature to identify different methods for multi-scale decision making, conduct trials of these for water resources planning and potentially develop new methods which may utilise fuzzy logic, compromise programming, game theory or stochastic systems modelling. The primary EPSRC research area relevant to this project is Water Engineering, in particular R2: to ensure a reliable infrastructure; and R5: to build new tools to adapt to clim</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>fairly sure</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Multi-scale optimisation/decision methods for water-resources planning and infrastructure (abstractions/storage/transfers); self-identified 'Water Engineering' (civil). Env Sci(water resources/freshwater/planning) considered</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/validation/discipline_verification_sample.xlsx
+++ b/data/validation/discipline_verification_sample.xlsx
@@ -481,39 +481,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4934160C-271D-468F-9B54-DAB37FD52481</t>
+          <t>45DA5F20-7407-4376-97DD-80F7B20396A4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Yellow Sub Hydro</t>
+          <t>CloudEARTHi: Innovation capacity building for the use of Big Data in Environmental Sciences, Sustainability and Circular Economy in HEIs and their entrepreneurial ecosystems</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>The post COVID-19 challenge is to build-back-better. Yellow Sub Hydro will instigate a step-change in the way the global mining industry manages our most precious of finite resources - water. United Nations research suggests more than half of the global population will be exposed to severe water scarcity within the next four decades as a result of both climate change and growing demand. We all have a stake in ensuring water is used ethically, responsibly and sustainably. One of the most water-intensive industries is the metals and mining sector, where no water literally means no business. Mine operators rely on 'water-balance' models to underpin many of their strategic decisions and risk management. These are mathematical representations of the way the water cycles from precipitation through the ground before ultimately leaving the local system via an outflowing river. The current state-of-the-art water-balance modelling typically takes a team of highly specialised hydrogeologists 1-3 years and up to a million dollars for a single mine site (there are tens of thousands of mine sites globally). Our idea is to use digital and machine learning technology, together with proprietary algorithms to reduce the modelling output into near real time, whilst losing none of the accuracy. Yellow Sub Hydro aims to help mining companies meet their environmental and social obligations (and their licence to operate) at the same time as saving them time and money. The innovation we are delivering will promote circular economy by providing a new landscape for other advances in efficiency and impact reduction from mining operations. For us, driving a sustainability agenda and making an impact socially and environmentally as well as economically has huge appeal, and we envisage this manifesting through driving a step-change in water resource management across a globally important industry.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Core work is ML/digital modelling product for mine water balance; hydrology application (Env Sci) considered</t>
-        </is>
-      </c>
+          <t>The project will bring together a consortium of five higher education institutions (HEIs) and one business partner to review, assess and improve institutional innovation and entrepreneurship practices. The consortium’s vision is to build capacity for innovation across HEIs, students, and businesses in the area of big data, environmental science, sustainability, and circular economy. This area has been assessed as a key strength of the consortium and is essential to society in order to understand, adapt to, and mitigate against the climate crisis and wider sustainability issues, building entrepreneurial and innovation capacity across all actors in society. The project benefits from an alignment with the goals of EIT Climate-KIC, EIT Digital and EIT RawMaterials, and its outcomes will support the strategic aims of these Knowledge and Innovation Communities (KICs). The consortium benefits from high-level institutional commitment to improving innovation activities, as well as an impressive track record in building academia-industry partnerships, nurturing student and academic entrepreneurship, and delivering worldleading education and teaching. The project uses the EIT’s knowledge triangle model to build innovation capacity, supporting a knowledge-based and data-driven integration of research institutes and businesses to advance the use of big data in the subject area through a multidisciplinary approach. The project has mapped four knowledge gaps between the components of the EIT knowledge triangle: - a gap in improving the adoption of data and its role in the subject area across HEIs; - a research-education gap; - a business-education gap; - a gap between society’s needs and all other components. Bridging these gaps will help society to adopt a more informed and data-driven approach to decision-making, leveraging the full potential of big data in relation to climate change, sustainability, and the shift to circularity. The consortium believes that the HEIs are best pl</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,39 +511,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5824C3AE-A2EC-4B40-B3FE-E7E0A1CAC32D</t>
+          <t>C39F6B01-10A6-406A-B2E6-5ED9C83FB0F0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ISCF</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Unpackaged: A Circular Supply Chain Solution To Scale Bulk in Retail</t>
+          <t>Baby Equipment for the Circular Economy</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Single-use plastic (SUP) packaging is now firmly on the public agenda. Whilst the government and industry have started to look for solutions, most innovation to date has focused on creating alternatives to SUP packaging, such as bio plastics or paper, or improving collection and recycling systems, because this allowed 'business as usual' to continue. Whilst these are valuable improvements, we believe the focus should be at the top of the waste hierarchy - i.e. the reduction and reuse of packaging - which would represent a true shift from a linear to a circular economy solution for plastic packaging. With over 13 years of experience in zero-waste retail, and actively promoting reuse across the sector, Unpackaged proposes to work with a consortium of experts and industry partners to explore the feasibility of reusable packaging in the supply chain. We will leverage existing logistics infrastructure to move bulk products in a 100% circular system in order to service bulk dispensers in-store. We believe that innovation in this area is necessary to enable retailers to implement and scale bulk (zero packaging) solutions for their customers. We aim to prove that it is possible to get rid of SUP packaging within the supply chain with a reusable alternative that is financially, operationally and environmentally viable. The results of this research will lead to live in-store trials with our partners as we test and build our solution.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Supply-chain/retail feasibility for reusable packaging; effort is logistics/operations, not packaging technology</t>
-        </is>
-      </c>
+          <t>This project explores the technical, economic and commercial viability of applying the circular economy to certain baby products, including design and testing to ensure that they can continually meet British Standards in a business model based around re-utilisation.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,39 +541,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1FF83B4F-0A38-437D-9026-0D10D511834A</t>
+          <t>C5597E18-F85C-4FA3-98E8-54CC8F9065DD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>W2W Zero Emission Energy Generation and Storage</t>
+          <t>West of England Industrial Cluster Local Industrial Decarbonisation Plan</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>This project will allow Steamology to demonstrate zero emission off grid power and storage at the micro grid scale in Kenya with our partners Strathmore University, specialists in Renewable Energy (RE) research and training. Steamology is an innovative technology development company with an extreme engineering pedigree and a land speed record breaking heritage. Steamology is developing a zero-emission energy generation and storage system designed to be used with RE generation such as PV solar, geothermal or wind turbine. Our W2W (Water to Water) system contains a compact energy dense steam generator. Steam is generated using energy stored as compressed hydrogen and oxygen gas in tanks. High pressure superheated steam is used to drive a turbine to do useful work generating electricity. RE is used to power electrolysis to generate and compress hydrogen and oxygen gas into storage tanks. Traditional battery solutions for off grid energy storage use a wide range of often toxic or scarce chemistries such as Lithium, Cadmium, Lead, Antimony. These batteries have limited charging cycles (typically 500- 2,000) and do not have recycling plans in place for end of life. The W2W system has: - Zero emission - No CO2, NOX, SOX, or particulates - High power and torque - 10kW to 1MW range, scalable and modular units - Low noise and thermal signature - Quiet vibration free operation, low temperature signature - Operating temperature agnostic - Functional in a wide range of environments - Low maintenance - Few moving parts made of standard engineering materials - Without loss of performance over charging cycles -- Long life and service interval - Without toxic or scarce materials -- No Pb, Sb, Cd, Li or other rare earth elements It is widely accepted that global energy is required to meet net zero emissions by 2050. Steamology have a product to meet this challenge and realise the market opportunity. RE is plentiful but intermittent, 10,000 times more solar energy strikes the earth ev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Zero-emission generation and storage system; energy is the object of the research</t>
-        </is>
-      </c>
+          <t>The West of England Industrial Cluster (WC) Industrial Decarbonisation Plan (WCIDP) will create a comprehensive strategy to decarbonise industry in the West of England. The cluster centres on a hub of major industrial activity around Portbury, Avonmouth, Severnside, and the Port of Bristol. The 'spokes' of the hub span dispersed industrial emitters across neighbouring areas including Swindon, Wiltshire, Gloucestershire and Somerset and together represent diverse industries including cement, chemicals, manufacturing, food production, waste, recycling and power. The project encompasses 7CO2's carbon capture and shipping hub which will be the first dispersed CCS hub in the UK, and Bristol City Leap which supports Bristol's decarbonisation through a 20 year concession by Ameresco and heat network partner Vattenfall. This is a world-first project with over £400 million committed in the first five years and stimulating over £1billion inward investment over the concession demonstrating the area's ambition to address climate change and decarbonise at scale. Major projects are being developed by groups across the region, including renewables, energy storage, hydrogen, biofuels and CCUS, with the potential to spearhead emerging national industries in the field of decarbonisation. The region's exceptional access to biogenic emissions at scale from several energy from waste plants will be harnessed by the carbon-neutral production of sustainable aviation fuel and e-methanol. Critically, LIDP funding will allow WCIDP to: \Create a coherent, overarching decarbonisation strategy with a clear baseline and targets \Identify and connect existing projects and initiatives, sharing decarbonisation infrastructure and accelerating opportunities for new developments \Unite public and private sector stakeholders ensuring the social, economic and environmental benefits of decarbonisation are fully realised Established industry/stakeholder groups including SevernNet, Hydrogen South West and t</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,39 +571,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>309EC800-5B24-4F12-BD13-4940CB82A146</t>
+          <t>5A862722-D936-4D7C-80BD-B81A77EAFB53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Excavation Waste London Clay Utilisation in Concrete Applications ("Ex-Clay")</t>
+          <t>Project DETAIN: Designing an intelligent EV battery storage facility capable of the DETection and contiAINment of thermal runaway</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>As part of the biggest infrastructure project in the UK (High Speed 2), enormous quantities of material are being excavated due to tunnelling and other operations, approximately 5,000,000 m3, its majority London Clay. Transportation of the excavated clay for off-site disposal leads to significant carbon dioxide emissions and costs. Current practice for repurposing of the excavated material is regarded as "low value" since it is normally sent to landfill. An innovative approach for high value repurposing of the excavated clay has been developed, where the excavated London Clay is treated and repurposed in concrete. A method has been established to process and calcine the spoil to use them in specific concrete mixes as a Portland cement replacement. Since Portland cement is the primary contributor of CO2 emissions in concrete, the proposed method offers major improvements in terms of reducing the carbon footprint of the significant concrete volumes that are going to be cast as part of High Speed 2 works and beyond. For context, Portland cement in project specific concretes can be replaced with up to 70% calcined London Clay while maintaining the onerous requirements for 120-years service life which results in major savings in concrete embodied carbon and promotes high value waste utilisation. Construction logistics, particularly for projects in dense, urban environments such as London, are complex to execute, challenging to budget and programme, and impact the environment and local surroundings. It is estimated that this pioneering approach reduces the carbon footprint for the concrete and associated disposal operations by up to 70%, revolutionizing the way excavated clay materials can be repurposed towards sustainable infrastructure development with maximised circularity. Additionally, this technology can be transferred to other major infrastructure projects or mining operations across the UK and beyond where clayed spoils are generated, with immense potential to red</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>High-value repurposing of excavation waste; engineering in character but object is waste/resource recovery</t>
-        </is>
-      </c>
+          <t>Project DETAIN brings together the expertise of Unipart Logistics, Aspire Engineering, HORIBA MIRA, and Instrumentel, to develop an 'intelligent' high voltage battery storage solution to mitigate the risks associated with thermal runaway. The consortium have an ambition to use intelligent systems to DETect and contAIN thermal runaway: DETAIN. Project DETAIN draws on the varying expertise, responsibilities and growth ambitions of the consortium to review industry-wide requirements and develop an intelligent storage facility to provide the end-to-end Electric Vehicle supply chain with a sustainable alternative to sacrificial storage and the 'let it burn' approach. The Faraday Challenge has set a target to eliminate thermal runaway at pack level by 2035\. Until that is achieved, the batteries that are designed and built will still be susceptible to thermal runaway, particularly when damaged or faulty, and will need to be safely stored. Project DETAIN aligns with the supply chain need to better manage the batteries currently in production and enable the imminent growth predicted. The project also supports the Faraday challenge for recyclability, as safe and effective storage solutions will be key to development of efficient remanufacturing, reuse for End-of-Life and recycling. To detect thermal runaway there will be three areas of focus: 1) BMS thermal runaway detection algorithms for next generation hardware, 2) externally mounted (on battery) thermal runaway detection systems, and 3) distributed sensor networks for battery storage facilities. To contain thermal runaway, Project DETAIN will investigate automation, fire suppression materials, and combinations of the two, to deliver an effective unmanned containment response when thermal runaway has been detected. The project has additional focus on the safety, legislative and regulatory requirements to ensure solutions being developed are approved by relevant Insurance bodies, and the testing requirements to approve the</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,39 +601,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>901101BA-8CED-44F9-8F3C-9001593C42F6</t>
+          <t>F7E16B61-25E6-4C43-A093-82D47C6AC1E4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Developing advanced metrics for real-time monitoring of anaerobic digestion (AD).</t>
+          <t>Lineat - ReCaFiDi Recyled Carbon Fibre Dispersion</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>The project aims to develop advanced metrics that can be used to develop and test control algorithms for real-time monitoring of anaerobic digestion (an initial step for artificial intelligence control of biorefinery). Anaerobic digestion (AD) is a nature inspired technology converting organic waste to biogas and nutrition rich digestate. The implementation of AD can lead to generation of renewable energy and circular economy solutions to organic waste. However, uptake of industrial-scale AD in the developing world, and high standards of process control have been limited by monitoring equipment and the limited local research work done on locally available feedstock. For the same reason, existing AD plants offer no rapid or detailed diagnosis of the biochemical balance of digesters, such as stress, build-up of inhibitors, scope for feedstock to be fed or reduced etc. As a result, most AD plants are not optimally operated, are oversized, and still run blind regarding the onset of inhibition or toxicity. No real-time metrics have been developed for use by industry to proactively optimise performance through new feedstock, nutrient supplementation, changes in organic loading rate, or temperature. This project, supported by Anaero Technology, aims to develop advanced metrics that can be used to develop and test control algorithms for real-time monitoring (an initial step for artificial intelligence control of biorefinery), and to acquire or develop dedicated Nano sensors for industrial control probes. The research will involve a range of methods including statistically-robust experimental work, analytical chemistry protocols, and big data analytical methods etc. The student will be required to work closely with Anaero Technology, have access to their state of art facilities and spend a minimum of three months in Anaero Technology based in Cambridge.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Monitoring/control of anaerobic digestion, i.e. bioprocess control; sensors and algorithms serve the digester</t>
-        </is>
-      </c>
+          <t>This Analysis for Innovators project applies Swansea ASTUTE Centre of Excellence expertise on on material surface characterisation to Lineat's novel carbon fibre recycling process. Carbon fibre is well known for its high strength and lightweight properties but has a heavy cost and environmental burden. It is 40x more expensive than steel with 20x higher CO2 emissions per kg, yet less than 10% is recycled making it one of world's most expensive single-use materials. Carbon fibre may be recovered from articles made from carbon fibre composites, but less than 10% is re-used with about 50,000 tonnes landfilled globally p.a. And, the UK relies heavily on carbon fibre import. Improved and expanded capabilities for recycling carbon fibre is a clear and urgent need. Recycled use is currently limited to filler or felt, with poor performance, and as a consequence the market is volume and value limited to less than 10,000 tonne or 200mn USD for basic compounding applications. Lineat has shown how up to 50% of virgin fibre can be replaced with its aligned recycled fibre, offering a high value solution. Lineat's processes recovered short chopped fibre into a new continuous tape consisting of aligned discontinuous fibres which when aligned can substitute virgin material. Alignment is done by first dispersing fibres into water and then spraying them through a patented hydro-alignment set-up. However, the productivity and economics of the process are at present limited by difficulties in dispersing fibre at higher concentrations. The surface of the carbon fibres can vary greatly between waste sources and require different dispersion strategies. Based on theoretical limits, a 10x increase in production speed should be possible helping to save more carbon fibre otherwise destined for landfill. To achieve this objective ASTUTE will use advanced techniques for characterisation of the fibre surface, leading to optimal selection of additives to promote fibre dispersion. In parallel, Line</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -691,39 +631,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4CC7269C-F34A-4275-B51B-D395450CCECD</t>
+          <t>425846A7-928E-4949-A7B7-4FBE662F7F27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Supply Chain Digitalisation towards a Circular Economy</t>
+          <t>pilot Centre of Expertise for Advanced Materials and Sustainability</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>The introduction of digital technologies in the fourth industrial revolution is rapidly transforming supply chains (Ridgway, Clegg, &amp; Williams, 2013). The early adoption of digitalisation in the supply chain is already resulting in a disruptive change in many industries. Companies are realising the importance of digital technologies early adoption to stay competitive and prosper (Srai, et al., 2017). Most research on this topic has been focusing on novel technologies rather than what the technologies can offer. Recent issues with supply chains stressed the need for them to be more visible, transparent, responsive, dynamic. Digital transformation technologies can provide greater flexibility through digital platforms, greater transparency through controlled towers, be able to better meet variable supply and demand than traditional supply chains, and the potential for developing a circular economy. As these seem to be structural changes, the use of configuration as a lens to explore the adoption of digital technologies becomes an interesting and exciting area to pursue. The research question to be covered are: 1. How can supply network reconfiguration through digital technologies enhance organisational performance and resilience? 2. How can digital supply chain technologies and a systems approach be used to develop a circular economy?</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Supply chain management research; organisational performance and resilience</t>
-        </is>
-      </c>
+          <t>The pilot Centre of Expertise for Advanced Materials and Sustainability (CEAMS) (formerly Sustainable Materials Translational Research Centre (SMTRC)) is a collaboration funded by the Innovation Accelerator (IA) programme (2023-2025) via Greater Manchester Combined Authority (GMCA) and Innovate UK (IUK). It is led by major regional and national stakeholders in material science research and innovation and builds upon Greater Manchester's expertise in advanced materials in support of the growing adoption and scaling of sustainable materials and products. CEAMS is being delivered as part of Innovation Accelerator programme (2023-2025), to support the development of sustainable materials and products. This builds on Greater Manchester's leadership in advanced materials and is being delivered in partnership with leading national organisations in material science. To date, the consortium has delivered projects to companies (of which 25 are SMEs), across a wide range of sectors, with strategic themes emerging in sustainability, circularity and clean energy. New capabilities have been developed to address industrial challenges, from the identification of sustainable replacement polymers for corrosion resistant pipes to the development of coatings for sustainable ceramics and the recycling of carbon fibre and other complex products. The consortium has expanded GM innovation capacity via new job creation as well as developing new processes to work together effectively and efficiently to deliver to stakeholders, including common business development activities, a single front door, and jointly delivered projects across multiple centres. This will be a direct and enhanced continuation of CEAMS (with some focusing of project partners), with delivery of new translational R&amp;D projects primarily with SMEs across Greater Manchester that align to the key areas for CEAMS's long-term future, and at least three technology development projects and two grand challenge projects that addres</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -733,39 +661,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AF436DCF-2243-4AC8-AB7D-1D72E74C7F78</t>
+          <t>F66EFAA5-9425-4845-8F43-167E13FACCB5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>COVID</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>The Circular Books Project</t>
+          <t>Reversible Acrylic Polymers based on Covalent Adaptable Networks</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>The Circular Books Project will create a circular economy and more sustainable method of manufacturing for the UK publishing sector by exploring innovative materials and methods of book production for children's books that will extend book life, enable them to be re-manufactured at end-of-use and reduce the volume of books reaching landfill. It will also lower the high carbon footprint of the children's books industry -- printing in the UK instead of relying on overseas imports. Focusing on remanufacturing waste high-density polythene plastic (from sources such as carrier bags and milk bottles) into a pliable, printable and robust 'paper', we plan to create a series of colourful and engaging books for babies and toddlers. The Project helps achieve UK publishing goals of ending air freight, halving its carbon footprint by 2030 and being carbon neutral by 2050\.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Remanufacturing waste HDPE into printable 'paper' and book production methods; materials processing/manufacturing</t>
-        </is>
-      </c>
+          <t>Covalent Adaptable Networks (CANs) are a new paradigm in polymer science and consist of dynamic crosslinks. Although different chemistries have been recently reported, the understanding of the physical properties of these systems is limited. The initial aim of the research is to comprehensively compare different types of dissociative or associative dynamic exchange reactions in the same acrylic network and critically examine their material performance including rheology, thermal and mechanical properties. This critical knowledge will be used to design new reversible acrylic polymer networks which perform in use as adhesives but can be triggered to provide reversibility and enable re-use of materials - relevant to a future more sustainable circular economy.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -775,39 +691,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>69D678A4-AA0E-4E3F-8818-6680E76C8109</t>
+          <t>71547A26-C7D2-4C97-B2AD-9BD50F983CB8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>DAM-2: A novel enzyme for Nylon-6,6 recycling</t>
+          <t>Sustainable Succinic Acid Production using an Integrated Electrochemical Bioreactor and Renewable Feedstock</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Challenge: Nylon-6,6 is produced by the esterification of adipic acid (ADP) and hexamethylenediamine (HMDA) monomers via energy intensive industrial processes (consuming between 80-60 MJ per tonne Nylon-6,6 manufactured). Annual global Nylon-6,6 manufacturing releases ~12 million tonne CO2 and ~2 million tonnes of nitrous oxide (NOx). 75% of the world's ADP is used for Nylon-6,6\. ADP manufacturing is itself highly problematic: ~1% of global NOx emissions and 0.2% of CO2 emissions are caused by ADP production. The benzene feedstock is a non-renewable petroleum compound and volatile carcinogen. Spent metal catalysts create toxic waste streams. The high temperatures and pressure required for ADP manufacture consume 100-120 GJ energy per tonne of ADP manufactured. Nylon-6,6 can be recycled mechanically, but the recycled material can contain impurities and is not as a strong as virgin Nylon-6,6 polymer. Chemical recycling of Nylon-6,6 can generate a higher quality of remanufactured product. However, the chemical recycling methods available are more complex and more expensive than mechanical recycling. Moreover, chemical recycling of Nylon-6,6 requires harmful and toxic chemical adjuvants. There is an unmet need for improved Nylon-6,6 recycling methods, reducing demand for virgin Nylon-6,6 and reducing demand for ADP and HMDA monomers. Innovation: Epoch Biodesign (formerly Mellizyme Biotechnology) recently purified a nylon hydrolase codenamed 'DAM-2'. Laboratory work-to-date shows DAM-2 can catalyse the depolymerization of Nylon-6,6 at room temperature and atmospheric pressure -- representing significant innovation in the processes currently available for Nylon-6,6 recycling. Project focus: Epoch will use proprietary synthetic biology tools and approaches to improve the activity of DAM-2\. They will also generate protocols for extruding new Nylon-6,6 filament from the degradation products of the DAM-2 mediated depolymerisation reaction. By completing this work Epoch will</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Enzyme engineering via synthetic biology (molecular scale); Chem Eng (biocatalysis) considered. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>Project summary: Project summary LUCRA will exploit the EU’s underutilized and abundant, Municipal Solid Waste and Wood waste as feedstocks for the large scale production of platform building block biobased chemicals at high yield with significant industrial end-user interest using a circular bioeconomy biorefinery approach. It will provide optimized and scaleable ‘breakthrough first of a kind’ innovative technology to create a step change from pilot to large scale integrated fermentation with novel electrochemical extraction of succinic acid (SA) at TRL7 that will facilitate its industrial implementation, business models and market feasibility. This will be achieved by the circular utilization of the mentioned renewable resources as feedstocks which will reduce to a large extent the dependence on fossil resources and achieves at the same time a sustainable SA production route. To fit the needs of the industrial level, LUCRA will optimize the hydrolysis process of the different feedstocks to obtain efficient cellulose and hemicellulose conversion. Enzymatic cocktails will be demonstrated aiming to maximize hydrolysis of fermentable carbohydrate content with low inhibitors production. The crude sugar-rich hydrolysates will be used as fermentation feedstock in an electrochemical membrane bioreactor for efficient extraction and production of SA. In situ extraction of SA will be achieved through an anion exchange membrane resulting in simultaneous acidification, concentration, lower NaOH consumption for pH regulation and less unit operations for SA purification. To demonstrated the produced SA that will be able to compete directly their fossil-based counterparts from petrochemical processes, different polyurethane dispersions and resins will be produced at semi-industrial scale. The process implemented in LUCRA targeting to reduce the cost of bio-SA and will demonstrate an 50% GHG reduction against conventional SA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -817,39 +721,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ED7FC44-73F0-4452-B171-734BF79960ED</t>
+          <t>0C64C0E6-E699-400B-BD67-FDAF88218FF4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ISCF</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Market Research Feasibility Study: A Small-Scale Combined Heat &amp; Power Renewable Energy Biomass Gasification System by ALP Technologies Ltd</t>
+          <t>rCF4NCF</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>What if you can power your workplace with renewable energy alone? Achieve up to 90% fuel efficiency compared with 35-45% of a typical power plant? Cost 30-50% less per kWhr than grid prices? Heating for building that is nearly free all year round? Have a system that is scalable and customisable to the type and size of space to maximize efficiency and cost? ALP Technologies Ltd is developing a fully automated, small-scale, combined heat and power (CHP) biomass gasification power plant for a renewable energy generating system that will have minimal moving parts and will provide heating and power at low cost. Our innovative and greatly simplified design will be at least half the production cost than currently offered small scale CHP systems, will be easy to maintain, reliable, fully automated and operate from local fuel sources. It will be ideally suited to the CHP requirements of dwellings, small to medium sized offices and retail spaces. It therefore has the potential to be a world leading, near-zero carbon CHP technology that will utilise local circular economy principles for almost any communities on earth.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Funded work is a market research feasibility study; the CHP technology is the subject, not the work</t>
-        </is>
-      </c>
+          <t>Lineat have produced a first to market highly aligned pre-preg tape, made out of recycled carbon fibre (rCF). Feedback across the market has been very good, but most interest lies in dry tape material, that can be pre-pregged later, or used in other applications like non-crimp fabrics (NCFs). The aim of this project is to develop the process of adding a low weight binder to Lineats tape and develop the manufacture of NCF material made from rCF. These rCF-NCFs will be made in collaboration with ITA &amp; Saertex, one of the market leaders in NCF manufacture. These rCF-NCF materials will be characterised and used to make a demonstrator in collaboration with Greenboats, to showcase the potential of rCF in NCFs. Alongside this guidelines for the use of rCF NCFs in manufacture will be published, along with a life cycle analysis (LCA). By developing an rCF NCF it will introduce recycled carbon fibre to a brand new audience. The goal of using Saertexs waste to produce new NCF will be an exciting demonstration of the potential of rCF and the circular economy. This will help to reduce the growing problem of carbon fibre waste, diverting significant amounts from landfill and saving CO2\. It will also expand Lineats market offering both through accessing the NCF market, as well as through the development of a dry tape system</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -859,39 +751,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B1A4286F-7E91-4AFB-B33D-07C58EAE2906</t>
+          <t>ADC287D1-C154-4B78-A190-35F21EADC1F3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Enhancing the Sustainability of Aluminium Production and Products</t>
+          <t>PigProGrAm – Developing a Circular Economy for UK Pig Production through Green Ammonia Harvesting</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>This project is associated with the EPSRC LightForm programme grant ( led by the University of Manchester, in collaboration with Cambridge University and Imperial College. The overall goals of LightForm are to develop the enabling science to embed materials engineering into manufacturing practice, driving improved performance and sustainability in applications of Al, Mg and Ti alloys. This DTP-funded project is in collaboration with Norsk Hydro (Norway and UK), who are providing a CASE top-up. As the Al industry strives for an increasingly circular economy, there is an urgent need to address the implications of impurity build-up on the formability, microstructure and final properties of wrought alloys. The objectives of this project are: (a) targetted experimental and modelling work on the sensitivity of key process steps to specific impurities, e.g. extrudability, sheet formability and age hardening of 6000 series alloys containing increased levels of Mn; (b) exploration of the potential for "alloy compensation", i.e. further alloying additions that counteract the detrimental effects of higher impurity levels in wrought Al alloys.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Impurity effects on microstructure/formability/properties of Al alloys; material behaviour focus. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>PigProGrAm aims to develop and demonstrate a novel farm-focused solution for the harvesting of green ammonia from livestock. This innovation will help to create a more sustainable livestock industry in the UK, reducing the environmental impacts of production by reducing ammonia emissions, whilst at the same time creating an additional income stream for farmers. The generation of green ammonia and conversion to hydrogen from agricultural waste streams delivers valuable products used to decarbonize power and transportation.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -901,7 +781,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>75BCB9CC-B42E-4AE1-92E7-ECC1AFEBB933</t>
+          <t>1F2EF233-9FCA-4E9C-BE9D-B5C99D72A715</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -911,29 +791,17 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Longer Life for Natural &amp; Synthetic Materials</t>
+          <t>CellScope: A marketplace for recycling/upcycling Battery Cells from e-waste powered by traceable health analytics data</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>An innovative technology for materials of the future. The aim of the project is to increase the longevity of clothing and increase remanufacturing services through sustainable transformative innovation.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Abstract too thin/generic (two sentences); could be materials technology or clothing remanufacturing service</t>
-        </is>
-      </c>
+          <t>CellScope presents a pioneering solution to the escalating challenge of electric vehicle (EV) battery waste management. In a world where over 26 million EVs are on the road, with batteries constituting a significant portion of vehicle costs, the need for an effective circular economy around battery recycling and upcycling has become imperative. Our project introduces a revolutionary digital marketplace that harnesses the power of battery health data, connecting e-waste aggregators with recycling and upcycling vendors seamlessly. The innovation lies in the integration of a low-cost off-the-shelf battery tool, public datasets related to battery health, and advanced backend algorithms, enabling precise assessment and pricing of recovered battery cells. Key Components: 1\. Digital Marketplace: CellScope establishes a dedicated platform where e-waste aggregators can assess the health of old battery cells and connect with recycling and upcycling vendors efficiently. 2\. Battery Health Data Integration: The platform incorporates a low-cost battery characterization tool, empowering e-waste aggregators to collect data from recovered cells. Advanced backend algorithms analyze this data, predicting the remaining useful life of listed cells. 3\. Predictive Analytics: Leveraging data-driven insights, CellScope enables e-waste aggregators to determine accurate pricing for recovered cells in the secondary market. 4\. Physical Twinning Integration: CellScope seamlessly integrates with our Physical Twinning service, enhancing the overall value of the battery ecosystem. Impact on Sustainability: - Circular Economy: CellScope contributes to the establishment of a circular economy for battery cells, ensuring their optimal use even after their initial purpose in EVs. - Reduced Electronic Waste: By providing a marketplace for recycled and upcycled battery cells, CellScope minimizes electronic waste and addresses the environmental impact of battery disposal. Economic and Environmental Ben</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -943,39 +811,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A0B27DF9-BD8D-4765-A926-5D7BBFAE7400</t>
+          <t>6F65F6C4-81D0-4305-8B13-E791BC09CB48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AHRC</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>The Many Lives of Cardboard</t>
+          <t>CO2Fuels - Direct Conversion of Carbon Dioxide to Renewable Fuels</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>‘The Many Lives of Cardboard’ will establish a new multi-disciplinary network to investigate a versatile material that is essential to contemporary culture, yet often overlooked. Cardboard is a ubiquitous symptom of everyday consumption and the global movement of stuff under late capitalism. As packaging, it is transient and disposable; yet it is also economically valuable, dubbed ‘beige gold’ after pandemic-related shortages. Cardboard takes humans from cradle to grave: since 2017 a government-sponsored cardboard ‘baby box’ has been offered to every newborn in Scotland, providing a safe place to sleep, while there is a growing market for cardboard coffins. It is promoted as a ‘sustainable’ alternative to plastics, yet the environmental impacts of its production and recycling are considerable. It holds conflicting cultural meanings, from temporariness and permanence, to preservation and decay. The varied life cycles of cardboard signal wider issues of contemporary environmental culture, politics and practice. This project is a scoping exercise to identify areas for future arts, humanities and GLAM research, collaboration and network development. It will create a network for exploratory research, linking three institutions from London to Orkney (The National Archives (TNA); University of Edinburgh (UoE); University of Highlands &amp; Islands (UH&amp;I)). This new collaboration will unite histories of cardboard documented in the records of the state at TNA with people, collections, and institutions in Scotland, a key site in the history of paper and cardboard production in the British Isles. Exploring the local lives of this global material within the UK, this cross-border project extends recent trends in environmental humanities, especially sustainability and circular economies, waste and discard studies, and histories of resource extraction, to develop an exemplar of collaborative experimental research practice. Co-led by three ECRs with complementary expertise in histories</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Off-list field: Arts and Humanities (environmental humanities/heritage network on cardboard, AHRC)</t>
-        </is>
-      </c>
+          <t>Fossil-derived liquid fuels have dominated the aviation and motor transport industry due to their high energy density and ease of manipulation. However, ever-growing concerns over CO2 emissions and improving battery technology are leading to rapid changes in energy sources for motor transportation. Consequently, the UK government, like many others, has announced a ban on the sale of new petrol and diesel cars from 2035. Unfortunately, batteries cannot be deployed for commercial aviation due to the low power to weight density of current battery technology. Developing carbon neutral aviation fuel through CO2 hydrogenation, where H2 is derived from water electrolysis, is a priority for the aviation industry and UKRI ( Recent reports show that intimate combinations of zeolite catalysts with zinc-based hydrogenation catalysts produces a multifunctional material that can hydrogenate CO2 to liquid range fuels (e.g. Nat. Commun., 2017, 8, 15174; ACS Cent. Sci., 2020, 6, 1657). Early work has shown that macroscopic control of the catalyst composite can tune the product range to different fuel types (gasoline vs jet fuel). However, much less is known about how the speciation and microscopic intimacy of the catalyst components affects product selectivity. Using our knowledge and control of zinc speciation in modified zeolites (Sustainable Energy Fuels, 2021, 5, 2136 and ChemPhysChem, 2020, 21, 673) we will develop structure-function activity relationships that will enable rational catalyst design to target sustainable jet fuel. The multifunctional catalysts will be made solely from earth abundant, non-toxic elements (Al, Si, Zn, Fe, Cu) and enable a circular aviation fuel economy.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -985,39 +841,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A247AAF6-64F9-47C9-8730-842B6EB757A3</t>
+          <t>46A706D0-B875-48BD-BBEE-28FAE66C9669</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>APC</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Establishing feasibility for safe, sustainable transportation of end-of-life EV batteries for recycling to Cathode Active material and reuse in a battery supply chain.</t>
+          <t>Reclamex - A Feasibility Study for a UK Aluminium Smelting Wastes Treatment Facility</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>As the second largest market for EVs in Europe and with the sale of new petrol and diesel cars banned from 2030, the UK is at the forefront of the transition to an electrified transport sector. However, with growing demand for the critical raw materials required for the production of EV batteries and concerns over global supply chains, an industrial scale battery recycling industry is urgently needed to help secure a stable and sustainable domestic supply of these materials. The UK is dependent on the global market for these raw materials, which presents a number of challenges. International supply chains are complex and vulnerable to disruption from geopolitical events, while environ­mental, social, and governance (ESG) factors are also becoming a growing concern for the EV industry. With this challenge comes an opportunity -- to build a sustainable and stable supply chain by developing a circular economy for critical battery minerals here in the UK. Altilium Metals is the only company in the UK recovering critical minerals from end-of-life EV battery waste. These valuable materials are recovered in a quality and format that can be directly reused in battery manufacturing in the most environmentally friendly and cost-effective way. Unlike existing pyrometallurgical processes, it can recover the lithium and manganese. Altilium's first UK plant is expected to be operational in Teesside by 2026, with the capacity to process 50,000 tonnes per annum (tpa) of lithium-ion battery black mass, equivalent to approximately 150,000 EVs per year or 10 GWh/annum. This strategic waste will be processed to make 30,000 tpa cathode active metals (CAM) to be recovered and supplied back into a UK EV automotive supply chain. This feasibility study will see the company partner with Lunaz, the UK's fastest growing vehicle electrification and upcycling business, to develop an innovative and sustainable solution for the transportation and discharging of end-of-life EV batteries, prior to r</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>EoL EV battery transport/discharge feeding recycling chain; object is the resource recovery system</t>
-        </is>
-      </c>
+          <t>RECLAMEX - A Feasibility Study for a UK Aluminium Smelting Wastes Treatment Facility Aluminium is the second most widely used metal after steel, it is of strategic importance to the UK economy as it moves towards more sustainable and circular models of production and consumption and as demand increases for light-weighting of products in the automotive and aerospace sectors and especially electric vehicles. Aluminium smelting creates large volumes of waste, nearly all of which are deemed to be hazardous and not appropriate for landfill. The UK aluminium industry is presently constrained by having no UK treatment option for its wastes, and currently has to export it for treatment. Dependence on overseas solutions for hazardous waste treatment is complex, expensive, and as recent geopolitical events have demonstrated, brings significant supply chain risk. Moreover, with the right treatment, valuable resources can be reclaimed from the wastes and reused in the UK circular economy leaving zero for landfill. This project, RECLAMEX, is to conduct a comprehensive feasibility study to assess the viability of a UK Aluminium Smelting Wastes Treatment Facility, bringing together into one integrated plant, the technologies Ultromex has developed so far to treat ALL UK smelting wastes for re-use in the UK, a first for the UK and a first for the world.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1027,39 +871,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6F65F6C4-81D0-4305-8B13-E791BC09CB48</t>
+          <t>ACAE6135-5BB3-454A-A25E-22F8B0EFD781</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>CO2Fuels - Direct Conversion of Carbon Dioxide to Renewable Fuels</t>
+          <t>New bio-based and sustainable raw materials enabling circular value chains of high performance lightweight biocomposites</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Fossil-derived liquid fuels have dominated the aviation and motor transport industry due to their high energy density and ease of manipulation. However, ever-growing concerns over CO2 emissions and improving battery technology are leading to rapid changes in energy sources for motor transportation. Consequently, the UK government, like many others, has announced a ban on the sale of new petrol and diesel cars from 2035. Unfortunately, batteries cannot be deployed for commercial aviation due to the low power to weight density of current battery technology. Developing carbon neutral aviation fuel through CO2 hydrogenation, where H2 is derived from water electrolysis, is a priority for the aviation industry and UKRI ( Recent reports show that intimate combinations of zeolite catalysts with zinc-based hydrogenation catalysts produces a multifunctional material that can hydrogenate CO2 to liquid range fuels (e.g. Nat. Commun., 2017, 8, 15174; ACS Cent. Sci., 2020, 6, 1657). Early work has shown that macroscopic control of the catalyst composite can tune the product range to different fuel types (gasoline vs jet fuel). However, much less is known about how the speciation and microscopic intimacy of the catalyst components affects product selectivity. Using our knowledge and control of zinc speciation in modified zeolites (Sustainable Energy Fuels, 2021, 5, 2136 and ChemPhysChem, 2020, 21, 673) we will develop structure-function activity relationships that will enable rational catalyst design to target sustainable jet fuel. The multifunctional catalysts will be made solely from earth abundant, non-toxic elements (Al, Si, Zn, Fe, Cu) and enable a circular aviation fuel economy.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Catalyst speciation and structure-function for CO2-to-jet-fuel; mechanism/characterisation, not process scale-up</t>
-        </is>
-      </c>
+          <t>New lightweight High-Performance Composite (HPC) materials and efficient sustainable processing technologies will have an enormous environmental and performance benefit in all sectors of application. However, current sustainable HPC application is limited to large sectors due to their limitations in terms of long processing times, high prices and low recyclability. To overcome these limitations, rLightBioCom propose a paradigm shift in the way HPC are manufactured and recycled, unlocking sustainable-by-design production of lightweight HPC. Therefore, the project will enable new circular value chains towards r-LightBioCom results, contributing to environmental-related EU goals and reducing the HPC waste generation and the use of non-sustainable fossil resources. To this end, a sustainable catalogue of new advanced biobased and recycled HPC materials will be initially developed with inherent recyclability properties (at least 3 new types of bio-resins, 4 new biomass-derived nanofillers and additives, and 3 families of sustainable fibre-based textile products). To reduce current associated manufacturing costs and high energy consumptions and emissions, efficient processing techniques will be developed (2 new fast curing techniques) combined with recycling technologies for the new catalogue of materials to reduce waste generation and induce circularity. A new open method and related tools (Coupled Ecological Optimisation framework) will promote and standardise holistic sustainable HPC design, modelling and systematic optimisation, leading to continuous sustainable catalogue growth and inclusion of new families of biobased, recyclable lightweight HPC at competitive cost. All results will be validated in 3 use cases at automotive, infrastructure and aeronautic industries with specific business cases, contributing to establishing new resilient, sustainable and innovative value chains in the EU HPC industry, promoting a change of paradigm from linear to circular ones.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1069,39 +901,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAB3A3BC-1322-444D-9729-CCFF2DE6F0C5</t>
+          <t>2931EABD-22CB-4E7E-A261-BBE43D147C12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>APC</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>Making and analysing more recyclable multilayer polymer packaging films</t>
+          <t>ERGO-R ( Emissions Reduction via Generative Optimisation &amp; Recycling )</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>Most polymer films used in food packaging are multilayer laminates of very different polymers or metal films, due to the wide range of properties which need to be satisfied and balanced. Unfortunately, such mixed materials are extremely difficult or impossible to recycle, reducing the overall sustainability of polymer packaging. In addition, the polymers are mostly made from non-renewable sources and are non-degradable. Approaches to these challenges include: (a) producing laminates that can be separated for recycling by "debonding on demand" with an external chemical or physical trigger, allowing the material layers to be separated; (b) producing films and laminates from renewable sources which can be degraded at end-of-life. Such innovations will be key for decreasing polymer waste and enabling recycling and the circular economy for plastics. However, characterization of multilayer polymer films, and other polymer films which have through-thickness variation in chemistry (e.g. resulting from degradation or small molecule uptake) is challenging. This main objective of this project is to develop a new analysis capability - infrared spectroscopic ellipsometry (IRSE) - for the in-situ analysis of multilayer polymer laminates and polymer films with through-thickness variation in chemistry. This optical technique is fast, non-destructive and can be used with measurement cells for heating, solvent or vapour exposure, allowing dynamic processes such as curing, drying, swelling, degradation and delamination to be observed in-situ. Commercial IRSE systems are not widely available and the technique has been rarely applied to polymer challenges. We will use the new IRSE capability within the Henry Royce Institute Sustainable Materials Innovation Hub at Manchester to develop this key enabling technology for polymer innovation. The student will measure model multilayer polymer samples (including real polymer packaging samples and in-house fabricated films) by IRSE and develop t</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>IRSE characterisation of multilayer polymer films; material behaviour. Chemistry (chemical measurement) considered. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>Significant development effort has been invested in the reduction/elimination of tailpipe emissions, light-weighting and the general improvement and on-shoring of battery technology, bringing huge gains and new knowledge for car manufacturers and their suppliers. However, the industry must now look toward a NetZero future (manufactured goods and associated services represent 43% of greenhouse gas (GHG) emissions related to UK consumption \Green Alliance\). As an industry we must identify how we can reduce and then eliminate the carbon dioxide (CO2) impact during production of vehicles for the transportation sector. As 75% of carbon is locked in at the design phase (based on Gestamp data), we must look to design methodologies, manufacturing processes and materials, energy costs, recoverability, re-use and recyclability to consider the full embedded/embodied carbon (CO2e) cost across a vehicle's lifetime and create a true circular economy for the automotive industry. Emissions Reduction via Generative Optimisation (Project ERGO) The ERGO Consortium will therefore come together to take the first steps towards aligning business and customer needs with future global automotive carbon legislation/incentives/certification. ERGO will deliver a sustainable design methodology enabling the design of CO2e optimised parts and address the need for sustainable Carbon Fibre (CF). ERGO will: Develop a design methodology facilitating sustainable solutions to automotive light-weighting initiatives. Develop novel materials/manufacturing processes compatible with this methodology. Practically demonstrate the methodology on prototype automotive components.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1111,39 +931,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4B2B3D86-085F-43F8-AB9E-E61BC2110EF8</t>
+          <t>CEDB8FC7-FD53-479F-8B52-17C1E9A9C96E</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Enhancing Sheep Farming Resilience in Mid and North Wales through Biochar Utilization: A Field Trial Approach</t>
+          <t>Toward a Circular Economy in Plastics: Advanced Numerical Modelling and Positron Imaging of Waste Plastic Recycling Systems</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>This project aims to support sheep farmers in Mid and North Wales by enhancing soil fertility and crop yields using biochar, a sustainable soil amendment produced from local agricultural and forestry residues. As the cost of traditional fertilisers rises and climate change impacts farming, this innovative approach offers a practical solution to improve grass and root crop production, essential for feeding sheep flocks throughout the year. We will conduct field trials on a one-hectare farmland site in Denbighshire, using biochar produced locally from sawmill offcuts. The trials will compare different application methods of biochar, including its combination with organic materials like sheep manure and goose dung homemade fertiliser. Our goal is to determine the most effective practices for incorporating biochar into the soil to boost crop growth while reducing the reliance on synthetic fertilisers. The project will increase the capacity of a local biochar production facility by adding a third kiln and improving drying processes. This will enable the production of up to 300kg of biochar per day, meeting the needs of the trials and supporting future agricultural applications. The biochar production process is sustainable and verified by ISO 14064-3, ensuring its environmental integrity. By demonstrating the benefits of biochar through scientifically rigorous trials, we aim to provide sheep farmers with a viable, cost-effective alternative to traditional fertilisers. This project has the potential to revolutionise agricultural practices in the region, promoting a circular economy that utilizes local waste materials and enhances soil health. Our findings will be shared widely to benefit the broader farming community, ensuring that the knowledge gained contributes to sustainable agriculture across Wales. Additionally, this project will help mitigate the environmental impact of agricultural practices by reducing greenhouse gas emissions associated with synthetic fertiliser</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Agricultural and Biological Sciences</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Biochar field trials for soil fertility and crop yields on farmland</t>
-        </is>
-      </c>
+          <t>This research program employs advanced positron emission particle tracking (PEPT) instrumentation and algorithms to resolve three-dimensional tracer trajectories, instantaneous velocity fields, circulation patterns, residence time distributions and mesoscale structures in opaque gas-solid fluidized beds across laboratory and large (multi-metre) scales anddiverse configurations; it quantifies how distributor/nozzle design, gas injection strategy and scale influence solids mixing, bubble dynamics, back-mixing and flow non-uniformities, while novel post-processing methods enhance multi-particle localization accuracy and data density for rigorous benchmarking of CFD and coarse-grained CFD-DEM hydrodynamic, mixing and heat/mass transfer predictions. The goal of the project is to provide new, underpinning knowledge for the development of improved, fluidised-bed-based chemical recycling technologies that divert mixed and contaminated plastic streams from landfill or incineration and advance circular resource and emissions objectives.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1153,39 +961,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2FB1E606-FC52-4E54-B54E-B9C0DFB11844</t>
+          <t>333D2B76-7D35-4EF5-815F-F2835A21D060</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Cell engineering to enhance biohydrogen production from agricultural waste</t>
+          <t>Data-Driven Luminaire Remanufacture Supplychain</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Hydrogen is considered one of the most promising substitutes for fossil fuels, being a source of green energy that could potentially lead to decarbonization. Its combustion only delivers water and heat energy as reaction products, making it a pollution free alternative. Dark fermentation (DF) is a biological hydrogen production method in which under anaerobic conditions and absence of light, microorganisms break down complex organic matter into simpler compounds producing biohydrogen and volatile fatty acids (VFAs). Given the high cost of using pure carbohydrates as a substrate on a commercial scale, there has been a lot of interest in biohydrogen production using renewable and less expensive feedstocks. Over 220 billion tonnes of agricultural waste are generated yearly, making it an accessible renewable resource to use as feedstock for dark fermentation. Therefore, using agricultural waste for biohydrogen production is a circular economy approach in which organic waste is treated to produce renewable energy, making the dark fermentation of these substrates both environmentally and economically compelling. Theoretically, a maximum of 12 mol of H2 can be obtained from the complete oxidation of one mole of glucose. However, only 4 mol of H2 can be obtained per mole of glucose through dark fermentation, with acetate and CO2 as the other fermentation end products, and this yield is obtained when the particle pressure of H2 is kept adequately low. Theoretically, during the acidogenesis for fermentative hydrogen generation, one-third of carbon from glucose is broken down into hydrogen (H2) and carbon dioxide (CO2), while the remaining two-thirds remain soluble as VFAs in the and less than 20% of the chemical oxygen demand (COD) is removed. Nowadays, the yield of biohydrogen production by dark fermentation is between 1.2 and 2.3 mol H2/mol hexose, which is only 30-50% of the maximum theoretical production of 4 mol H2/mol glucose. The low yield of H2 by biohydrogen producti</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Cell/strain engineering for biohydrogen; molecular-cellular scale; Chem Eng bioprocessing considered. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>EGG Lighting and Reath are investigating a luminaire data management system to accelerate and de-risk the industry's transition to "remanufacture not replace". This system will keep a "digital twin" for every light, providing any approved remanufacturer the necessary information on-demand. This digital technology will enable the UK lighting industry to remanufacture and upgrade good-quality luminaires instead of recycling used lights and importing more new ones -- saving 60 tonnes of waste per year by 2025\. With Reath's asset data management system, luminaire remanufacture can be safe, compliant, 30-40% cheaper and 50% less environmentally damaging than buying new lights. At a time when businesses are looking to reduce capital and energy costs as well as environmental impact through circular economy practices, this project will urgently overcome the barriers to adoption across the UK lighting industry. The approach will enable approved remanufacturers to easily share data with previous and future users, suppliers and retailers; de-risking and streamlining the remanufacture process and strengthening their confidence in adopting circular economy business models. Remanufacturing is the best available technique in the circular economy and restores luminaires to new condition or better - with a warranty and guarantee to match. This approach will create at least 15 full-time jobs by 2025 and generate revenue from this undervalued waste stream -- simultaneously giving more businesses access to affordable, sustainable and high-quality lighting. As well as reducing waste and saving costs, data-driven remanufacture strengthens the domestic supply chain by retaining value in the local economy. This encourages a move towards high-quality luminaires; which the UK industry excels at but are often substituted by cheaper imported products. With climate change and the covid-19 pandemic, it's more important than ever that we look for innovative sustainability and cost-saving solutio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1195,7 +991,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0638D9C4-F317-4307-BBD8-8D84C3D5D1C5</t>
+          <t>0FCEC38D-AB44-404A-810D-580C4647CEA1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1205,29 +1001,17 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Removing the friction in establishing trading locations for a mobile refill service and developing a playbook for scale</t>
+          <t>Market-outlets for Energy-efficient Consumption and Connection Access in Africa (MECCA2)</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>TOPUP TRUCK presents an innovative solution to combat single-use plastic waste and promote a circular economy. Our mobile refill service operates from electric vehicles, strategically positioned in various neighborhoods, offering convenient access to sustainably sourced products. By encouraging refill shopping and reducing reliance on plastic packaging, TOPUP TRUCK aims to revolutionise traditional retail practices and strive towards net zero. As we near the completion of the Sustainable Street Plan Project (SSPP), supported by Innovate UK, we are excited to introduce TOPUP TRUCK version 2.0\. Building on insights gained from extensive research and development, we have enhanced our service range, vehicle design, website functionality, and overall user experience. Now, we seek pre-commercialisation support to further refine and test our innovative concept in the market, focusing on key areas such as: 1. Marketing Strategy Development: Our marketing approach emphasises the "place" element, strategically positioning our trucks in high-footfall locations to maximise consumer engagement. Through a data-driven marketing plan, we aim to attract and retain customers cost-effectively to support our longterm growth while leveraging insights from previous interventions 2. Scheduling Optimisation: Streamlining our scheduling process is essential for scaling TOPUP TRUCK efficiently. By collaborating with local councils and aggregating customer interest, we aim to automate scheduling decisions, ensuring optimal trading locations and maximising uptake 3. Stakeholder Engagement: Establishing strong relationships with local authorities and community organizations is crucial for securing favourable trading locations and regulatory support. By addressing these challenges and opportunities, we aim to position TOPUP TRUCK for nationwide scalability and long-term success. Our project falls under the umbrella of marketing plan development, with a focus on validated market research and cus</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Marketing strategy, scheduling optimisation, stakeholder engagement for refill retail service</t>
-        </is>
-      </c>
+          <t>Most marketplaces in Africa and emerging market, in general, are typically constructed from materials that do not allow for temperature-controlled storage of perishable goods, resulting in high levels of food wastage. An estimated £1.6 billion of income is lost in Eastern and Southern Africa alone every year due to post-harvest wastage. Food spoilage is a health, economic and environmental hazard that leads to resource waste. Otaski Energy Solutions (OtaskiES) is pioneering Africa's first intelligent marketplace utilising renewable energy, sustainable infrastructure, and machine learning energy management technology to deliver tailored place-based circular economies and reduce energy cost/emission in marketplaces -- Market-outlets for Energy-efficient Consumption and Connection Access in Africa (MECCA2). This is targeted at achieving scalable sustainable energy, reduce food wastage in the agricultural value chain and provide equality, diversity and social inclusion. The MECCA2 project provides temperature-controlled infrastructures to reduce food perishability in Sub-Saharan Africa and all markets of the developing world. We effectively use solar energy in conjunction with Artificial Intelligence (AI) to deliver sustainable, affordable and reliable energy access to marketplaces whilst also reducing food-miles through on-site food storage/production. This is achieved by designing/building marketplaces with roof-top solar panels that cater to various energy needs. MECCA2 positively impacts the following areas of Africa's agricultural value chain: 1\. Post-harvest loss 2\. Energy access 3\. Infrastructure and cold/warm storage 4\. Water access sanitation and hygiene (WASH) 5\. Waste management 6\. Market trading activities/operations This is a first-of-its-kind holistic solution that combines: 1\. Sustainable food storage solutions 2\. Renewable energy sources 3\. Green architecture OtaskiES and our partners offer: 1\. Architectural and energy design 2\. AI energy data</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1237,7 +1021,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0430F793-2946-4154-825C-72A23516801A</t>
+          <t>8BD6856A-ACA6-4A0F-8B06-40867808292D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1247,29 +1031,17 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>UK's first Circular Economy Construction Hub</t>
+          <t>Recycling and Reuse of Components for Water Electrolysers (R2WE)</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>The London Borough of Newham (LBN) is working in partnership with Tipping Point East (TPE) -- led by founding experts Material Cultures, Yes Make and RESOLVE Collective -- to pilot a new model for circular construction and demonstrate how reclaimed and bio-based materials can be used at scale in the built environment sector. The outcome will be the UK's first Circular Economy Construction Hub: a space that captures and reuses materials, proves operational systems at scale, engages businesses and the community, and provides market-tested pathways for councils and developers to follow. By doing so, it reduces emissions and waste from the construction while creating local green jobs and upskilling opportunities for local residents. Our project focuses on transforming a disused site in Silvertown into a Circular Economy Construction Hub built entirely from reclaimed and low-carbon materials. This retrofit is a live test case for how councils, contractors, and communities can adopt more resource-efficient approaches to our built environment industry. The project has three key pillars. First, reclaiming a disused site and delivering an industrial retrofit using 100% circular and bio-based materials: Newham has identified the lack of local storage and processing space as a critical barrier to reuse of construction materials. This project directly addresses that gap by transforming a disused site into an operational logistics hub through the retrofit of a decommissioned building using 100% reclaimed and bio-based materials, unlocking critical physical infrastructure while providing a live test case for material reuse. Second, Circular Economy Construction Hub with operations testing at scale and market activation: the project includes setting up an operational logistics hub for material reuse, enabling flows from demolition contractors, developers, and reuse platforms to be captured and redeployed at scale. We will develop and test physical and logistical infrastructure tha</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Construction materials reuse hub; object is a reuse/recycling system, methods built-environment in character</t>
-        </is>
-      </c>
+          <t>R2WE is a project to develop a new to market remanufacturing capability for used components used in electrolytic hydrogen generators.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1279,39 +1051,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20E8C47E-4975-4433-B6CC-F7F05FBA3FAE</t>
+          <t>8C3A0A56-020B-472D-B538-0638B999668C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Project EKOALPAKA</t>
+          <t>Sustainable solutions for upgraded smart wearables and equipment in sport</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>We are the only design studio to offer high quality luxury products from alpaca fibre sourced in Europe where we can control the entire supply chain from farm to fashion. Our project will address both cycles in the circular economy, the technical cycle and the biological cycle. The introduction of digital passports will provide a system of certification for all products focusing on animal welfare ethical sourcing and environmentally friendly process for the garments created Our USP \Utilization of a renewable raw material which is wasted and has not reached its potential in Europe \Controlling the production and processing of the raw material to ensure that there are no artificial polymers or hazardous substances introduced at any stage of the cycle in the conversion to product \Working with nature and within the natural environment to produce our products which will be totally compostable \Controlling our supply chain so we can ensure that from the outset products are designed and manufactured so that materials used can continuously cycle through the system maintaining the highest value at all times \Making to remake reusing with innovative designs \Offering repair and recycling of our products</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Circular supply chain control and product certification for a fashion firm</t>
-        </is>
-      </c>
+          <t>Textile industry is facing major challenges. It is one of the most polluting industries, and consumers, as well as European regulations, are pushing for change. Indeed, global demand is changing, and consumers tend to expect more sustainable and smart textiles. Moreover, the EC is committed to a green and digital transition and needs to be more competitive globally. In this context, UPWEARS aims to contribute to structural resource efficiency and a sustainable economy by unlocking the potential of a new generation of biobased and hybrid fabrics for e-textile. UPWEARS e-textile will feature high performance, cost-effective multi-functionality, such as functionalized yarn and fibre, biomimetic fabrics, imbedded electronics and energy sensors. Partners will ensure a reduced environmental impact on the manufacturing value chain and end product – a country cycling suit – fully recycled. UPWEARS development will minimise manufacturing waste thanks to artificial intelligence technology and multiscale testing. It will also reduce chemical utilisation thanks to enzymatic &amp; eutectic green solvents. For this, UPWEARS will: -Create an innovative &amp; sustainable value chain from the native fibre to functional device end-of-life; -Switch from a traditional towards a modern textile fabrication process supporting the textile industry's digital and sustainable transformation; -Eco-design an e-textile for high added-value sportswear applications meeting European consumer's demand and contributing to EU competitiveness. UPWEARS implementation and exploitation will have many environmental, societal and economic impacts. It will contribute to EU policies like the EU Green Deal since it combines electronic devices and natural fibres and works on circularity. Finally, UPWEARS consortium covers the full value chain: formulation, functionalization; e-textile design &amp; production; digital transformation; reliability &amp; durability; industrial validation and recycling &amp; additive manufacturing.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1321,7 +1081,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>94B26365-9D0E-435F-923D-22D64F122FB8</t>
+          <t>32AE1576-7CF9-4568-B2B7-2FFF0609E005</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1331,29 +1091,17 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Novel device to capture and reuse half a million tonnes of rubber dust created annually by commercial vehicle tyre wear for creation of a circular tyre economy</t>
+          <t>Alt Pipe</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Our vision is to transform the one of the most environmentally-damaging resources used in society, vehicle tyres, into a circular economy by reusing materials that currently cause air and ocean pollution, which have a detrimental impact on human health. In this project, The Tyre Collective will complete development of three critical components of their novel tyre rubber capture device: the cleaning mechanism, storage tank and power configuration. The Tyre Collective will also work with Atlantis Carbon Black, experts in tyre pyrolysis and Europe's leading manufacturer for turning micronized rubber powder into regranulated rubber for tyre treading. We will work together to understand the scalability, manufacturability and commercialisation for reuse of our high grade and uncontaminated powderized tyre rubber. This project completes the lifecycle: capturing tyre rubber particulate matter at tyre source, conducting materials characterisation, matching the material quality to appropriate reuse market and building scalable and route-to-market at speed. Tyres shed half-a-million tonnes of carcinogenic, toxic carbon dust every year. Accelerating the shift to low carbon transport will increase carbon emissions from tyres as a direct consequence. EVs and ULEVs are heavier and have higher torque, causing their tyres to wear down 30% faster.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Capturing tyre-wear particulate (air/ocean pollution) and enabling rubber reuse; pollution capture + resource recovery convention outweighs the device-engineering aspect</t>
-        </is>
-      </c>
+          <t>As the owner of the National Transmission System (NTS), National Gas is committed to responsibly managing our redundant assets in a manner that contributes to a sustainable, lower-carbon future by decommissioning them responsibly, refurbishing for re-use where viable, and/or or changing their purpose where possible. This discovery project will identify decommissioned elements of redundant pipework on the transmission system which are unlikely to be used for refurbishment or part of any wider repurposing of the core network, and explore the potential of repurposing these for alternative uses including the storage and/or transmission of electrical energy, heat, fuels, water and data.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1363,7 +1111,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F18853F2-50D4-481A-9FDD-6623EBD89FEB</t>
+          <t>2D1D070A-0F0A-4D52-BD75-06B145938F44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1373,29 +1121,17 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>High-Value Biorenewable Peptides from Proteinaceous Biomass</t>
+          <t>EcoSeaweed-BioRefinery: Resource-Efficient Processing of UK Seaweed for High-Value Circular Co-Products (SEACoRe)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bell &amp; Loxton Innovations is a highly innovative, circular-economy spin-out from a working farm in South Devon. Our consortium has recognised an opportunity to produce high-value biorenewable (HVB) materials from abundant agricultural and food-processing co-streams. Many co-streams such as oilseed presscake created during oil extraction and spent brewing yeast and grain are high in protein and are routinely discarded or used downstream in low-economic value applications. Proteins from different natural sources have unique compositions of amino acids both in prevalence and in terms of their sequence. Consequently, proteolysis of these biorenewable proteins will create unique distributions of smaller peptides that differ in size, amino acid compositions and sequence. This diversity enables different high-value market sectors to be catered for such as nutrition, personal care and pharmaceuticals as different peptides have different biological properties. Historically, bespoke peptides have been chemically synthesised at high cost from chemical/fossil fuel feedstocks. Identifying unique high-value biorenewable proteins and then producing tailored peptides and blends (hydrolysates) will enable a circular economy approach to supplying multiple industry sectors with a consequent benefit to the environment. Our consortium brings together the necessary parts for developing a successful and scalable 'green' chemicals business: Bell &amp; Loxton Innovations with its strong farming, food and agricultural production experience, The Biorenewables Development Centre (BDC) with its in-depth knowledge of waste and co-stream valorisation techniques, and Thomas Swan &amp; Co Ltd as an established chemicals manufacturing business to enable scale-up production coupled with a mission to move to 100% biorenewable feedstocks. Continuing this project from a successful valorisation feasibility study conducted with the BDC, we will work with our route to market manufacturing partner, Thomas Swan, to </t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Valorising agri/food protein co-streams into peptides via proteolysis, with scale-up; bioprocessing. Chemistry considered</t>
-        </is>
-      </c>
+          <t>The EcoSeaweed-BioRefinery (SEACoRe) project will test a new lab-scale technology for turning UK seaweed into multiple sustainable products, such as biofertilisers, bioplastics, and nutrient-rich extracts. Unlike conventional methods, which are energy-intensive and produce only one product, this innovative enzymatic process aims to improve yield, efficiency, and value per tonne of seaweed while reducing waste. The study will provide feasibility data to help scale up UK seaweed processing and support coastal resilience, circular economy growth, and the transition to net zero.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1405,7 +1141,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B6232D93-6C9B-43DF-9893-D788B198743B</t>
+          <t>9C5D8E6D-5CDB-41AC-860D-9AE9D3B25D20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1415,29 +1151,17 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>ReCLAIM: Recovery of polymers Containing Legacy Additives in MEP</t>
+          <t>Birl: transforming resale in the fashion industry and beyond</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>"The move to a circular economy is vital for the development of industry and the protection of the environment. One material constantly in the spotlight is plastics. Plastic is a highly engineered, indispensable material used over a wide range of applications. One of the strengths of thermoplastics is the potential ability to recycle the same material many times and make use of it in a circular economy. However, there is still a significant volume of plastic that is not recycled currently, and is destined for landfill or incineration. This material is the residual Mixed Engineering Plastics (MEP), which contains a wide range of less-common polymer types and importantly a significant proportion of legacy additives which are a concern when recycling the material. Within the ReCLAIM project, Axion Recycling, Trojan Services, Crompton Mouldings, and University of Birmingham will address these problems by: developing new processes for greater recovery of polymer fractions from MEP; creating chemical and physical methods for making BFRs biologically unavailable in the recycled polymers and verifying their efficacy; and proving that the polymer is suitable for real end markets. The results from ReCLAIM will boost competitiveness of the partner organisations by adding to their product lines, increasing revenue, and reducing operating costs. The benefits to the UK will be increased economic activity, new jobs, a reduction in waste incinerated or sent to landfill, and significant CO2 savings."</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Recovery/recycling of polymer fractions from mixed engineering plastic waste; object is recycling/resource recovery though methods are chem/physical</t>
-        </is>
-      </c>
+          <t>Birl is revolutionising the fashion industry by spearheading the transition towards circular fashion through an easily adoptable, trusted "consumer-first" resale solution. It responds to enormous demand from brands and consumers within fashion and across secondary markets including electronics, sports, jewellery, and homeware. The Birl solution will provide brands with one-click resale functionality, allowing them to embrace circular fashion without changing their operations or having to 'touch' traded in garments. Uniquely, our solution is also customer-focussed, allowing a seamless customer experience with instant credits for traded-in clothes and free shipping. The project is motivated by urgent need for greater circularity within the fashion industry, which accounts for 10% of global carbon emissions with over 100bn garments manufactured annually with only 5% resold and &lt;1% recycled into new garments. 75% end up in landfill, resulting in £400bn lost annually from recyclable clothing wastage. There is significant consumer interest in resale as a sustainable practice, with estimates suggesting 18% of wardrobes will comprise second-hand goods by 2030, up from 4% in 2021\. However, for this to be achieved, key challenges remain, including around scarcity, cost and fraud, with many brands facing barriers to resale (or being reluctant to offer high levels of credit) due to significant volumes of counterfeit products, e.g., high incidences of fake Nike, North Face, Canada Goose apparel. The problem is pervasive across secondary target markets, e.g., Fjällräven Kanken backpacks. Ray-Ban sunglasses, Apple AirPods, Tiffany jewellery. Brands and consumers additionally need trusted valuations of garments. This project will deliver cutting-edge image recognition to provide the verification of authenticity and condition of garments that brands (and buyers) need, and advanced machine learning to provide trusted valuations based on evaluations of seasonality, geography, and wid</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1447,7 +1171,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50CBF6A2-FB98-4931-BBDF-B8F1868FAC79</t>
+          <t>E9CFF00F-0278-4E32-808E-30990196EFA7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1457,29 +1181,17 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Design considerations for improved pDNA and therapeutics production</t>
+          <t>Microalgal synthesis of metal nanoparticles - towards a circular economy</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Non-viral, plasmid DNA (pDNA) is the focus of great interest as therapeutic as well as a starting material for gene and cell therapies. The quality and quantity of the pDNA recovered from industrial processes is however affected by context-related impact of the plasmid, the presence of cryptic sequences, multimerisation leading to instability and non-optimal coiling. In this project we will work with AstraZeneca to consider how therapeutic plasmid sequences impact on the host cell and use engineering design rules to minimise such interactions while maximising plasmid replication stability and quality. The constructs of interest are already in use at AstraZeneca (AZ) and we will use transcriptomic analysis and engineering control rules to re-design them in order to achieve improved quantity and quality of the pDNA while minimising impact on the host. Lab work will entail state-of-the-art molecular cloning, transcriptomic analysis and design of CRISPR-based and RNA-based feedback controllers.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Re-designing plasmid DNA via molecular cloning, transcriptomics, CRISPR/RNA controllers; molecular/genetic work. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>Heavy metals, such as cadmium, essential components of various dyes or other industrial processes, are listed among the ten chemicals of major public concern by the WHO for their potential to be carcinogenic and inflict acute organ damage. Algal systems for bioremediation (phycoremediation) are highly attractive as they are autotrophic - relying on sunlight and carbon dioxide as inputs. This project aims to address sustainable development goals by creating scalable methodologies for wastewater treatment using microalgae to extract and upgrade heavy metals into valuable metal nanoparticles. Using a model system, this project seeks to understand how photobioreactor technologies suitable for in-situ remediation might be developed. Under heavy metal exposure, plants and algae produce phytochelatins (PC) - glutathione-derived compounds. These peptides form stable complexes with metal, protecting the cells. The diatom alga Phaeodactylum tricornutum has been selected as a model organism for this project as it is known to bioaccumulate cadmium (Cd) and can tolerate a wide range of salinities. The aim of this project is to characterise the interactions between upstream cultivation parameters and cadmium nanoparticle formation and how these might relate to process scale up. Through the design of novel experimental systems for studying heavy metal uptake and engineering characterisation of the microenvironment, this project will seek to understand how the form of metal nanoparticles can be manipulated. The objectives identified: OBJECTIVES O1: To quantify the impact of cultivation conditions on cell growth and Cd uptake through growth experiments, cell viability testing and analysis. The nanoparticles formed will undergo morphological characterisation of size, shape and distribution. O2: To examine the impact of reactor design and operation on retention times, to identify strategies for maximising throughput by understanding geometries and fluid flow conditions for improved ma</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1489,7 +1201,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D102D9C8-CBD7-458E-A4F9-4863D4C3524B</t>
+          <t>EC36B408-E11C-447F-84CF-2677DCD2D12F</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1499,29 +1211,17 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Computational biofilms: analogue spatial computing with bacterial colonies</t>
+          <t>Catalytic Silylation of Aryl C-H Bonds with Earth Abundant Metal Catalysts</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Our aim in this project is to engineer arbitrary analogue computation into bacterial biofilms. To explore this, we will implement a type of artificial neural network (ANN) using engineered bacterial populations arranged spatially and linked by intercellular signals. Previous work on computation in biological systems has mostly tried to emulate the digital logic capabilities of electronic circuits. This is a potentially limiting constraint on the naturally analogue processes that occur in biological systems. In comparison, ANNs are not constrained by these limitations, meaning they could be a useful framework for building artificial biological computers. We will engineer E. coli strains with intercellular signalling (quorum sensing) systems, where spatial separation of communicating colonies form a neural network structure. There are three objectives: 1. Develop an in silico design process for computational biofilms 2. Create engineered bacterial neurons 3. Demonstrate computational capabilities of spatial biofilms Our approach will open up new ways to perform biological computation, with applications in synthetic biology, bioengineering and biosensing. Ultimately, these neural-network-inspired bacterial communities will help us explore information processing in natural biological systems.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Synthetic-biology cell engineering (E. coli, quorum sensing) is the bulk of effort, but 'analogue computing/ANN' framing gives Computer Science a near-equal claim; bioengineering also possible. Field not in dropdown</t>
-        </is>
-      </c>
+          <t>Silylation of organic molecules remains a potent challenge in the field of synthetic chemistry, still requiring lengthy synthetic pathways involving wasteful, intensive stages. Despite silyl-containing molecules having unique interactions with receptor proteins in the body, causing different pharmacochemical activities compared to a carbon analogue, this issue remains a fundamental roadblock in their application. In addition, catalysts for silylation reactions have historically been dominated by platinum-group metal-centred complexes such as those based on iridium and rhodium. These metals are significantly more expensive and also generally more toxic than their more earth abundant counterparts. A number of other issues plague silylation chemistry currently. Hydrogen scavengers, such as alkenes are added to reaction mixtures in super stoichiometric quantities to drive the thermodynamic equilibrium of the reaction forwards. Directing groups are often needed for silylation reactions to progress and can be sensitive to the silane being used, the production of which uses wasteful, toxic reagents. Finally, to form the active catalytic species, stoichiometric or even super stoichiometric oxidants are needed to generate the active catalyst. As a result, the continued development of new catalysts and condition sets which combat these issues and allow access to different substrates is of paramount importance. The aim will be to develop iron and manganese containing complexes with -accepting ligands and test their efficacy as homogeneous catalysts for the silylation of anisole as a standard to optimise the catalysts. Once the catalysts have been optimised for this aromatic, we will investigate functional group tolerance and selectivity, and will extend the methodology to different substrates, ranging from heteroaromatics (pyridine, pyrrole, furan, thiophene and indole) whilst also testing aromatics with weaker directing groups such as acetylbenzene with the aim of advancing e</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1531,39 +1231,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FE974018-2295-421A-A391-CD17261937E1</t>
+          <t>2DE39745-AC11-45E5-8E8E-25704B9B38E6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AHRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>From ownership to usership: light as a service in the circular economy</t>
+          <t>An innovative borrow-and-return reusable takeaway packaging system that makes reuse as convenient as single-use, bringing in corporate funds and responsibility to reduce waste from lunchtime takeaways.</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Since the industrial revolution, society and industry has been adopting a linear approach to business and production i.e. 'Take, make, dispose'. With the world's population expecting to increase to 9 billion, the world's economy will quadruple creating a greater demand for energy and natural resources. If new concepts and business models are not conceived and implemented, there could be considerable environmental implications. By exploring the principles of emotional durable design, the circular economy and service innovation we cold find new ways to create value for industry, delight the consumer and fulfill their needs while reducing the strain that modern day consumption has put on the environment. But most importantly do good design; create better, smarter products and services that will bring about a more sustainable future. Since the industrial revolution, society and industry has been adopting a linear approach to business and production i.e. 'Take, make, dispose'. With the world's population expecting to increase to 9 billion, the world's economy will quadruple creating a greater demand for energy and natural resources. If new concepts and business models are not conceived and implemented, there could be considerable environmental implications. By exploring the principles of emotional durable design, the circular economy and service innovation we cold find new ways to create value for industry, delight the consumer and fulfill their needs while reducing the strain that modern day consumption has put on the environment. But most importantly do good design; create better, smarter products and services that will bring about a more sustainable future.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Product-as-a-service ('light as a service') business models and service innovation; design framing is method. Engineering(design) considered</t>
-        </is>
-      </c>
+          <t>UK lunch-on-the-go generates 11 billion pieces of single-use packaging waste each year (Hubbub). Today, unless people bring their own reusable container for lunch, they inevitably generate single-use packaging waste from most to-go meals. Takeaways have become a workplace standard and are a major component of the office waste stream, despite 8 in 10 UK consumers trying to reduce their plastic waste (Guardian). As employees return-to-work in the wake of COVID, there is an unprecedented opportunity to change behaviours and redefine consumption norms within offices. junee is tackling the single-use takeaway packaging challenge by making reuse as easy as single-use. junee partners with companies and restaurants to create a convenient borrow-and-return system of reusable containers that employees can use during their workday lunch. In this project, junee will research and develop innovative tech and reverse logistics processes that will enable a transition from single-use packaging to reusable packaging for lunchtime takeaways and beyond.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1573,39 +1261,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>704F2E29-B301-4D05-A19D-203FF688D475</t>
+          <t>4EDEBFCB-8D43-484E-BD7D-C3422A16E2AF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AHRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>New Composites: Diversifying material sources in a circular textile economy</t>
+          <t>Developing a rental model for short-life campaign and work wear clothing</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>The fashion and textile industries are significant contributors to pollution, resource depletion, and climate change. To steer human activity back within the limits of the earth's carrying capacity, the way we produce, use, and dispose of textiles needs to undergo radical transformation. This work is embedded in principles of sustainability such as reducing negative social and environmental impacts at each stage of a product or material's lifecycle, alongside circularity as a leading approach to sustainability, which endeavours to circulate resources without waste. The New Composites project aims to increase the diversity of resources used in textile design as a contribution to sustainability targets while embedding recyclability in textile design. The industry currently relies in overwhelming majority on two types of fibres, cotton and polyester, which together account for 76% of all global textile production (Textile Exchange, 2021). While improvements can be made in these fibre categories by using organic or recycled input, it is imperative that a wider variety of fibres should complement their use. The current focus on such a narrow range of resources leads to a lack of resilience in the sector as current price spikes or major disruptions caused by conflict or other obstructions of trade routes have shown. The project tackles the environmental and social impacts linked to the reduced biodiversity which comes from a focus on conventional fibres. Exciting and diverse innovation is currently taking place in the sector of alternative materials, for example materials made from pre- and post-consumer recycled fibres, bio-polyesters from corn, or regenerated cellulose from agricultural waste. However, these innovations are often not fully transparent in their composition and are difficult to access at scale. Moreover, as current guidelines for circular design focus on the fibres with the highest market share, little is known about how these new fibres are best employed</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Textile/material design for circularity (diversifying fibres, embedding recyclability); design maps to Engineering, but AHRC practice-led design could be Arts and Humanities. Near coin-flip</t>
-        </is>
-      </c>
+          <t>The National Union of Students is partnering with the University of Bradford to tackle the problem of uniforms and promotional clothing being used for only short periods before being thrown away. Very often campaigns t-shirts, bar staff clothing and uniforms are used for less than an academic year before being disposed of. Working with NUS’ clothing company, Epona, the partnership intends to explore the feasibility of a rental model for providing clothing to students’ unions, universities and colleges. Clothing would be rented and then returned, before being remanufactured and reprinted ready for the next rent. The public sector in the UK procures £900m clothing per year, £410m of this is work wear.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1615,39 +1291,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8CBA7BD8-754B-43E3-BE51-0B83D7EBC8D6</t>
+          <t>1E2F252C-2D1A-4267-83F8-358D7EEACD17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>SusPharma - Merging Sustainable and Digital Chemical Technologies for the Development of Greener-by-Design Pharmaceuticals</t>
+          <t>Bloca - Sustainable Building Blocks</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Safe-and green-by-design are pre-market design approaches whereby the objectives of minimizing the use of hazardous chemicals, reducing greenhouse gas emissions, and fostering the reuse and recycling of materials in a circular economy are built into product design. SUSPHARMA fits the European need for sustainable development in modern industry and will develop during the action greener routes to prepare molecules, such as therapeutics and diagnostics. The breakthrough innovation will involve: - use of renewable (bio-based) carbon for the building block of scaffolds and motifs for drug synthesis; - cleaner synthetic methodologies for C-X bond formation (that is, C-H functionalization to obtain C-C, C-F, and C-I bond formation); - development of new benchtop continuous purification methods, to remove impurity and recycle synthetic solvents; - integration of digitalization methods. - LCA and TEA assessment for sensibly reducing the impact of pharmaceutical production. The project will thus benefit from an interdisciplinary domain, involving: - recent advances in biomass conversion for drug synthesis; - new developments in heterogeneous catalysis; - cutting-edge flow chemistry technologies (including synthesis and purification); - automation and machine learning. To address the challenge of green and digital transition and proper supply of health technologies and products, SUSPHARMA will focus on research and innovation activities that aim at integrating five breakthrough concepts: CAT-to-PHARMA, WASTE-to-PHARMA, FLOW-to-PHARMA, PUR-to-PHARMA, and DIGITAL to PHARMA. This will deliver results that are directed to pharmaceutical industries, researchers, and innovators, prompting them to develop and produce greener pharmaceuticals that are either greener by design, intrinsically less harmful for the environment, or use greener and economically more sustainable manufacturing processes and technologies.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Greener synthetic methodology (C-H/C-X bond formation, bio-based building blocks) is the scientific core; heavy flow-chemistry/continuous-purification/catalysis content gives Chemical Engineering a near-equal claim</t>
-        </is>
-      </c>
+          <t>The Bloca Project is the development of a new construction method for housing. It has been developed as response to the exposed fragility of global supply chains from Covid-19\. The concept is based around decarbonising and circular economy principles, with the maximum possible sustainable content, and a design approach which allows the entire component to be reused at the end of its first application Scottish Gaelic for "block", Bloca enables rapid building construction, is materially efficient yet structurally stable, highly energy-efficient, sustainably and locally sourced, and adds economic value to local resources. It is a flexible system that can be reused time and again, allowing buildings to be constructed, extended, modified, rebuilt and easily recycled. The standard nature of Bloca means that it literally fills the gap between custom full SIP (Structural Insulated Panel) construction (bespoke manufacture - expensive, large and heavy) and full build at site (time &amp; expertise consuming). The assembled team represents a blend of innovation, experience, materials expertise, customer input and research capability: 4c Engineering, the lead partner, are an innovation &amp; engineering consultancy with a track record of leading technology development from complex wave power devices, through to aquaculture innovation and novel PPE. 4c Engineering will apply an engineering innovation &amp; manufacturing mindset to conventional construction. Macbeath Architects/Thermopassive, another innovative company, are a Highland based architecture firm with nearly 40 years experience, and they are experts in the design of SIP-based domestic constructions.. Norbord, the local producer of OSB (oriented strand board), will provide technical advice on the material properties, and provide sample material. The University of the Highlands and Islands (UHI) are contributing expertise from their Construction &amp; the Built Environment Team. Providing customer input, Highlands and Islands Enterpris</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1657,39 +1321,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>71BA1928-1B10-45A7-88C6-E070B3EF0030</t>
+          <t>C261C2C3-C055-441C-A48B-2F88254430EF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>R&amp;D for a Virtual Ward Sensing Device for High-Risk Chronic Patients</t>
+          <t>REFORM - PRINTED ELECTRONICS FOR THE CIRCULAR ECONOMY</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>WarnerPatch is a medical device for non-invasive remote monitoring (virtual ward). It measures tissue health to predict disease worsening using a specifically designed sensing method and developed AI-algorithm. While being used at the hospital or at home, early degrading symptoms are identified so clinicians can give preventive care to improve patient outcomes and reduce care costs. We are focusing on diabetes and vascular diseases (i.e. peripheral vascular disease (PVD)), which can be the result of, or cause, heart attack, stroke, general infection, ulceration or gangrene, potentially leading to amputation and death. Worldwide, 200M people are at risk of developing this condition accounting for 13M in EU27, slightly more in the USA and 5M in the UK. Amputation is performed on 600K patients a year, with 50% death rate within two years after amputation and 30% of unnecessary amputation due to late recognition of disease-worsening. During the pandemic and with the long COVID-19 syndrome, the number of patients requiring emergency hospital care has increased by 60%, significantly stretching the current remaining resources. The minimum viable product development was finalised with its AI-algorithm and tested/validated in a simulated environment. The goal of this project is to finalise the R&amp;D of the physical product under regulatory requirement while improving the product manufacturability including recycling/refurbishment processes of non-critical parts. At the end of the project, we will be able to start the certification processes for commercial activities. We will continue working with the Leeds-Teaching-Hospital-NHS-Trust (LTHT) and NHS-Arden-and-Greater-East-Midlands-Commissioning-Support-Unit (AGEM) for a more detailed data-pack development with health-economics (budget-impact and cost-effectiveness). Using our device will improve patient outcomes while reducing care costs by: 1. Quickly identifying patients at risk of developing life threatening conditions, to t</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Developing a physical medical sensing device (instrumentation/sensors) and its manufacturability; embedded AI algorithm is a component. Computer Science considered</t>
-        </is>
-      </c>
+          <t>REFORM (pRinted Electronics FOR the circular econoMy) sets out to address the environmental and sustainability challenges around conventional surface mounted and embedded functional electronics. The project aims to accelerate and guide the development of a new European green functional electronics supply chain. It seeks to use ecodesign principles to ensure that functional electronics can be produced that meet multiple application requirements for technological performance and compliance, while also meeting societal and environmental needs for sustainability. To achieve this, REFORM will develop environmentally benign electronic ‘building blocks’ focusing on green, bio-derived adhesives, conductive inks and flexible substrates. These will be integrated into industry-led functional electronics systems and supported by innovations in conformance testing and material recovery methods. Taking a holistic approach to development across the supply chain positions, this project is unique in not only achieving a step-change in technology compatible with industrial reality, but also producing prototype showcase systems with direct future impact on sustainability. REFORM brings together a world-leading consortium of academics, non-profit RTOs, industrial associations, private SME partners and large firms from eight countries across Europe. The project is female-led and coordinated by CIDETEC, a specialist RTO in surface engineering and energy storage based in Spain with a strong track record of leading large collaborative European projects. By combining the consortium’s unique and complementary expertise, REFORM aims to give Europe an innovation lead in green functional electronics, enhancing European competitiveness, and helping meet the ambitions for the European Green Deal. The immediate outcome of REFORM will be three demonstrators: a green smart logistics tag, a green embedded wireless sensor and a microsupercapacitor, taking the project from TRL 2/3 to TRL 5.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1699,39 +1351,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAF7E52F-431B-4837-8B47-0DB1FB1F6BEE</t>
+          <t>84FCB878-512D-4971-8A82-914068C6B33A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>BBSRC</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Knowledge Based Net Zero Solution for Manufacturing Sector</t>
+          <t>BIOSCIENCE FOR RENEWABLE RESOURCES AND CLEAN GROWTH - Bioengineering novel platforms for one-pot plastic upcycling</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>Development of Knowledge base systems for optimisation and automation of electrical car engine within the manufacturing sector towards achieving the Net Zero targets in the manufacturing sector. This project aims to develop a a proof of concept Knowledge Based systems as an application, with generative and intuitive capabilities to optimise and automate electrical car engine design processes and principles enabling fast tracking of the UK manufacturing sector towards achieving UK Net Zero targets. The project will address the environmentally focused manufacturing design, for the delivery of supply chains and circular economy challenge as part of this call, with the focus on Manufacturing design for Net Zero using knowledge base engineering, Artificial intelligence (AI) , symbolic languages and advanced computing.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Building knowledge-based/AI systems (symbolic languages, generative, advanced computing) for manufacturing design; work is the software/AI. Engineering(manufacturing) considered</t>
-        </is>
-      </c>
+          <t>Background: Plastic pollution is a major environmental threat and sequesters carbon-rich materials derived from finite, petrochemical resources. Environmental, sustainability and economic drivers demand that we develop novel and robust technologies to tackle the plastic waste crisis and move towards a circular economy through valorisation of post-consumer materials. The young fields of plastic degradation and plastic upcycling are advancing rapidly to address this challenge. Notably, numerous enzymes have been reported to degrade polyester substrates under mild reaction conditions, including engineered variants of PETase (Ideonella sakaiensis) and leaf branch compost cutinase. Furthermore, we and others have demonstrated the potential of bio-based plastic upcycling pathways to convert low-value, post-consumer plastics into high-value small molecules such as the flavour molecule vanillin (Green Chem., 2021, 23, 4665-4672). Importantly, these target molecules are predominantly currently synthesised directly from finite petrochemical resources. However, plastic degradation efficiencies remain a major bottleneck and robust technologies to interface plastic degradation with upcycling pathways are lacking. The project: This highly interdisciplinary project will harness the latest developments in plastic degradation, synthetic biology and biocompatible chemistry to develop novel enabling biotechnologies to directly interface polyester degradation with bio-based upcycling pathways. We will initially focus our attention on optimisation of microbial biofilms for adhesion to and depolymerisation of plastic surfaces. We will then explore microbial co-culturing approaches to enable one-pot polyester degradation and upcycling, using our existing vanillin pathway as a model system. This will include exploring opportunities for incorporating non-enzyme catalysed, biocompatible chemistry approaches (RSC Chem. Biol., 2021, 2, 1073-1083) to improve the efficiency of plastic degradatio</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1741,39 +1381,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C12C9BC2-2419-42F7-BDB5-91DF7B3ACC66</t>
+          <t>21A45C5C-29D8-473F-9298-87EFD3AE8E4B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Modification and evaluation of natural polysaccharides and their application in fabric care</t>
+          <t>Future Availability of Secondary Raw Materials</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>The global impact of laundry detergent production on energy consumption and environmental conservation underscores the need for innovative solutions, particularly in the development of organic and eco-friendly laundry care products1. While surfactants remain integral to laundry formulations, the current detergents have evolved to also include polymers, builders, bleaching agents, enzymes, and chelating agents, playing a crucial role in controlling cleaning performance2. Despite the several benefits of polymers and how they improved today's quality of life, the fossil nature of over 98% of current polymers and their disposal via incineration contribute significantly to CO2 emissions3. Addressing this challenge requires the utilization of polymers designed for complete biodegradation or degradation into environmentally benign products, given the limited biodegradability of many currently employed polymers4. Biological polymers, such as chitosan, cellulose, and starch, provide a promising foundation for the development of biodegradable polymers due to their non-toxic nature and natural metabolization. However, native biological polymers often lack the desired performance for specific applications, necessitating chemical modification. Hybrid polymers, combining biological and synthetic components, represent an approach to leverage the best properties of both polymer classes3. Chitosan oligosaccharide (COS), derived from chitosan, exhibits excellent water solubility and low viscosity, even under strong alkaline conditions5. The presence of reactive amino and hydroxyl groups in chitosan's macromolecular structure allows for various modifications, such as alkylation, acylation, and Schiff base formation, tailoring its properties for diverse applications. However, chemical modifications can compromise the biodegradability of chitosan, since molecular weight, macromolecular architecture and the end groups of the polymer can affect this property4. Hydrophobic modifications ha</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Chemical modification (alkylation/acylation/Schiff base) and evaluation of polysaccharide polymers for detergents; synthetic polymer chemistry. Materials Science considered</t>
-        </is>
-      </c>
+          <t>The Future Availability of Secondary Raw Materials (FutuRaM) project seeks to (1) develop knowledge on the availability and recoverability of secondary raw materials (SRMs) within the European Union (EU), with a special focus on critical raw materials (CRMs), to enable fact-based decision making for their exploitation in the EU and third countries, and (2) disseminate this information via a systematic and transparent Secondary Raw Materials Knowledge Base (SRM-KB). The FutuRaM project will establish a methodology, reporting structure, and guidance to improve the raw materials knowledge base up to 2050, and facilitate the exploitation of SRMs with a particular focus on CRMs. The project will integrate SRM and CRM data to model their current stocks and flows, and consider economic, technological, geopolitical, regulatory, social and environmental factors to further develop, demonstrate and align SRM recovery projects with the United Nations Framework Classification for Resources (UNFC). The project will address the following waste streams: Batteries; Waste Electrical and Electronic Equipment; End-of-Life Vehicles; Mining waste; Slags and Ashes; and Construction and Demolition Waste. FutuRaM will further develop and test the UNFC methodology through 18 case studies across the six FutuRaM waste streams. FutuRaM research into the future availability of raw materials is relevant to the specific aspects of the work plan. It will contribute to a transition to climate-neutral, circular and digitised economy; develop an understanding of anthropogenic resources; develop the necessary criteria to establish a resource classification approach; combine new &amp; existing data and present it in a UNFC format; develop a proposal for EU statistics for SRMs; and contribute to raising awareness of raw materials supply challenges in the EU and the possible solutions.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1783,7 +1411,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8DEBBD85-37DD-47B0-97F4-2DCD6B801C49</t>
+          <t>68ACD569-EA48-4023-991C-D2BF0F9075D1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1793,29 +1421,17 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>FARRM: Fiberight Advanced Recovery and Recycling of Materials</t>
+          <t>Energy Pet</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Covid-19 has impacted many sectors; one such sector is the waste management and recycling industry. The sector is facing many challenges; increasing levels of waste generated by households during the pandemic and disruption to waste and recycling collection services, against a background of stagnant recycling rates, increased public and regulatory pressures and a collapse of global recycling markets. A solution is needed which responds to these challenges and supports the UK's green recovery, by developing sustainable and circular economy. The FARRM (Fiberight Advanced Recovery and Recycling of Materials) project is a feasibility study of Fiberight's circular economy technology which creates value-added products from residual waste. In Phase 1 of the project the opportunity for an innovative advanced recovery and recycling solution for the UK's municipal solid waste stream will be evaluated.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Feasibility of advanced recovery/recycling of municipal solid waste into value-added products; object is waste recovery. Business(feasibility) considered</t>
-        </is>
-      </c>
+          <t>400170 Power Poster – Public Project Description The Power Poster project combines novel interactive printed and online tools to give feedback to users on real-time electricity use in a simple and engaging manner. It converts this energy data and human emotional data into clear, simple and beautiful designs. The issue of feedback to users of buildings is a persistent challenge. Buildings typically perform significantly below their efficiency design standards in part because users get no feed back in real-time or in a form that engages them and encourages them to want to do better. Until this issue is effectively addressed, we will as a society, continue to struggle with maximising the energy and resource efficiency of buildings, whether these are new or refurbished. The printed and online tools will result in the development of technologies and techniques that encourage people to care about their building's energy use through emotional rewards. This will be achieved by providing visual feedback loops in real-time, enabling building users to appreciate the impact of their behaviour and present this information in a form that makes users want to adopt energy efficient behaviour. This user-centred approach is a novel and low-tech solution to a significant challenge for UK industry, government and the environment. The project will develop and refine online and printed products that will be used and assessed in school and office settings. Novalia has developed a proprietary printed platform technology ideally suited to the needs of this project. The technology enables the creation of interactive posters that have touch sensitive ink linked to a low cost environmentally friendly power supply, sound device and micro-controller. Novalia is developing a low-cost method of manufacturing its technology with partners. The project will develop an product that uses combines Novalia’s technology with live energy use capture technology to create a platform that enables the visualis</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1825,39 +1441,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>81EB3658-2297-41E0-B156-9F2363CDC208</t>
+          <t>FE0AA8DB-854C-44C9-9484-FBCE4D6597E2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Novel Concepts for SAfer, LIghter, Circular and Smarter VehiclEStructure DesigNfor Enhanced CrashworThiness and Higher Compatibility</t>
+          <t>Tuning Gene Expression in Mammalian Cells by Transcriptional and Post-transcriptional Control</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>Automotive safety is one of the most crucial factors in vehicle development and future vehicles need novel, lightweight structures that are safer and sustainable throughout their life-cycle. Hence, the long-term aim for SALIENT is to make our roads safer and reduce serious injuries and fatalities. To reach this ambition, SALIENT will present novel structural and vehicle concepts that are safer, lighter, circular, and smarter, which can be adapted to accommodate different crash scenarios. SALIENT will focus on innovating new technologies and will develop, demonstrate, and validate the effectiveness of light front-end structure (FES), considering eco-design and circular economy principles, to enhance vehicle safety. SALIENT will adapt advanced light materials, improved manufacturing and joining techniques, innovative circular design, and emerging active safety technologies to develop a smart FES with high energy absorption capability and to be adapted (prior crash events) with future mixed traffic scenarios to meet or exceed future vehicle demands in terms of safety, structural integrity, crashworthiness, and compatibility. SALIENT will build a pathway for the newly accumulated strategic knowledge to impact EU industries and society. Its ambition is to create global impacts and to play a key role to support EU strategic needs, and economic and societal challenges. The consortium consists of twelve partners from seven countries, representing the full automotive value chain, with leading European car manufacturer working alongside world-class research and education organisations, plus innovative SMEs. The project has been engineered to ensure maximum impact for the automotive industry in particular and society as a whole, significantly contributing to the evolving field of automotive safety.</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Lightweight vehicle front-end structural design for crashworthiness, manufacturing/joining; mechanical/structural engineering</t>
-        </is>
-      </c>
+          <t>Cell-based therapies are the new technology of choice in biomedicine, and synthetic biology offers a rational design route towards engineered cells that sense in the human body and record and respond as required. In this project we will use synthetic biology rules to design and build modular genetic systems for programmable sensing in model lymphocyte cell lines. This will involve genome engineering to rewire GPCR-based biosensors to sense small molecules such as melatonin and serotonin, and in parallel using RNA-based detection to sense miRNAs that are the hallmarks of cancer. The project will involve the use of CRISPR and Golden Gate assembly systems to integrate multigene constructs into lymphocyte cell lines and testing the resulting cells in lab-based assays. Collaboration is planned between signalling modelling teams and cancer research experts who can assess cell performance in mouse models.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1867,7 +1471,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3259E363-2955-49DD-8B0E-0D6ABD30CFF2</t>
+          <t>5FCAA9DA-53A4-4E49-A719-1474C7BF4B5B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1877,29 +1481,17 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>The Oxford Box Aerosol Shield &amp; The Paediatric Oxford Box Aerosol Shield</t>
+          <t>Next Door Repairs</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARS-2-Covid is not an airborne virus, but it has been proven that during aerosol generating procedures, such as intubation and extubation, the virus becomes airborne. Healthcare staff performing these procedures are at high risk of contracting the virus. Even with adequate PPE, the viral load transmitted to the face, neck and trunk of healthcare staff makes the process of 'doffing' (safely removing PPE) extremely dangerous. An aerosol shield box: significantly reduces the amount of viral load transmitted to staff significantly reduces settling time to the environment improves staff safety has positive psychological effects on healthcare staff who, by protocol, have to consider all patients positive to COVID19 if not previously tested allows operating theatres to be cleaned and turned round more quickly, without compromising safety Existing aerosol shield boxes that are currently available have a number of ldesign imitations that restrict their use across the healthcare sector. Through a collaboration between renowned medical specialists and high tech innovators, the Oxford Box aerosol shield has been designed to overcome the identified limitations by: 1\. allowing more access for staff to manoeuvre their arms and equipment within the box 2\. accommodating larger patients 3\. being able to be used on a variety of bed and trolley widths 4\. being lighter 5\. being suitable for thorough cleaning and re-use 6\. being compact, foldable and easy to store 7\. being affordable As a result of its innovative design the Oxford Box will be a safe, cost effective shield that will continue to be used as a means of barrier protection long after the pandemic has subsided, as the aerosol infection risk will always be present during intubation and extubation. A proof of concept prototype of the Oxford Box has already been built and tested, and medical approval has been recently granted by Oxford University Hospitals NHS Trust. A proof of concept prototype of a paediatric Oxford Box </t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Design of a physical aerosol-shield device (product/mechanical design) for clinical use; instrumentation/product engineering</t>
-        </is>
-      </c>
+          <t>Next Door Repairs were born from a simple idea: connecting you who require small clothing repairs with those who enjoy getting them done, turning leisurely making into an opportunity for additional income. Have a knack for adding buttons, fixing bobbly jumpers, visible mending or hand-stitched embroidery? We provide a unique opportunity for you to turn your skills into extra cash. Earn and learn as you connect with individuals in need of your crafty expertise. We take a minimal service fee for connecting you with those who appreciate your skills. What Sets Us Apart: We focus on the joy of making (if you enjoy it) and the ease of repair (if you don't) -- we want to be the go-to platform for both: the individuals who love indulging in small repair and decorative textile projects during their free time... and for those who don't. It's a match! We want you to be able to connect; making peer-to-peer interactions seamless. Unlike other platforms, we're not just about professional services; we're about fostering a community of non-professional makers who find relaxation and fulfilment in the craft of repair. We are launching a pilot program in East London, making it convenient for you to offer your services locally. A State of Nature Shop in Hackney allows for a hassle-free drop-off/pick-up point, reducing the need for arranging meetings or shipping and making repairs more accessible. We believe in the circular economy, where every stitch counts. We are your gateway to a world where resources and skills are cherished, contributing to a sustainable future.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1909,39 +1501,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E7CA0EA6-8667-4CD8-8ED8-4A1661E43EDE</t>
+          <t>9C3E3684-F788-494E-8D53-4E44E6E83EEA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>ResiCharge</t>
+          <t>Resource recovery from municipal wastewater with forward osmosis membrane-based process</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>The ResiCharge project will extend an existing planned field trial of ELEVEN's innovative home battery by 60 units to include 30 second life EV battery modules sourced from vehicles in the UK to be installed alongside 30 new modules for comparison. The use of second life EV modules in ELEVEN's all-in-one home battery helps to build a circular economy for EV batteries and extends time before modules are recycled allowing industry to improve processes. At the time of writing it is common for used batteries to be either sold on the grey market, stockpiled or incinerated due to the cost and immaturity of recycling processes. The project will provide an impact validation report to cover reduction in whole life carbon impact (manufacture of battery, use in EV, use in static storage, disposal/recycling) to include offset / payback in second life, energy system efficiencies, cost and end of life disposal.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Field trial of home battery energy storage using second-life EV modules; energy storage/system is the object. Environmental Science (reuse) considered</t>
-        </is>
-      </c>
+          <t>To achieve sustainable wastewater treatment in the context of circular economy, various technologies have been studied to harness resources in wastewater such as anaerobic digestion for energy recovery, struvite crystallisation for nutrient recovery and reverse membrane for water recovery to reduce environment impact of wastewater treatment. The highly diluted nature of municipal wastewater, however, makes these technologies unfeasible or too costly. Forward osmosis (FO) membrane filtration driven by osmotic pressure has attracted intense attention recently because of its potential for wastewater preconcentration to allow direct use of the above-mentioned technologies for simultaneous water purification and resource recovery. Thus, a promising prospect of forward osmosis filtration as a key unit to design next-generation wastewater treatment plants can be expected due to its smaller footprint, more flexible operation, lower membrane fouling propensity and lower energy consumption if the draw solution is well selected and the process is well designed. Most studies, however, focus on a single or a few model chemicals to investigate FO membrane filtration. Studies on wastewater, and interactive relationships between the chemistry of wastewater and the draw solution, and their effects on flux, membrane fouling and cleaning, pollutant rejection etc, are lacking, which makes the real-world application of FO membrane for wastewater treatment challenging. This PhD project is dedicated to this issue, with the ultimate goal to allow energy, nutrient and water recovery from municipal wastewater cost-effective and sustainable.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1951,39 +1531,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C47A38A8-F411-471D-9FA8-903B0EFB5CA8</t>
+          <t>7C319437-8AD4-404E-A44D-1EBC28897E67</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COVID</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Processing Plastics and Textiles: Deriving Circularity Through Improving Recyclate</t>
+          <t>AI-driven approaches to developing a 'nylonase' enzyme for recycling waste plastics</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>This research project explores the mechanical and chemical recycling of waste plastics and textiles to both understand and optimise value in these materials to promote circularity. This involves both the separation of materials, the chemical depolymerisation of products and the mechanical processing and extrusion of commercially relevant plastics and textiles. The challenge is to understand how processing conditions can be optimised to create more consistent value in the recyclate quality in concert with improved sorting methods. The project has a strong sustainability and circular economy focus as well as targets on future manufacturing.</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Mechanical/chemical recycling of waste plastics and textiles, optimising recyclate quality; object is recycling/resource recovery. Chem Eng (processing) considered</t>
-        </is>
-      </c>
+          <t>Moving towards a circular economy requires rapid progress to develop energy efficient new technologies for recycling waste plastics. In this project we take a new approach to develop enzymes for nylon degradation, using a combination of computational biology and directed evolution. Using primary protein sequence data we will build and screen 3D-computational models (AlphFold2) of known and previously unexplored hydrolase enzymes for appropriate substrate binding sites and catalytic architecture. Docking of nylon oligomers with these models will allow identification of the best starting points for new enzymes that bind nylon and stabilise the transition state for amide bond cleavage. Molecular dynamics simulations will help assess substrate binding and the spacial arrangement for key interactions in the active site to facilitate efficient catalysis. The predicted enzymes will be expressed and tested on model polyamides and on post-consumer nylon to provide validation and further refinement of the models. Successful variants will identify key residues that may be further mutated to find optimal combinations of mutations to provide the required 'nylonase' activity.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1993,39 +1561,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9A17F3DB-FFB3-4035-9A15-32314270FD0B</t>
+          <t>A1D991D1-B89F-4031-B7E4-003863BAFA31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AHRC</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Investigating the design of 3D woven materials for the circular economy</t>
+          <t>A Multilevel Analysis of Supply Chain Configuration in the Construction Circular Economy: Supply Push vs. Demand Pull</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>Aim: To use the latest 3D manufacturing technology to create aesthetic, functional and sustainable woven materials for the 21st century. Objectives: 1. To identify the historical developments of the weaving loom and understand those aspects of standardisation that contribute to the 2D nature of weave. 2. To evaluate methods of integrating traditional weaving with 3D technology. To combine craft with digital to provide new visual, tactile and structural properties. 3. To identify characteristics required of new materials that may benefit from the integration of 2D technology with the latest 3D technology. 4. To develop new techniques for the manufacture of new smart materials with the circular economy in mind. Background: There is currently an absence of 3D printing technology in weave design. We have seen a move towards the 3D printing of textiles, but this focuses on the development of knitted structures and less on woven ones (CITA's Hybrid Tower). A weave structure is an interlacing of yarns that cross one another at right angles. As a weaver, I understand the potential weave structures have to influence the nature of fabrics. Lack of consideration of the circular economy in textile design is apparent. There are many projects that focus on the re-use and recycling of textiles, but few that are considering the future of textiles with a cyclical life cycle. Research Methodology: Year 1 Literature reviews, start of practice-led action research, first hand interviews with design studios/ makers/ other research institutions. Research visits to museums, textile mills. Life Cycle Assessment training course. Testing of equipment such as digital jacquard loom, 3D printing facilities. Continue in the collaborative partnership with Sosanya, formed during Sophie's time at the RCA, to develop a hybrid 3D printing/weaving machine in collaboration with the Centre for Fine Print Research at UWE Bristol. Year 2 Continuation of practice led action research. Sophie will develop tec</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Developing 3D-weaving manufacturing techniques and a hybrid 3D-printing/weaving machine; design/manufacturing maps to Engineering, but AHRC practice-led craft could be Arts and Humanities. Near coin-flip</t>
-        </is>
-      </c>
+          <t>Supply chain (SC) configuration is strategically associated with supply push (SP) and demand pull (DP) strategies that often deal with corporate inventory. It can also be related to promoting knowledge or awareness. SP and DP measures have been weighed differently depending on varying contexts. Some studies argued that current policies about promoting innovations were overwhelmingly dominated by DP measures whose effectiveness of inducing non-incremental innovation was largely doubted due to the technological incapability resulted from SP negligence. There are also some studies claiming that current practices of promoting entrepreneurship relied heavily on SP factors, whereas some SP factors were proved with no correlation to start-up rates in high-tech industries. By comparison, a dynamic process is introduced from an innovation chain perspective, where the configuration of novel technology SC gradually moves from SP measures (e.g. technology push, public funded) to DP settings (e.g. market pull, mostly private funded) with the increasing level of technology maturity. However, there is hardly any understanding of SP and DP in the context of construction circular supply chain (CSC) in the existing literature that also lacks an explicit definition of DP and SP. The challenges in circular economy (CE) implementation are not only involved with institutions pushing the development of new ideas or technologies but also the market creating the demand for them. The overwhelming adoption of either SP or DP measures can result in a growth plateau. For example, some 'waste-to-value' CE approaches such as production of bioplastic from sewage or recycling or LED lamp waste, are technically feasible but not economically competitive in the market. In this respect, pull measures are supposed to gain more attention to enhance 'market pull'. The research question formulated for this project is 'what are the possible configurations that achieve both circularity and resilience in cons</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2035,7 +1591,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>378CC79E-97FA-4C45-935E-7830A66CD219</t>
+          <t>02BA6D84-EB1B-4D83-B932-93B454471E71</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2045,29 +1601,17 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Single shaft plastics shredder</t>
+          <t>Locblock turning a plastic and non-recyclable textile waste issue into a housing solution: Phase 2 - System and prototype completion</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>Development of a shredder to assist with the processing of problematic global waste streams to aid the circular economy towards achieving Net Zero by 2050\.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Developing a shredder (a machine/product) for waste processing; object is a machine per boundary rule. Thin abstract; Environmental Science (recycling) considered</t>
-        </is>
-      </c>
+          <t>Locblock turning a plastic and non-recyclable textile waste issue into a housing solution. Locblock is a new 'fire rated structural composite block construction system' with smart features built-in: Safe- Structurally designed to be simple, strong and a robust alternative to masonry, metal, or timber framing. Guaranteed performance- Locblock will gain a British Board Accreditation (BBA) providing tested and independent performance. This will prove the systems fire safety, structural loadings, improved U-values, airtightness, acoustic and thermal performance. Through advanced manufacturing processes Locblock provides a built-in performance while eliminating human error and installation risks. Cheaper energy bills- Locblock will provide lower running costs through reduced heat loss, reduced condensation, improved comfort and ultimately reduced carbon emissions. Service ducting built-in providing service routes and removing unsightly boxing in or surface fixed services. Fire safety- Locblock will redefine how structural polymers should be applied in the construction industry. Creating a new building system that addresses fire safety at the construction phase to conform with HSG168 by reducing fire loads, through to occupation by obtaining an independently tested and proven fire rated system. Construction costs- Locblock is so simple to erect, it will become the 'building for dummies' construction system - like building blocks are for children, Locblock is for adults. A fast simple installation, that does not require highly trained personal, addressing the growing skills shortages, whilst reducing the construction labour costs. The results are cheaper overall costs compared to tradition systems. Improved productivity- Locblock will mean more houses are built every year, not only does Locblock allows for quicker onsite installations compared to traditional systems, as it can be installed in adverse weather conditions, windy, wet, cold days do not affect the installation,</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2077,39 +1621,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>F6B4DB61-D9DF-4465-90F2-929EF78031C5</t>
+          <t>959B7BF6-9D9D-4DDD-8D6F-4C0218AA345E</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>BBSRC</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>ASP A novel method to de-water alum sludge to provide a powder ingredient that can be used to manufacture binders</t>
+          <t>Sustainable Photonic Pigments Made of Bacteria</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>UK-based SME, Aspcold, aims to develop a pioneering alum-sludge treatment solution that offers an energy-efficient, alternative End-of-Waste option for alum-sludge and a circular economy avenue as an additive to high-performance building adhesives. Alum-sludge is a waste by-product generated by water-treatment and is traditionally disposed of in landfills. No viable treatment options currently exist for alum-sludge. In the UK, ~500,000 tonnes of alum-sludge is landfilled annually costing ~£53m. Worldwide the production of alum-sludge is ~10m tonnes each year. The rate of this production is expected to increase with water demand (~20-30% by 2050). With landfill space in the UK expected to run out in 20 years and alum-sludge documented to leach harmful levels of aluminium into the ground. UKWIR has objectives to achieve zero waste by 2050, and the Environment Agency sets out to enforce reuse of sludge where possible, highlighting the demand for alternative/circular treatment options for untreatable waste like alum-sludge. Aspcold has created a demonstrable prototype that uses a low-energy process to convert water-bound alum-sludge into a dried product that can be used as a low-carbon additive to high-performance building adhesive. The process relies on readily accessible materials, allowing rapid manufacturability and scalability. Aspcold anticipates the serviceable available market (Water-and-Waste-Water-Treatment) of ASP is £4bn. In this 21-month project, Aspcold will optimise its unique alum-sludge water separation and drying process to identify the most efficient combination for use by water-treatment facilities. Industrial testing and research of the dried solid as an additive to building adhesives will inform on the best circular use cases. ASP addresses the global need for a cost-effective and sustainable alum-sludge End-of-Waste solution.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Treating alum-sludge waste (End-of-Waste) into a reusable powder additive; object is waste treatment/resource recovery. Chem Eng (dewatering/separation) considered</t>
-        </is>
-      </c>
+          <t>Pigments are ubiquitous components of our everyday life as they are used for colouring several materials including paint, ink, fabrics, food and cosmetics. However, the manufacturing process of conventional pigments places a high burden on the environment, as it consumes high energy and resources, among them, irreplaceable petroleum. Moreover, many traditional pigments pose high risks for human health as they contain heavy metals or inorganic particles. Additionally, their production requires hazardous substances and mining for mineral pigments, in particular in developing countries, have devastating effects both for the environment and society. Our project aims at the development of new bio-based pigments that are sustainable, bio-compatible and easily scalable for mass production. In particular, we want to develop a methodology to exploit bacteria as building blocks for pigments. The vision of this research proposal is to harness the ability of bacteria to show bright colouration as a result of the physical organisation of cells within colonies. Their colouration is therefore not caused by pigmentation, but it is due to sub-micron organisation, which function as photonic crystals reflecting light only at specific wavelengths. This phenomenon is called "structural colour" and is at the base of the colouration of many living organisms (e.g. the peacock feathers or morpho butterfly wings). Depending on the size of the nanostructures, a specific colour is reflected and, depending on the regularity of the patterned areas, the effect can be matte (angularly independent ) or metallic iridescent (strongly affected by the viewing angle). Recently, in collaboration with the SME Hoekmine BV, under the remit of BBSRC-funded research, we show that we can genetically modify marine flavobacteria. We were able to change their organisation and their motility, thereby altering their interactions with lights. As a consequence, we were able to change their colour and to tune it in th</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2119,39 +1651,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>E936795D-139B-4E23-8FA8-2ABEAA2E844B</t>
+          <t>0CC9BB64-B6D0-4882-B936-B363E151B401</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>Towards tURbine Blade production with zero waste (TURBO)</t>
+          <t>Synbio production of monoterpenes through computationally-guided enzyme engineering</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>10000 wind turbine blades (WTBs) were installed in Europe in 2019, and the largest are &gt;100 m long. Yet the manufacturing methods have not changed significantly since the 1970s, with little or no NDT or in-line control, leading to high defect, repair and scrap rates. TURB0 will reduce defects and improve repair strategies in WTB composites and coatings. -Improved composite production processes: By using the latest simulation techniques to avoid defect formation and understand how defects affect structural integrity. -In-line NDT: Combining three cutting-edge NDT technologies (dielectric, wireless, sensor-less) for the first large scale in-line in situ composite production monitoring. -Sub-surface WTB coating inspection: Currently coatings only undergo visual surface inspection or destructive testing. TURB0 will combine ultrasound and mid-IR OCT for the most detailed coating assessment ever performed. -Digital twin and data warehouse: Production equipment, monitoring and in-line NDT data will be combined to establish a digital twin for real-time analysis of production. This has never been attempted for a large-scale composite part. It will populate a data warehouse accessible from multiple production sites. -In-line system control: Using the digital twin, a ML-based algorithm will provide closed-loop process control to minimise defect formation and waste and optimise process efficiency. -Automated repair strategy: The digital twin enables a ML analysis of defect severity in composites, with automated strategies to reduce repairs by 90 % and increase recycling of off-cuts. -Full-scale demo: A demo on a full size &gt;80 m WTB section will be performed at the SGRE factory in Aalborg. -Quantified sustainability improvements: including life cycle analysis (LCA), social LCA and circular economy assessments to quantify environmental and socioeconomic benefits. -Dissemination and exploitation activity: includes a powerful Advisory Board, training, standards and business plan.</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Composite manufacturing process for wind-turbine blades (defect reduction, in-line NDT, process control, digital twin); work is manufacturing/materials processing, energy is the sector. Energy considered</t>
-        </is>
-      </c>
+          <t>Monoterpenes (C10 isoprenoids) are a large group of structurally diverse natural compounds that are attractive to industry as flavours, fragrances and fuels. Monoterpenes are produced from a single linear substrate, geranyl diphosphate, by a group of enzymes called the monoterpene cyclases/synthases (mTC/Ss) that catalyse high-energy cyclisation reactions involving unstable carbocation intermediates. Efforts towards producing monoterpenes via biocatalysis or metabolic engineering often result in the formation of multiple products due to the nature of the highly branched reaction mechanism of mTC/Ss. We have established platform microbial strains for the production of these compounds using automated synthetic biology strain bioengineering approaches in the Manchester Synthetic Biology Research Complex (SYNBIOCHEM; ChemistrySelect. 2016, 1, 1893-) and have discovered and characterised a range of new mTC/S enzymes using a multidisciplinary approach including enzyme biochemistry, structural biology and computational chemistry (ACS Catal. 2017, 7, 6268-). This project will focus on the optimisation of mTC/S enzymes and pathways for the in vivo (bacterial) biosynthesis of specific compounds of interest; initially, pinene, cineol and linalool with scope to expand this selection after consultation with additional industry partners. An iterative approach using computational methods to design variants that are then characterised experimentally using our established mTC/S assays. Initial work will focus on an existing large, and ever-growing library of mTC/S sequences and product profiles collated in Manchester, which will be used for benchmarking computational predictions and to train machine-learning algorithms.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2161,39 +1681,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>67C47E46-2327-4087-916B-9857A77BC683</t>
+          <t>82B4EE57-1CED-4D48-B5BC-DA4CDCB1E15D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Closing the Loops of Fast Moving Consumer Goods</t>
+          <t>Designed for Humans, Powered by AI: Designing a user-centred waste textile sorting software for waste textile collectors.</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>The Fast-Moving Consumer Goods (FMCGs) sector aspires to transition to a Circular Economy (CE) but there is a lack of knowledge and support methods. This research has investigated how material resources flow in FMCG systems and developed new design support for the sector. Initially, we focused on the moment when resources become obsolete which can disrupt flows. Consumers were found to have critical roles to ensure resource revalorisation and the findings of this study can inform the design of future revalorisation services. We then looked at Product-Service Systems (PSSs) and studied the elements that could help overcome obsolescence and enable closed loops resource flows. A framework presents these elements, mapped against requirements for PSSs that close loops. Subsequently, we investigated the resource flow-system, which encompasses all the elements in place to produce a resource flow. A new modelling method is proposed that describes the movements and transformations of resources, and helps configure FMCG sector-specific system elements. The model can be used to explain how FMCG systems work. Finally a tool is presented, which embeds the modelling method as well as the process to apply it and analyse the model. The tool enables industrial users to develop a holistic view and an in-depth understanding of the resource flow-system informing the development of future systems solutions. Journal papers featuring work presented in this thesis Zeeuw van der Laan, A. and Aurisicchio, M. (2020), "A framework to use product-service systems as plans to produce closed-loop resource flows", Journal of Cleaner Production, Vol. 252, p. 119733. Zeeuw van der Laan, A. and Aurisicchio, M. (2019), "Archetypical consumer roles in closing the loops of resource flows for Fast-Moving Consumer Goods", Journal of Cleaner Production, Vol. 236,. Conference papers featuring work presented in this thesis Zeeuw van der Laan, A. and Aurisicchio, M. (2021), "The Flow Mapper : A Tool to Model S</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Product-service systems, consumer roles and resource-flow modelling/design support for the FMCG sector; management-of-resource-flows problem. Engineering(design) considered</t>
-        </is>
-      </c>
+          <t>Eslando is a circular fashion tech company on a mission to accelerate textile recycling. Our Artificial Intelligence(AI) powered sorting software leverages Digital Product Passports(DPP) to sort textile waste for recycling with pinpoint accuracy. By connecting fashion's disconnected end-of-life supply chain with data, we solve the biggest problem in waste-textile sorting for recycling. Our innovation reduces landfill waste by 75%. Enables waste-textile collectors to recover materials efficiently. This project is a collaborative partnership between Eslando, a Fashion-Tech Company (Lead), Terra Further, Human Centred Design Agency, and Andrew Blackshire, a Human Centred User Experience (UX) Researcher. Our common objective is to achieve a successful human-centred design research project that leads to a user-friendly and impactful sorting software solution for textile waste collectors. 85% of leading fashion brands (by sales) have net zero targets; By 2030, more than 35 fashion sustainability regulations, including Extended Producer Responsibility and Product Passport requirements, will be implemented; 133 million tons of recycled fibres could be required by 2030 \[Boston Consulting Group, 2023\]. Fashion produces 100 billion clothes every year, and less than 1% are recycled into new clothes; The fashion industry contributes 3.29 billion tons of carbon annually. \[Quantis, 2018\]. Production of virgin fibres and disposal account for 41% of these emissions. \[McKinsey &amp; Ellen MacArthur Foundation, 2017\]. We will reduce carbon emissions by 25 kg per kilogram of waste textiles. We will reduce over 50 million tonnes of carbon emissions and advance UK Net Zero goals, through recycling. We propose UK materials security by circularising textile resource flows. We will reduce waste exports. We will advance the transition towards a circular economy by providing research and understanding</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2203,7 +1711,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>826F1B88-6F2C-4972-9BA9-F5EFF8CD8EBB</t>
+          <t>75906106-1423-4EFC-A7B4-74683DB96DD9</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2213,29 +1721,17 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Valorise: A Digital Platform for Agri-Food By-Product Valorisation</t>
+          <t>Design for Lightweighting, Material recovery, And disassembly Technologies (DeLiMAT)</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>In the UK 51% of food is wasted before it gets to the consumer during agricultural post-harvest distribution or processing. Globally, over one third of all food produced across the food chain is wasted. A significant proportion of food loss relates to the inherent physiology of the crops, poor control of post-harvest biology and the efficacy and appropriateness of the control systems applied. To generate economic value from waste, the valorisation of agri-food by-products (AFBPs) and mapping of supply chains to manage agricultural waste systems is crucial. There is a lack of consolidated knowledge of existing agricultural waste, its categorisation and potential uses, including how agri-food by-products (AFBPs) can become a valuable feedstock resource for other applications and products. Currently huge portions of agricultural waste are undervalued and underutilised. This project encompasses the development of a proof-of-concept digital platform for trading in AFBPs, setting the scene from a move away from a waste model to a resource that has economic value. We are aiming to use a Human Centered Design model for the creation of a digital marketplace, by interviewing representatives from the value-chain, we will gain information for the design of the platform that will be of use for both food producers, processors and those looking to purchase feedstock. The Human Centered Design (HCD) approach, combined with performance testing of the digital platform, will ensure that future developments in the digital platform meet the requirements of prospective end-users, increasing their acceptability, uptake and use. Our business plan is based on a subscription model for those looking to buy or sell feedstock. The platform will be free to researchers in the public sector based on anonymised data sets that could be used for development of public policy. Sustainability is crucial and set to remain firmly at the centre of future international agricultural policy given the continue</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Building a digital marketplace/platform (HCD, performance testing) for trading agri-food by-products; work is the platform. Business(marketplace/model) considered</t>
-        </is>
-      </c>
+          <t>Hive Composites is pioneering a transformative shift in lightweight vehicle manufacturing by delivering fully recyclable, high-performance thermoplastic composites combined with in-situ bonding and disbonding technology in a project called DeLiMAT (Design for Lightweighting, Material recovery, And disassembly Technologies). Our innovative approach addresses one of the most pressing sustainability challenges in the industry---material recovery and circularity. By demonstrating advanced bonding and on-demand disbonding solutions for these fully recyclable materials, we enable recovery, reuse, and recycling of vehicle components, dramatically reducing waste and lifecycle emissions. Why this matters: Fibre-reinforced plastic composites are essential for decarbonising transportation through lightweighting, which directly improves electric vehicle range and efficiency. Although thermoset composites dominate today's market due to ease of processing, their inability to be recycled poses significant environmental and economic obstacles. Fully melt-reprocessable thermoplastic composites represent a game-changing, sustainable alternative---yet their adoption has been slow due to technical challenges such as high melt viscosity and demanding processing conditions, which limit fibre impregnation and increase production costs. Hive's solution is a revolutionary low-melt viscosity thermoplastic resin, METOL, which uniquely combines the best of both worlds: it can be processed using conventional thermoset techniques (prepreg and resin infusion), achieves superior mechanical properties with high fibre volume fractions (\&gt;70%), and offers full recyclability through solvolysis---recovering base materials without degradation, avoiding downcycling and extending material lifecycles. By replacing high-carbon, conventional structural materials with this new generation of fibre-reinforced thermoplastic composites combined with disbond-on-demand technologies, Hive Composites is enabling a fu</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2245,7 +1741,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1F5F5111-0B7A-412C-991F-5082E8C0F2BB</t>
+          <t>46C26966-1104-4388-B3B8-0B54B0E11723</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2255,29 +1751,17 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Feasibility of high-performance, customised 3D-printers and a distributed manufacturing network across Europe.</t>
+          <t>Transfor-methane: Integrated Transformation of Dairy Slurry into recovered Nutrients and Clean Energy</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>Batch.works is using 3D-printers to create new methods for prototyping and sustainable product design utilising continuous production methods. This reduces speed from design-to-manufacture and enables use of higher quantities of recycled materials. Our vision is to disrupt traditional manufacturing, creating a circular network of distributed 3D-printing sites around the world. Decentralisation enables designers/retailers/manufacturers to rapidly produce products on-site and in time will enable closed-loop manufacturing. We want to see products remanufactured at the end-of-life. This project is a global collaboration feasibility study exploring the opportunities in a booming 3D-printing market in Germany. We will establish a new global collaboration with Caribou3d, a high-performance 3D-printing business in Germany to explore the technical possibilities of using their machinery under a new collaboration. This collaboration will also enable us access to the European single market through the existing value chains Caribou3d has established.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Distributed 3D-printing/additive-manufacturing network feasibility; domain is manufacturing, but heavy market-entry/business-collaboration framing gives Business a claim</t>
-        </is>
-      </c>
+          <t>WASE has developed a novel reactor that processes wastewater and cattle slurry and recovers energy from the waste as biogas. The reactor applies electricity across a mix of waste and microbes to break down material 6 to 10 times faster than traditional anaerobic digesters. This project aims to prove that nutrients can also be recovered from slurry as a concentrated solid, giving farmers a substitute for expensive chemical fertilisers that are themselves environmentally damaging to produce. WASE will collaborate with the UK Agri-Tech Centre to design, build, and test a lab-scale prototype that combines this reactor with a downstream solid-liquid separation step. The system will be trialled on two feedstocks: digestate from a UK industrial anaerobic digestion site, with a nutrient profile comparable to dairy slurry and currently spread on farmland; and dairy slurry representative of UK dairy farms. The project will also design a farm-scale prototype with input from farmers and other stakeholders, and assess its environmental and economic benefits. Outputs will address farming needs around slurry storage costs, regulatory compliance, and cheaper fertiliser substitutes, with wider benefits for soil and water quality, air quality and greenhouse gas emissions, renewable energy generation, rural development, and the circular economy.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,39 +1771,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3CE1A08B-FE2F-4AC5-9EDE-291C93CE95E6</t>
+          <t>D1CDE730-E014-4ADE-AD00-96B4194A2FB4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>New bio-based and sustainable raw materials enabling circular value chains of high performance lightweight biocomposites</t>
+          <t>Securing Drinking Water Supplies: the Role of Organic Matter on Water Treatability</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>New lightweight High-Performance Composite (HPC) materials and efficient sustainable processing technologies will have an enormous environmental and performance benefit in all sectors of application. However, current sustainable HPC application is limited to large sectors due to their limitations in terms of long processing times, high prices and low recyclability. To overcome these limitations, rLightBioCom propose a paradigm shift in the way HPC are manufactured and recycled, unlocking sustainable-by-design production of lightweight HPC. Therefore, the project will enable new circular value chains towards r-LightBioCom results, contributing to environmental-related EU goals and reducing the HPC waste generation and the use of non-sustainable fossil resources. To this end, a sustainable catalogue of new advanced biobased and recycled HPC materials will be initially developed with inherent recyclability properties (at least 3 new types of bio-resins, 4 new biomass-derived nanofillers and additives, and 3 families of sustainable fibre-based textile products). To reduce current associated manufacturing costs and high energy consumptions and emissions, efficient processing techniques will be developed (2 new fast curing techniques) combined with recycling technologies for the new catalogue of materials to reduce waste generation and induce circularity. A new open method and related tools (Coupled Ecological Optimisation framework) will promote and standardise holistic sustainable HPC design, modelling and systematic optimisation, leading to continuous sustainable catalogue growth and inclusion of new families of biobased, recyclable lightweight HPC at competitive cost. All results will be validated in 3 use cases at automotive, infrastructure and aeronautic industries with specific business cases, contributing to establishing new resilient, sustainable and innovative value chains in the EU HPC industry, promoting a change of paradigm from linear to circular ones.</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Developing new bio-based recyclable composite materials (bio-resins, nanofillers, fibres) plus processing; materials development leads, but processing(Engineering) and Chemistry are close. Field not in dropdown</t>
-        </is>
-      </c>
+          <t>The aim of this project will be to determine the features of organic matter in surface water that controls their removal in water treatment processes. This will allow for proactive management of water treatment systems to make more informed decisions on water blending and transfers, as well as future WTW operation and treatment process selection.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2329,39 +1801,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B6A43CCA-38B7-4A59-A3A9-4FD307676383</t>
+          <t>D98BA794-D11A-46A3-9EFA-CED0AE5890F1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UKRI FLF</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>A Triad for Upcycling Plastic Waste: Catalysis, Copolymers and Compatibilizers</t>
+          <t>REMP - Remanufacturing E-Marketplace for a Circular Digital Supply Chain</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>Plastics have helped to build the modern world, and the current era has been dubbed “The Plastic Age” due to the ubiquity and influence of these materials. Yet plastics are both a friend and foe to the environment. While plastic pollution poses a very real environmental danger, plastics are also powering the green revolution as key components of wind turbine blades, batteries, and lightweight electric vehicles. Plastics have reduced CO2 emissions across Europe by a factor of 5-9, and address the global challenge of food security by reducing food waste by 20%. However, current production methods are unsustainable. Over 99% of plastics are currently produced from crude oil, and by 2050, annual plastic production is predicted to use 20% of global oil reserves and generate twice as much CO2 as the aviation industry. Approximately 60% of the 8300 Mt of plastic produced globally by 2015 has been discarded. Plastic waste is thus an attractive alternative feedstock to help conserve oil stocks and avoid energy intensive cracking processes. Transitioning from a linear plastic production model to a circular economy is of urgent importance, yet this requires innovative scientific technologies. Only 10% of plastics are currently recycled. This is partly because "recycled" materials are generally downcycled, with a reduction in material properties such as strength and flexibility leading to progressively lower value applications until recycling is no longer cost effective. This process is further complicated because plastic products often contain multiple types of plastic, such as polyethylene (PE) milk cartons which have lids and labels made from polypropylene (PP). Recycling feedstocks thus often contain a mixture of different plastics that require intensive separation processes and subsequent recycling as individual components. Creative scientific solutions are crucial to address these problems in order to upcycle plastic waste into useful value-added products. The creation of</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Catalysis + copolymer/compatibilizer chemistry to upcycle plastic waste; bench chemistry method development. Chem Eng(catalysis) and Env Sci(plastic waste) are strong alternatives</t>
-        </is>
-      </c>
+          <t>Remanufacturing returns end-of-life (EOL) products to a like-new functional state with matching warranty, thus, extending product service life (200% to 300%), capturing residual value from EOL components and providing superior economic and environmental benefits compared to traditional Original Equipment Manufacturer (OEM) new production. Remanufacturing can reduce greenhouse gas (GHG) emissions by more than 80% in appropriate sectors, reduce new material requirements(costs) by a similar amount and create employment through increasing skilled labour hours by up to 120% \[IRP 2018\] while still reducing overall cost. However, despite these triple-win benefits the UK remanufacturing industry is still at its infancy, e.g. the ratio of remanufacturing to manufacturing is strikingly low, only at around 2% (ERN 2015). In addition, almost 98% of remanufacturers are small and medium-sized enterprises (SMEs) \[SIR 2020\] and struggle with inadequate resources to establish their brand, limited access to cores (used products as starting material for remanufacturing) and scarce sales channels to reach their customer base. Crucially the sector has an image problem and customers do not trust the quality of remanufactured products. Furthermore, as a result of significant inefficiencies and inhibitive costs arising from small scale remanufacturing volumes, remanufacture is often abandoned in favour of other lower value end-of-life processes such as recycling of the materials. SMEs have benefited greatly from the Electronic Marketplace Places (EMPs) such as eBay and Amazon which introduce the network effect of bringing together market participants so that increasing numbers of customers to attract a greater number of merchants and partners, and vice versa. However, such EMPs are not suitable for remanufactured products as they do not address the fundamental issue facing remanufacturing, namely a lack of quality control for remanufactured products and intermittent access to cores. Wi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2371,39 +1831,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5EE16228-E7E3-406D-A920-CD764694E4CC</t>
+          <t>66C7B3AF-D6D5-477B-9FEE-C7DE77B41845</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>BuildZero: transforming the UK's buildings for zero material extraction, zero carbon and zero waste</t>
+          <t>IntelliJeni: The Future of 3D Printing Automation</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>Buildings and infrastructure are responsible for over 30% of the UK's carbon emissions, produce over 60% of the UK's waste, and consume approximately 50% of all extracted materials globally. Radical change is urgently required to achieve a sustainable construction sector. The circular economy (CE) is a well-recognised opportunity to turn waste into resources while reducing carbon emissions. CE aims to keep materials at the highest value possible, via a hierarchy of strategies, e.g. first prioritising extending the lifetime of buildings, then reusing building elements directly in-situ or on another site, then remanufacturing elements, and finally recycling material to conserve resources and avoid disposal. However, CE is still far from typical construction practice. Action to date has largely focused on one-off case studies of individual buildings, or recycling targets leading to wasteful downcycling, and lacks the national-scale, systems-level impact that is so desperately needed. BuildZero's vision is one of a building stock that delivers the UK's space requirements but no longer relies on extraction of new resources, by leveraging the CE to meet materials needs, and eliminating both waste and carbon emissions from material extraction and production. Using this highly ambitious end goal as a springboard, we will explore CE solutions across multiple scales, identified, co-created and co-delivered with our highly engaged industrial consortium, assess the extent to which this vision is achievable nationally, regionally and in relation to individual buildings, and determine the conditions in which the BuildZero vision leads to favourable social, environmental, and economic outcomes. This new knowledge base will provide a platform to enable these solutions to be translated into practice at scale, catalysing regional and national policy to stimulate real change. To achieve this, we will develop an interdisciplinary, multi-scale systems model of buildings and resources fl</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Circular economy for the building stock: waste-to-resource, material reuse, systems model at national/policy scale; object is materials/waste/resources. Engineering(built environment) and Social(policy) considered</t>
-        </is>
-      </c>
+          <t>In the LEAD (Low Energy Autonomous Digital) Factory project, a consortium of world-leading companies joined forces to innovate and develop a ground-breaking automation system. The process involves creating functional plastics from plant waste, converting them into usable, eco-friendly polymers. This clean, low-energy manufacturing process is entirely controlled digitally, minimizing harmful emissions and ensuring circularity through an innovative recovery process for end-of-life plastics. Building on the success of the LEAD Factory, the IntelliJeni project aims to revolutionize the way plastic parts are created by scaling up the automated concept machine for deployment. Jeni is a modular, turnkey automated 3D printing solution that increases productivity, resource and energy efficiency, and digital technology adoption while localizing manufacturing. By being a turnkey, modular, automated, and mobile system, Jeni significantly reduces the technical and cost barriers to entry for adopting 3D printing in mass production operations. This data-driven machine will standardize and automate the production of large volumes of polymer parts, utilizing machine learning for improved output and reliability. One of the key challenges and opportunities in scaling up additive manufacturing is that each part can be unique, requiring multiple iterations to optimize the production process, consuming time and material. By applying machine learning to the system, IntelliJeni will be able to suggest optimized production parameters based on input parts, learning from all previous iterations. Digital part creation has numerous energy, productivity, and waste reduction benefits, including greater optimization potential, reduced carbon emissions, and on-demand manufacturing near the point of need. This disruptive, game-changing alternative to injection moulding has the potential to spark the next digital industrial revolution in the UK. With its cutting-edge approach to manufacturing and com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2413,39 +1861,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2FEF3161-191B-4401-9551-2FB523B26902</t>
+          <t>F72DDAFE-5488-47D9-9D51-9EAF279A8807</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>UKRI FLF</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>Circularity in volatile anaesthetics</t>
+          <t>Indoor power harvesting using hybrid perovskite materials</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>SageTech Medical have developed a highly innovative technology that captures, recovers, and recycles anaesthetic gases that are used in healthcare facilities around the world. We have developed this technology because anaesthetic gases, when released to the atmosphere after use, contribute significantly to global warming because of their high carbon footprints. Globally, anaesthetic gases contribute approximately the same carbon footprint as 5000 flights between London and New York. There is no need to dispose of used gases and manufacture brand new anaesthetics - that process itself produces high levels of carbon dioxide equivalents needlessly - the gases are minimally metabolised in the body, they are robust chemicals, and relatively easy to handle and process. These factors make them ideal targets for capturing and reusing. As this technology is adopted by healthcare facilities around the world, the scale of the technological and operational systems must evolve to maintain optimal levels of sustainability. If successful, this grant will enable SageTech to work with industry experts to bring transformational developments to the core innovative technology that SageTech has built. This will make it possible for SageTech to build a truly ground-breaking business with global reach, here in the UK. SageTech have enquiries from healthcare markets around the world and we are highly motivated to take the business to the next level.</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Capturing, recovering and recycling anaesthetic gases to cut emissions; emissions reduction + resource recovery. Chem Eng(gas separation) considered</t>
-        </is>
-      </c>
+          <t>The world is increasingly using low-power, electronic devices in myriad ways, including as sensors for the Internet of Things (IoT), where billions of objects are connected to the internet to make a smart network, and in wearable electronic devices such as smart watches. Sensors are the fundamental components in the success of these ground-breaking technologies. By 2022, the total number of connected sensors and devices in IoT is expected to exceed 50 billion. How will all these devices be powered? Connecting every device to the electrical grid is too complex and expensive as it requires extensive installation and wiring, and furthermore increases electricity consumption. The use of batteries will limit the life span, bring service interruptions during battery replacement and will pose severe environmental issues at their disposal. My proposed research will bring a practical solution to this by developing inexpensive and environmentally friendly, new technologies to power these small electronic components. My research vision is to power these wireless sensors and internet connected smart devices, using cost-effective and self-sustaining indoor energy harvesters. For this I will suitably 'tune' the properties of a family of electronic materials called 'hybrid perovskites' which combine favourable attributes of both organic and inorganic materials. The two physical properties that I envisage to exploit for this 'multiple' energy harvesting are (a) photovoltaic - converting light to electricity and (b) piezoelectricity - converting mechanical vibrations to electricity. In hybrid perovskites these two properties co-exist, opening new opportunities for multiple energy harvesting. Inside buildings a vast reservoir of untapped energy is available in the form of lighting, mechanical vibrations and movement. Usually these are wasted energy inside the buildings. By combining the strengths of co-existing photovoltaic and piezoelectric activity in hybrid perovskites, I will dev</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2455,7 +1891,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7A8ADFDA-F313-4685-BBA0-AA79604B5DF5</t>
+          <t>93A16B4F-AE94-4877-9577-01F70AD60D7A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2465,29 +1901,17 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Clean Tech Circular Textiles</t>
+          <t>Sustainable UK modular construction: Nanocomposite enhanced recycled materials with improved mechanical properties, fire retardancy and recyclability.</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>A New, clean, low-carbon technology to reclaim valuable nylon textile materials from swimwear and womens tights, and create a circular economy business model to close the loop on pre and post consumer waste.</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Technology to reclaim nylon from swimwear/tights textile waste; textile recycling/resource recovery. Thin; business-model element noted</t>
-        </is>
-      </c>
+          <t>Wider environmental considerations will transform what we build, the materials we use, and how we build. In 2019-20, the total housing stock in England increased by around 244,000 homes, approximately 1% higher than the previous year. The number of new homes supplied annually has been growing for several years but is still lower than estimated need. In addition, there is enormous pressure to improve the energy performance of buildings. Tackling these issues represents a real opportunity with global growth forecast in green and sustainable building construction 22.8% p.a. on average between 2012 and 2017\. This project will increase the content of recycled materials in modular construction products without compromising quality and performance enabling the use and reuse of larger quantities of recycled materials in production and integrate recycled polymers into a construction prefab cradle-to-cradle circular economy.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2497,7 +1921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B398787A-BA31-411A-80C1-2616F3FA791D</t>
+          <t>9415CD7C-86FE-4DBD-BA9D-FCEAD091C752</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2507,29 +1931,17 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>HARPERS</t>
+          <t>Circular solutions for fishing gears</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>The project aims to establish and clarify the benefits and added value of more aligned and harmonised regulations and standards for prioritised topics related to decommissioning and initial phases of radioactive waste handling, including shared processing facilities between Member States (MS). The project has a two-phase approach: first engaging with Stakeholders to assess needs and pros/cons for harmonisation and identify priority areas for deeper analysis (WP2). The second phase will pursue deeper engagement with Stakeholders to further assess the highest ranked priority areas in Work Packages (WP) focusing on (i) cross border services and cooperation (WP3), (ii) circular economy (WP4), and (iii) advanced technologies (WP5). These WPs will review (inter)national practices, capture lessons learned, and assess opportunities. WP6 on Regulatory Framework will identify regulatory differences between MS and evaluate strengths, weaknesses, opportunities, and threats associated with harmonisation, while quantifying the benefits of aligned regulations and proposing harmonisation methodologies. The project will: - support coordination between Stakeholders - enhance existing commitments to facilitate sharing and exchange of knowledge and experience - develop strategies for shared treatment and storage facilities, cross border services and cooperation, and explore additional mechanisms to build capacity in MS - assess and clarify the benefits and any disadvantages of harmonisation, - deliver S&amp;T-based solutions and share best practices by engaging and supporting coordination between different actors through the TSOs and regulators - define conditions and opportunities of a high safety circular economy. The action will reinforce the activities of the EURAD, PREDIS, and SHARE projects, while encompassing activities within MS national programmes and the wider European Community, including e.g. ERDO, ENSREG, WENRA, IAEA, OECD NEA, IGDTP, SNETP, and DigiDecom.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Social Sciences</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Harmonising regulations/standards and stakeholder coordination for radioactive-waste decommissioning; law/regulation/institutions. Env Sci(radioactive waste) considered</t>
-        </is>
-      </c>
+          <t>SEARCULAR aims at reducing the amount of marine litter and microplastic from the most relevant European fishery contributors (demersal trawlers, demersal seiners, tropical tuna purse seiners) and to introduce circular economy practices within the fishing sector value chain including ports, by fostering behavioural change. SEARCULAR will do this b developing/testing/validating 4 closeto-market sustainable and circular solutions (TRL7-9). Three of the solutions are related to the use of more sustainable materials as alternatives to the traditional non-circular plastic used in fishing gears: Solution1 proposes a dolly rope made of recycled polyamide (rPA) from discarded fishing nets (thus it is focused on circularity and more durable materials), Solution2 is based on certified marinebiodegradable materials for demersal seine ropes (the focus is on less impact gears), Solution3 represents an eco-designed biodegradable drifting Fish Aggregating Devices (dFADs) used by tropical tuna purse seine fishery. And Solution4 proposes an End-of-Life (EOL) fishing gears solution for ports by promoting a replicable management system that enables the pyrolysis of EOL fishing gears for a plastic2plastic application. The 4 solutions will be tested under real conditions: onboard commercial vessels (Solutions 1-3) and for the Basque country region (Solution 4), and they will be validated by stakeholders. Therefore, SEARCULAR solutions eliminate waste generated from fishing gears, circulate materials and regenerate nature.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2539,39 +1951,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0198E3DA-3EC6-47C5-91F1-3AD22BA8CE69</t>
+          <t>0DE8D7DB-A3D2-4CD1-A546-C900E139747A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Reimagining digital research infrastructure in environmental science for a sustainable future</t>
+          <t>A Proactive Approach to the Recovery and Recycling of Photovoltaic Modules</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>Digital research infrastructure (DRI) is revolutionising environmental science, enabling a new data-driven approach for monitoring and modelling that enhances scientific collaboration and decision making. At the same time, these infrastructures are made up of digital technologies that emit carbon across every phase of their lifecycle (i.e., manufacture, use, disposal), causing significant waste and social risks (e.g., harms to international communities from waste exports). A careful balancing act, therefore, lies ahead: the environmental gains achieved through DRI-enabled science must be levelled against its social and environmental costs. How can the crucial scientific progress required to support people and the planet be ensured, whilst also remaining within planetary boundaries? How can DRI systems be designed to achieve this future balance? This project seeks to address these questions, creating a bold initiative that reimagines DRI futures with environmental scientists to increase sustainability across its lifecycle by emphasising sustainable design, reuse, and waste reduction (i.e., circularity). Focusing on land use as a case study to contextualise our research, we will work with stakeholders in the scientific community to build an in depth understanding of the DRI landscape and its complexities; from this, we will add to current systems with new digital tools, data science techniques and innovation processes that maximise the benefits of DRI use in environmental science whilst minimising its detriments. Recognising the need for a cultural shift within the scientific community for these futures to be realised, we have embedded a range of impact and engagement activities to work with, and extend, our powerful network of stakeholder experts and partners, and support the wider DRI and digital technology communities in achieving a more circular and sustainable future. This project offers a crucial first step that is essential in mitigating digital technology's po</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Reimagining digital research infrastructure and building digital tools/data-science for its sustainability; object is the digital infrastructure. Env Sci(e-waste/circularity) and Social(STS/culture) near-equal</t>
-        </is>
-      </c>
+          <t>Current recycling practices for Photovoltaic (PV) waste modules are unrefined and recover low volume and low value materials. To be economical and sustainable the recycling of PV waste needs to efficiently recover all of the material constituents at a quality suitable for the reuse in new PVs, with minimal impact. APOLLO will create a circular approach to link legacy recycling, future production and future recycling. A pilot line will be demonstrated and used to process an input of 40 tonnes of PV waste which will be recycled, resulting in enough reclaimed materials for 1 tonne of remanufactured silicon and 30 exemplar PV modules. Incoming modules will be streamed by glass composition, enabling batch recovery of high-quality glass, to be used for new solar-grade glass. A novel continuous ‘sonification’ technique, (ultrasonically excited etchant) will rapidly separate silicon, silver, copper and other metals in a sequence along a pipe-based process. Used liquid etchants will be recycled in a closed loop resulting in low waste, small footprint. Further, recovered silicon will be refined to a purity suitable for new PV-grade ingot growth. The objective isto deliver purified silicon with a minimum purity of 99.9999%. Multiple innovations increase the percentage weight recovery from 18% to 93%. APOLLO will prove the suitability of the recycled silicon by growing new ingots, manufacturing solar cells and then new PV modules. 20 PERC-based modules, 10 Tandem modules and 30sqm of single junction perovskite cells will be made. These modules will incorporate new designs, materials and manufacturing methods, and be designed for disassembly and recycling. Blockchain-based Digital Product Passports (DPPs) for PV will be designed and implemented as well as an online marketplace for reused, remanufactured and/or recycled PV components. DPPs provide secure and trustworthy data for the life of the product and aid recycling by supplying material, hazards and history on request.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2581,7 +1981,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>53B9CA1E-90D1-4104-91DE-488B4EEB562C</t>
+          <t>129207AC-761F-4FAF-8B49-6B2CC7C939B4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2591,29 +1991,17 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>Peat-Free+ Recycling horticultural cropping substrates in a circular economy</t>
+          <t>De Montfort University and Generation Phoenix Limited (AKT3) 2024</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>This feasibility study will enable peat-free production of mushrooms and leafy salads by recycling plant-based substrates from other sectors (including anaerobic digestion, soft fruit and mushrooms). The main technical challenges in recycling peat-free organic materials for these specialist sectors are quality, consistency, crop timing and nutrient balance. This project will help to meet the DEFRA target of phasing out peat from UK horticulture. Currently exemptions are proposed for mushroom growing and salad propagation where no peat-free substrates exist on the market. By delivering a circular economy solution we will also contribute to achieving net zero emissions. The project team conducting the work includes leading growers, scientists and substrate processing experts.</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Agricultural and Biological Sciences</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Peat-free horticultural production of mushrooms/salads via recycled substrates; crop production/horticulture (timing, nutrient balance). Env Sci(substrate recycling) considered</t>
-        </is>
-      </c>
+          <t>This project, a collaboration between Generation Phoenix and De Montfort University, aims to transform post-consumer fashion leather waste into high-quality materials through advanced fibre characterisation and processing techniques. By recycling post-consumer leather, the initiative reduces landfill impact, promotes fashion circularity, and meets market demand for sustainable circular fashion materials.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2623,39 +2011,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>345A970C-1EF0-4010-AEF1-16CCA01FE456</t>
+          <t>1B6346D6-81E0-4DFE-B27E-F302F98C16A2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>Staffordshire University and ATP Industries Group Limited</t>
+          <t>FIREFLY</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>To establish an holistic test development environment enabling design engineers to create and end users to execute test procedures on leading-edge automotive powertrain management systems for remanufacture.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Test-development environment and test procedures for automotive powertrain management systems for remanufacture; systems/automotive engineering. Thin; CS(test software) considered</t>
-        </is>
-      </c>
+          <t>The FIREFLY project rises to the sustainable evolution of the catalyst-based chemical industry, towards its electrification and reduced third-party dependence on metals and fossil energy. The controversial sustainability challenges and opportunities in catalysts recycling/ production and catalyzed chemical processes motivated the synergy of 16 partners proposing the FIREFLY concept, relying on the development of: i) Electro-driven technologies for metal recycling from spent, waste, and off-specification catalysts available in Europe —including a modelling, optimization, and engineering approach; ii) Efficient integration of renewable electricity; iii) A digital tool for predictive decision-making; iv) Production of (electro)catalysts for innovative (electro)chemical processes that overcome traditional production associated with high operating conditions, greenhouse gas emissions, and lack of circularity. The 48-month project foresees 3 stages: i) The technologies involved in the concept will be developed to TRL4, accompanied by an integrated sustainability assessment that will support the selection of the most promising technology routes based on their environmental and techno-economic performance. ii) The selected flowsheets will form the FIREFLY process, in a small-scale pilot. They will be demonstrated at TRL6 in the predictive, RES powered, and flexible production of new metal-based (electro)catalysts from secondary resources as well as in the application of these outputs in innovative (electro)chemical processes of selected chemicals: ammonia and hydrogen peroxide (with current environmental and operational concerns), depolymerization of lignin and biomass processing for bio-based chemicals (in support of defossilization of the chemical industry). iii) The activities and results will be effectively communicated, disseminated, and exploited to a wide set of stakeholders.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2665,7 +2041,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2D34D8DB-1A07-49D3-B5EF-0F229F4E79A7</t>
+          <t>A8613C25-D08C-4D9B-9673-AD05C085C9E5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2675,29 +2051,17 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>Combining in vitro peptide display and in vivo directed evolution to search for entirely de novo folds of DNA-binding domains</t>
+          <t>Novel Additives to Enhance the Performance of Low Carbon Cements for a Net Zero Future</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>This project will take recent advances in protein evolution methods to develop entirely novel DNA binding domains as a basis for new synthetic transcription factors in genetic regulation. The development of new-to-nature protein functionality remains a significant challenge even given recent computational advances in protein structure determination. To address this we will take an experimental approach that combines CIS peptide display for the in vitro expression and selection of massive libraries (Patel et al. Protein Engineering, Design &amp; Selection 26, 307-315, 2013), with phage-based in vivo selection (Brodel et al. Nature Communications 7, 13858, 2016), which gives exponential amplification of genetically selectable traits. At 66 amino acids, lambda cro is perhaps the smallest known transcription factor that functions in E. coli, and it can be converted into an activator (Brodel et al. Science Advances 6: eaba2728, 2020). Therefore, providing an unstructured gene sequence coding for 70 - 100 aa, could in principle provide a reasonable starting point for de novo evolution of a transcription factor. The ~1091 - 10130 amino acid combinations seem daunting, but that is also why it is a fascinating question to ask whether the compounding advantages of evolution, which we will employ, will lead to an exponential selection trajectory. The project will take a staged approached to ensure viable progression and development of the techniques during the project. Initially, we will screen large libraries of structured but non-DNA binding sequences based on familiar DNA regulatory elements (e.g. helix-turn-helix), using in vitro CIS display. Subsequently, this will be expanded to create massive libraries of unstructured proteins to screen for novel DNA binding scaffolds. DNA binding domains from these studies will then be developed as transcription factors using further protein engineering and in vivo accelerated evolution using a phage-based microbial gene drive as well as a</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Protein evolution/engineering of de novo DNA-binding domains and synthetic transcription factors; molecular biology/genetics. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>Cement is the 'glue' in concrete, the foundation upon which our modern civilisation is built. However, this comes with a huge environmental cost - cement production generates 8% of global CO 2 emissions, and half of all materials extracted from Earth are used in concrete. Luckily, recently developed low-carbon cements that we are investigating exhibit enhanced properties and reduce CO 2 emissions by &gt;80%, compared to traditional Portland cement (PC), and are made almost entirely from industrial wastes. These cements require superplasticising copolymer dispersants to improve workability and flow characteristics, particularly for ultra-high performance concrete. However, dispersant behaviour differs significantly in each case due to extensive differences between aqueous and solid state chemistry in these cements, compared to PC. New alkali-resistant high-performance dispersants are urgently required for these next- generation low-carbon cements to make them practical for use in large-scale construction applications. In this PhD project we will examine the interactions between organic superplasticisers and inorganic cement particles in these next-generation low-carbon cements, and then use this knowledge to design novel superplasticisers with enhanced performance. We will adopt a new in situ characterisation approach (including surface-specific techniques and both spectroscopic and microstructural characterisation) to investigate the mechanisms and kinetics of organic- inorganic interactions, and their effects on cement performance. We will discover the fundamental processes controlling dispersion, fluidisation and reaction of these next-generation low-carbon cements, and use this knowledge to design, synthesise and test novel superplasticisers with enhanced performance. This will drive implementation and a circular economy, help decarbonise cement production, and help give humanity the best possible chance of mitigating climate change.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2707,39 +2071,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5B712D03-0EE4-4F30-AD5F-04BC8C0ECED7</t>
+          <t>68B2F9AB-ABBB-4937-B978-4958E8F4225E</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>Novel, Sustainable Composite Stone Heating Eco Radiators</t>
+          <t>CHaMP: Circularity in Healthcare Materials Provision</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>To meet the UK Governments commitment to net zero we must move away from using gas and oil to heat homes and commercial space. Our new products can make an important contribution to solving this problem. We are developing a novel sustainable heating product incorporating recycled materials. This project will develop new processes to increase these recycled materials to high percentages without adversely affecting the product's performance. The project will enable the development of a truly circular business model for manufacturing and recycling of this novel product The next stage of development for us, is to increase our recycled materials used in our products from 40% to potentially 95%. This will make our products more appealing to environmentally conscious clients as it adds to their eco life cycle, circular economy product.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Developing a heating product (radiator) and processes to raise recycled-material content; product development/materials processing. Energy(heating application) and recycled-content considered</t>
-        </is>
-      </c>
+          <t xml:space="preserve">CHaMP (Circularity in Healthcare Materials Provision) is a collaboration between Bupa Ltd. and the University of Manchester (UoM). This 3-year project explores circular pathways for the diverse materials enabling healthcare provision, using interdisciplinary methods to unpick opportunities, barriers and unintended consequences for reuse, mechanical recycling and depolymerisation in health clinics, dental practices, and care homes. The project explores material selection, social practice, product segregation, sterilization and quantified sustainability to create actionable circular solutions across Bupa’s 380 dental practices, 80 health clinics, 130 care homes and the Cromwell Hospital. The project builds from an emerging research partnership between the two organisations specifically in efforts to improve the sustainability of healthcare. The proposal has been co-created to both maximise potential impact and explore the fundamental challenges in circularising healthcare materials. Integrating assessments of social practice and life cycle impacts of proposed fates optimises systemic sustainability. This new way of assessing the intersections between economic efficiency, climate change, material selection and waste management is to be explored in the medical sector for the first time, building on strong motivation in the sector for sustainable change. While the scale and harm of material consumption in the healthcare sector has been defined, the consequences of reduced consumption, reuse models and alternative materials is hidden. This partnership will explore the fundamental engineering and material science questions that will enable authentic reduction in environmental footprints in material provision in healthcare settings. Changes in material selection and segregation, for both reuse and recycling, in clinical settings where alignment with patient outcomes and logistical limitations are paramount, are challenging and require fundamental research to understand and </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2749,39 +2101,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C0B245C8-0757-497E-9D82-340F4FC47C74</t>
+          <t>48DF4436-32DA-408C-8116-6966E06E30B2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>AHRC</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>ReMake Glasgow Extension</t>
+          <t>The photobook as a physical site for a regenerative relationship with the environment</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>The ReMake Glasgow Extension project builds on the success of the original ReMake Glasgow initiative, which established a world-class Remake Hub in the Glasgow City Region. This project will expand and scale the impact of circular manufacturing by engaging with businesses across multiple sectors to drive sustainable production, economic growth, and environmental benefits. Circular manufacturing is key to achieving net-zero goals, reducing waste, and retaining value in high-integrity sectors such as aerospace, energy, and construction. The ReMake Glasgow Extension will deliver five key work packages: 1. Circular Manufacturing -- Repair, Remanufacture, Recycle Engage businesses to implement circular economy principles. Develop new remanufacturing processes to address industrial challenges. Facilitate co-investment in sustainable technology adoption. 1. Digital Product Passport (DPP) -- Compliance and Implementation Deploy functional and scalable DPP systems with companies. Extend DPP adoption to sectors such as construction and textiles. 1. Skills -- CPD, Culture, and Workforce Reskilling Deliver CPD training for businesses to adopt circular manufacturing practices. Develop new in-person training courses to support industry transformation. 1. Design for Circularity Support companies in implementing Design for ReX (remanufacture, repair, reuse) principles. Contribute to Glasgow's Circular Economy Route Map by embedding sustainable design practices. 1. Exploitation, Commercialisation, and Investment Support commercialisation opportunities for circular economy solutions. Engage in Glasgow's investment ecosystem to enable long-term sustainability of circular initiatives. The expected impact of the project includes: Engaging businesses in circular economy adoption. Directly supporting companies in transitioning to circular manufacturing. Delivering CPD training to companies, equipping the workforce with essential skills. Reducing emissions, contributing to Glasgow's net-ze</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Business engagement, adoption, DPP, commercialisation and skills to scale circular manufacturing; largely business/economic development + skills. Social(skills) and Engineering(remanufacturing) considered</t>
-        </is>
-      </c>
+          <t>This practice-based research project will set out to explore regenerative design principles within the making of photographic work and photobooks. The research will situate this subject within a wider framework of philosophical and environmental thinking, and of the physical making of books. The project will involve the creation of my own small scale publishing projects, as well as the collaborative development of a book with an industry partner to explore how these ideas can be taken forwards within a larger scale commercial publishing framework. Sustainability has been at the forefront of my research and artistic practice for more than 6 years. Sustainable book making is not just about selecting the right paper or printer, although of course these choices are important. It's about relearning the way that we think about the process from start to finish. It's about what you put in your backpack when you go out into the world, what camera you take with you, how the photographs made will find their way off the memory card and into the physical world. We need to radically rethink all of these points in the creation and dissemination of photographic work. And this need to rethink is only becoming more and more urgent as the photobook publishing world continues to grow. My own photographic work is made in the landscape: on foot, carrying my own shelter, and leaving no trace. I walk in the landscape for up to a week at a time, alone and self-sufficient, open to what may come from these encounters. These experiences have fundamentally changed my relationship with the world and with people and have made me more conscious than ever of the need to ask questions about how science and society have shaped our rules of engagement with the non-human world. When I began to make books of this work in 2016, I began to question how I could continue this dialogue with the environment. There is a conscious smallness to my own publishing both in the physical size of the books and the edi</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2791,39 +2131,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>D336D2C2-2806-4CA1-82E1-21C4B05034C0</t>
+          <t>9F9692C5-08BA-41B0-8FBA-1F2F9C2150B7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Sustainable Sails: Novel recycling of carbon composites</t>
+          <t>Green Infrastructure: understanding its role in mitigating current and future flood risk in urban areas</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>Sustainable Sailing is a marine industry R&amp;D company, with a track record of innovation to address the grand challenges of the industry. In this project the challenge of recycling carbon fibre composites is targeted, specifically sails. Modern carbon sails are built from high technology carbon fibre composites, however like most composites, recycling and reuse of these sails once they have reached the end of their useful life are not currently available for sailors across the UK. With over 1.5 million yachts and 1 million dinghies globally, this source of waste is one which is both growing and is not being addressed within the industry. Working with B&amp;M Longworth, the Advanced Materials Research Centre, Farapack polymers and Precision Yachting, Sustainable Sailing is building upon existing collaboration to scale-up their recycling process. They will do this by going from 0.5kg of sails recycled to 50kg in the next 6 months. Along the way, this collaboration will understand the effects of their recycling process upon the different components of the sails. This will include analysis of the fibres to maximise their useability for future projects, including development of technologies to improve Sustainable Sailing's existing Chlorofoils product line. Furthermore, their existing work suggests that some other components of the recycled sail can also be reused, so this project will be using advances in industrial and green chemistry the return these components back other products. This project aims to "close the loop" of high-performance carbon fibre composites, by returning all the components that make up these sails into other products. This will help the UK and the marine industry realise the "circular economy" in which all waste products can be reused and returned into circulation. By focusing upon sails this project will demonstrate that it is possible to recycle other carbon fibre composites, reducing the environmental impact of carbon fibre production and eliminati</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Scaling a recycling process for end-of-life carbon-fibre composite sails to recover/reuse components; recycling/resource recovery. Chem Eng/Materials(fibre analysis) considered</t>
-        </is>
-      </c>
+          <t>In England alone, 3.2 million households are located in areas at risk of surface water flooding, with annual damages exceeding £300 million. It is projected that this cost of associated damage could increase by 40% by the 2050s. Green infrastructure (GI) can provide a means of reducing the amount of water entering drainage systems via infiltration, interception, transpiration and providing both temporary and more longer-term storage. Evidence is needed to understand how, where and when GI aids flood risk mitigation over time and space. This project will consider the following research questions: How can we better represent the structure and function of green infrastructure in our flood risk impact models? How can we design green infrastructure into the existing urban fabric to maximise benefits and reduce costs? How effective will green infrastructure be as a flood mitigation measure under future climate? This project will conduct a number of controlled experiments at the National Green Infrastructure Facility and at locations of different GI types across the city. Observations will then be used to inform a reliable and robust physically-based infiltration component in CityCAT, a hydrodynamic model capable of simulating flood risk, and the role of GI in mitigating that risk at high resolutions over large spatial domains. Outcomes from this project will include improved understanding of GI performance; assess long-term performance and costs of GI, including management and maintenance; and aid design of future GI strategies to mitigate climate-induced flood risk in urban areas.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2833,39 +2161,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CCC0FCB9-882E-4F70-9EB0-1E1C721AF8DC</t>
+          <t>7ED1F7C3-1BC3-460B-A3A5-CFC7DD507E60</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>Ceramic nanofiltration: Creating a resilient future for drinking water supply</t>
+          <t>Modular Laser Sources For Sustainable Production Of Short Personalized Production Series (WAVETAILOR)</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>Polymeric nanofiltration membranes are used for organics removal from raw water during drinking water production. A highly selective separation is fostered by accommodating a strict pore size which can also improve continuity in downstream asset operation (e.g. disinfection), therefore enhancing resilience of drinking water supply. However, current polymeric membranes exhibit several challenges. Ceramic nanofiltration (C-NF) is an emerging technology that introduces a thin separation layer to foster selectivity without significant loss to permeability. Several advantages are proposed. While these unique properties can foster a radical shift in the economics, operability and resilience of nanofiltration, C-NF has yet to be developed explicitly for drinking water treatment, where these separation attributes must be challenged to evidence their translatability to this industrial context. This project therefore seeks to evaluate C-NF as a next generation technology for the production of drinking water from organic rich raw waters.</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Ceramic nanofiltration membrane separation for drinking-water production (selectivity/permeability); separation process. Env Sci(water treatment) and Materials(ceramic membrane) near-equal</t>
-        </is>
-      </c>
+          <t>WAVETAILOR focuses two industrial scenarios which are related to the complex multi-material component and assembly. The first one is Directed Energy Deposition of a multimaterial leading edge for a hypersonic hydrogen-driven airplane, while the second relates to the Powder Bed Fusion of complex multi-material assembly of a drone for urban delivery. The challenges in both cases are related with zero defect manufacturing, sustainability and first-time-right manufacturing. WAVETAILOR aims to solve the high-precision in complex material structure manufacturing, the disassembly, reuse and recycling of components, while reducing the environmental footprint of both manufacturing process and the components itself. To achieve this, three main pillars are developed in the project: 1) flexible energy efficient photonic setup based on modular diode-based laser source and multi-wavelength optics; 2) full reconfigurability of this setup, to use minimal energy and material resources in manufacturing of two use cases and 3) ZDM and ZDW strategies at assembly level controlling the compliability of complex multimaterial products at machine level, shop floor level and delocalized manufacturing chain level. The latter pillar will be based on digital sibling (shop floor level) and twin (cloud level) for automatic assessment of component/ assembly design for circularity; first-time right process planning using synthetic legacy data and ZDM/ZDW based on real time process and post-process monitoring. When the WAVETAILOR objectives are achieved, the manufacturing process of the two use cases will have spent 200MWh of energy less, 923kg of waste less, while the production costs are going to be 50-65% lower. In order to prove this a dedicated sustainability study is provided along the project.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2875,39 +2191,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>D1EAAECC-5F35-46DF-A139-9A830643E2D6</t>
+          <t>368B27E8-A8E4-45CB-B0CE-05AA8EBC3624</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>Bioremediation of elastane within the textile industry</t>
+          <t>Design of Battery Packs for Reuse, Remanufacture and Recycling</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>In 2019, the global textile market reached 111 million tons (mt), with less than 1% coming from textile-to-textile recycling (Exchange, 2020). Synthetic fibres and polymer blends are often used, with 63% of the current market being comprised of petroleum-based virgin fibres (Borneman, 2015). Recycling of these polymer blends and petroleum-based fibres is difficult, and lack of component recovery means a large number of these materials end up in landfills or incinerators. Reaching a circular textile economy by recovering individual components of these non-renewable polymer blends, with emphasis on achieving the same properties (e.g., thermal and tensile strength) as the respective starting materials, is imperative for sustainability and reduction of environmental impact (Jönsson et al., 2021). Elastane, a poly(urethane-urea) copolymer, is often used in textile blends to increase elasticity and tensile strength (with e.g., denim, cotton, or polyamide) (AK and Bansal, 2018; Dhouib, 2006). Approximately 20% of recyclable textile waste contains elastane (Jönsson et al., 2021). Current separation methods fail to fully separate elastane for reprocessing. For example, melt filtration and melt spinning are not sufficient to separate elastane from polyamide (PA), as the elastane degrades and passes through filters. Also, mechanical separation results in elastane disappearing from the tearing machine in PA fabric with high elastane content (~22%), and fails to fully separate PA fabric with low elastane content (~5%). Therefore, reprocessing cannot continue as elastane acts as a contaminant (Jönsson et al., 2021). A method for separating elastane and achieving the same properties as the virgin fibre does not currently exist. The aim of this research is to develop a method to enzymatically degrade elastane for the de-polymerisation of textiles, whilst investigating chemical/thermal pre-treatment, and optimising biotransformation conditions affecting conversion yields - for futur</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Developing/optimising an enzymatic biotransformation to depolymerise elastane for textile recycling; bioprocessing. Env Sci(textile recycling) and BGMB(enzymatic) are strong alternatives</t>
-        </is>
-      </c>
+          <t>With the growing concern over global warming and pollution from vehicle emissions, regulations and government policies are becoming more stringent. In line with this trend, more and more zero emission and low emission vehicles are being introduced in the market across all segments. In the passenger car segment, most established OEMs are already offering several electric and hybrid models, with the commercial vehicle segment also following the trend. Lithium-ion batteries are almost exclusively used as electrical energy storage system for these electric and hybrid vehicles. With the accelerated growth in uptake of zero and low emission vehicles, a large quantity of lithium-ion batteries will be introduced in the market. At the vehicle end of life, there will be a significant waste management challenge as lithium-ion batteries pose serious environmental risks when used as landfill or exposed to ground water. Consequently, there will be a growing demand of automotive battery pack design which will enables sustainable end of life processes - reuse, remanufacture and recycling. In this project, existing battery pack design processes will be assessed in terms of suitability for end of life processes. Based on this assessment new battery pack design guidelines will be developed to facilitate efficient reuse, remanufacture and recycling processes. Generalised guidelines for sustainable battery pack design using other battery chemistries (e.g. solid state) will also be developed to address potential future technological shifts. Using an assessment metric a battery pack design, an end of life impact assessment tool will be developed to evaluate the suitability of any given design in terms of recycle, reuse and remanufacturing. The project outcomes will enable OEMs to use these already developed sustainable battery pack design process in their product development cycle while meeting end of life battery packs management legislative requirements. This project will help the UK to</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2917,39 +2221,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DC62D46B-AB2E-4110-ABED-E1ABE7D700A7</t>
+          <t>9C9AEC62-ECBF-402A-882C-2FA7FD7FD35A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>RePolyWise: Selective Chemical Recycling of Plastic to C3 molecules</t>
+          <t>CircEUlar (Developing circular pathways for a EU low-carbon transition)</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>RePolyWise: Revolutionizing Waste Recycling RePolyWise is on a mission to revolutionize waste recycling by introducing an innovative method for atomic recycling. Founded by two leading researchers from the Chemistry Department at the University of Oxford, RePolyWise is dedicated to addressing the challenges of plastic waste recycling in the UK, leveraging their extensive expertise in chemical processing. At the core of RePolyWise's pioneering work is a groundbreaking process that enables the recycling of polyolefin plastics atomically back to their monomers. This breakthrough offers a transformative solution, paving the way for a fully circular plastics economy. RePolyWise's vision for recycling is set to redefine the future of plastic waste management, promoting sustainability, and ushering in a circular economy for plastics not only in the UK but on a global scale. With their unwavering commitment to innovation and sustainability, RePolyWise is poised to make a profound impact in the field of waste recycling.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Chemical/atomic recycling of polyolefins back to monomers (C3), by chemists; molecular-level conversion. Thin/promotional; Chem Eng(process) and Env Sci(plastic waste) alternatives</t>
-        </is>
-      </c>
+          <t>The CircEUlar project aims to understand the dynamics and levers for societal transformation towards a net-zero emission circular economy. CircEUlar will develop new modelling approaches for analysing circularity from a systems perspective accounting for: 1) dematerialisation and the transition to a service-based economy to limit material stock growth; 2) lifetime extension of material stocks through repair, maintenance, reuse; 3) waste treatment and material recycling. CircEUlar’s approach will be comprehensive, combining new data and modelling of economy-wide material stocks and flows, greenhouse gas (GHG) emissions, and industrial value chains across interlinked sectors, with deep-dive analysis of mobility and buildings as material-intensive demand sectors. These two focus areas have large material stocks, potential for circular transformation, and strong dependence on both circular consumption and production practices. CircEUlar will also focus on digitalisation as a potential enabler of dematerialisation and supply chain circularity. CircEUlar integrates multiple fields of data, knowledge and expertise including: 1) empirical analysis of firm and consumer propensities towards circular economy measures; 2) industry input on process-level innovations and circular economy business models; 3) modelling analysis of economy-wide material stocks and flows, and policy levers of change towards societal transformation. CircEUlar will integrate new insights on circular economy potentials and impacts into EU and global modelling frameworks for: 1) analysing alternative pathways to net-zero GHG emissions; 2) testing effective policy levers for both circular production and consumption. 3) assessing outcomes for climate, environment, economy and society, in line with European Green Deal objectives.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2959,39 +2251,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4772326E-AB28-46AC-8F72-939B288C63DF</t>
+          <t>02E19F87-053A-48A1-AB30-7500D22D373E</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>Sustainability &amp; Safety in Second Life Batteries</t>
+          <t>Digitally-enhanced multi-level solution for smart human-centric remanufacturing</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>Due to the growing demand in Energy Storage Systems (ESS) in Europe, Chimera Energy's aim through this feasibility study to is to learn and establish a route to market that will have a considerable impact to the circular economy. Besides the UK, Germany and Italy have a considerable market share within this sector, so understanding the market policies and needs in these territories would be advantageous in delivering a crucial solution without delay. Time is of the essence. Chimera Energy proposes packs constructed with proprietary weld-free technology designed for re-manufacture and second-life potential ensuring unrivalled: Scalability (flexibility) Performance Safety Longevity (endurance) Cost effective solution Currently working on projects addressing the ATV, Forklift and Marine markets, Chimera Energy's focus is to provide a unique and innovative solution for the Energy Storage sector and more importantly, work towards a net-zero future globally.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Feasibility study to establish route-to-market and assess market policies for second-life battery energy storage; market/business focus. Energy/Engineering(battery packs) considered</t>
-        </is>
-      </c>
+          <t>The European remanufacturing industry is crucial for the sustainable transition of Europe, thanks to the savings in energy, materials and functionality that is guaranteed by the process. In fact, the socio- economic benefits of remanufacturing, in terms of number of workers, skills development and technological uptake, are as impactful as the environmental benefits. However, to future-proof the European remanufacturing industry and increase its competitiveness, the obstacles facing the human worker need to be addressed as a matter of strategic urgency. Currently, established remanufacturing sectors recognized the barriers in the limited automation, poor human inclusion, lack of traceability and restricted use of digitalization. Hence, rEUman aims at developing and demonstrating a novel paradigm of human-centric remanufacturing approach for the European industry; acting at factory and value-chain levels. At factory level, the main industrial need is to guarantee high regeneration rates of the remanufactured products and to achieve traceability of the remanufacturing process-chain. While at value-chain level, the main industrial need is to guarantee stability in terms of volume and quality of the post-use products. rEUman shall demonstrate the new remanufacturing paradigm, which is intrinsically human-safe, target-driven in regeneration and certification, flexible while facing variability in post-use parts, robust and replicable to new circular business cases. To that end, rEUman addresses the call topic by (i) developing cutting edge remanufacturing approaches (factory level) and integrating them into the value-chain , (ii) demonstrating functional retention in three sectors (Automotive, Home appliances and Optoelectronics), (iii) introducing traceability in remanufacturing by implementing the first remanufacturing-centred DPP, (iv) considering operation and economic viability by showcasing complete business cases coupled with designed training material.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3001,39 +2281,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>83517E91-F20C-42D2-86FE-030CDDD0793E</t>
+          <t>13A67640-4E0D-4048-A747-12C3D72608B3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>LINK – Creating a digital direct connection between owners and buyers of salvaged construction material (Circular Economy)</t>
+          <t>Nanomechanical Hardware Platforms for Edge Computing</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>This project (LINK) will develop a digital system to connect end-user buyers directly to salvage material owners (usually construction/renovation/demolition/deconstruction sites). This will minimize logistics costs and thereby reduce price and increase usage. LINK will include Machine learning-enabled Rapid listing mobile app (Rambo): Extender: digital extension that allows SC2M connect their customer bases directly to salvage construction material owners (SCMOs) Connector: Online commercial platform that connects buyers directly SCMOs Material reuse data to support green credentials(G-cert)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Building a digital system/marketplace (ML listing app, online commercial platform) to connect salvage-material owners and buyers; work is the platform. Business(marketplace) considered</t>
-        </is>
-      </c>
+          <t>Challenging operating environments are common across many important internet of things (IoT) applications related to enterprises and the circular economy, including automotive, aerospace, industrial and power generation. However, conventional electronics are not suitable for operation in challenging and harsh environments, e.g. at high temperatures. i-EDGE establishes an enabling nanoelectromechanical (NEM) switch technology platform for IoT edge devices operating under demanding conditions, i.e. high temperature (&lt;300 °C) and/or high-radiation (&lt;1 Mrad), uses zero standby power, non-volatile memory and has low compute performance requirements. i-EDGE will realize a proof-of-concept demonstrator of a NEM “system-on-chip” (SoC) IoT node with an FPGA, non-volatile memory, and a temperature sensor, powered by a high-temperature capacitor bank, with a wireless power receiver for trickle charging the capacitor, and a simple data transceiver and sensor readout to interface to the on-chip FPGA and non-volatile memory. The FPGA fabric will be based on the NEM switch technology for digital logic, and integrated with a non-volatile memory array, analog utility blocks for wireless power transfer, data exchange and sensor readout. We will develop a NEM physical design kit (PDK) for design and circuit simulation, which will facilitate broad usage by application engineers. The technology and design flow will be demonstrated with a condition monitoring application, that has been developed for industrial IoT processes. In several previous EU and national projects, our technology has matured to TRL3 and i-EDGE will bring it to TRL5. The i-EDGE consortium has all expertise to establish a full supply chain, from basic logic and memory cell design to Systems-on-Chip and a migration path to pilot manufacturing of the NEM technology in Europe. Thus, i-EDGE will help position the EU at the cutting edge of chip design and manufacturing capabilities, as envisaged by the EU Chips Act.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3043,39 +2311,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1B19C2E4-EBAE-4F14-9277-DF857207913E</t>
+          <t>3AA9F9E4-8EEA-427C-A5BD-BA526DD19161</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>APC</t>
+          <t>SPF</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>UK-RELOAD: Economic feasibility for setting up a recycled graphite anode plant in UK</t>
+          <t>Integrated CD&amp;E waste processing and unfired GeoBrick manufacturing: upscaling a novel technology into a circular-economy business model</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>UK-RELOAD, is an initiative by Talga Anode UK Ltd, aiming to establish an innovative lithium ion battery anode manufacturing plant in the UK. Graphite, an active anode material, is the single most abundant material in lithium ion batteries. It is currently almost exclusively imported to the UK from Asia, predominantly China. Graphite is recognised as both a critical as well as a strategic raw material. This project focuses on repurposing recycled graphite from used batteries and battery production scrap back into battery use. The project builds on the company's knowledge of manufacturing pristine, natural graphite anode material as well as on a previous successful technical feasibility study for the repurposing of recycled graphite. The project is focused on establishing the commercial viability of the product manufacturing in the UK. The project deliverables include process engineering design, process scaleup trials for customer validation, financial model, comprehensive project risk analysis and an execution plan. This innovative project supports circular economy by reusing a valuable critical raw material, graphite, sourced from UK's battery recycling businesses and marketed into UK's battery manufacturing. It also enhances the sustainability of battery manufacturing through low carbon footprint manufacturing processes and by minimizing waste in battery production. Additionally it provides a crucial solution towards achieving regulatory recycled content targets for the electric vehicle value chain in Europe.</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Economic/commercial feasibility of a recycled-graphite anode plant (financial model, risk, execution plan); firm-level viability. Chem Eng(process design/scale-up) and Env Sci(graphite recycling) considered</t>
-        </is>
-      </c>
+          <t xml:space="preserve">This industrial research project aims to demonstrate the ability to produce a valuable product from currently unused waste; generating a more energy-efficient product with at least a 45% lower carbon footprint compared with existing products. The technology will open up new sources of revenue for CCC and reduce energy usage and CO2 emissions from brick and concrete production. Enabling the waste management industry's waste streams to be used as a raw material for a new product for brick and block manufacturers has the potential to divert a significant volume of material from landfill sites and breathe new life into the recovery options through an energy-efficient way. The development of an alkali-activated GeoBrick with patented technology, where the combination of alternative calcium-silicate-rich materials and CFC that do not require burning, would circumvent current limitations and enable a technological breakthrough in the construction sector. In this project, CCC will scale up the patented technology in their CD&amp;E recycling plant to achieve a production capacity of around 200 bricks/day. The manufactured brick will be used to build a demonstration structure to investigate their performance. The new bricks' mechanical and environmental properties will be also investigated by third-party test facilities as required by the building regulator. CCC Ltd has over 37 years of experience in collecting and recycling CD&amp;E waste and marketing recycled aggregate. CCC's innovative approach will disrupt the construction sector by providing market-ready products using LJMU technology and converting the CFC wastes with validated properties as set by the building regulators. Boosting the consumption of local waste-based resources is one of the most sustainable and ethical practices that lower emissions and meet the principles of circular economy, making other industries greener. This project is highly innovative, ambitious, and pioneering, addressing key environmental and waste </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3085,7 +2341,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FAD2EFE7-ABAD-4C71-98D6-F884E2E822C0</t>
+          <t>24C8BB6E-5931-4AB3-8925-260562ACAB27</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3095,29 +2351,17 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>Circular Economy Based Uninterruptible Power Supply Battery System for Greener and Sustainable Remote Working</t>
+          <t>Mainstreaming Biopolymers on Teesside</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>The internet's energy and carbon footprints are estimated to exceed those of air travel with around 1.7 billion tonnes of greenhouse gas emissions per year produced in the manufacture and running of digital technologies (climatecare.org and BBC 2020). Computers and network hardware such as data centres must be powered and cooled drawing electricity from non-renewable fuel sources. During the height of COVID19 lockdown, UK's internet usage surges to record levels. Time spent online due to working from home is up by 67% compared with pre-lockdown usage (Opinium April 2020 survey). Remote online work has significantly increased the energy and associated carbon footprint that power the internet and the equipment that support it such as the data centres and server networks at companies and offices that enable remote working. A promising solution to address this problem is to transform an idle backup energy storage device into an asset with an investment return and carbon savings potential. UPS - Uninterruptible Power Supply - systems are commonly used in commercial buildings and industries to protect hardware such as computers, data centers, telecommunication equipment or other electrical equipment in case there are any unexpected power disruptions that could cause injuries, fatalities, serious business disruption or data loss. UPS can be used as energy storage systems additionally to their primary use in order to generate additional benefits to their users. Alp has developed a utility scale smart battery system called BRIC which reduces total system cost by over 30% by using smarter electronics and AI. With environmental sustainability and circular economy principles in mind, BRIC is designed and tested to utilize new or second-life cells and substantially increase useful life. Our game changing innovations accomplish this by an electronic design, AI and software that proactively monitor and manage the battery at the individual cell level to anticipate issues before the</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Smart battery-management system (electronics + AI, cell-level monitoring) for UPS/energy storage; electrical/electronic advance, energy is the setting. Energy(storage) and CS(AI) considered</t>
-        </is>
-      </c>
+          <t>Climate change, net zero and the biodiversity crisis.....Chestnut Bio - the trading name of Chestnut Natural Capital Limited is creating materials and processing technology as well as being very self aware to the circular economy. Legislation and public opinion is driving change in the world of plastic. Nature based solutions require nature based materials. Take tree planting as an example; most tree planting in the UK is being increasingly impacted from high levels of plant failure due to drought, unseasonable weather and or a shortage of microbes and fertility to get the best level of plant productivity and survival. Chemical fertilisers are demonstrated to have a negative impact on natural microbial activity in the soil, slowly degrading the soil over time, requiring more and more chemical additives to support crop yields. The innovation is a significant upgrade in how seedlings are treated to get full productivity with multiple economic, environmental and societal outcomes. Replacing non-biodegradable fossil-based plastics is a key aim for CNC's (Chestnut Natural Capital Ltd.'s) work; the company has been working on their novel blends as direct drop-in replacements for existing oil-based plastics, using existing manufacturing technologies. The development of the novel encapsulation will enable wider plastic-replacement, while also contributing to soil and plant health through additional functionality. The mainstreaming of regenerative agriculture in the UK has created a commercial opportunity to raise productivity by looking after soils using nature-based solutions. CNC's brand Chestnut Bio will use the unique material developed and protected by patent to create a powder encapsulation system, from which several products for agriculture/forestry/horticulture/top fruit will be created. The initial product will be a solid capsule system impregnated with organic soil enhancers made from a natural blend of microbes and micronutrients and drought resistant powder - Aq</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3127,7 +2371,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8A327C14-27C8-4FDC-9258-BBA7CC330456</t>
+          <t>51644E2F-BB93-44EF-9B6B-BC9DD022DC38</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3137,29 +2381,17 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>Scaling Feed-Grade Lanolin</t>
+          <t>Feasibility Study on Spray Drying vs. Heat Drying for Porphyridium purpureum culture/biomass Preservation and Valorisation</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>Welsh Wool into Premium Feed Ingredients The Challenge Welsh farmers often pay more for shearing than they receive for shorn wool, a significant business problem. Current wool processing wastes valuable lanolin as expensive sludge, costing the industry £19.2 million annually (Standard Wool, 2025). Meanwhile, the UK imports £90 million worth of soy and palm oil for livestock feed annually, driving deforestation and creating supply chain vulnerability that threatens food security (DEFRA 2022). Our Innovation LanoTech has developed breakthrough extraction methods that recover significantly more grease from wool than the industry standard---a 4x productivity improvement. This project refines this into feed-grade lanolin with higher energy density than soy, creating three commercial products from one waste stream: feed-grade lanolin, cholesterol for aquaculture, and cleaned wool. Our business model ensures the value of this innovation is returned to farmers within Mid and North Wales. Impact for Mid and North Wales Economic Regeneration: Our sourcing model targets often unsold wool and improves rural cash flow. This creates immediate economic benefit for upland farmers who rely more heavily on sheep income than lowland counterparts. Strategic Job Creation: Wool processing will create 50+ positions across engineering, chemisty and operations. These facilities target rural Mid and North Wales areas, breathing new economic life into communities. Environmental Leadership: Each tonne of Welsh lanolin that replaces imported soy oil, may reduce carbon emissions by up to 3-4 tonnes CO2e and supports Wales' Net Zero commitments. Our innovation creates a circular agricultural economy; farmers supply wool and eventually purchase the lanolin-based feed, eliminating waste while strengthening local supply chains. Proven R&amp;D Journey This project builds on validated progression through three consecutive R&amp;D phases. Innovate UK New Innovators established lanolin feed feasibility, SBRI We</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Extraction/refining process to recover lanolin from wool into feed-grade products; separation/processing is the core innovation. Agricultural(animal feed) and Business(model) considered</t>
-        </is>
-      </c>
+          <t>This feasibility study will explore how to dry UK-grown microalgae in a way that saves energy while maintaining the quality of valuable natural compounds. The project will compare two drying methods --- spray drying and conventional heat drying --- to find the most efficient and sustainable approach for future large-scale use in the UK's growing bio-based industries. Drying is one of the most important and energy-intensive steps in turning microalgae into useful products. Traditional low-heat drying is affordable and simple but can damage sensitive ingredients such as natural pigments, proteins, and oils that give microalgae their value. Spray drying, although typically more energy demanding, can better preserve these beneficial compounds when the process is carefully optimised. This project will test both approaches under controlled laboratory and pilot conditions to measure how well they perform in terms of energy use, quality preservation, and cost-effectiveness. By analysing the dried material, the team will assess how each drying method affects the composition and functionality of key ingredients. The study will also evaluate which process delivers the best results for future scale-up and commercial use. The goal is to generate clear, evidence-based guidance that will help UK companies make informed decisions when developing new algae-based bioproducts, such as food ingredients, natural colourants, cosmetics, and sustainable materials. Swansea University will lead the cultivation and preparation of high-quality microalgae, ensuring consistent biomass for testing. CleoburyPM/Aberystwyth University will focus on improving and comparing the two drying techniques, drawing on its expertise in downstream processing. Together, the partners will analyse the results to determine which drying route offers the best balance of efficiency, sustainability, and product value. The expected outcomes include comparative data on energy use and performance, evidence of how well va</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3169,7 +2401,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C710DBBF-A110-4211-8E91-570A2BA41CB9</t>
+          <t>252E176E-C0BE-498D-896D-B80C6182F38D</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3179,29 +2411,17 @@
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>Carbon Lifecycle Evaluation for Authority Reviews (CLEAR)</t>
+          <t>High Efficiency Precious Metals Recovery from E-waste</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>The UK construction sector is one of the largest contributors to carbon emissions and waste. Local planning authorities (LPAs) play a crucial role in reducing these impacts, as planning decisions determine what is built, how, and with what materials. However, despite ambitious policies such as the London Plan's Whole Life Carbon Assessments (WLCAs) and Circular Economy Statements, Scotland's NPF4, and emerging retrofit-first requirements, many LPAs lack the digital infrastructure and expertise needed to enforce compliance. The CLEAR project (Carbon Lifecycle Evaluation for Authority Reviews) will demonstrate how PACER --- the UK's first digital WLCA review platform --- can provide LPAs with the tools and evidence required to enforce carbon and resource efficiency policies. CLEAR emphasises clarity and transparency in WLCA compliance, enabling officers to move from manual, fragmented processes (such as Excel spreadsheets and static PDFs) to an automated, consistent, and transparent digital review process. Running from November 2025 to March 2026, the project will be delivered by Preoptima Ltd, a UK climate-tech company founded on over 25 years of academic research into whole life carbon. The project will be carried out in partnership with Tower Hamlets and the City of London, who will provide real planning cases for testing. To guarantee sufficient case data, the project will also draw on publicly available Greater London Authority (GLA) referable schemes. During the project, PACER will be used to process planning applications twice --- once at baseline and once for comparative review --- to demonstrate measurable improvements and enforcement outcomes. Key features to be tested include: WLCA review and compliance checking against local and national policy. Retrofit vs. new-build comparison tools to evidence retrofit-first decisions. Local benchmarking engine to create datasets specific to boroughs and typologies. Officer guidance and applicant--officer portal to impr</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Demonstrating a digital whole-life-carbon review platform (automated compliance checking, benchmarking) for planning authorities; work is the platform. Env Sci(environmental planning/carbon) and Social(planning policy) near-equal</t>
-        </is>
-      </c>
+          <t>The aim of this project is to both shorten the supply chain and halve the overall losses of precious metals (PM) during their recovery from e-waste. This project will enable the UK to disrupt this inefficient chain and create an indigenous business, leading to self-sufficiency, from an estimated 400k tpa e-waste arising. The project represents a route to achieving the missing links in the circular economy business model based on the existing pure metal to product recycling industry. This will be achieved through the combined partners’ expertise in waste collection and sorting; smelting based efficiency PM recovery and refining. Novelty is both commercial, in the integrated business approach, and technical in the use of a copper-based recovery process, instead of the iron-based process used for high efficiency PM recovery from catalysts. This programme aims to develop a sustainable process for maximising the value of PM recovery by the development of novel waste processing technologies, with higher recovery efficiencies and lower environmental impacts, complimentary to the trend in commerce to move away from ownership to service-based models, with life cycle material management.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3211,7 +2431,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>34B54215-B481-46D4-9CDE-9F13770EEC47</t>
+          <t>694226F6-57F2-42D3-95F4-A2990231FBE8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3221,29 +2441,17 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>Enabling the Brewing Industry’s Circular Economy</t>
+          <t>Development of a novel circular economy plant protein derivative as a readily digestible dietary ingredient to support healthy ageing</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>Introduction 'Enabling the Brewing Industry's Circular Economy' is a bold project to transform the brewing industry. This proposal has been submitted by the founders of Draught Drop -- a young, ambitious company. We bring local draught beer to your door in reusable glass growlers and are known as the milkman for beer! We began Draught Drop to help the UK's vibrant brewing industry and offer customers high quality draught beer in the comfort of their home, in a way that is kind to the planet. - Project opportunity COVID-19 has had a particularly detrimental impact on the brewing industry which we will detail throughout this proposal. However, it has also provided the opportunity to bounce back greener and accelerate the transition to a circular economy. The global brewing market is worth $592bn with growth and long-term trends meaning Draught Drop and the UK industry are well placed to capitalise. As the sole operators in this market we have identified the technological and commercial constraints to be overcome and are proposing this six-month project, costing c.£100,000 to focus on two categories of innovation: Technical R&amp;D is needed to design and test core technologies required for a wider roll-out of the Draught Drop business model Business model innovation to help scale the Draught Drop business and accelerate the positive environmental impact for the beer industry - Execution plan and team We have a detailed plan of how we would conduct this project, the resources required and the deliverables we will produce, namely: 1. A detailed design for the ecosystem and the technical requirements of the industry 2. Functioning prototypes of the unsolved technical challenges 3. The IP protection and potential patents to exploit this work Our team have successful careers in beer, e-commerce and innovation and have significant experience in managing innovative projects and programmes, recruiting talent and working with multiple organisations to achieve outcomes. We have als</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Reusable-growler beer-delivery circular business; business-model innovation with supporting technical R&amp;D. Engineering(prototypes/technical R&amp;D) considered</t>
-        </is>
-      </c>
+          <t>Sarcopenia, or the decline of skeletal muscle tissue with age, is one of the most important causes of functional decline, frailty and loss of independence in older adults leading to increased hospitalizations and mortality rates. There will be ~2Bn people over the age of 65 by 2050 representing the world's fastest growing age-group with a corresponding increase of 68% in the incidence of sarcopenia. However, as life expectancy continues to increase, older demographics are likely to play more significant roles in societies and economies. Adequate nutrition and targeted exercise remain the gold standard for the therapeutic treatment of sarcopenia. The annual cost to the NHS of treating age-related musculoskeletal decline is estimated at £5.7 billion (5% of net expenditure) and in the United States, sarcopenia has been estimated to have an economic burden related to health care expenditures of $18.5 billion per year. Commercially, the global sarcopenia treatments market size was estimated at $2.8 billion in 2022 and is projected to reach $3.8 billion by 2028, exhibiting a compound annual growth rate (CAGR) of ~4.7% during the forecast period. Bell &amp; Loxton Innovations Ltd is addressing this growing health challenge by developing an easily digestible, sustainable plant-based food ingredient, that can be incorporated into normal food via fortification or as a standalone food supplement. The ability to digest various food groups decreases with age which is further compounded by the need to consume a greater amount of certain nutrient classes than a younger person to maintain health and strength. B&amp;LI is a circular economy company which innovates through extracting high-value biorenewables from abundant agri-food waste streams to create active ingredients of therapeutic and nutritional value. Our plant-based product will be made available to seniors to contribute towards a healthy diet that supports mobility and strength and prolongs independent living thereby reducing the</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3253,39 +2461,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20B89AA6-C966-4E1E-B8FC-C5621505956F</t>
+          <t>457EEDCA-F759-4467-AB4C-DF187D68F3E5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>Sustainable Technologies for Reducing Europe’s bAttery raw MaterialS dependance (STREAMS)</t>
+          <t>Repurposing robots - improving sustainability in the robotics industry</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>In STREAMS, a comprehensive portfolio of at least 12 scalable and flexible technologies and pilot scale solutions for the sustainable production of battery-grade precursors and their respective anode and cathode active materials will be developed, evaluated and successfully demonstrated. These technological processes will be applied to materials from primary and secondary sources including recycled battery mass and photovoltaic waste. This will strengthen Europe’s domestic battery materials supply chain and reduce Europe’s dependency on imported critical and strategic raw materials supplies. The production technologies will also increase Europe’s resilience, competitiveness and strategic autonomy in the global battery manufacturing industry. STREAMS’ technological solutions will meet EU requirements for environmentally responsible design, and scale up, and anticipate regulatory compliance by conducting techno-economic, environmental, social impact and integrated risks assessments combined with life cycle sustainability and circularity assessments. The cathode and anode active materials synthesized in STREAMS will be used to manufacture 10 Ah battery cells at pilot scale using sustainable electrode processing. Prototype cells will be tested according to established standards and subjected to advanced post-mortem characterization. STREAM will also identify optimal conditions for future exploitation of the project results.</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Developing scalable production/pilot processes for battery-grade precursors and anode/cathode materials from primary and recycled sources; process/scale-up. Materials Science, Energy, Env Sci considered</t>
-        </is>
-      </c>
+          <t>PhD aim: The aim of this PhD is to investigate the viability of repurposing robots when they reach the end of their primary life. Motivation and background: Circular economy principles aim to break the culturally accepted linear product lifecycle of "take - make - use - dispose" [1]. In a circular economy, products are repaired, reused, remanufactured, and repurposed to provide an extended life with their original owner or additional lives with new owners [2]. Evidence from research completed during the 1st year summer project phase of this PhD found both designers and industry users of robotic systems rarely, if ever, considered the end of a robot's life beyond breakdown and disposal of the system via landfill and recycling. It is known that the production of electronic products is harmful to the environment, causing pollution and greenhouse gas emissions [3], so by ignoring the opportunities for a circular economy, working and resource-rich products are wasted. This PhD will investigate the factors that influence the ability to repurpose a robot. It will examine the technical and commercial feasibility, as well as the human decisions that underlie purchasing habits for new and second-hand robotic systems.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3295,7 +2491,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5FA8BED7-3477-477F-9B1D-6C98B13E6166</t>
+          <t>03F21411-83D1-4094-B8E5-28B8BC504DAC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3305,29 +2501,17 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>Utilisation and value chain development of renewable agro residues for improved bioeconomies</t>
+          <t>Synthesis of bio-based supramolecular gelators to act as thickeners in industrial applications</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>This work aims to evaluate and utilise agricultural co-products, byproducts and green waste streams that are currently not properly accounted for and create new and innovative approaches for resource recovery and sustainable energy generation using anaerobic digestion. Anaerobic digestion of agricultural residues could not only help to produce biomethane but could be tailored to produce and recover high value chemicals for various industrial applications. The integration of anaerobic digestion of agricultural residues with the biorefinery concept will not only advance the field but also open up different avenues for underutilised residues which in turn help in creating a sustainable and circular economy in the agricultural and green energy sector.</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Chemical Engineering</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Anaerobic digestion/biorefinery of agricultural residues for biomethane and high-value chemicals; bioprocessing. Energy(bioenergy), Env Sci(resource recovery), Agricultural considered</t>
-        </is>
-      </c>
+          <t>Project background (identification of the problem and its importance and relevance to sustainability) Following a recent increase in social and environmental pressures, along with new regulations to control microplastic release into the environment; industry has put a huge focus on ensuring formulations are made from readily biodegradable, sustainable materials. Thickeners are a key component of many formulations however they are often formed of high molecular weight polymers, such as poly (acrylic acid), which are favoured for their ability to form gels at a very low weight percent. Unfortunately, these high molecular weight polymers have poor biodegradability, and are often sourced from petrochemicals, whilst bio-based polymer alternatives, such as hydroxyethyl cellulose, are costly and require heavy extraction. Thus, the challenge arises to create an alternative to high molecular weight polymers, that are bio-degradable, designed with consideration of sustainability, and that perform equally at a similar weight percentage. Proposed solution and methodology It is proposed that by designing low molecular weight structures (&lt;2000Da) with the ability to self-assemble though supramolecular, non-covalent interactions, gels can be formed with similar properties to the polymer-based systems. When a low molecular weight gelator (LMWG) is mixed with a solvent and a stimulus is applied, non-covalent interactions (such as hydrogen-bonds, pi-pi stacking or van-der-waals forces) can lead to the formation of fibrils, which entangle together and entrap solvent molecules within the matrix forming a gel. Since the backbone of these fibrils are non-covalent, they can be broken by applying another physical or chemical stimulus, which could be tailored to conditions in waste-treatment. One of the main challenges is to design LMWG's that can form gels in polar solvents such as water and propylene glycol, as the preferred solvents in personal-care formulations. Solvent effects are comp</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3337,39 +2521,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FF5771FE-5390-4B66-ADF0-2535E60E3C57</t>
+          <t>12AB2071-C1D4-4B54-9361-9876F2358D6A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Joint Industrial Data Exchange Pipeline</t>
+          <t>Interfaces, Stability and Energy Efficiency: Photo-chemical Characterisation of Perovskites for Printable Photovoltaics</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>Currently, economies worldwide are pursuing mostly a linear model of production which leads to massive material losses, dependency on geopolitically instable states and volatile markets for primary resources. A circular economy, on the contrary, seeks to counter this approach to preserve the value of utilized resources and materials as long as possible, to use them as frequently as possible, and to produce as little waste as possible. European industry needs solutions to mitigate the barriers for industrial data reusability and facilitate the unlocking of value from data. Joint Industrial Data Exchange Platform is a place where industrial data is fused for interconnecting seemingly different sectors into the collaboration pipeline. It builds upon the principles of Industry 4.0, by adopting a coherent approach for the semantic communication between diverse actors aimed towards direct or indirect contribution to the EU’ s climate neutrality goals of 2050. JIDEP is a landing place to any organization which has any kind of data obstacle to be addressed, on its paths towards delivering more sustainable material, product, service, or solution. Within JIDEP, built-in tools are made available for unlocking the value of the data, which can lead to the development of more sustainable solutions, technologies, and materials. JIDEP is also an optimizing continuum, covering the entire product lifecycle and steering it towards circular standards implementation at technological and regulatory levels. Finally, JIDEP is a tool equipped with resilience frameworks for growing organizational and industrial capacities to withstand supply chain disruptions in short-, medium- and long-term clauses. As such, JIDEP ingests industrial data and produces sustainability, resilience, and circularity artifacts for its participants.</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Industrial data-exchange platform (data fusion, semantic interoperability, analytics tools) for circular value chains; data infrastructure. Business(supply-chain collaboration) considered</t>
-        </is>
-      </c>
+          <t>This project aims to investigate the photochemistry of perovskites to better understand their performance and degradation behaviour, particularly in printable perovskite devices. To assess the environmental impact of lead-based perovskites and investigate methods to reduce this impact. The main focus of reducing the lead impact is to account for all the lead at end-of-life and thus the project is aiming to systematically determine the lead content of devices before and after manufacturing and after multiple re-manufacturing cycles with UV/Vis, fluorescence spectroscopy and microwave plasma-atomic emission spectroscopy. The work also involving tuning the deposition of the perovskite material to understand the effect of deposition (i.e. 1 step vs 2-step deposition) on the degradation and the subsequent re-manufacture to determine the "re-manufacturability" of devices. The ultimate aim is to understand how re-manufacturing cycles affects the fundamental properties of the perovskite material, how many times the material can by cycled and to determine standardised protocol for doing so with accounting for all the lead in the system and ensuring no lead leeching from devices. For the studies on remanufacturing the photophysical properties of the film are studied with UV/Vis and steady state and time resolved fluorescence measurements and the morphology is monitored with XRD.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3379,39 +2551,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93CF5015-F364-4895-BDE5-3D3DCE803281</t>
+          <t>8436E80E-17D9-493A-BCEC-A50317880702</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ESRC</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>Waste as resource in the "age of austerity". Sustainable development and circular economy in local communities. A case study.</t>
+          <t>CirPla: Advanced catalyst and mechanochemical process for Circular Plastic feedstock recycling</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>Research aim The main aims of this project are: to understand the role of waste1 (Thompson 1979) in a community affected by the economic crisis ("age of austerity", Streeck and Schafer 2013); to study a community organization in a context of transformation promoted by a process of re-thinking of waste as community resources. My research is an ethnographic engagement related to the concepts of "sustainable development", "circular economy" and "waste studies" (O'Brien 2008). Since 2012, the EU commission has proposed several legislative amendments about resources and waste management (Gregson et.al.2015), introducing the idea of "circular economy" (European Commission 2014). This idea 1 I will take into consideration mostly households waste with exception for pulper waste from paper mills' residuals. refers to an economy premised on keeping resources in circulation for as long as possible and so aims to eradicate waste. This "long term solution" is defined as "sustainable" development (Miller 2012). In this context, wastes are considered useful materials in order to partially reduce the European demand for natural resources. To consider wastes as resources is important to think those as materials (e.g.paper). These materials have monetary value if categorized and sold separately.</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Social Sciences</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Ethnographic case study of a community re-thinking waste as resource; sociology/anthropology, waste studies, sustainable development (ESRC)</t>
-        </is>
-      </c>
+          <t>The accumulation of plastic wastes is a severe environmental challenge. Present estimates suggest that over 380 Mt plastics are produced annually worldwide, only 16% are currently recycled, while 150-200 Mt plastics are accumulated in landfill or leaked to the natural environment. On the other hand, the global demand for carbon-based chemicals and materials is expected to double in the next 10 years to over two billion tons, which we cannot simply still rely on sourcing from fossil fuels. We need to supply these feedstocks from recycling waste materials, such as plastics. However, until now, there remains significant challenge in bridging the gap between waste management and the resource demand for materials and commodity chemicals. The ultimate way to overcome this challenge is to close the loop by recovering the monomer feedstocks from waste, yet such chemical recycling cannot be easily achieved by traditional thermo-chemical processes, due to the poor tolerance to feedstock contamination, low economic value of products and sizable energy input. On this aspect, mechanochemistry, which utilises mechanical energy to initiate chemical reactions, has clear advantages over traditional thermochemical processes. These advantages arise from reactions taking place in a solventless, solid-state environment, with a high tolerance to variation feedstock qualities. Historically, this technique solely relies on supplying enough energy input to overcome the thermodynamic energy threshold of the chemical reactions. Yet plastics are made to last, therefore the polymer chemical bonds are difficult to break. Therefore, capitalising on the team’s strong background on catalysis and polymer processing, through building collaboration with the mechanochemical community in the UK, CirPla will demonstrate for the first time how catalysis + mechanochemistry can transform the plastic recycling and manufacturing sectors. The catalysts will decrease the activation energy of the polymer chain b</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3421,7 +2581,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A40EF996-8304-4B51-AA73-0F77F5835DDE</t>
+          <t>D61A1B7D-3375-4869-B86D-20651750EC89</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3431,29 +2591,17 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>Sustainable Home Survey (Intelligent Domestic Screening Survey System)</t>
+          <t>BB-REG-NET (Biobased and Biodegradable materials REGulatory NETwork)</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>The Sustainable Home Survey Company (“SHS”) works with community partners, refurbishment providers and homeowners to identify and catalyse domestic energy efficiency improvements. SHS was the first CIC to be certified as a Green Deal Assessor Organisation. As an adjunct to the core business of providing regulated energy surveys, in mid-2012 SHS identified a need for an innovative assessment system that enables the cost effective screening of households prior to a full Green Deal Assessment (“GDA”). The proposition was successfully market tested as part of a TSB “Proof of Market” study. The introduction of the Green Deal in 2013 marked the start of “the biggest home improvement programme since the Second World War”. However, the mass consumer market remains reluctant to pay upfront for assessments. Green Deal Providers profitability will be materially impacted by absorbing “at-risk” costs of ~£125-150 per GDA at anticipated 25-33% conversion rates. The basic SHS screening system uses key information on the property to estimate the set of measures that can be economically implemented combined with householder behavioural survey results to evaluate their propensity to implement the measures. This enables scarce surveying resources to be directed to the highest potential households, boosting conversion rates to reduce net costs per implemented Green Deal package by at least £150. This project will allow SHS to develop a cost-effective area based household engagement system. SHS proposes to repurpose political engagement systems, integrate existing GIS stock data and household survey data. By tracking actual implementation by household, the system will develop intelligent, self-learning lead-scoring algorithms. The successful launch of the SHS screening service is estimated to directly create up to 40 new jobs and help accelerate the uptake of the Green Deal which is estimated will deliver carbon savings of 1.8MtCO2 MtCO2 p.a. by 2020, with an NPV of £8.3billion.</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Self-learning lead-scoring algorithms plus GIS/behavioural data to target homes for energy-efficiency uptake; algorithmic screening system. Business(marketing) and Energy(efficiency) considered</t>
-        </is>
-      </c>
+          <t>World-leading sustainable bio-based chemicals and materials (BB-Materials) developed, designed and manufactured in the UK, offer a once-in-a-generation opportunity to transition away from oil-and-gas, creating a resilient-engine for net-zero, and securing and growing hundreds-of-thousands of highly-skilled and productive jobs. Chemicals are in everything we use in our daily lives - food, textiles, energy, batteries, defence products, mobile phones and medicines - ensuring our food security, clothes we wear, heating our homes, affording national security, enabling communications and delivering treatments for diseases. Today, almost all chemicals are made from fossil oil-and-gas, being responsible for ~10% of Global-Greenhouse-Gas-Emissions. The UK chemicals industry has an ambition. By 2050, it will have doubled in size, sourcing 30% of its carbon feedstock from biomass (Innovate UK, 2024, unpublished), with manufacturing of just 15 biochemicals having potential to contribute 5.2 million-tonnes CO2eq GHG-savings and £1.6 billion annually to the UK economy (DESNZ, 2024, unpublished). Through accelerating the commercialisation of BB-Materials, if 30% of chemicals could be bio-based by 2050, this has potential for £26.25 billion annual income. The UK is the home of BB-Materials academic excellence, but other areas of the world are already implementing policies/regulations to drive this sector forwards and the UK is rapidly losing this competitive advantage. Our engagement with 186 individuals and 102 organisations during the Discovery phase concluded that a lack of overarching strategy has led to disconnected departmental policies that hinder BB-Materials commercialisation, and regulations that are better suited to fossil-based incumbents. Due to the nascent nature of the sector, there is limited scientific data and evidence for robust development of regulations, detrimentally impacting the growth trajectory of BB-Materials. Standardised terminology and adequate languag</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3463,7 +2611,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0F079D2B-EAEC-4B4C-9D7D-1ADC7DA36BDE</t>
+          <t>1B3D6EE8-E709-4B95-AB12-3CB2E0FCCDA7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3473,29 +2621,17 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>Accelerating the Circular Economy for Consumer Goods within Islington</t>
+          <t>Managing and Trading Batteries as Assets</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>GoodMine is an early stage growth business that has developed a waste prevention platform that collates open source data and creates networks to connect the dots between consumers and the circular ecosystem. The platform includes a data analytics dashboard for local authorities to observe local waste prevention activities and behaviours as they work towards net zero goals. This project relates to a demonstrator trial of GoodMine's technology within the London Borough of Islington in collaboration with Islington Council.</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Waste-prevention platform collating open data with an analytics dashboard for local authorities; digital platform/analytics. Env Sci(waste prevention) considered</t>
-        </is>
-      </c>
+          <t>EMB Power, in collaboration with Keele University and industry stakeholders, is leading a project to develop a large lithium battery asset management and trading platform to address the clean energy and road-to-zero carbon emissions agenda, by providing deeper understanding of the physical condition and value of lithium batteries throughout their life. The toolset will support: Effective lifecycle decisions Assessment of environmental sustainability factors Optimisation of return on investment Technological battery development will improve kWh cost, number of cycles, safety, volumetric and gravimetric energy and power density, impacting favourably on effectiveness, environmental considerations and return on investment. However these all increase complexity for asset evaluation. The system will exploit AI "big-data" technology to provide real-time information to support decisions on how to maintain and deploy assets at each stage of a battery's lifecycle. The innovative, algorithm driven approach has already been validated: Two patents are pending, proceeding to grant with no major Prior Art or Freedom to Operate challenges yet identified Extensive customer/influencer dialogue indicates no market solutions of similar utility are available/planned Academic research with Keele and Warwick University validates the novel nature of the approach EMB Power benefits from its founder's extensive experience and connections in automotive electronics engineering in OEM and other organisations throughout the battery lifecycle. Phase 1 is addressing a feasibility study, consequent specification of system requirements to form the basis for a Phase 2 development of prototype applications, initially to support exploitation of commercial opportunities in improving business and industry efficiency for a wide range of stakeholders including: battery manufacturers, land, marine and aviation vehicle manufacturers, insurers, vehicle dismantling, battery remanufacture, vehicle rental and us</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3505,7 +2641,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>47C6A058-4EE3-49A2-BAB1-AE2F98B7F321</t>
+          <t>621767EB-A9F6-42BF-9075-6B06B8B6C230</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3515,29 +2651,17 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>Improving Iron Catalysed Kumada Couplings in Flow</t>
+          <t>Carbon Utilisation in the South Wales Industrial Cluster</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">This project is focused on developing a methodology to improve iron catalysed alkyl-alkyl Kumada cross couplings. This type of reaction is a promising sustainable alternative to traditionally palladium catalysed reactions, but improving the efficiency, selectivity, and catalyst turnover is important to make the reaction more sustainable and viable for industry. This will be done by developing and using flow apparatus to explore kinetics and reaction pathway. This type of reaction has been previously reported in the literature using Fe(II) acetate, and a xantphos or N-heterocyclic carbene (NHC) ligand; these reactions have achieved yields up to 64% for the xantphos system after 15 mins, and 67% after a total of 27 hours for the NHC reaction. Whilst these yields are promising further optimisation of the catalyst and reaction conditions would make the reaction a cheap, sustainable, and viable option for large-scale chemical production; in particular for the pharmaceutical, agrochemical, and fine chemicals industries , where more expensive and environmentally costly palladium catalysts are commonly relied upon. We plan to exploit the fact that reactions carried out in continuous flow reactors can be probed at steady state to better insight into the reaction and aid the optimisation process. It is anticipated that the additional control over the reaction that can be achieved using flow equipment will also aid in this process. Additionally, this project will focus on expanding the substrate scope to enable the synthesis of beta-functionalised amines, such as functionalised piperadines, azetidines, and man-made amino acids. These are valuable building blocks e.g. for fragment based drug discovery and the synthesis of active pharmaceutical intermediates (APIs). The project will focus on developing a model reaction and general method that can used and applied by other research groups and industry. Finally, throughout this project we will investigate designing a flow reactor </t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Developing iron-catalysed Kumada cross-coupling methodology (kinetics, reaction pathway, substrate scope, synthesis of amines); synthetic chemistry/mechanism. Chem Eng(flow/catalysis) considered</t>
-        </is>
-      </c>
+          <t>Research into industrial decarbonisation is essential to asset the growing mix of low-carbon technologies that will dominate in the Net Zero future. This research focuses on identifying business-case carbon capture utilisation (CCU) applications across South Wales Industrial Cluster (SWIC). CCU is a recognised (and commercialised) method of industrial decarbonisation and sustainable waste management. Utilisation of waste-CO2 reduces a process' carbon footprint by avoiding emissions from conventionally fossil-derived inputs. In some cases CCU can permanently store CO2 in products i.e., mineralisation in construction materials. Furthermore, utilisation of waste-CO2 as a feedstock enables local circularity, and reduces resource consumption by adding value to waste, helping decarbonisation of traditionally hard to abate sectors (e.g., sustainable aviation fuel generation from waste-CO2). Although CCU is a viable decarbonisation method, particularly in dispersed industrial sites, it is not as well researched nor applied as other low-carbon technologies. This is mainly due to insufficient carbon pricing, technology immaturity with energy penalties and lack of CCU awareness. Thus, the following research aims to hurdle such challenges by applying circularity and green-industrial symbiosis concepts with CCU by sharing low-carbon infrastructure and locally reusing waste-CO2. We hope to identify what CO2 utilisation pathways best suit SWIC; and where CO2 derived products can be incorporated locally. Hence research objectives are to simulate relevant CCU plants within the a SWIC landscape case-by-case. This will be done using chemical/system engineering software Aspen Plus. Currently, renewable methanol synthesis from waste-CO2 emissions was found to have relevancy, thus a model is being developed to evaluate its potential in SWIC.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3547,39 +2671,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6EBEC294-3CA1-4374-B3F0-68D74407D96A</t>
+          <t>DF9D3681-2334-4495-A1D4-865702DA7AAE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>ISCF</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>Enhancing the Circular Economy of Subsurface Green Energy Projects</t>
+          <t>Friction Stir Welding Crawler for Internal Repair and Refurbishment of Pipelines - FSWBot</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>The reality of climate change is something that governments across the world are having to come to terms with. It is imperative that greenhouse gas emissions are both reduced and offset to prevent global warming, with the aim of limiting temperature increases to a maximum of 1.5 degrees by the end of the century. In order to limit this global temperature rise, many countries have committed to achieving net zero emissions by 2050, which is to say that man-made greenhouse gas emissions are cut as close to zero as possible, while remaining emissions are removed naturally (such as by forests or oceans). There are many different pathways needed to achieve this such as wind, solar, and carbon capture &amp; storage (CCS), to name a few. The focus of this project is to look at the waste streams generated from subsurface green energy projects such as CCS, hydrogen storage, and geothermal. These projects generate large volumes of waste brines that need to be treated and disposed of. Due to the geochemical environment that these brines are formed in, they may contain technologically critical elements (TCEs) in solution such as lithium, cobalt, or rare earth metals, that are valuable in other green technologies such as batteries and solar cells. They may also contain high concentrations of toxic elements such as cadmium which require a higher degree of treatment to dispose of. This project aims to address three different areas regarding subsurface green energy projects in the UK. The first is to analyse groundwater data currently available in the UK to understand where the geochemical conditions are best for the formation of TCE rich brines. Statistical analyses and geographic information systems (GIS) will be used to visualise the groundwater data that has been compiled. Secondly, it is important to understand the chemical composition of the brines that are already being produced by CCS clusters in the UK, and this will be done by analysing samples from four of the UK's CCS cluste</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Treating waste brines from CCS/geothermal/H2 storage and recovering critical elements; resource recovery + pollution treatment. Earth Sciences(geochemistry/groundwater, off-list) and Energy considered</t>
-        </is>
-      </c>
+          <t>"Steel pipelines corrode due to of the nature of the liquids they contain. Also, cracks can form over time leading to failure and leakage of the contents, resulting in severe economic losses and environmental pollution. To avoid this, inspection, evaluation, and repair activities are performed periodically. Internal cracks and areas of corrosion and metal loss are monitored by the use of intelligent inspection devices (PIGs) which carry special sensors. Sections of pipeline that are found to be likely to fail are reinforced using an externally applied bolt-on clamp which is both costly and is difficult and dangerous to install. The FSWBot project will see the development of a radical new solution to internal corrosion and cracks that form inside pipelines. Meeting the objective will result in a much cheaper, safer repair process that will enable pipeline asset owners and their service providers to produce very high- quality welds in steel pipelines without shutting down and purging petroleum pipelines and without the use of divers and surface vessels. This is of enormous importance especially in respect to inaccessible pipelines and those which are installed in parallel groups where space around pipes is restricted. The objective of the project is to develop a robotic platform with a payload consisting of unique hydraulic friction stir welding equipment which produces no sparks. Data obtained by prior high-resolution mapping of anomalies that are produced by metal loss and corrosion will be used to provide information for mission planning. Repair will be carried out in-situ using no external power and no welding consumables. The robot will generate electricity from the liquid flow in the pipeline via a variable pitch turbine diving a generator, which will supply power to a hydraulic pump and a battery which drives the magnetic tracks. FSWBot will bring about a step change in the competitiveness and growth for 3 UK business -- namely Forth Engineering, Proserv and In</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3589,7 +2701,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1134E99F-E81E-4528-9429-07263A9E4B14</t>
+          <t>8F6EB85B-0133-4AC8-81DE-44E03122F9D7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3599,29 +2711,17 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>ReCinder Ceramics</t>
+          <t>Recyclable precision materials to capture forever chemicals with reduced carbon footprint</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>By combining design with ground-breaking material research, The Home of Sustainable Things is pioneering "ReCinder Ceramics". A project aiming to convert challenging industrial waste into a primary material and high-quality goods for the market. ReCinder Ceramics however, is not solely about the creation of sustainable products. It is about fostering collaboration, reducing environmental impact and promoting the transition towards a circular economy with focus on developing a locally produced sustainable homeware. The material source consists of discarded, broken and defective fired ceramics, primarily a by-product from the ceramic producers. Annually, the UK generates over 32 million tonnes of fired scrap. Using waste as raw material will decrease the amount of waste sent to landfills, minimise material loss and reduce dependency on natural materials, while concurrently offering sustainable alternatives to everyday products traditionally manufactured in environmentally unfriendly ways. Waste materials will be sourced from a network of ceramic producers, capitalising on established relationships and scaling the supplier base as production grows. The Home of Sustainable Things will introduce a range of tableware and tiles, followed by raw materials, including ceramic glazes. The range is intended to meet the needs of domestic, commercial and educational sectors.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Converting industrial ceramic waste ('fired scrap') into a primary material and homeware; waste valorisation/resource recovery. Materials Science and Engineering/design(product) considered</t>
-        </is>
-      </c>
+          <t>Perfluoroalkyl and polyfluoroalkyl substances (PFAS) are \&gt;4700 human-made chemicals, used in broad applications in UK industries (OECD). The UK government (April 2023) published a report on Regulatory Management Options Analysis (RMOA) on PFAS; the launch of the UK REACH programme intended to restrict PFAS, noting that 'there is widespread human and wildlife \[detrimental\] exposure via surface waters and groundwater'. The looming regulatory landscape requires a step-change in PFAS management in industry to continue operations and maintain competitiveness. Current state-of-the-art for PFAS removal is petroleum-derived ion-exchange and carbon-based granular activated carbon, designed to be single use and ineffective at meeting the more stringent 2023 regulations, leaving an immediate market gap. End- of-life fate for these PFAS-laden materials is incineration or landfill, highlighted in the April 2023 RMOA report as a major environmental exposure route for PFAS. This holds back the Net Zero journey by requiring additional carbon footprint to manufacture virgin material, dispose of single use material at 1100C incineration and transport large volumes of hazardous waste. A substantial void exists for a sustainable "cradle-to-grave" PFAS treatment process, to protect the environment and businesses from future PFAS liabilities. Puraffinity has developed a predictive materials development engine for sustainable PFAS targeted adsorbent material. We will develop the next generation of recyclable adsorbents in this project using a TRL3-proven step called regeneration, thereby enabling Safe Engineered End of Life and aligning PFAS treatment to the Net Zero journey. The technology targets industrial sectors that require PFAS water treatment at source, and additional markets needing PFAS removal. Markets are local and international, focusing on regulated EU and US geographies. The manufacturing sector is valued at $trillions with a CAGR\&gt;10%, making it attractive for technolog</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3631,39 +2731,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BA774ABD-1F73-4CFF-A8EE-2ACDD49C4F75</t>
+          <t>12557B6D-7154-4A99-A2AF-CE2C885ABD4C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>Developing the feasibility of local perovskite solar cell manufacturing; supply chains, indigenous and sustainable materials</t>
+          <t>SPIWACS: Sustainable PIgments from WAste Cellulose Streams</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>This project aims to evaluate the feasibility of establishing local manufacturing capabilities for perovskite solar cells (PSCs) by investigating supply chains, indigenous materials, and sustainable development pathways. In addition to exploring locally sourced, sustainable materials for PSC production, the research will quantify waste generation and assess the potential for using secondary materials within the manufacturing process. This dual focus on waste reduction and material reuse seeks to address environmental impacts associated with PSC production, reduce reliance on imported, high-impact materials, and strengthen regional supply chains. By examining the availability, compatibility, and performance of alternative, locally derived materials, this work aligns with goals for a sustainable energy transition and energy access in developing regions, advancing scalable manufacturing solutions that support economic resilience, lower production costs, and promote environmentally responsible technology deployment</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Feasibility of local perovskite-solar-cell manufacturing (supply chains, sustainable materials, waste); manufacturing/supply-chain focus. Energy(PV), Business(feasibility), Materials, Env Sci all in play</t>
-        </is>
-      </c>
+          <t>Pigments add shine and colour to a multitude of daily products. They are ubiquitous in cosmetics, fashion, packaging, paints, and even food. However, as currently formulated, they contain a mix of problematic materials such as microplastics, mineral oxides, like titania and mica, and high GHG refined metals. Extractive mining is a major environmental and social concern for which there are currently very limited technological alternatives that would offer plant-based, renewable and high performance metallic-effect colourants. Without a fundamental design and innovation shift in pigment technology, direct pollution to the natural environment and GHG emissions from existing processes and supply chains enabled by petroleum consumption and extractive mining will never be eliminated. It is now clear that pigment materials have a negative impact on the environment across their entire life cycle and are not sustainable. They are associated with negative human health effects, are accumulating in the environment and have the potential to be toxic to animal and plant life. Therefore, there is an unmet need to develop truly sustainable alternatives. The solution is now available: the project partners Sparxell (SX) and Impossible Materials (IM) are start-ups aimed at the commercial delivery of breakthrough sustainable pigments based on plants: Sparxell has developed unique new pigments using cellulose-derived nanocrystals to deliver metal-like effects without metal; Impossible Materials' first product is a cellulose-derived white pigment, addressing one of the most environmentally problematic and high-volume pigments - titanium dioxide. In this collaboration, we will build a new manufacturing process platform by transforming the primary waste cellulose stream from the production of white pigments (IM) into functional cellulose nanomaterials that are the main and sole ingredient of metallic-effect pigments (SX). The overall process will be monitored and accompanied by a cradle-to</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3673,39 +2761,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>129207AC-761F-4FAF-8B49-6B2CC7C939B4</t>
+          <t>D6EC97D5-F048-4835-92CE-591F9C59D516</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>De Montfort University and Generation Phoenix Limited (AKT3) 2024</t>
+          <t>Effects of microplastics on interactions between soil biota, soil structure and crop performance in sewage sludge-amended soils</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>This project, a collaboration between Generation Phoenix and De Montfort University, aims to transform post-consumer fashion leather waste into high-quality materials through advanced fibre characterisation and processing techniques. By recycling post-consumer leather, the initiative reduces landfill impact, promotes fashion circularity, and meets market demand for sustainable circular fashion materials.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Recycling post-consumer leather waste into materials via fibre characterisation and processing; recycling/resource recovery. Thin; Materials Science(characterisation) and Engineering(processing) considered</t>
-        </is>
-      </c>
+          <t>The aim of this PhD is to investigate the effects of MPs in BS on soil biota, soil structure and crop performance in BS-amended soils. It will assess interactions between BS with various levels of MP contamination and soil organisms directly involved in maintaining soil structure (earthworms and symbiotic fungal partners of roots), under different arable land management practices, and how the latter affect the decomposition and mobility of MPs within the soil environment. The project will combine controlled laboratory / greenhouse experiments with complementary field studies (at the University of Sheffield Arthur Willis Environment Centre (AWEC) and ICAIR facility).</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3715,39 +2791,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E91C05D7-0E20-4C20-B9E0-B73AF777E605</t>
+          <t>4CFEB12C-C5FA-4602-BB16-585B0A2CEC3D</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>AHRC</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>Merlin - phase 2</t>
+          <t>Modelling and Evaluating Industrial Symbiosis in Agri-Food Networks through Advanced Simulation - Moving Towards Circular Economy in the UK</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>We seek support for the development of an in-depth market analysis and a robust market strategy for the exploitation of highly versatile, portable equipment for machining, grinding and lapping of gas safety valves to facilitate a total in situ refurbishment solution. We have 30 years experience and a proven track record in the service and repair of gas safety valves in the UK, Europe and Asia. Through our in-house research and development have identified a gap in the market for in-situ repairs which can significantly reduce operational down time in large scale industrial facilities. We are seeking support to investigate a route to development for an prototype machine that has already been proven on a bespoke basis with a selection of our industrial clients. We would like to offer the market a generic tool that can allow in-situ repairs across a range of safety critical infrastructure platforms in the oil, gas and power industries. To achieve this we need to increase the visibility of our company and expand our client base through a programme of targeted visits and attendance at key trade shows, thus we can develop a deeper understanding of the market and the requirements of our primary clients and develop our working prototypes to meet industrial need. The development of a generic repair tool is a challenging idea for our company and would be a step change for our current business, however our strong international profile means we are expertly placed to exploit the current gap in the market.</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Business, Management and Accounting</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Market analysis and commercialisation strategy for portable in-situ valve-repair equipment; this phase is market/exploitation. Engineering(tool/prototype) considered</t>
-        </is>
-      </c>
+          <t>Industrial Symbiosis (IS) represents a concept in a specialised domain within the field of Industrial Ecology, with its primary objective centred on synergistic relationships among entities. These relationships encompass a tangible exchange of materials, energy, and services strategically orchestrated to yield concurrent economic and environmental advantages. Industrial Symbiosis Network (ISN) can be viewed as complex adaptive systems where the network facilitates these symbiotic relationships, providing a framework for businesses to identify, establish, and manage resource exchanges effectively. In Northern Ireland (NI), the dairy production and processing industry accounts for 31% of the overall gross agricultural output (DAERA, 2022). Businesses like farms, beer breweries and anaerobic digesters also play a pivotal role in NI's gross output. The significant production in these sectors also generates substantial by-products, and inadequate waste handling results in severe environmental repercussions. For example, large discharge of farming waste is suspected to be one of the main reasons for the contamination of Lough Neagh, the largest freshwater lake in the UK, supplying 40% of NI's drinking water (BBC News, 2023). Although the industries have traditionally incorporated environmental measures, there are persistent challenges in pursuing sustainable production practices, particularly concerning the effective closure of material loops. The literature identifies numerous applications of those by-products, which can be re-utilised for other purposes or production. For example, the use of cheese whey in milk-based soaps as replacement for raw milk and spent grains as animal feed in farms. This creates an opportunity to develop ISN comprising industries that can share or exchange resources. While previous studies have explored advanced modelling and simulation techniques within individual industries, there is a notable scarcity of literature regarding their applicatio</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3757,39 +2821,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>9F9692C5-08BA-41B0-8FBA-1F2F9C2150B7</t>
+          <t>A845D48E-8F3D-4892-9BA2-560492477ED9</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Ayrton Fund</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>Green Infrastructure: understanding its role in mitigating current and future flood risk in urban areas</t>
+          <t>Innovative Recycling of E-waste for Critical Metals and Sustainable Economy in Malaysia (iRECYCLE-Malaysia)</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>In England alone, 3.2 million households are located in areas at risk of surface water flooding, with annual damages exceeding £300 million. It is projected that this cost of associated damage could increase by 40% by the 2050s. Green infrastructure (GI) can provide a means of reducing the amount of water entering drainage systems via infiltration, interception, transpiration and providing both temporary and more longer-term storage. Evidence is needed to understand how, where and when GI aids flood risk mitigation over time and space. This project will consider the following research questions: How can we better represent the structure and function of green infrastructure in our flood risk impact models? How can we design green infrastructure into the existing urban fabric to maximise benefits and reduce costs? How effective will green infrastructure be as a flood mitigation measure under future climate? This project will conduct a number of controlled experiments at the National Green Infrastructure Facility and at locations of different GI types across the city. Observations will then be used to inform a reliable and robust physically-based infiltration component in CityCAT, a hydrodynamic model capable of simulating flood risk, and the role of GI in mitigating that risk at high resolutions over large spatial domains. Outcomes from this project will include improved understanding of GI performance; assess long-term performance and costs of GI, including management and maintenance; and aid design of future GI strategies to mitigate climate-induced flood risk in urban areas.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Green infrastructure for urban flood-risk mitigation (infiltration/storage, hydrodynamic flood modelling, climate); freshwater/climate/environmental planning. Engineering(civil/hydraulic modelling) considered</t>
-        </is>
-      </c>
+          <t>The iRECYCLE-Malaysia project aims to revolutionise e-waste management in Malaysia through the development of sustainable and profitable technologies for recycling plastic-contaminated printed circuit boards. This interdisciplinary research program brings together expertise from institutions in Malaysia and the UK to address the pressing challenge of e-waste in Malaysia, where generation is projected to reach 1.4 million tonnes annually by 2030. Currently, only 25% of Malaysia's e-waste is formally recycled, with 75% handled by the informal sector using outdated, unsafe practices that pose significant environmental and health risks. This situation urgently calls for innovative solutions to transform e-waste management, improve safety, and generate high-quality employment. The project aligns with Malaysia's 12th Plan (2021-2025), which emphasises transitioning to a circular economy and implementing Extended Producer Responsibility for e-waste. By developing customised recycling solutions for Malaysia's tropical climate and local context, iRECYCLE-Malaysia will contribute to the country's goals of increasing household recycling rates by 40% and scheduled waste recycling by 35%. Key objectives include: Developing sustainable metal leaching strategies using hydrophobic deep eutectic solvents and bioleaching to replace hazardous mineral acid leaching. Establishing processes for separating mixed plastic waste using supercritical fluids to avoid toxic emissions from burning. Designing new separation flowsheets for full recovery of precious and critical metals. Building a pilot-scale demonstration of an integrated e-waste recycling process in Malaysia. Ensuring alignment with circular economy principles and economic feasibility. Developing formal e-waste policies for Malaysia based on stakeholder engagement. The project will deliver step changes in e-waste management by advancing biotechnology applications, developing innovative metal recovery methods, and demonstrating sus</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3799,39 +2851,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24E4C184-3EA3-4792-B431-901231522EF6</t>
+          <t>BAF0F355-95F3-4C23-A846-CE7660E680C5</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ISCF</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>SNAPP - Sustainable Nutrition for Animal Protein Productivity</t>
+          <t>Metrological traceability of measurement data from nano- to smallmicroplastics for a greener environment and food safety</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>The use of novel feed materials to increase sustainable protein production whilst improving the health and survival of piglets post-weaning will be addressed. Poor growth rates and high disease incidence are associated with the early post-weaning period due to factors such as oxidative stress that causes gut damage. Sustainable alternatives to zinc oxide, added to feed as an anti-microbial and growth promoter, are required to reduce morbidity and mortality and improve subsequent growth and productivity. Improved pig nutrition across the lifespan will also improve meat quality, reducing import dependence. The project will build on prior feasibility studies where supplementation of pig feed with polyphenols provided protective effects, improving piglet gut health and survival, as well as meat quality and shelf life. Polyphenols are anti-microbial, anti-inflammatory, anti-oxidant compounds present in plant materials. Agri-food by-products (AFBPs) generated by agriculture and food processing activities are readily available for processing to provide a sustainable source of polyphenol-rich feed supplements. Conventional methods (e.g., drying and milling) will be used to process AFBPs for inclusion in pig feed. Polyphenol extraction using previously developed sustainable methods will enable separation of polyphenols from plant fibre. These polyphenol rich extracts can then be standardised for use as supplements. Separation from fibre is important when feeding the young pig as high dietary fibre around weaning reduces nutrient utilisation and thus feed effciency. The benefits of polyphenol supplementation will be examined across the pig lifespan through controlled feeding trials at the University of Leeds National Pig Centre and commercial farms at Cranswick facilities. The economic and sustainability benefits of these innovative approaches will be compared to existing practices. Successful AFBP exploitation will generate additional revenue streams for farmers, divert wast</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Agricultural and Biological Sciences</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Pig nutrition/animal science: novel feed supplements (polyphenols) for piglet health, growth and meat quality via feeding trials. Chem Eng(extraction of supplements) considered</t>
-        </is>
-      </c>
+          <t>PlasticTrace aims to address the urgent need for development and harmonisation of methods for the chemical identification, physical characterisation and quantification of released small micro/nanoplastics (SMPs/NPs) in drinking water, food and environmental matrices, as required by the EU’s Circular Economy Action Plan (CEAP). In this context, hyphenated and complementary analytical approaches will be developed, optimised, compared and harmonised, leading to the establishment of metrological traceability of measurements through robust validation studies. Novel and environmentally relevant SMP/NP reference materials will be developed within the project. International cooperation with key stakeholders globally will be considered as the basis for a European Metrology network.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3841,39 +2881,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EBBDE84A-3DF5-467C-949E-E40AD31375AF</t>
+          <t>DD53D664-AC4A-4E4D-BC0B-716C459BAE4D</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>AHRC</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>The University of Warwick and F W Thorpe plc</t>
+          <t>Forging And Belonging: Researching children's social relations and Imagined futures through Crafting in rural West Africa (FABRIC)</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>To transfer and embed Circular Economy knowledge and related innovation.</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Abstract too thin to judge: single sentence ("transfer and embed Circular Economy knowledge and related innovation"), no field content. Looks like a KTP; field indeterminable</t>
-        </is>
-      </c>
+          <t>FABRIC addresses three research gaps: the changing value of crafting in West Africa; children's modalities of craft learning and its sociocultural value; and how children in 'middle childhood' imagine their futures in a rapidly changing world. The economic value of crafting in West Africa is changing in two directions: there is falling demand for artisanal crafts in preference to cheaper industrial and second-hand alternatives; yet tourist and art markets are opening new markets for crafts that may re-invigorate the sector. The cultural and epistemological value of crafting continues to be highly esteemed in rural communities and within government policy on the creative and cultural industries. Crafters have adapted their practice to incorporate new materials, including recycling scrap metal and textiles. Growing interest in sustainability and circular economies is also stimulating policy interest in artisanal craft. Crafting is gendered and is often organised by caste-like rules that attach status groups and/or ethnic groups to specific crafts. Therefore, crafting is also bound up with how social belonging and social relations between castes, ethnicities, faiths, and genders are expressed. In this highly labile context children's craft learning takes on particular importance for understanding how social belonging is instantiated in material culture and how changes in the organisation of material culture create space for new ways of imagining social belonging and what the impacts of these new ways are on how the future is imagined and comes into existence. The impact of the transformation of craft practices on children's social belonging now and in the future is a critically important question because how children in West Africa, in which 40 per cent of the population is under 15 years of age, instantiate social belonging and imagine their futures will fundamentally impact on the prospects for economic growth and local and regional political stability. FABRIC will e</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3883,39 +2911,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EB771303-6B44-4A23-8637-DC38360C3653</t>
+          <t>AA9E17BB-AA37-4E0B-9833-1A3C89874476</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>ReSuB - Renewable &amp; Sustainable Biomass</t>
+          <t>CircularPSP – Public Service Platforms for Circular, Innovative and Resilient Municipalities through PCP</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>Covid-19 has impacted many sectors; one such sector is the waste management and recycling industry. The amount of waste generated by households in the 'first wave' of the pandemic has increased significantly, whilst the collection of recyclables has been suspended by many local authorities. The current waste management and recycling sector struggles to efficiently cope with changes in waste volumes and composition. In parallel there are calls for a 'green recovery' for the UK, with waste management, recycling and renewable energy at the forefront of the much-needed transformation. The ReSuB (Renewable &amp; Sustainable Biomass) project responds to both these challenges. The project will demonstrate and develop new value chains and markets for recycled paper, simultaneously supporting the UK's growing renewable energy industry. Fiberight has developed an innovative circular economy solution to create value-added products from residual waste, which is typically landfilled or incinerated. The ReSuB project will demonstrate the recovery of pulp from residual waste and the manufacture of products for the biomass fuels market. This market is actively searching for alternative products to current wood-based materials due to shortage of supply and therefore increasing costs. The project will carry out market testing with a biomass plant producing electricity. The ReSuB project will generate significant positive environmental impacts by diverting recyclable waste from landfill, by recovering valuable materials to be used again, by displacing virgin materials and helping to combat climate change. There will also be wider advantages of developing UK industry, with associated job creation and wider socio-economic benefits.</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Recovering pulp/materials from residual waste and diverting from landfill (Fiberight, as V032); recycling/resource recovery. Energy(biomass fuel) considered</t>
-        </is>
-      </c>
+          <t>CircularPSP brings together 7 procurers from 7 countries, representing 45 million citizens, to invest €5.64 million in R&amp;D to tackle the common challenge of accelerating digital transition towards a Circular Economy (CE). The Buyers Group represents highly attractive national markets (DE, FI, TR, SE, IE, PT, SI) supported by a Preferred Partner in UK, including capitals with global influence (Berlin, Helsinki, London, Istanbul). The consortium represents European CE-transition and PCP leaders in science and practice. Suppliers are expected to deliver a new green digital public service and data platform enabling entire municipal operations (city) and the local economy (market) to choose, open up, and consume existing and new data. The solution is to support business processes and workflows to plan, procure and implement innovative CE-solutions across Europe more quickly and at larger volume. The unmet procurement needs are: tools to improve organisational and operational performance; data analytics using taxonomies to exploit and exchange CE information and data; removal of language barrier to unlock EU-wide knowledge and learnings. To enable the transition suppliers will answer with ICT innovation in the cross-cutting combination and leveraging of existing and new strategic digital technologies: 1) scalable platforms for city and SMEs users, 2) CE data analytics using EU taxonomy, open linked data, injected by AI, and 3) natural language processing (NLP) to break language barriers across the EU and beyond. The envisaged solution is relevant for all European authorities including cities, ministries, agencies, and housing. Activity triggered by the solution will increase the volume of circular procurement and widen commercialisation opportunities for green digital companies and result in EU leadership in Circular Economy. With interoperability at the core and innovative tools for data sharing and open standards, the solution will provide a use case for the upcoming Co</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3925,39 +2941,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>58ECCF6F-6B3D-47F9-9D03-4DF518F6B356</t>
+          <t>748B4B7F-2943-4549-A053-331AC5B03F50</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>Re-REwind</t>
+          <t>Novel machine learning techniques to generate high spatio-temporal resolution urban climate observations for climate adaptation</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>Rare earth magnets, based upon neodymium iron boron (NdFeB), are a key component / material in direct drive wind turbines, where they are used in the generator. However these materials are top of the risk register on the UK's critical minerals list. The UK has vast wind resources and as such the government has invested heavily, in particular, in offshore wind turbines where direct drive turbines play a key role. As these turbines reach end of life it will present a significant opportunity as a secondary source for recycling or re-use. The aim of the Re-REwind project is to develop a circular economy for rare earth magnets from end-of-life wind turbines. This additional volume will be critical for not only the UK, but also the global decarbonisation agenda, with this being 'additional' material which can help avoid the upcoming global supply shortfall which is predicted. This project will look to build the basis for a new complete circular supply chain for these magnets, a completely new industry and sector which the UK currently does not have. To do this, it will tackle several key challenges; firstly how to dismantle the turbines, secondly to develop techniques to safely demagnetise and separate the rare earth magnets from the generators and then how to purify and to recycle the extracted materials back into new NdFeB magnets with properties which can be used in another generator. The Offshore Renewable Energy Catapult (OREC) will undertake a life cycle, and techno economic assessment, looking at the opportunity for recycled magnets, and critically their CO2 footprint, relative to virgin supply. This will allow the UK to fully understand the additional material which can be supplied, and the competitive advantage these will bring. All partners are also heavily involved in improving and disseminating industry best practise with regards to the safe handling of magnets. This will look at demagnetisation options, in addition to handling of full assemblies, magnet stack</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Circular economy/recycling of rare-earth magnets from end-of-life wind turbines (dismantle, demagnetise, purify, recover); resource recovery of critical materials. Materials(magnets) and Engineering(separation) considered</t>
-        </is>
-      </c>
+          <t>As cities worldwide expand, urban areas are experiencing rising air and surface temperatures. These temperature increases exacerbate the impacts of climate change, threatening the health, well-being, and livelihoods of urban populations. To mitigate these risks, urban planners and policymakers must adopt climate adaptation and resilience strategies that account for the specific conditions of each city. This requires access to accurate, high spatio-temporal resolution urban climate data. This data can help assess risks, hazards, exposure, and vulnerabilities to climate impacts. However, many cities, particularly in the Global South, lack the necessary resources or infrastructure to gather this data in sufficient detail, limiting their ability to plan for climate change effectively. This research proposes an innovative approach to address this challenge by integrating crowdsourced urban climate observations from Citizen Weather Stations (CWS) with satellite and remote sensing data. The aim is to generate high-resolution urban atmospheric dynamics (500m) observations in data-scarce cities. The research methodology will focus on three cities located in different climate zones, allowing for a comparative analysis of urban climates across diverse environments. The research will develop a full statistical analysis of existing data sources and employ machine learning techniques, particularly deep learning models, to develop high-resolution datasets generated by the integration of CWS and remote sensing data. Finally, novel transfer learning techniques will be used to apply models trained on cities with rich datasets to those with sparse or incomplete data. This approach would allow for more accurate predictions of urban climate behaviour globally, even in data-poor areas. A key novelty of this thesis lies in the use and integration of novel and rich urban datasets with advanced machine learning techniques. The project will use CWS data, which is crowdsourced and often hyper</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3967,39 +2971,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D2C508FE-5E71-4714-90D0-3BD7EC4A4A79</t>
+          <t>89490A4D-94EE-4FB4-ADB0-EBB3B5BC319D</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>COVID</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>Organofunctionalisation of Polyoxometalates for Photocatalysis</t>
+          <t>Optimisation of multi-rotor wind turbines combined with advanced design techniques to enable lower environmental impacts and reduced cost of energy.</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>The fundamental goal of this collaborative research project is the development of synthetic methodologies that will allow for the efficient construction of medicinally relevant compounds from simple, readily available starting materials. In this context, the project involves the design and synthesis of novel photocatalysts that can be exploited in synthetic organic reactions. Harnessing light to promote reactivity can be viewed as a more sustainable and economic energy source when compared to conventional methods such as heat and can be used to overcome significant reaction barriers. The most used catalysts in organic photoredox chemistry involve transition-metal complexes comprised of iridium, rhodium, or ruthenium. However, these platinum-group metals are rare, expensive, and usually require pre-functionalised starting materials for the reactions to proceed. In recent years, the development of catalysts that avoid these metals have shown promise in this field. However, these catalysts have limitations including low selectivity and the requirement of high energy UV-light. Furthermore, the reactions developed using these catalysts can be low yielding, be limited in scope and display competitive product decomposition. Crucial to progressing in this area is the development of novel visible light responsive photocatalysts that can be modified to (i) enhance the catalytic efficiency, (ii) exhibit additional functionality - that can be used to facilitate catalyst isolation and/or recycling, and (iii) increase the reaction rates and yield. This has sparked the drive towards more sustainable, tuneable, and selective visible-light active photocatalysts that can be used in synthetic organic reactions. In terms of organic reaction types, particular attention will be focused on photocatalytic C-H functionalisation for this project. Couplings through C-H bond functionalisation involves the use of simple substrates that are directly converted into more complex molecules, without</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Designing/synthesising novel photocatalysts and synthetic methodology (photoredox C-H functionalisation) to make compounds; bench synthetic chemistry</t>
-        </is>
-      </c>
+          <t>As illustrated by Vestas' V236 - 15 MW turbine, the driving economics of wind turbines have led to gigantic blades made of high-performance materials such as thermosets glass and carbon fibre reinforced polymers (FRP). However, there currently exists no viable process to recycle thermoset FRP blades without degradation of material properties. Hence, blades often end their life in landfills or are incinerated; undesirable scenarios resulting in significant Environmental Impacts (EIs) and loss of material capital 1. This issue is further exacerbated by the fact that the manufacture of carbon fibres is energy intensive and has substantial Global Warming Potential (GWP ), i.e. more than 10 times that of glass 2. This lack of sustainability and circularity is a thorny problem which the wind industry and academia are trying to solve using thermoplastic and vitrimer resins to enable, in theory, fully recyclable blades 1. Even if promising, these technologies are still in development and many technical and practical questions remain regarding, for instance, the quality of the recyclate; how to separate complex blades into their constituents; and the EIs of these recycling processes. More importantly, replacing one resin system by another doesn't fundamentally alter the wind turbine design and its scaling laws, meaning that blades will continue to require extensive amounts of carbon fibre and other raw materials.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4009,39 +3001,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7A77B730-23CD-4720-BE28-3EA2C641F0B4</t>
+          <t>94F32820-6C33-4DF9-BFDD-ECC5EF87978B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Horizon Europe Guarantee</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>Pushing the Frontier in Computational Catalysis with the Development of kinetic Monte Carlo Methods for Complex Surface Reactions</t>
+          <t>MODULAR ELECTRICAL GENERATOR PTO SYSTEM FOR WAVE - MEGA PTO WAVE</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>Solid catalysts are employed in more than 85% of industrial reactions, whose economic impact is estimated to 30-40% of global GDP. Heterogeneous catalysts also play a central role in the production of high-value chemical compounds, such as fuels and additives, pharmaceuticals, and polymers (plastics). Recently, these materials have attracted significant interest in the context of sustainability, CO2 utilisation, and green-chemistry, as they can facilitate transformations such as CO2 or biomass to useful chemicals at high efficiencies. Thus, motivated, the project will develop advanced computational methodologies and an integrated kinetic Monte Carlo (KMC) framework for the simulation of complex reaction kinetics on solid surfaces, focusing in particular on photo(electro)catalysts which may undergo structural changes as the reaction progresses. In this D.Phil. project, these methods will be extended aiming at (i) improving the robustness of the approximate acceleration algorithms by introducing mathematically rigorous ways to calculate error norms and improved strategies to down-scale kinetic constants, (ii) tackling the simulation of dynamic lattices, to take into account catalytic surface reconstruction explicitly in the modelling, (iii) introducing photo(electro)chemical events in the KMC framework making it possible to model chemistries relevant to sustainability, such as solar-powered CO2 conversion to valuable products. The project includes mainly mathematical computational method development activities, and will deliver a general-purpose framework for the accurate simulation of photo(electro)chemical processes. The host lab has previously developed computationally efficient approaches, algorithms and code, based on the KMC method, enabling the high-fidelity modelling of catalytic reactions in which several parallel and competing reaction pathways exist, and the participating surface species may exhibit alternative binding configurations and may be subject to l</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Computational kinetic-Monte-Carlo method development for reaction kinetics/mechanisms on catalytic surfaces; reaction dynamics/mechanisms. Chem Eng(catalysis and surfaces) is a strong alternative</t>
-        </is>
-      </c>
+          <t>The world faces the challenges of transitioning to net zero emissions to combat climate change, requiring a shift from fossil fuels to renewable energy sources, like wave energy. Yet, the integration of wave energy into the global energy mix is not without hurdles. Harnessing the power of ocean waves requires innovative and reliable technologies that can withstand the harsh marine environment while ensuring consistent energy generation. Moreover, the pursuit ofsustainable energy production extends beyond emissionsreduction, to embrace circular economies. Circular economies advocate for a holistic approach where resources are continually reused, repurposed, and recycled, thus minimising waste and maximising resource efficiency. For the wave energy sector, this means not only developing efficient power take-off systems but also considering the lifecycle impacts of materials, manufacturing, installation, operation, and decommissioning. The MEGA PTO Wave project aims to provide an enabling technology to transform ocean waves into clean, reliable energy. Through this project, a smart, scalable system will be created that adapts to changing conditions and keeps working even if a part of the system experiences a fault. By designing all aspects of the MEGA PTO to be highly modular, incorporating novel axial flux magnetic gear, electrical generator technology and adaptable power electronics, the project will make energy production more efficient and eco-friendly. This modularity creates a system that is easier to manufacture, transport, install, maintain, remove and recycle, than alternatives. The MEGA PTO Wave project brings together expertise from all over the EU to create a PTO linked to sustainable supply chains, to accelerate wave energy commercialisation to capture vast amounts of predictable energy in a sustainable and cost effective manner, in order to meet EU NetZero targets by 2050.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4051,7 +3031,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8518323A-43F3-4CF5-BAEF-0E85C3C1D998</t>
+          <t>1DDC2707-B0B1-4EB5-9852-363D10DDFB75</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4061,29 +3041,17 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>Photonic breadboards: next generation components for net-zero photonics research</t>
+          <t>JWEL ltd. - Ethical, Sustainable, Fair Trade Jewellery</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>Photonics is set to become the UKs third most productive manufacturing sector by 2035 with many innovations enabled by photonic integrated circuits (PICs). The development of PICs, whilst necessary, requires many energy intensive cycles which negatively affect the environment. These development cycles are needed because once fabricated the layout of the device cannot be improved without additional fabrication. At Light Trace Photonics, we are developing the next generation of optics components that go beyond the limited scope of current fibre-based componentry and which enable reconfigurability without additional fabrication. Our component modules provide high-performance, tunable, optics componentry that can be used to cut the number of energy intensive development cycles required to bring photonic products to market. Crucially, our core technology is long lasting and therefore can be leased to multiple users over its lifetime, helping to contribute to the circular economy. Our innovation, if brought to market, will help reduce the footprint of photonics innovation - crucial for helping the UK tackle many of its other key strategic challenges such as the ageing society and future mobility.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Developing reconfigurable/tunable photonic (optics) components and integrated circuits as products; applied photonics/electronic engineering. Physics(photonics, off-list) considered</t>
-        </is>
-      </c>
+          <t>JWEL is an innovative circular economy and sharing based retail and B2B platform with the aim of reducing and offsetting the depleting resources and detrimental environmental/societal impacts of the jewellery industry. The brand that focusses on being an ethical, sustainable, resource efficient choice for the consumer that would otherwise not consider the impact of their purchases. As a society we are becoming more conscious of traceability with food, clothing, household goods, etc. but not jewellery. JWEL aims to change that. Our collections are: 1. Antique - Historical, pre-loved pieces to re-use what is already in circulation. Avoiding the depletion in resources being the most Eco-Friendly way of purchasing jewellery. 2. Handmade - Collaborating with brands, artists and our in-house jeweller to create limited edition pieces from Fair Trade or refined from recycled electronics - precious metals and minerals. 3. Mother Earth - Using sustainable innovative methods such as meteorite impact surface mining, locally sourced precious minerals, etc. to produce trend focussed styles targeted towards the healing, yoga and reiki consumer at affordable prices. 4. Fine Silver - Recycling discarded silver to create high quality trending pieces to directly compete with high-street giants such as Pandora. 5. Watches - the promotion and sale of antique, rare watches that are otherwise discarded. As the male sports watches increase to an achievable price, the consumer is turning to alternative brands and smaller sizes as trends shift, JWEL caters to and thrives within this demographic. Our collections give the consumer a user friendly way to share the impact of maximizing the social good with an auditable and fair supply chain when purchasing jewellery by being innovative and providing traceability &amp; transparency. JWEL does this by making use of technology and more sustainable and ethical methods of production such as the use of recycled gold from electric waste, lab grown, locally</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4093,39 +3061,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10B0ED4C-4182-4FCD-B5A2-F4E91A870A30</t>
+          <t>11AA98DF-6876-48D9-B271-8C7FF9AC5049</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>ISPF</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>Circular Robot 5.0: Industry-Wide Data-Driven Circular Economy of Industrial Robots</t>
+          <t>Empowering Green Womenpreneurs</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>Research aim: To investigate digital solutions to promote a circular use of traditional/collaborative industrial robots (IR) in manufacturing lines by extending the useful life as well as enabling their end-of-life (EoL) remanufacturing and recycling of embedded critical raw materials (CRM). Context: The UK, being the eight largest manufacturing economy, is increasing its reliance on industrial robots (IR) within its manufacturing sector. According to BEIS's research, the country's industrial robots market is projected to grow at over 40% annually from 2020-2030. However, this rapid integration brings concerns with regards to environmental sustainability, given that decommissioned robots and related equipment often contain large amount of CRM. Challenge: The primary challenge is managing the environmental impacts of the widespread use of IR in various sectors like automotive, aeronautical, and healthcare. Current maintenance practices in the UK often rely on manual checks and standard procedures, leading to over-maintenance, high costs, and missed faults. (lack of trusted monitoring data) during use stage, the EoL management involves costly refurbishment to enable a secondary use cycle (often by a different end-user) and/or downcycling of CRM due to adoption of inappropriate material recycling processes. Objectives: Enable real-time access to authentic performance and service history data of IRs recorded within a digital passport, using advances in AI and blockchain. Prolong the operational life of IRs, thereby reducing the need for repairs or replacements. Facilitate remanufacturing and circular use of CRM. Develop a digitally-enabled EoL management system for IRs. This system aims to predict future IR failure scenarios, promote industry-wide collaboration, and enhance operational efficiency and resilience. Implement a proactive, data-driven lifecycle maintenance approach that is cost-efficient, optimizes equipment performance, and ensures environmental sustainabil</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Digital solutions (AI, blockchain digital passport, predictive analytics) for circular use/EoL management of industrial robots; the research is the digital/data system. Engineering(robots/remanufacturing) is a strong alternative</t>
-        </is>
-      </c>
+          <t xml:space="preserve">This project aims to develop a Circular Economy (CE) model specifically for micro and small beauty sector businesses led by women in Brazil, with benefits that extend to Global South countries. As the initial phase of a larger collaboration, this project will lay the groundwork by establishing essential connections and gathering preliminary data, with the goal of promoting sustainable and environmentally friendly women-led entrepreneurship. The initiative is a partnership between Coventry University in the UK and Fundação Getulio Vargas (FGV) University in Brazil. The beauty sector in Brazil, predominantly led by women, produces 120 billion pieces of packaging annually, representing 70% of its total waste. This significant environmental challenge, exacerbated by chemical waste from beauty products, threatens soil, water, climate, and human health. Women are central to this industry, with 285,000 female-led micro-sized businesses in São Paulo alone. They constitute 46.7% of Brazil's 13.2 million micro-entrepreneurs, contributing over £8 billion annually to the economy. To address these challenges, the project will empower female entrepreneurs in Brazil by leveraging UK best practices in CE, focusing on sustainable waste reduction, treatment, and management. As key drivers of economic activity and primary decision-makers in 72% of Brazilian households, women have the potential to influence broader societal behaviors and norms through sustainable practices. Targeting women aligns with Sustainable Development Goal 5 (Gender Equality) by removing barriers to their economic participation and ensuring equal access to resources. This project also supports SDGs for industry innovation (SDG9), sustainable cities (SDG11), responsible consumption (SDG12), climate action (SDG13), and global partnerships (SDG17). Empowering women in this sector addresses gender inequality while driving environmental sustainability and economic growth, with the potential to boost inclusive growth </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4135,39 +3091,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>32849D76-D030-4E27-BC4E-199DFA8A3545</t>
+          <t>341C276D-F054-4203-8240-2E9408C81464</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Computational Chemistry Supported Investigation of Sustainable Organic Coatings</t>
+          <t>Development of a low-carbon cementitious material by recycling Calcium Carbide Residue (CCR) waste from foundation industries to decarbonise construction sector</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>The main objective of this project is to computationally design sustainable organic coated steel (OCS) products with tailored functional properties that meet operational performance while addressing environmental and social concerns. Global challenges associated with resource scarcity, climate change, overpopulation and overconsumption have resulted in recent global and regional initiatives such as the United Nation's 2030 Agenda with the sustainable development goals (SDG) and the European Green Deal. Such initiatives, in parallel with social concerns, have highlighted the importance of driving sustainability across most of the sectors of our society. Aligning with these ambitions of achieving climate neutrality by 2050, implementing circular economy principles, reducing waste, and increasing materials efficiency and resiliency, the steel industry must make pioneering changes towards new product and process developments for all its upstream and downstream value chain operations. This project will provide a computational design framework to assist the development of sustainable OCS materials, with a focus on molecular reactivity, electronic and mechanical properties, in connection to materials' flexibility, corrosion, and stability under UV light.</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Materials Science</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Computationally designing organic-coated-steel materials and their properties (corrosion, mechanical, stability); material behaviour. Chemistry(computational/molecular reactivity) strong alternative. Field not in dropdown</t>
-        </is>
-      </c>
+          <t>The principal motivation behind this project is to develop a technologically feasible and economically viable alternative low-carbon cementitious material by utilising Calcium Carbide Residue (CCR), a 'zero recovery value' waste material produced in vast quantities within bulk chemical manufacturing and metallurgical industries. The idea is to expand circularity and enhance symbiosis between the foundation industries by utilising CCR waste to produce structural and non-structural concretes and bricks with a reduced carbon footprint.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4177,7 +3121,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>31D3D9C3-1F84-41A2-A622-888F79EFE238</t>
+          <t>E26C4093-DE5B-4235-9D13-F0AF995BF7C7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4187,29 +3131,17 @@
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>University of the Arts, London and Haiper Limited AKT3</t>
+          <t>Creating a low carbon, environmentally sustainable and socially just value chain for rare earth magnets</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>To revolutionise fashion content creation by using Haiper's AI model to transform single photographs into diverse digital content, reducing the need for multiple shoots. This innovation can facilitate sustainable choices such as minimising travel, reducing resources, and enhancing demand planning, driving the fashion industry towards a more circular economy.</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Applying a generative AI model to turn single photos into varied fashion content; AI/ML is the innovation. Thin; Arts(fashion) considered</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NdFeB magnets drive low-carbon futures. Their unique high performance properties outclass alternatives, including SmCo magnets. Securing sustainable rare earth (RE) sources for NdFeB magnets is vital to meet global sustainability and climate goals. However, global RE value chains are associated with poor environment, social and governance (ESG) performance. This increases risks and undermines sustainability aims, whilst adversely impacting new generations of RE mines and refineries being created by UK companies such as Pensana. This project supports innovative business model creation, incorporating low-carbon, environmentally sustainable and socially just approaches to ensure a resilient and sustainable supply chain for NdFeB magnets. Limitations in data cause RE lifecycle assessments (LCA) to run only as mine-to-magnet, ignoring the impacts of the use, end of life and circular economy phases. Moreover, gross estimations are forced, to fill data gaps, creating impact assessment difficulties and challenges for improving ESG performance, whilst undermining supply chain resilience. This project has two aspects. 1.A novel and unique assessment of environmental and social impacts across the entire NdFeB value chain, surpassing traditional LCA analysis by identifying individual impact measures, and considering both positive and negative impacts and how they interface with each other. 2.Combining industrial and academic expertise to identify potential material interventions, thereby maximising environmental sustainability and adding social value across the entire value chain. The project uses Route2's innovative V2S platform to assess impacts across six major capital categories in sustainable global value chains; from Pensana's mine in Angola to the global centre for RE processing in Hull, to Polestar's downstream use and end-of-life phases. Route2's model uses an integrated reporting focus, allowing for both positive and negative impact assessment. The unique partnership </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4219,39 +3151,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ECEC40D1-3085-44D0-861D-7AC11E6B3FFA</t>
+          <t>5117C25D-6B3D-4F9F-963A-34E33E461E44</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>AHRC</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>ECOSENS: Economic and Social Considerations for the Future of Nuclear Energy in Society</t>
+          <t>Sustainability and biodiversity in Scottish tea growing: a design-led approach to automated production practices</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>Using a deliberative approach, ECOSENS will analyse citizens’ views and risk perceptions, benefits and potentials of current and new nuclear technologiesin the context of majorsocietal challenges(climate crisis,sustainable energy policies, energy security). It will review through a socio-ethical lens the uptake of recommendations on stakeholder engagement and transdisciplinarity (notably integration of social sciences and humanities) in nuclear research and decision making, developing recommendations to overcome challenges. Societal stakeholders (authorities, industry, academia and civil society) are engaged to explore and co-construct possible energy futures and the role of nuclear energy therein. Sustainability assessment of current nuclear energy technologies will take into account the entire life of the nuclear investment including the nuclear fuel cycle. Integration of new technologies (Gen III+, IV, SMR) is then explored in the context of the future energy market and societal developments to identify the possible roles of nuclear energy in the climate neutral economy targeted for 2050. Multiple perspectives (nuclear experts, social scientist, stakeholder, society) are integrated and methodological recommendations for sustainability assessment are agreed. To address the weaknesses of existing economic models, ECOSENS develops a novel model based on the system of provision approach in order to create and calculate indicators relevant for a plethora of stakeholders (consumers, governments, suppliers). The model will include the “social discount rate” and considers the limits of our planet, as reflected in the “circular economy” system. A series of national case studies evaluates the model and provides relevant recommendations to stakeholders. ECOSENS activities and results will be largely communicated and disseminated through the network of stakeholders established to support innovative involvement, as well as through Open Access facilities</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Social Sciences</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Deliberative analysis of citizens' views/risk perceptions and socio-ethical/stakeholder study of nuclear energy's societal role; sociology/STS/policy. Economics(the economic model) considered</t>
-        </is>
-      </c>
+          <t>This project will result in the first carbon-neutral Scottish tea and a framework for how ecological and sustainable farming practices can be implemented in this nascent UK industry. It will be achieved through a design-led approach to the environmental profiling of the tea growing process, implementation of an autonomous and sensor-equipped mower, and the evaluation of performance using a digital profiling platform. There are currently around 30 tea gardens in Scotland. Islay Henderson of Glen Caladh Tea chairs a group of 13 tea growers called Tea Scotland who work together, sharing skills and knowledge around the challenges of growing and processing tea in a northern climate. As the first growers in this small industry, with no precedent to be confident of tea cultivation skills specific to the region and microclimates in Scotland, there is an opportunity to establish effective and responsible practices. To this end, research and development is critical to making a success of a circular economy model in Scottish tea growing, and to influence growers towards creating a positive industry for the environment at the outset. Growing tea has huge potential to be a positive ecological activity. The lifespan of a tea plantation is 50-100 years which provides long habitat continuity, hosting multiple species of flora and fauna contributing to biodiversity and sustaining a healthy soil. The Glen Caladh Tea plantation can maintain and support sub-habitats, allowing for a mosaic of multiple land-covers. In an organic system, mowing is the main method of weed control and feeding the tea. In this context, it is critical during the first seven years of growing to keep weeds down and help the plants uptake the nutrients they need. This is relevant to all the main activities on the plantation once the plants are moved outside from the nursery, including composting, mulching, weed control, and feeding. We therefore propose the implementation of a smart, autonomous, electric mower t</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4261,7 +3181,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C665C824-CDF7-4179-A355-D3C95376770D</t>
+          <t>99488AEA-4B48-4A2F-958B-9C54FD13648E</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4271,29 +3191,17 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>EPSRC Manufacturing Research Hub in Robotics, Automation &amp; Smart Machine Enabled Sustainable Circular Manufacturing &amp; Materials (RESCu-M2)</t>
+          <t>Novel, bioinspired, aligned-discontinuous reclaimed fibre composites for enhanced compressive performance</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>The Circular Economy requirements and sustainability goals have been set out by the UK government and the United Nations to address the climate crisis and maintain our standard of living. The environmental impact from the global consumption of engineering materials is expected to double in the next forty years (OECD: Global Material Recourses to 2060, 2018), while annual waste generation is projected to increase by 70% by 2050 (World Bank What a Waste 2.0 report, 2018). A radical departure from traditional forward manufacturing is needed that no longer exclusively focuses on the original manufacturing process and the end of life dispose of manufactured products, parts, and materials. Processes are needed that will significantly prolong the useful life of engineering and especially critical materials (minerals with high economic vulnerability and high global supply risk e.g. rare earth elements for batteries, magnets and medical devices) by increasing the effectiveness of reuse, repurpose, repair, remanufacture, and recycle (Re-X) manufacturing processes. These Re-X processes are currently 3-6 times more labour intensive than traditional manufacturing processes. They are often not economic resulting in many engineering materials being disposed on landfill sites, degraded, or incinerated. UK businesses could benefit by up to £23 billion per year through low cost or no cost improvements in the efficient use of resources. The vision of this hub is to pursue an integrated, holistic approach toward creating a new manufacturing ecosystem for circular resource use of high value products through advances in AI and intelligent automation, empowering the UK to be a world leader in circular manufacturing. To deliver this ambition the hub will focused on two grand challenges: GC1: Radically transform the sustainable use of critical materials. (Goal: &gt;75% Critical components reuse; &gt;20% critical material use decrease; &gt;50% component reclaim increase). GC2: Radically improve the p</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Re-X (reuse/repair/remanufacture/recycle) circular-manufacturing processes with robotics/AI automation for critical materials; manufacturing. Env Sci(circular resource use) considered</t>
-        </is>
-      </c>
+          <t>Despite over 60 years of active research and considerable improvements in properties relating to tensile strength and impact resistance, compressive strength levels in composites are still some 40% lower than measured longitudinal tensile strengths. This relative weakness, and the difficulty in systematically modelling the resultant anisotropic failure mechanisms, represents a significant barrier to the wider industrial adoption of these materials. This research project forms part of the EPSRC supported Next Generation Fibre-Reinforced Composites (NextCOMP) programme, concentrated on developing novel composite materials to meet this challenge. A principal focus is investigating hierarchically structured materials, inspired by natural composites such as bone and wood. These biomaterials feature dissimilar but complementary reinforcement systems across length scales and exhibit higher compressive load carrying capacities than traditional manufactured composites. It is anticipated that a new generation of manufactured composite materials able to mimic such architectures will find numerous innovative industrial applications including in the aerospace, energy, and automotive sectors. Discontinuous fibrous materials have historically been used as bulk reinforcement in manufactured composite structures due to lower overall mechanical properties. A key determinant of their performance being the degree of fibre alignment. The High-Performance Discontinuous Fibre (HiPerDif) process developed at the University of Bristol is a proven method for producing composite tapes of highly aligned discontinuous fibres of between 1 and 12mm in length, utilising water as a transfer medium. The process offers the potential to produce materials with mechanical properties comparable to those of continuous fibre composites, given a fibre aspect ratio high enough to allow load transfer and fibre pull out. Furthermore, highly aligned fibre composites have shown strong promise in overcoming curre</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4303,39 +3211,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>F95C60D9-82F9-45A0-854A-A6457940EF63</t>
+          <t>6E54086C-3F77-4DB4-8D50-B6B39EC1DE0E</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>NERC</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>Ammonia synthesis revisited: Moving towards the limits of catalysis</t>
+          <t>Understanding and enhancing plastics biodegrdation</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>Single atom catalysis (SAC) is an exciting, growing field of research which has attracted considerable attention over the last decade. While the field is in its relative infancy, single atom catalysts have been observed to hold a plethora of advantageous characteristics. Aside from an inherent decrease in degree of saturation which can result in higher activity, moving towards smaller catalyst systems results in a shift from the continuous energy bands present in bulk metals, to discrete energy levels in single atoms or small clusters. This change facilitates a range of unique electronic and geometric structures which possess distinct, size-dependent properties relative to the bulk material which have the potential to be exploited for applications such as catalysis, if the relationship between cluster-size and activity can be understood and controlled. In fact, a number of studies have reported distinct catalytic pathways observed for SACs in comparison to their nanoparticle counterparts, with some displaying enhanced activities and selectivities. This enhancement has been attributed to factors including a higher degree of unsaturation, quantum size effects, significant support-metal interactions and access to different quantum states and configurations. With each of these aspects imparting the possibility of tuneability, SACs provide an opportunity to revisit the optimisation of reactions from a completely new perspective and toolkit. The Haber-Bosch Process (HBP) is arguably the most famous catalytic reaction, which is estimated to account for 1% of the world's energy usage, because of the harsh operating conditions required. Despite 100 years having passed since the invention of the HBP and substantial research efforts, the ammonia synthesis industry remains dominated by the historic iron catalyst with operating conditions mirroring those described in Haber's Nobel lecture in 1920. This presents the perfect opportunity to revisit ammonia synthesis from a new lens</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Chemistry</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Fundamental single-atom catalysis: electronic/geometric structure, catalytic pathways, activity/selectivity for ammonia synthesis; catalyst science/mechanisms. Chem Eng(catalysis and surfaces) strong alternative</t>
-        </is>
-      </c>
+          <t>Reducing the impact of plastics on our environment is an urgent task that needs new fundamental and technological solutions. Part of the solution is to develop "better" plastics,well-designed for their intended use and with appropriate end-of-life options. This will include compostable and recyclable materials made from renewable resources at a cost and performance comparable to, or even better than, current petro-based equivalents. Thus, the past few years have seen an increasing demand for bio-based and/or non-durable plastics, so-called bioplastics. Poly(lactic acid), or PLA, is a bio-based polyester and the flagship of degradable bioplastics. Due to its properties and long-standing development, there is an increasing demand for PLA. Its annual production is currently at ~435 kT worldwide and an expected production capacity increase of 80% is predicted by 2026. Crucially, the change in claims regarding its end of life options over the past 15 years, from being biodegradable (implying complete degradation to CO2, water and biomass in natural conditions) to industrially compostable (degradation incontrolled conditions, including temperatures above 60 degree centigrade, controlled humidity and selected microorganisms) highlight how much the degradation of PLA, and bioplastics in general, is poorly understood and requires attention. Despite significant efforts, the biodegradation rate of PLA in industrial compost conditions remains low, reducing its acceptance in composting facilities (e.g. when PLA is used in disposable compostable packaging and collected along with mixed food waste). In home compost or soil (e.g. when deposited in the environment), PLA biodegradation is inexistent over a sustainable timeframe. In this project, we will design bespoke polymeric additives to enhance the composting of PLA. (e.g. by promoting microorganism growth to speed up the biodegradation process). We propose, not only to develop polymeric additives, but also to combine them with n</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4345,7 +3241,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>40BFE145-CF83-449E-AC3F-AABF57517212</t>
+          <t>4FAE6E2B-8DBE-47C0-A647-3C643A9D047B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4355,29 +3251,17 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>Developing a pipeline for rapid optimisation of transcriptional expression regulation</t>
+          <t>Engineering of human artificial chromosomes to decipher the mechanisms of chromosome instability-driven prostate cancer progression</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>A key challenge in engineering biological systems is the development of re-usable, precise and tunable gene expression control elements. Currently, developing these systems requires expensive and time-consuming experiments based on trial-and-error. This is particularly problematic for applications requiring complex systems with multiple co-regulated components or systems that use components obtained from non-model microorganisms. This project will develop tools to systematically characterise transcriptional control elements, uncovering their design rules to enable re-use of these control elements in alternative hosts and genetic contexts. Transcriptional regulation in prokaryotes is achieved primarily through the binding of transcription factors (TFs) to a promoter. Each TF has a specific binding preference, which determines its function (activator or repressor) and the location of its binding site(s) within a promoter. Knowing the biophysical binding preferences of TFs, hence, enables computational prediction of the regulatory logic and the transcriptional activity of any given promoter1,2. Currently, however, the biophysical binding preferences are known for only a handful of TFs, meaning that we cannot easily exploit heterologous TFs in bioengineering. In this interdisciplinary project, the student will utilize a range of molecular/synthetic biology, microbiology, and biophysical approaches to: (i) develop an experimental and data analysis pipeline that can determine the binding preferences of any given TF; (ii) unravel design rules of activators; (iii) use the pipeline to study the evolutionary rules governing how TFs adapt to heterologous hosts. As such the student will acquire skills that are highly relevant for future careers in the molecular biology and microbiology, biotechnology, biopharmaceutical, industrial biotechnology and related industries. Achieving these objectives will enable researchers to rapidly characterize the function (i.e. binding preferenc</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Biochemistry, Genetics and Molecular Biology</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>certain</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Characterising transcription factors/promoters and design rules for gene-expression control via molecular/synthetic biology; molecular genetics. Field not in workbook dropdown; coded per protocol's twelve</t>
-        </is>
-      </c>
+          <t>Prostate cancer (PCa) is the most commonly diagnosed cancer in the UK and Europe, and responsible for close to 110,000 male deaths annually. Up to 20% of PCa cases present hallmarks of genomic instability characterized by chromosomal amplifications in the right arm of chromosome 8 (Chr.8q) -commonly associated with treatment resistance and poor survival rates. The Chr.8q region harbours the c-Myc oncogene whose copy gain was thought to be a strong candidate to explain the poor prognosis. To note, c-Myc copy number alterations (CNA) in minimally gained 8q regions can involve the co-amplification of up to 40-50 other genes, some acting as oncogenes involved in prostate, ovarian and breast cancer.4 Given the genetic complexity of chromosomal gains, the functional consequences of these amplified loci remain unknown due to the lack of cell models that can recapitulate the full genetic sequence, and order of that sequence, for use in cell models, both in vitro and in vivo. Therefore, this proposal aims to implement and engineer human artificial chromosomes (HAC) to reproduce the observed genetic aberrations in patients to decipher the mechanisms of chromosome amplifications-driven increased metastatic capability of cancer cells. This project has the potential to create a brand-new gold standard approach to model, characterise and screen for new drug candidate against genomic instability-related diseases. Objectives: Objective 1. Implementation of human artificial chromosomes mimicking Chr-8a amplification; Objective 2. Computational analysis, assembly and incorporation of the Chr-8q amplified regions; Objective 3. Deciphering the impact of copy gain on cancer progression</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4387,39 +3271,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DC1041C2-7836-48F8-A8D4-103AF71B299F</t>
+          <t>53B9CA1E-90D1-4104-91DE-488B4EEB562C</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>Innovate UK</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>Hubs for Circularity European Community of Practice (H4C ECoP)</t>
+          <t>Peat-Free+ Recycling horticultural cropping substrates in a circular economy</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>Hubs for Circularity (H4C) are to be the European lighthouses of resource efficiency: through implementing best practice in industrial and urban symbiosis (I-US), the H4C are intended to achieve a step change in circular utilisation of resources and GHG emission reductions within given geographic areas. The European Community of Practice (ECoP) builds on and brings together ongoing work and expertise on H4C and I-US, initially supporting the H4C demonstrations funded under Horizon Europe. This project will develop both the ECoP network of stakeholders (commencing with funded H4C demo projects) together with an information and knowledge platform to enable stakeholders to take action. By creating awareness and fostering knowledge sharing between regions/cities and their industries, the H4C Platform will provide the tools and the evidence base for the approach to be adopted widely across Europe. A sustainable business model for deployment of the toolkit and services developed under the project will ensure the H4C ECoP is maintained well into the future. This consortium led by ISQ not only includes world leaders in the field (experienced in delivery, training, stakeholder engagement, models and methodologies) but also has the specific committed support and participation of many of the European bodies (those representing regions, cities, industry, educational institutions etc) that are needed to both disseminate the project outcomes and initiate implementation. Working closely with its sister consortium H4C-Europe, the H4C ECoP consortium is confident of delivering an ECoP and H4C platform that will achieve the target of greater circularity and carbon neutrality through profitable actions that also benefit communities/civil society.</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Social Sciences</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Building a community-of-practice stakeholder network and knowledge platform for industrial/urban symbiosis; knowledge exchange/coordination. Business(model) and Env Sci(industrial symbiosis) considered</t>
-        </is>
-      </c>
+          <t>This feasibility study will enable peat-free production of mushrooms and leafy salads by recycling plant-based substrates from other sectors (including anaerobic digestion, soft fruit and mushrooms). The main technical challenges in recycling peat-free organic materials for these specialist sectors are quality, consistency, crop timing and nutrient balance. This project will help to meet the DEFRA target of phasing out peat from UK horticulture. Currently exemptions are proposed for mushroom growing and salad propagation where no peat-free substrates exist on the market. By delivering a circular economy solution we will also contribute to achieving net zero emissions. The project team conducting the work includes leading growers, scientists and substrate processing experts.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4429,39 +3301,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6B342AF0-F434-47EF-B64E-209D07AF91B3</t>
+          <t>704F2E29-B301-4D05-A19D-203FF688D475</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>AHRC</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>TRICE – Tyre Rubber Into Circular Economy</t>
+          <t>New Composites: Diversifying material sources in a circular textile economy</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>The disposal of waste tyres is a significant environmental issue particularly as their disposal in landfill was banned in 2003 in the UK and Europe. Most tyres are "mechanically" recovered i.e. they're shredded, and the recovered rubber shreds and crumbs used in road and other rubberised surfaces and the recovered steel and textile reinforcements either re-melted or valorised, respectively. In the UK about a quarter of the 550,000 tonnes of arising waste tyres are exported as shreds -- much of it ending up in India, where they batch pyrolyse the shreds to produce tyre recovered oil, a heavily polluting sulphur containing fuel. In 2019, the Indian authorities began restricting tyre waste imports to the extent that this permanent change is expected by UK's Tyre Recovery Association, Environment Agency and Defra to place significant strain on UK recycler's ability to meet demand for recycling services. The UK desperately needs new capacity (in the form of pyrolysis operations and other technology) to avert heightening levels of fly tipping and make this waste stream more sustainable. BIG ATOM has developed the concept of a novel pyrolysis reactor with improved temperature control with the vision of a circular economy for waste tyres. We now propose to construct, test, and prove the concept of a quarter-scale reactor that is big enough to demonstrate the issues associated with scale-up. If the project is successful it will form the basis of a full-scale reactor for the commercial production of recovered Carbon Black (rCB) and Tyre Recovered Oil (TRO) of an improved quality that can be used as part of the circular economy to create new truly recycled materials.</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Waste-tyre pyrolysis to recover carbon black and oil (circular economy for waste tyres); recycling/resource recovery per the scheme's convention. The pyrolysis reactor + scale-up give Chem Eng a strong claim</t>
-        </is>
-      </c>
+          <t>The fashion and textile industries are significant contributors to pollution, resource depletion, and climate change. To steer human activity back within the limits of the earth's carrying capacity, the way we produce, use, and dispose of textiles needs to undergo radical transformation. This work is embedded in principles of sustainability such as reducing negative social and environmental impacts at each stage of a product or material's lifecycle, alongside circularity as a leading approach to sustainability, which endeavours to circulate resources without waste. The New Composites project aims to increase the diversity of resources used in textile design as a contribution to sustainability targets while embedding recyclability in textile design. The industry currently relies in overwhelming majority on two types of fibres, cotton and polyester, which together account for 76% of all global textile production (Textile Exchange, 2021). While improvements can be made in these fibre categories by using organic or recycled input, it is imperative that a wider variety of fibres should complement their use. The current focus on such a narrow range of resources leads to a lack of resilience in the sector as current price spikes or major disruptions caused by conflict or other obstructions of trade routes have shown. The project tackles the environmental and social impacts linked to the reduced biodiversity which comes from a focus on conventional fibres. Exciting and diverse innovation is currently taking place in the sector of alternative materials, for example materials made from pre- and post-consumer recycled fibres, bio-polyesters from corn, or regenerated cellulose from agricultural waste. However, these innovations are often not fully transparent in their composition and are difficult to access at scale. Moreover, as current guidelines for circular design focus on the fibres with the highest market share, little is known about how these new fibres are best employed</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4471,39 +3331,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BF545E07-CE6E-4D48-88EE-0245FEF15A46</t>
+          <t>ACE07A68-2B7C-4C31-8272-DB9743D0048A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Solar Battery Hub: A Safe, Secure, Sustainable and Affordable Alternative to Diesel Generators</t>
+          <t>Circular Economy for Offshore Wind</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>The Solar Battery Hub Phase 2 project is an ambitious project taking a holistic approach to addressing Nigeria's significant energy access challenges by replacing diesel generators with scalable, renewable energy systems tailored to underserved communities. With over 85 million Nigerians lacking access to energy, and 34 million SMEs reliant on costly diesel generators, this project delivers innovative clean energy solutions to bridge this gap. The Solar Battery Hub is a central energy distribution that will sit at the heart of communities, offering solar-powered battery swapping services for households, businesses, schools, and healthcare facilities. The holistic approach now also incorporates Moonlight Energy's e-mobility system that enhances renewable energy adoption through swappable battery technology for electric scooters and motorcycles, reducing reliance on diesel for transportation. Tree Associates' AirBattery introduces a novel compressed air energy storage system, delivering reliable baseload power for energy-intensive applications such as rice milling, healthcare, and irrigation. The project will be demonstrated in Tudun Wada, a rural community in Kano State with a population of over 228,000, where only 8 hours of electricity from the grid is available daily. The region heavily relies on diesel and petrol generators to support its vibrant agricultural economy, including 400 rice millers and over 3,470 SMEs. This demonstration will showcase how integrated clean energy solutions can transform productivity and resilience in regions facing severe energy access challenges. Key use cases include productive applications like agriculture, where 45% of farmers face post-harvest losses due to unreliable energy, and education, where 65% of schools lack electricity, hindering access to technology-based learning. By ensuring reliable electricity, the project directly addresses these critical sectors. The project creates economic resilience by creating local employment</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Renewable energy systems for energy access (solar generation, battery swapping, compressed-air storage) replacing diesel; energy is the object. Social(development/access) considered</t>
-        </is>
-      </c>
+          <t>Wind power is a renewable energy source which has seen a huge increase in usage over the past 50 years. For decades, wind power has been seen as a clean source of energy, but now increasing numbers of onshore wind farms are being decommissioned and the amount of waste generated is becoming a concern. With the increasing installation of offshore wind turbines, we are starting to ask, when is the best time to think about what happens to the turbines at their end of life? Circular economy (CE) is a way of thinking that challenges the traditional linear economy whereby raw materials are extracted, a product is manufactured, used and then is disposed of. It includes reducing the amount of material used right from the design stage, remanufacturing parts and recycling materials so that the end of life for one piece of equipment is linked to the beginning of life for another. This literature review looks at the research for different aspects of CE and reviews the metrics which are and could be used to measure circularity.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4513,39 +3361,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>69E93E66-744D-4DEF-808B-CC9CB7D24110</t>
+          <t>32609B87-FEEE-40CA-9FB8-BEDBBD710044</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee</t>
+          <t>EPSRC</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Smart and efficient ways to construct, maintain and decommission with zero emissions with transport infrastructure.</t>
+          <t>Circular Economy Innovation for Advancing Metal Substrate Perovskite Solar Cells</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>The overall objective of CIRCUIT is to develop a holistic approach supported by digital solutions and guidelines to foster the introduction of innovative engineering practices in the whole construction supply/value chain to foster The overall objective of CIRCUIT is to develop a holistic approach supported by digital solutions and guidelines to foster the introduction of innovative engineering practices in the whole construction supply/value chain enabling circular, sustainable resilient and smart transport infrastructure and a wider deployment of Green Public and Innovation Procurement. This will be achieved by: i. developing and deploying an innovative open-source digital platform (with advanced Circularity analytics and Supply/value chain matchmaking tools) interoperable with traditional engineering/ design (BIM, Digital Twinm LCC, LCA) and traffic simulation tools; ii. introducing modular solutions, ecodesign and reusing concepts as alternative to traditional designs; iii. maximizing the use of biobased, Secondary Raw Materials (SRM) and Secondary Construction Elements (SCE) as alternative to traditional ones; iv. including in the decision making process of transport infrastructures design and route planning, information from updated traffic simulation tools to reduce incidents, accidents, congestion and future scenarios with autonomous vehicles). New elements and technologies for Circular, Smart, Resilient and Sustainable transport will be included in the design process to facilitate infrastructures upgrading and a quick adaptation to smart mobility and operations. CIRCUIT will also provide knowledge and technicalsolutions by exploiting the potential of fourstrategic pillars: Digitalisation, Recycle, Reuse and Energy. Different technologies will be validated in each of the pillars to deliver a holistic approach suitable for different transport modes, the urban and interurban environment, and the different stages of the life cycle of infrastructures.</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>guess</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Circular, sustainable construction of transport infrastructure via engineering practices, modular/ecodesign, secondary materials; civil/built-environment. CS(digital platform/BIM) and Env Sci(circularity) considered</t>
-        </is>
-      </c>
+          <t>Although viewed as green-technologies due to their ability to generate renewable solar energy, emerging photovoltaic technologies, including perovskites, have environmental impacts associated with their production and will contain hazardous components. Widespread deployment will require a continued supply of critical materials and full lifecycle optimisation is necessary at this early stage in development to make these technologies truly sustainable. The current linear design of renewable energy technologies contributes to inefficient production and disposal practices, necessitating urgent innovation towards a circular economy. This includes minimizing production-related environmental impacts, developing end-of-life strategies, ensuring design longevity, optimizing cradle-to-cradle processes, selecting low-impact materials, and substituting primary resources. The project will focus on optimisation of end-of-life design for flexible metal-foil-based perovskite solar cells. This involves implementing processes like maintenance, refurbishment, remanufacturing, recycling, and transforming waste materials into manufacturing feedstocks. We will quantify the benefits of sustainability interventions, providing recommendations for sustainable materials, primary resource substitution, module designs, architectures, and processing methods. A priority list for materials recovery/substitution by employing resource availability mapping, lifecycle analysis, and sustainability indicators will be developed. Ultimately, the goal is to create eco-designed photovoltaic systems, enhancing the commercial viability and resource security of STRIPS technologies through the circular flow of materials.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4555,39 +3391,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>D4909ACC-503B-4F07-A969-5EE05DF7BDED</t>
+          <t>B862C76B-9689-447E-B4D1-1E6BB356134E</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>EPSRC</t>
+          <t>BBSRC</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>Transforming Islands in Sustainable Circular Energy Resource Hubs</t>
+          <t>Efficient utilization of biochar for water remediation and soil amendment - towards a circular economy</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>The purpose of this research project is to evaluate the future of islands and the potential of transforming them in sustainable energy resource hubs by taking into account of circular economy principles. The proposed Phd topic takes an interdisciplinary approach to analyse trade-offs associated with energy and resource use, by analysing consumption patterns and supply chains. Various environmental and economic factors will be considered to enable better management of energy resources in a circular economy. It will first start with a clustering analysis to identify patterns that might be relevant to several of them. Will then continue to gather data for energy and other resources for Scottish Islands and study the impact of various energy supply sources (e.g renewable energy, waste to energy, hydrogen) on energy demand-supply balance and potential for storage and interconnections under different climate scenarios. This will be achieved through scenarios analysis considering detailed modelling of energy demand (buildings, transport, service sectors), by determining the optimal combination of energy solutions for Scottish islands as a case study. The project is highly interdisciplinary one requiring an understanding of data processing, different modelling techniques, value stream mapping.</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Energy-systems analysis for islands: demand/supply modelling, supply sources, storage, scenarios; energy systems as a whole. Env Sci(resource use) and Engineering(systems) considered</t>
-        </is>
-      </c>
+          <t>Biochar is a sorbent material and the main solid product available from the thermochemical conversion of biomass. It has uses in a variety of environmental applications including the removal of pollutants from water and soil amendment. The global biochar market is set to reach a value of USD3.3 billion by 2025 based on its annual growth rate of 13% since 2015. Eutrophication in water bodies is a significant environmental problem cause by excess nutrients in water. One common cause of eutrophication is run off ground water contaminated with phosphate and nitrate from the leaching of chemical fertilisers. Biochar can adsorb excess phosphate and nitrate from water leaving a spent biochar which is suitable for use as a slow-release fertiliser - both cleaning water and removing a major pollution source. Currently multiple studies have been carried out in which various chemically activated biochars have been used for removal of phosphate and nitrate from water, then used as a slow-release fertiliser. While current research provides evidence this process could be successful, the research has been carried out at lab scale and predominantly in simple solutions of few different ions. Using experimental methods and computational modelling, this project will assess the performance of currently existing biochar activation methods in real eutrophic water and plant beds at SustainableThinkingScotland site. Following this, the project will aim to create a new novel biochar activation method with improved performance compared to current activation methods currently available in literature. This will allow for a more efficient process capable of being scaled up for real life use.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4597,39 +3421,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>D104C525-8363-41B5-9AD1-44A21758B451</t>
+          <t>2B9A3263-AC7A-49F1-950B-6B7263445992</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Innovate UK</t>
+          <t>COVID</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>Valorization and Upcycling the Concrete waste - a path toward net zero</t>
+          <t>Photochemical Characterisation of Perovskites to Inform Stability and Sustainability</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>Concrete, the most used material in the world after water, is responsible for 8% of global CO2 emissions. Most of such emissions come from the cement needed to give concrete its strength. At the same time, the UK's concrete industry extracts 180Mt/year of natural aggregates (sand/gravel) from our quarries and riverbeds, with huge negative environmental impact. The UK also produces 45Mt/year of 'waste' concrete from old, demolished buildings. Concrete absorbs CO2 through a chemical process called 'carbonation', which increases its strength. Concrete carbonation rarely happens naturally as it needs specific temperature, relative humidity, and can take 100+ years to occur. End-of-life concrete has huge potential to absorb significant amounts of CO2 and to be replace natural aggregates to produce new concretes. However, end-of-life concrete from demolition is very porous, and thus the strength of the new concrete is always below standards. Therefore the UK's concrete/construction industry downcycles end-of-life concrete in backfill/drainage applications. This project aims to develop new CO2-absorbing aggregates made of crushed upcycled end-of-life concrete from demolished buildings. We have an innovative technology that sequesters CO2 into end-of-life concrete (30% btw) and reduces carbonation time to around 100 hours, instead of years. By speeding up carbonation, we can a) reduce the porosity of end-of-life concrete from demolition, b) increase the strength and durability of new concrete, and c) replace natural aggregates with crushed end-of-life concrete in the production of new concrete for structural applications. Valorising the properties of end-of-life concrete and sequestering CO2 into it allows our technology to be economically viable at large scale. Our approach recycles end-of-life concrete and injects CO2 into it, making concrete a very low-emission material. The UK is committed to large infrastructure projects (HS2, Sizewell C, thus huge demand for concrete)</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Environmental Science</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Upcycling demolished-concrete waste into CO2-absorbing aggregates (accelerated carbonation) to replace natural aggregates; waste valorisation + CO2 sequestration (as V004). Engineering/Materials(concrete) and Chem Eng(carbonation) considered</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Solar energy is a key component of current and future renewable energy. However, analysis of materials requirements for large-scale PV deployment has shown that solar energy production may well be more limited, from a technological and sustainable point of view than initially supposed. Printable Photovoltaics (PPV), which include dye-sensitized, perovskite and organic solar cells, are promising green energy technologies in their infancy, and prime candidates for full lifecycle optimisation to create truly sustainable renewable energy technologies. The remarkable evolution of perovskite-based solar cells (PSCs) during the last few years, reaching certified power conversion efficiencies (PCEs) over 20% and the recent materials developments for organic photovoltaics (OPV) with higher efficiency and enhanced stability have confirmed PPV as an extremely strong candidate for low cost, low embodied energy, performance-competitive PV technology. Currently, international progress in PV research and technology is running at an unparalleled rate, with major contributions from the SPECIFIC group at Swansea University. This involves developing cheaper materials, along with reducing the energy, cost, and time needed to process materials. When these technologies emerge onto the market it is likely that they will be used initially in niche building and product integrated applications. Lifecycle optimisation for these products must include development of end-of-life (EoL) strategies, appropriate design optimisation and substitution of primary and critical resources. Full lifecycle optimisation for circular economy, however, requires further intervention enabling circular flows of PPV materials and products through reuse, remanufacturing and recycling. The overall aim of this project is to develop an understanding of device photophysics and photochemistry to inform development of remanufacturing and material substitution strategies for perovskite devices, resulting in world leading, </t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4639,7 +3451,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4B7F74F5-4AED-4C60-A77D-AEA276FB52EB</t>
+          <t>971EF28B-C1E1-40AC-8227-8FBD2F847CC2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4649,34 +3461,22 @@
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Multi-Scale Water Resources Planning in England &amp; Wales</t>
+          <t>Catchments as the first stage of treatment</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>England faces serious risks of water shortages, especially in the drier south and east. Climate change, an increasing population and the need to protect the environment bring further challenges to an already strained system. The National Infrastructure Commission is calling for £21 billion of investment over the next 30 years to avoid £40 billion in emergency response costs. As part of the new National Framework for Water Resources, this project will look at the best options for meeting this challenge within the Water Resources West region by optimal use of water abstractions, storage and transfers. The project requires engagement potentially across diverse topics such as climate change, aquatic ecology, fluvial geomorphology, surface and groundwater hydrology, water infrastructure engineering and economics. It will also require the application of new multi-scale optimisation methods to water resources planning and an evaluation of such an approach in a real-world application. The task is challenging as the Water Resources West region crosses a national border (with Wales) as well as catchment boundaries. New multi-criteria decision-making methods are therefore sought to satisfy the requirements at scales from individual catchments through water resource zones to multi-national, and across a wide range of sectors. There are currently no established industry methods for this in the UK. Part of this project will be to work alongside Water Resources West and its members to evaluate the approach used. It will also involve a review of the literature to identify different methods for multi-scale decision making, conduct trials of these for water resources planning and potentially develop new methods which may utilise fuzzy logic, compromise programming, game theory or stochastic systems modelling. The primary EPSRC research area relevant to this project is Water Engineering, in particular R2: to ensure a reliable infrastructure; and R5: to build new tools to adapt to clim</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>fairly sure</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Multi-scale optimisation/decision methods for water-resources planning and infrastructure (abstractions/storage/transfers); self-identified 'Water Engineering' (civil). Env Sci(water resources/freshwater/planning) considered</t>
-        </is>
-      </c>
+          <t>Utilising catchments or raw water infrastructure as the first stage of treatment will support the UK Water industry's transition towards chemical-free water treatment, offsetting the need for operational expenditure and infrastructure investment and the related environmental impacts. This PhD project, led by Newcastle University, in collaboration with UK Water Industry Research (UKWIR) and the University of Sheffield, looks to advance nature-based and physical interventions in catchments as treatment stages to supplement other catchment management approaches within the UK and Ireland. Fieldwork at Newcastle University's two research farms and experiments at the National Green Infrastructure Facility (NGIF) will establish the benefits of soil amendments or specific vegetation in buffer strips to enhance nutrient/pesticide/solids retention, while features such as ditch barriers, ponds, and leaky dams will also be evaluated for their water quality impacts. Sheffield University will contribute expertise and equipment to characterise the hydrological performance (e.g. pollutant attenuation and retention time) of such features under different flow rates. Newcastle University will deploy its "Lab in a Van" for onsite analysis of chemical and microbial water quality. Taking a holistic view of the catchment system, results from fieldwork, experiments and literature will be used to identify combinations of catchment, water body and raw water infrastructure interventions which realize the full benefits of catchment-based solutions. A decision support tool will be co-developed with water industry and land management stakeholders to define climate change resilient catchment-based treatment solutions and maintenance regimes that protect biodiversity, enhance the public amenity value of catchments and improve the quality of drinking water resources.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Fields!$A$2:$A$11</formula1>
+      <formula1>=Fields!$A$2:$A$14</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Confidence!$A$2:$A$4</formula1>
@@ -4692,7 +3492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4712,61 +3512,82 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Business, Management and Accounting</t>
+          <t>Biochemistry, Genetics and Molecular Biology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Business, Management and Accounting</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Chemistry</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Computer Science</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Economics, Econometrics and Finance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Environmental Science</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Social Sciences</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>Environmental Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Materials Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
